--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -1336,7 +1336,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ2">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1539,10 +1539,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="AQ3">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1745,10 +1745,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AQ4">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AQ5">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AQ6">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2363,10 +2363,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="AQ7">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2563,25 +2563,25 @@
         <v>2.38</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="AQ8">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU8">
         <v>5</v>
@@ -2769,25 +2769,25 @@
         <v>1.58</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ9">
         <v>0.75</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU9">
         <v>2</v>
@@ -2975,25 +2975,25 @@
         <v>3.7</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP10">
-        <v>2.13</v>
+        <v>1.63</v>
       </c>
       <c r="AQ10">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AU10">
         <v>10</v>
@@ -3184,22 +3184,22 @@
         <v>0</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP11">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AQ11">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS11">
         <v>0</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AU11">
         <v>8</v>
@@ -3393,19 +3393,19 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AU12">
         <v>8</v>
@@ -3596,22 +3596,22 @@
         <v>0</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP13">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ13">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="AR13">
         <v>0</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AU13">
         <v>2</v>
@@ -3799,25 +3799,25 @@
         <v>1.13</v>
       </c>
       <c r="AN14">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP14">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ14">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AR14">
         <v>0.52</v>
       </c>
       <c r="AS14">
-        <v>0.84</v>
+        <v>1.47</v>
       </c>
       <c r="AT14">
-        <v>1.36</v>
+        <v>1.99</v>
       </c>
       <c r="AU14">
         <v>5</v>
@@ -4005,25 +4005,25 @@
         <v>1.54</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP15">
         <v>0.75</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AR15">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>0.55</v>
+        <v>0.73</v>
       </c>
       <c r="AT15">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AU15">
         <v>5</v>
@@ -4211,25 +4211,25 @@
         <v>1.33</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO16">
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="AQ16">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="AR16">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AS16">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="AT16">
-        <v>3.68</v>
+        <v>3.89</v>
       </c>
       <c r="AU16">
         <v>4</v>
@@ -4417,25 +4417,25 @@
         <v>2.6</v>
       </c>
       <c r="AN17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP17">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AQ17">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR17">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AS17">
-        <v>1.13</v>
+        <v>0.95</v>
       </c>
       <c r="AT17">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="AU17">
         <v>8</v>
@@ -4623,25 +4623,25 @@
         <v>1.48</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP18">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="AQ18">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR18">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="AS18">
         <v>1</v>
       </c>
       <c r="AT18">
-        <v>2.26</v>
+        <v>2.01</v>
       </c>
       <c r="AU18">
         <v>5</v>
@@ -4832,22 +4832,22 @@
         <v>0</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP19">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AQ19">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="AR19">
-        <v>1.09</v>
+        <v>0.95</v>
       </c>
       <c r="AS19">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AT19">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="AU19">
         <v>8</v>
@@ -5035,25 +5035,25 @@
         <v>1.6</v>
       </c>
       <c r="AN20">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP20">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ20">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR20">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AT20">
-        <v>0.78</v>
+        <v>1.75</v>
       </c>
       <c r="AU20">
         <v>3</v>
@@ -5241,25 +5241,25 @@
         <v>2.53</v>
       </c>
       <c r="AN21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP21">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AQ21">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AR21">
-        <v>2.09</v>
+        <v>1.32</v>
       </c>
       <c r="AS21">
-        <v>0.76</v>
+        <v>1.04</v>
       </c>
       <c r="AT21">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="AU21">
         <v>7</v>
@@ -5447,25 +5447,25 @@
         <v>1.93</v>
       </c>
       <c r="AN22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO22">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP22">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AQ22">
         <v>0.75</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS22">
-        <v>0.98</v>
+        <v>1.14</v>
       </c>
       <c r="AT22">
-        <v>0.98</v>
+        <v>2.25</v>
       </c>
       <c r="AU22">
         <v>9</v>
@@ -5653,25 +5653,25 @@
         <v>1.42</v>
       </c>
       <c r="AN23">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AO23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP23">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AQ23">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AR23">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AS23">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AT23">
-        <v>3.33</v>
+        <v>3.05</v>
       </c>
       <c r="AU23">
         <v>7</v>
@@ -5859,25 +5859,25 @@
         <v>1.18</v>
       </c>
       <c r="AN24">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AO24">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AP24">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="AQ24">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="AR24">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AS24">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AT24">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="AU24">
         <v>6</v>
@@ -6065,25 +6065,25 @@
         <v>1.8</v>
       </c>
       <c r="AN25">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AO25">
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AQ25">
         <v>0.75</v>
       </c>
       <c r="AR25">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AS25">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AT25">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6271,25 +6271,25 @@
         <v>1.68</v>
       </c>
       <c r="AN26">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO26">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP26">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AR26">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="AS26">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT26">
-        <v>1.85</v>
+        <v>2.13</v>
       </c>
       <c r="AU26">
         <v>9</v>
@@ -6477,25 +6477,25 @@
         <v>3.3</v>
       </c>
       <c r="AN27">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AO27">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP27">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AQ27">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR27">
-        <v>1.97</v>
+        <v>1.46</v>
       </c>
       <c r="AS27">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="AT27">
-        <v>2.94</v>
+        <v>2.45</v>
       </c>
       <c r="AU27">
         <v>7</v>
@@ -6683,25 +6683,25 @@
         <v>1.25</v>
       </c>
       <c r="AN28">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AO28">
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AQ28">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="AR28">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AS28">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AT28">
-        <v>3.73</v>
+        <v>3.85</v>
       </c>
       <c r="AU28">
         <v>7</v>
@@ -6892,22 +6892,22 @@
         <v>1.5</v>
       </c>
       <c r="AO29">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP29">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="AQ29">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="AR29">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AS29">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AT29">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="AU29">
         <v>6</v>
@@ -7095,25 +7095,25 @@
         <v>2.05</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AO30">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP30">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="AQ30">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR30">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AS30">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AT30">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="AU30">
         <v>3</v>
@@ -7301,25 +7301,25 @@
         <v>1.33</v>
       </c>
       <c r="AN31">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AO31">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="AP31">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AQ31">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="AR31">
-        <v>1.82</v>
+        <v>1.47</v>
       </c>
       <c r="AS31">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AT31">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="AU31">
         <v>7</v>
@@ -7507,25 +7507,25 @@
         <v>1.34</v>
       </c>
       <c r="AN32">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="AO32">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP32">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="AQ32">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AR32">
-        <v>1.09</v>
+        <v>0.98</v>
       </c>
       <c r="AS32">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AT32">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AU32">
         <v>9</v>
@@ -7713,25 +7713,25 @@
         <v>1.45</v>
       </c>
       <c r="AN33">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AO33">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AP33">
         <v>0.75</v>
       </c>
       <c r="AQ33">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AR33">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AS33">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AT33">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AU33">
         <v>8</v>
@@ -7919,25 +7919,25 @@
         <v>2.45</v>
       </c>
       <c r="AN34">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO34">
         <v>0.67</v>
       </c>
       <c r="AP34">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="AQ34">
         <v>0.75</v>
       </c>
       <c r="AR34">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AS34">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="AT34">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="AU34">
         <v>8</v>
@@ -8125,25 +8125,25 @@
         <v>1.54</v>
       </c>
       <c r="AN35">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AO35">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AR35">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AS35">
-        <v>0.8100000000000001</v>
+        <v>1.12</v>
       </c>
       <c r="AT35">
-        <v>2.01</v>
+        <v>2.42</v>
       </c>
       <c r="AU35">
         <v>9</v>
@@ -8334,22 +8334,22 @@
         <v>1.33</v>
       </c>
       <c r="AO36">
-        <v>0.33</v>
+        <v>1.67</v>
       </c>
       <c r="AP36">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="AQ36">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AR36">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AS36">
-        <v>0.91</v>
+        <v>1.11</v>
       </c>
       <c r="AT36">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AU36">
         <v>3</v>
@@ -8537,25 +8537,25 @@
         <v>1.02</v>
       </c>
       <c r="AN37">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AO37">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AP37">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ37">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="AR37">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AS37">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AT37">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="AU37">
         <v>3</v>
@@ -8743,25 +8743,25 @@
         <v>2.3</v>
       </c>
       <c r="AN38">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AO38">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP38">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AQ38">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR38">
-        <v>1.97</v>
+        <v>1.56</v>
       </c>
       <c r="AS38">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AT38">
-        <v>3.33</v>
+        <v>3.09</v>
       </c>
       <c r="AU38">
         <v>5</v>
@@ -8949,25 +8949,25 @@
         <v>1.83</v>
       </c>
       <c r="AN39">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="AO39">
-        <v>0.67</v>
+        <v>1.6</v>
       </c>
       <c r="AP39">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AQ39">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="AR39">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AS39">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AT39">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="AU39">
         <v>11</v>
@@ -9155,25 +9155,25 @@
         <v>1.29</v>
       </c>
       <c r="AN40">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AO40">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AQ40">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AR40">
-        <v>1.88</v>
+        <v>1.59</v>
       </c>
       <c r="AS40">
-        <v>0.9399999999999999</v>
+        <v>1.54</v>
       </c>
       <c r="AT40">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="AU40">
         <v>6</v>
@@ -9361,25 +9361,25 @@
         <v>2.04</v>
       </c>
       <c r="AN41">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AO41">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AP41">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AQ41">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR41">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AS41">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AT41">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="AU41">
         <v>3</v>
@@ -9567,25 +9567,25 @@
         <v>1.28</v>
       </c>
       <c r="AN42">
-        <v>3</v>
+        <v>1.86</v>
       </c>
       <c r="AO42">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="AP42">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="AQ42">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AR42">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AS42">
-        <v>1.07</v>
+        <v>1.51</v>
       </c>
       <c r="AT42">
-        <v>2.39</v>
+        <v>2.65</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -9773,25 +9773,25 @@
         <v>1.95</v>
       </c>
       <c r="AN43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO43">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AP43">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AQ43">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AR43">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AS43">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AT43">
-        <v>3.13</v>
+        <v>3.06</v>
       </c>
       <c r="AU43">
         <v>3</v>
@@ -9979,25 +9979,25 @@
         <v>3</v>
       </c>
       <c r="AN44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO44">
-        <v>0.5</v>
+        <v>1.29</v>
       </c>
       <c r="AP44">
-        <v>2.13</v>
+        <v>1.63</v>
       </c>
       <c r="AQ44">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="AR44">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AS44">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="AT44">
-        <v>3.95</v>
+        <v>3.44</v>
       </c>
       <c r="AU44">
         <v>9</v>
@@ -10185,25 +10185,25 @@
         <v>1.68</v>
       </c>
       <c r="AN45">
+        <v>1</v>
+      </c>
+      <c r="AO45">
+        <v>1.14</v>
+      </c>
+      <c r="AP45">
         <v>1.25</v>
       </c>
-      <c r="AO45">
-        <v>1.33</v>
-      </c>
-      <c r="AP45">
-        <v>1.5</v>
-      </c>
       <c r="AQ45">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AR45">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AS45">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AT45">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="AU45">
         <v>3</v>
@@ -10391,25 +10391,25 @@
         <v>2.25</v>
       </c>
       <c r="AN46">
-        <v>2.33</v>
+        <v>1.86</v>
       </c>
       <c r="AO46">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AP46">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AQ46">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR46">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="AS46">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AT46">
-        <v>2.84</v>
+        <v>2.44</v>
       </c>
       <c r="AU46">
         <v>6</v>
@@ -10597,25 +10597,25 @@
         <v>1.79</v>
       </c>
       <c r="AN47">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AO47">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP47">
         <v>0.75</v>
       </c>
       <c r="AQ47">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR47">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AS47">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AT47">
-        <v>3.09</v>
+        <v>2.72</v>
       </c>
       <c r="AU47">
         <v>5</v>
@@ -10803,25 +10803,25 @@
         <v>1.85</v>
       </c>
       <c r="AN48">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AO48">
-        <v>0.5</v>
+        <v>1.29</v>
       </c>
       <c r="AP48">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AR48">
-        <v>1.74</v>
+        <v>1.45</v>
       </c>
       <c r="AS48">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AT48">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="AU48">
         <v>3</v>
@@ -11009,25 +11009,25 @@
         <v>2.22</v>
       </c>
       <c r="AN49">
-        <v>2.33</v>
+        <v>1.13</v>
       </c>
       <c r="AO49">
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AQ49">
         <v>0.75</v>
       </c>
       <c r="AR49">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="AS49">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="AT49">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="AU49">
         <v>3</v>
@@ -11215,25 +11215,25 @@
         <v>1.45</v>
       </c>
       <c r="AN50">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO50">
-        <v>1</v>
+        <v>1.63</v>
       </c>
       <c r="AP50">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ50">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AR50">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="AS50">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AT50">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11421,25 +11421,25 @@
         <v>2.3</v>
       </c>
       <c r="AN51">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AO51">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AP51">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="AQ51">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR51">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AS51">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AT51">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="AU51">
         <v>7</v>
@@ -11630,22 +11630,22 @@
         <v>1</v>
       </c>
       <c r="AO52">
-        <v>0.67</v>
+        <v>1.88</v>
       </c>
       <c r="AP52">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="AQ52">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="AR52">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AS52">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AT52">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="AU52">
         <v>4</v>
@@ -11833,25 +11833,25 @@
         <v>1.41</v>
       </c>
       <c r="AN53">
+        <v>2</v>
+      </c>
+      <c r="AO53">
+        <v>2.17</v>
+      </c>
+      <c r="AP53">
         <v>2.25</v>
       </c>
-      <c r="AO53">
-        <v>1.75</v>
-      </c>
-      <c r="AP53">
-        <v>2.38</v>
-      </c>
       <c r="AQ53">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="AR53">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="AS53">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="AT53">
-        <v>3.49</v>
+        <v>3.41</v>
       </c>
       <c r="AU53">
         <v>3</v>
@@ -12039,25 +12039,25 @@
         <v>1.53</v>
       </c>
       <c r="AN54">
-        <v>2.25</v>
+        <v>1.56</v>
       </c>
       <c r="AO54">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AP54">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="AQ54">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR54">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AS54">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AT54">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="AU54">
         <v>4</v>
@@ -12245,25 +12245,25 @@
         <v>3.75</v>
       </c>
       <c r="AN55">
-        <v>3</v>
+        <v>1.86</v>
       </c>
       <c r="AO55">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP55">
-        <v>2.13</v>
+        <v>1.63</v>
       </c>
       <c r="AQ55">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AR55">
-        <v>2.36</v>
+        <v>1.7</v>
       </c>
       <c r="AS55">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AT55">
-        <v>3.36</v>
+        <v>2.83</v>
       </c>
       <c r="AU55">
         <v>11</v>
@@ -12451,25 +12451,25 @@
         <v>2.7</v>
       </c>
       <c r="AN56">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="AO56">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AP56">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AQ56">
         <v>0.75</v>
       </c>
       <c r="AR56">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="AS56">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AT56">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AU56">
         <v>12</v>
@@ -12657,25 +12657,25 @@
         <v>1.35</v>
       </c>
       <c r="AN57">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AO57">
-        <v>0.4</v>
+        <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ57">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="AR57">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AS57">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AT57">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AU57">
         <v>3</v>
@@ -12863,25 +12863,25 @@
         <v>1.28</v>
       </c>
       <c r="AN58">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO58">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AP58">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ58">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AR58">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AS58">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AT58">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="AU58">
         <v>0</v>
@@ -13069,25 +13069,25 @@
         <v>2.4</v>
       </c>
       <c r="AN59">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AO59">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AP59">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AQ59">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AR59">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AS59">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AT59">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="AU59">
         <v>4</v>
@@ -13275,25 +13275,25 @@
         <v>2.25</v>
       </c>
       <c r="AN60">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AO60">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="AP60">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AQ60">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR60">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AS60">
-        <v>1.06</v>
+        <v>0.98</v>
       </c>
       <c r="AT60">
-        <v>2.74</v>
+        <v>2.47</v>
       </c>
       <c r="AU60">
         <v>9</v>
@@ -13484,19 +13484,19 @@
         <v>0.8</v>
       </c>
       <c r="AO61">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AP61">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="AQ61">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR61">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AS61">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AT61">
         <v>2.35</v>
@@ -13687,25 +13687,25 @@
         <v>1.75</v>
       </c>
       <c r="AN62">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AO62">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AP62">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AR62">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AS62">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AT62">
-        <v>2.21</v>
+        <v>2.41</v>
       </c>
       <c r="AU62">
         <v>5</v>
@@ -13893,25 +13893,25 @@
         <v>1.18</v>
       </c>
       <c r="AN63">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AO63">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AP63">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AQ63">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="AR63">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AS63">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="AT63">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="AU63">
         <v>2</v>
@@ -14099,25 +14099,25 @@
         <v>1.16</v>
       </c>
       <c r="AN64">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AO64">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="AP64">
         <v>0.75</v>
       </c>
       <c r="AQ64">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="AR64">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="AS64">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AT64">
-        <v>3.06</v>
+        <v>2.83</v>
       </c>
       <c r="AU64">
         <v>3</v>
@@ -14305,25 +14305,25 @@
         <v>1.45</v>
       </c>
       <c r="AN65">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AO65">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AP65">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="AQ65">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AR65">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AS65">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="AT65">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="AU65">
         <v>5</v>
@@ -14511,25 +14511,25 @@
         <v>1.6</v>
       </c>
       <c r="AN66">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AO66">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AP66">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AQ66">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="AR66">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="AS66">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AT66">
-        <v>3.22</v>
+        <v>3.07</v>
       </c>
       <c r="AU66">
         <v>3</v>
@@ -14717,25 +14717,25 @@
         <v>4</v>
       </c>
       <c r="AN67">
-        <v>3</v>
+        <v>1.89</v>
       </c>
       <c r="AO67">
-        <v>0.33</v>
+        <v>0.45</v>
       </c>
       <c r="AP67">
-        <v>2.13</v>
+        <v>1.63</v>
       </c>
       <c r="AQ67">
         <v>0.75</v>
       </c>
       <c r="AR67">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AS67">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="AT67">
-        <v>3.32</v>
+        <v>2.96</v>
       </c>
       <c r="AU67">
         <v>5</v>
@@ -14923,25 +14923,25 @@
         <v>1.85</v>
       </c>
       <c r="AN68">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AO68">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP68">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="AQ68">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AR68">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AS68">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AT68">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="AU68">
         <v>5</v>
@@ -15129,25 +15129,25 @@
         <v>1.47</v>
       </c>
       <c r="AN69">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AO69">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AP69">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ69">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AR69">
-        <v>0.89</v>
+        <v>0.98</v>
       </c>
       <c r="AS69">
-        <v>0.93</v>
+        <v>1.14</v>
       </c>
       <c r="AT69">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AU69">
         <v>5</v>
@@ -15335,25 +15335,25 @@
         <v>1.4</v>
       </c>
       <c r="AN70">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AO70">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AP70">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ70">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR70">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AS70">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AT70">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="AU70">
         <v>4</v>
@@ -15541,25 +15541,25 @@
         <v>2.1</v>
       </c>
       <c r="AN71">
-        <v>2.6</v>
+        <v>1.64</v>
       </c>
       <c r="AO71">
-        <v>0.83</v>
+        <v>1.27</v>
       </c>
       <c r="AP71">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AQ71">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AR71">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AS71">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AT71">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="AU71">
         <v>9</v>
@@ -15747,25 +15747,25 @@
         <v>1.51</v>
       </c>
       <c r="AN72">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AO72">
-        <v>0.83</v>
+        <v>1.75</v>
       </c>
       <c r="AP72">
+        <v>1.63</v>
+      </c>
+      <c r="AQ72">
+        <v>2.06</v>
+      </c>
+      <c r="AR72">
+        <v>1.44</v>
+      </c>
+      <c r="AS72">
         <v>1.56</v>
       </c>
-      <c r="AQ72">
-        <v>1.38</v>
-      </c>
-      <c r="AR72">
-        <v>1.52</v>
-      </c>
-      <c r="AS72">
-        <v>1.35</v>
-      </c>
       <c r="AT72">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="AU72">
         <v>7</v>
@@ -15953,7 +15953,7 @@
         <v>1.69</v>
       </c>
       <c r="AN73">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AO73">
         <v>1</v>
@@ -15962,16 +15962,16 @@
         <v>0.75</v>
       </c>
       <c r="AQ73">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR73">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AS73">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AT73">
-        <v>2.49</v>
+        <v>2.24</v>
       </c>
       <c r="AU73">
         <v>5</v>
@@ -16159,25 +16159,25 @@
         <v>1.31</v>
       </c>
       <c r="AN74">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="AO74">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AP74">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AQ74">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AR74">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AS74">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="AT74">
-        <v>2.34</v>
+        <v>2.67</v>
       </c>
       <c r="AU74">
         <v>5</v>
@@ -16365,25 +16365,25 @@
         <v>1.15</v>
       </c>
       <c r="AN75">
+        <v>1.17</v>
+      </c>
+      <c r="AO75">
         <v>1.8</v>
       </c>
-      <c r="AO75">
-        <v>1.33</v>
-      </c>
       <c r="AP75">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="AQ75">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="AR75">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AS75">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="AT75">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="AU75">
         <v>5</v>
@@ -16571,25 +16571,25 @@
         <v>1.3</v>
       </c>
       <c r="AN76">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AO76">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AP76">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="AQ76">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AR76">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AS76">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AT76">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AU76">
         <v>3</v>
@@ -16777,25 +16777,25 @@
         <v>2.9</v>
       </c>
       <c r="AN77">
-        <v>2.67</v>
+        <v>1.92</v>
       </c>
       <c r="AO77">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AP77">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AQ77">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR77">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AS77">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AT77">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="AU77">
         <v>7</v>
@@ -16983,25 +16983,25 @@
         <v>1.12</v>
       </c>
       <c r="AN78">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AO78">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="AP78">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ78">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="AR78">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="AS78">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AT78">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="AU78">
         <v>2</v>
@@ -17189,25 +17189,25 @@
         <v>2.2</v>
       </c>
       <c r="AN79">
-        <v>2.5</v>
+        <v>1.64</v>
       </c>
       <c r="AO79">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="AP79">
-        <v>2.13</v>
+        <v>1.63</v>
       </c>
       <c r="AQ79">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AR79">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="AS79">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AT79">
-        <v>3.45</v>
+        <v>3.01</v>
       </c>
       <c r="AU79">
         <v>4</v>
@@ -17395,25 +17395,25 @@
         <v>2.8</v>
       </c>
       <c r="AN80">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AO80">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AP80">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AQ80">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR80">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="AS80">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AT80">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
       <c r="AU80">
         <v>-1</v>
@@ -17601,25 +17601,25 @@
         <v>0</v>
       </c>
       <c r="AN81">
-        <v>2</v>
+        <v>1.31</v>
       </c>
       <c r="AO81">
-        <v>0.43</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP81">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="AQ81">
         <v>0.75</v>
       </c>
       <c r="AR81">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AS81">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AT81">
-        <v>2.39</v>
+        <v>2.51</v>
       </c>
       <c r="AU81">
         <v>2</v>
@@ -17807,25 +17807,25 @@
         <v>0</v>
       </c>
       <c r="AN82">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AO82">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP82">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AQ82">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AR82">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AS82">
-        <v>0.97</v>
+        <v>1.13</v>
       </c>
       <c r="AT82">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="AU82">
         <v>6</v>
@@ -18013,25 +18013,25 @@
         <v>1.85</v>
       </c>
       <c r="AN83">
-        <v>2.67</v>
+        <v>1.85</v>
       </c>
       <c r="AO83">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP83">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AR83">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="AS83">
         <v>1.2</v>
       </c>
       <c r="AT83">
-        <v>2.96</v>
+        <v>2.69</v>
       </c>
       <c r="AU83">
         <v>6</v>
@@ -18219,25 +18219,25 @@
         <v>1.16</v>
       </c>
       <c r="AN84">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="AO84">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AP84">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="AQ84">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AR84">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AS84">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="AT84">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AU84">
         <v>3</v>
@@ -18425,25 +18425,25 @@
         <v>1.47</v>
       </c>
       <c r="AN85">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AO85">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AP85">
         <v>0.75</v>
       </c>
       <c r="AQ85">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR85">
+        <v>1.25</v>
+      </c>
+      <c r="AS85">
         <v>1.46</v>
       </c>
-      <c r="AS85">
-        <v>1.38</v>
-      </c>
       <c r="AT85">
-        <v>2.84</v>
+        <v>2.71</v>
       </c>
       <c r="AU85">
         <v>7</v>
@@ -18631,25 +18631,25 @@
         <v>1.2</v>
       </c>
       <c r="AN86">
-        <v>1.57</v>
+        <v>1.23</v>
       </c>
       <c r="AO86">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AP86">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AQ86">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="AR86">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AS86">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="AT86">
-        <v>2.57</v>
+        <v>2.85</v>
       </c>
       <c r="AU86">
         <v>2</v>
@@ -18837,25 +18837,25 @@
         <v>1.72</v>
       </c>
       <c r="AN87">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AO87">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AP87">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ87">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR87">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AS87">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="AT87">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="AU87">
         <v>8</v>
@@ -19043,25 +19043,25 @@
         <v>2.65</v>
       </c>
       <c r="AN88">
-        <v>2.71</v>
+        <v>1.93</v>
       </c>
       <c r="AO88">
-        <v>0.71</v>
+        <v>1.21</v>
       </c>
       <c r="AP88">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AQ88">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AR88">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AS88">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AT88">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="AU88">
         <v>6</v>
@@ -19249,25 +19249,25 @@
         <v>1.75</v>
       </c>
       <c r="AN89">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AO89">
-        <v>1.14</v>
+        <v>1.93</v>
       </c>
       <c r="AP89">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="AQ89">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="AR89">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AS89">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="AT89">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="AU89">
         <v>3</v>
@@ -19455,25 +19455,25 @@
         <v>3.2</v>
       </c>
       <c r="AN90">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AO90">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="AP90">
-        <v>2.13</v>
+        <v>1.63</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AR90">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="AS90">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AT90">
-        <v>3.23</v>
+        <v>2.84</v>
       </c>
       <c r="AU90">
         <v>11</v>
@@ -19661,25 +19661,25 @@
         <v>1.47</v>
       </c>
       <c r="AN91">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AO91">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AP91">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AQ91">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AR91">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AS91">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AT91">
-        <v>2.68</v>
+        <v>2.79</v>
       </c>
       <c r="AU91">
         <v>3</v>
@@ -19867,25 +19867,25 @@
         <v>1.9</v>
       </c>
       <c r="AN92">
-        <v>2.17</v>
+        <v>1.57</v>
       </c>
       <c r="AO92">
-        <v>1.14</v>
+        <v>1.8</v>
       </c>
       <c r="AP92">
-        <v>2.13</v>
+        <v>1.63</v>
       </c>
       <c r="AQ92">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="AR92">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AS92">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AT92">
-        <v>3.39</v>
+        <v>3.24</v>
       </c>
       <c r="AU92">
         <v>9</v>
@@ -20073,25 +20073,25 @@
         <v>1.11</v>
       </c>
       <c r="AN93">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AO93">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AP93">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ93">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AR93">
-        <v>0.89</v>
+        <v>1.02</v>
       </c>
       <c r="AS93">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="AT93">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="AU93">
         <v>2</v>
@@ -20279,25 +20279,25 @@
         <v>1.8</v>
       </c>
       <c r="AN94">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="AO94">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AP94">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="AQ94">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR94">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AS94">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AT94">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="AU94">
         <v>5</v>
@@ -20485,25 +20485,25 @@
         <v>1.36</v>
       </c>
       <c r="AN95">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AO95">
-        <v>0.71</v>
+        <v>1.13</v>
       </c>
       <c r="AP95">
         <v>0.75</v>
       </c>
       <c r="AQ95">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AR95">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AS95">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AT95">
-        <v>2.53</v>
+        <v>2.37</v>
       </c>
       <c r="AU95">
         <v>2</v>
@@ -20691,25 +20691,25 @@
         <v>2.1</v>
       </c>
       <c r="AN96">
-        <v>2.71</v>
+        <v>2</v>
       </c>
       <c r="AO96">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="AP96">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AQ96">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AR96">
-        <v>1.72</v>
+        <v>1.49</v>
       </c>
       <c r="AS96">
-        <v>0.96</v>
+        <v>1.09</v>
       </c>
       <c r="AT96">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="AU96">
         <v>4</v>
@@ -20897,25 +20897,25 @@
         <v>4.5</v>
       </c>
       <c r="AN97">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AO97">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AP97">
-        <v>2.13</v>
+        <v>1.63</v>
       </c>
       <c r="AQ97">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR97">
-        <v>2.11</v>
+        <v>1.76</v>
       </c>
       <c r="AS97">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AT97">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="AU97">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -1336,7 +1336,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ2">
-        <v>1.63</v>
+        <v>1.13</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1539,10 +1539,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1745,10 +1745,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AQ4">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ5">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AQ6">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2363,10 +2363,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="AQ7">
-        <v>2.06</v>
+        <v>1.38</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2563,25 +2563,25 @@
         <v>2.38</v>
       </c>
       <c r="AN8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="AQ8">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="AR8">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU8">
         <v>5</v>
@@ -2769,25 +2769,25 @@
         <v>1.58</v>
       </c>
       <c r="AN9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ9">
         <v>0.75</v>
       </c>
       <c r="AR9">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AU9">
         <v>2</v>
@@ -2975,25 +2975,25 @@
         <v>3.7</v>
       </c>
       <c r="AN10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.63</v>
+        <v>2.13</v>
       </c>
       <c r="AQ10">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="AR10">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AU10">
         <v>10</v>
@@ -3184,22 +3184,22 @@
         <v>0</v>
       </c>
       <c r="AO11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="AQ11">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AR11">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AS11">
         <v>0</v>
       </c>
       <c r="AT11">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AU11">
         <v>8</v>
@@ -3393,19 +3393,19 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AQ12">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR12">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AU12">
         <v>8</v>
@@ -3596,22 +3596,22 @@
         <v>0</v>
       </c>
       <c r="AO13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP13">
-        <v>0.9399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="AQ13">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR13">
         <v>0</v>
       </c>
       <c r="AS13">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AU13">
         <v>2</v>
@@ -3799,25 +3799,25 @@
         <v>1.13</v>
       </c>
       <c r="AN14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO14">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.9399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="AQ14">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AR14">
         <v>0.52</v>
       </c>
       <c r="AS14">
-        <v>1.47</v>
+        <v>0.84</v>
       </c>
       <c r="AT14">
-        <v>1.99</v>
+        <v>1.36</v>
       </c>
       <c r="AU14">
         <v>5</v>
@@ -4005,25 +4005,25 @@
         <v>1.54</v>
       </c>
       <c r="AN15">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO15">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP15">
         <v>0.75</v>
       </c>
       <c r="AQ15">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="AR15">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AS15">
-        <v>0.73</v>
+        <v>0.55</v>
       </c>
       <c r="AT15">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AU15">
         <v>5</v>
@@ -4211,25 +4211,25 @@
         <v>1.33</v>
       </c>
       <c r="AN16">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="AQ16">
-        <v>1.63</v>
+        <v>1.13</v>
       </c>
       <c r="AR16">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AS16">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AT16">
-        <v>3.89</v>
+        <v>3.68</v>
       </c>
       <c r="AU16">
         <v>4</v>
@@ -4417,25 +4417,25 @@
         <v>2.6</v>
       </c>
       <c r="AN17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR17">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AS17">
-        <v>0.95</v>
+        <v>1.13</v>
       </c>
       <c r="AT17">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="AU17">
         <v>8</v>
@@ -4623,25 +4623,25 @@
         <v>1.48</v>
       </c>
       <c r="AN18">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO18">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="AQ18">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AR18">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AS18">
         <v>1</v>
       </c>
       <c r="AT18">
-        <v>2.01</v>
+        <v>2.26</v>
       </c>
       <c r="AU18">
         <v>5</v>
@@ -4832,22 +4832,22 @@
         <v>0</v>
       </c>
       <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
         <v>1.5</v>
       </c>
-      <c r="AP19">
-        <v>1.25</v>
-      </c>
       <c r="AQ19">
-        <v>2.06</v>
+        <v>1.38</v>
       </c>
       <c r="AR19">
-        <v>0.95</v>
+        <v>1.09</v>
       </c>
       <c r="AS19">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AT19">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AU19">
         <v>8</v>
@@ -5035,25 +5035,25 @@
         <v>1.6</v>
       </c>
       <c r="AN20">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO20">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP20">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ20">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AR20">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="AS20">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="AT20">
-        <v>1.75</v>
+        <v>0.78</v>
       </c>
       <c r="AU20">
         <v>3</v>
@@ -5241,25 +5241,25 @@
         <v>2.53</v>
       </c>
       <c r="AN21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP21">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AQ21">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="AR21">
-        <v>1.32</v>
+        <v>2.09</v>
       </c>
       <c r="AS21">
-        <v>1.04</v>
+        <v>0.76</v>
       </c>
       <c r="AT21">
-        <v>2.36</v>
+        <v>2.85</v>
       </c>
       <c r="AU21">
         <v>7</v>
@@ -5447,25 +5447,25 @@
         <v>1.93</v>
       </c>
       <c r="AN22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO22">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ22">
         <v>0.75</v>
       </c>
       <c r="AR22">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AS22">
-        <v>1.14</v>
+        <v>0.98</v>
       </c>
       <c r="AT22">
-        <v>2.25</v>
+        <v>0.98</v>
       </c>
       <c r="AU22">
         <v>9</v>
@@ -5653,25 +5653,25 @@
         <v>1.42</v>
       </c>
       <c r="AN23">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AO23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP23">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="AQ23">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AR23">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AS23">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AT23">
-        <v>3.05</v>
+        <v>3.33</v>
       </c>
       <c r="AU23">
         <v>7</v>
@@ -5859,25 +5859,25 @@
         <v>1.18</v>
       </c>
       <c r="AN24">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AO24">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="AQ24">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR24">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="AS24">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AT24">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="AU24">
         <v>6</v>
@@ -6065,25 +6065,25 @@
         <v>1.8</v>
       </c>
       <c r="AN25">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AO25">
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AQ25">
         <v>0.75</v>
       </c>
       <c r="AR25">
+        <v>1.32</v>
+      </c>
+      <c r="AS25">
         <v>1.15</v>
       </c>
-      <c r="AS25">
-        <v>1.19</v>
-      </c>
       <c r="AT25">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6271,25 +6271,25 @@
         <v>1.68</v>
       </c>
       <c r="AN26">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO26">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP26">
-        <v>0.9399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="AQ26">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="AR26">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AS26">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AT26">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="AU26">
         <v>9</v>
@@ -6477,25 +6477,25 @@
         <v>3.3</v>
       </c>
       <c r="AN27">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AO27">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP27">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR27">
-        <v>1.46</v>
+        <v>1.97</v>
       </c>
       <c r="AS27">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="AT27">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="AU27">
         <v>7</v>
@@ -6683,25 +6683,25 @@
         <v>1.25</v>
       </c>
       <c r="AN28">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="AO28">
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AQ28">
-        <v>1.63</v>
+        <v>1.13</v>
       </c>
       <c r="AR28">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AS28">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AT28">
-        <v>3.85</v>
+        <v>3.73</v>
       </c>
       <c r="AU28">
         <v>7</v>
@@ -6892,22 +6892,22 @@
         <v>1.5</v>
       </c>
       <c r="AO29">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP29">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="AQ29">
-        <v>2.06</v>
+        <v>1.38</v>
       </c>
       <c r="AR29">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AS29">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="AT29">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="AU29">
         <v>6</v>
@@ -7095,25 +7095,25 @@
         <v>2.05</v>
       </c>
       <c r="AN30">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AO30">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="AQ30">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AR30">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AS30">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AT30">
-        <v>2.79</v>
+        <v>2.63</v>
       </c>
       <c r="AU30">
         <v>3</v>
@@ -7301,25 +7301,25 @@
         <v>1.33</v>
       </c>
       <c r="AN31">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AO31">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ31">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR31">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="AS31">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AT31">
-        <v>3.17</v>
+        <v>3.5</v>
       </c>
       <c r="AU31">
         <v>7</v>
@@ -7507,25 +7507,25 @@
         <v>1.34</v>
       </c>
       <c r="AN32">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="AO32">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP32">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="AQ32">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AR32">
-        <v>0.98</v>
+        <v>1.09</v>
       </c>
       <c r="AS32">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AT32">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AU32">
         <v>9</v>
@@ -7713,25 +7713,25 @@
         <v>1.45</v>
       </c>
       <c r="AN33">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AO33">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AP33">
         <v>0.75</v>
       </c>
       <c r="AQ33">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="AR33">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AS33">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="AT33">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="AU33">
         <v>8</v>
@@ -7919,25 +7919,25 @@
         <v>2.45</v>
       </c>
       <c r="AN34">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO34">
         <v>0.67</v>
       </c>
       <c r="AP34">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="AQ34">
         <v>0.75</v>
       </c>
       <c r="AR34">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AS34">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AT34">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="AU34">
         <v>8</v>
@@ -8125,25 +8125,25 @@
         <v>1.54</v>
       </c>
       <c r="AN35">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AO35">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP35">
-        <v>0.9399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="AQ35">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR35">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AS35">
-        <v>1.12</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT35">
-        <v>2.42</v>
+        <v>2.01</v>
       </c>
       <c r="AU35">
         <v>9</v>
@@ -8334,22 +8334,22 @@
         <v>1.33</v>
       </c>
       <c r="AO36">
-        <v>1.67</v>
+        <v>0.33</v>
       </c>
       <c r="AP36">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="AQ36">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="AR36">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AS36">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
       <c r="AT36">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AU36">
         <v>3</v>
@@ -8537,25 +8537,25 @@
         <v>1.02</v>
       </c>
       <c r="AN37">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AO37">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AP37">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ37">
-        <v>1.63</v>
+        <v>1.13</v>
       </c>
       <c r="AR37">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AS37">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="AT37">
-        <v>2.98</v>
+        <v>2.74</v>
       </c>
       <c r="AU37">
         <v>3</v>
@@ -8743,25 +8743,25 @@
         <v>2.3</v>
       </c>
       <c r="AN38">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AO38">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP38">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AQ38">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AR38">
-        <v>1.56</v>
+        <v>1.97</v>
       </c>
       <c r="AS38">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AT38">
-        <v>3.09</v>
+        <v>3.33</v>
       </c>
       <c r="AU38">
         <v>5</v>
@@ -8949,25 +8949,25 @@
         <v>1.83</v>
       </c>
       <c r="AN39">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="AO39">
-        <v>1.6</v>
+        <v>0.67</v>
       </c>
       <c r="AP39">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AQ39">
-        <v>2.06</v>
+        <v>1.38</v>
       </c>
       <c r="AR39">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AS39">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AT39">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="AU39">
         <v>11</v>
@@ -9155,25 +9155,25 @@
         <v>1.29</v>
       </c>
       <c r="AN40">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AO40">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="AQ40">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AR40">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="AS40">
-        <v>1.54</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT40">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="AU40">
         <v>6</v>
@@ -9361,25 +9361,25 @@
         <v>2.04</v>
       </c>
       <c r="AN41">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AO41">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR41">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AS41">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AT41">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="AU41">
         <v>3</v>
@@ -9567,25 +9567,25 @@
         <v>1.28</v>
       </c>
       <c r="AN42">
-        <v>1.86</v>
+        <v>3</v>
       </c>
       <c r="AO42">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="AQ42">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AR42">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AS42">
-        <v>1.51</v>
+        <v>1.07</v>
       </c>
       <c r="AT42">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -9773,25 +9773,25 @@
         <v>1.95</v>
       </c>
       <c r="AN43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO43">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AQ43">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AR43">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AS43">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AT43">
-        <v>3.06</v>
+        <v>3.13</v>
       </c>
       <c r="AU43">
         <v>3</v>
@@ -9979,25 +9979,25 @@
         <v>3</v>
       </c>
       <c r="AN44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO44">
-        <v>1.29</v>
+        <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.63</v>
+        <v>2.13</v>
       </c>
       <c r="AQ44">
-        <v>2.06</v>
+        <v>1.38</v>
       </c>
       <c r="AR44">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AS44">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AT44">
-        <v>3.44</v>
+        <v>3.95</v>
       </c>
       <c r="AU44">
         <v>9</v>
@@ -10185,25 +10185,25 @@
         <v>1.68</v>
       </c>
       <c r="AN45">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO45">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AP45">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AQ45">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="AR45">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AS45">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AT45">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AU45">
         <v>3</v>
@@ -10391,25 +10391,25 @@
         <v>2.25</v>
       </c>
       <c r="AN46">
-        <v>1.86</v>
+        <v>2.33</v>
       </c>
       <c r="AO46">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP46">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ46">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR46">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AS46">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AT46">
-        <v>2.44</v>
+        <v>2.84</v>
       </c>
       <c r="AU46">
         <v>6</v>
@@ -10597,25 +10597,25 @@
         <v>1.79</v>
       </c>
       <c r="AN47">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="AO47">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AP47">
         <v>0.75</v>
       </c>
       <c r="AQ47">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AR47">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AS47">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AT47">
-        <v>2.72</v>
+        <v>3.09</v>
       </c>
       <c r="AU47">
         <v>5</v>
@@ -10803,25 +10803,25 @@
         <v>1.85</v>
       </c>
       <c r="AN48">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AO48">
-        <v>1.29</v>
+        <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ48">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR48">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="AS48">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AT48">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="AU48">
         <v>3</v>
@@ -11009,25 +11009,25 @@
         <v>2.22</v>
       </c>
       <c r="AN49">
-        <v>1.13</v>
+        <v>2.33</v>
       </c>
       <c r="AO49">
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="AQ49">
         <v>0.75</v>
       </c>
       <c r="AR49">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="AS49">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="AT49">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="AU49">
         <v>3</v>
@@ -11215,25 +11215,25 @@
         <v>1.45</v>
       </c>
       <c r="AN50">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO50">
-        <v>1.63</v>
+        <v>1</v>
       </c>
       <c r="AP50">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ50">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="AR50">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="AS50">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AT50">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11421,25 +11421,25 @@
         <v>2.3</v>
       </c>
       <c r="AN51">
+        <v>0.75</v>
+      </c>
+      <c r="AO51">
+        <v>2</v>
+      </c>
+      <c r="AP51">
         <v>0.88</v>
       </c>
-      <c r="AO51">
-        <v>1.57</v>
-      </c>
-      <c r="AP51">
-        <v>1.25</v>
-      </c>
       <c r="AQ51">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AR51">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AS51">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AT51">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AU51">
         <v>7</v>
@@ -11630,22 +11630,22 @@
         <v>1</v>
       </c>
       <c r="AO52">
-        <v>1.88</v>
+        <v>0.67</v>
       </c>
       <c r="AP52">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="AQ52">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR52">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AS52">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AT52">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="AU52">
         <v>4</v>
@@ -11833,25 +11833,25 @@
         <v>1.41</v>
       </c>
       <c r="AN53">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AO53">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AP53">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AQ53">
-        <v>1.63</v>
+        <v>1.13</v>
       </c>
       <c r="AR53">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="AS53">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="AT53">
-        <v>3.41</v>
+        <v>3.49</v>
       </c>
       <c r="AU53">
         <v>3</v>
@@ -12039,25 +12039,25 @@
         <v>1.53</v>
       </c>
       <c r="AN54">
-        <v>1.56</v>
+        <v>2.25</v>
       </c>
       <c r="AO54">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="AQ54">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AR54">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AS54">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AT54">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="AU54">
         <v>4</v>
@@ -12245,25 +12245,25 @@
         <v>3.75</v>
       </c>
       <c r="AN55">
-        <v>1.86</v>
+        <v>3</v>
       </c>
       <c r="AO55">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AP55">
-        <v>1.63</v>
+        <v>2.13</v>
       </c>
       <c r="AQ55">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="AR55">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="AS55">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AT55">
-        <v>2.83</v>
+        <v>3.36</v>
       </c>
       <c r="AU55">
         <v>11</v>
@@ -12451,25 +12451,25 @@
         <v>2.7</v>
       </c>
       <c r="AN56">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="AO56">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AP56">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AQ56">
         <v>0.75</v>
       </c>
       <c r="AR56">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="AS56">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="AT56">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AU56">
         <v>12</v>
@@ -12657,25 +12657,25 @@
         <v>1.35</v>
       </c>
       <c r="AN57">
+        <v>1.25</v>
+      </c>
+      <c r="AO57">
+        <v>0.4</v>
+      </c>
+      <c r="AP57">
+        <v>1.14</v>
+      </c>
+      <c r="AQ57">
         <v>1.38</v>
       </c>
-      <c r="AO57">
-        <v>1.33</v>
-      </c>
-      <c r="AP57">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AQ57">
-        <v>2.06</v>
-      </c>
       <c r="AR57">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AS57">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AT57">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AU57">
         <v>3</v>
@@ -12863,25 +12863,25 @@
         <v>1.28</v>
       </c>
       <c r="AN58">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO58">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP58">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ58">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AR58">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AS58">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AT58">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="AU58">
         <v>0</v>
@@ -13069,25 +13069,25 @@
         <v>2.4</v>
       </c>
       <c r="AN59">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AO59">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AQ59">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR59">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AS59">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AT59">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="AU59">
         <v>4</v>
@@ -13275,25 +13275,25 @@
         <v>2.25</v>
       </c>
       <c r="AN60">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="AO60">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="AP60">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="AQ60">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR60">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AS60">
-        <v>0.98</v>
+        <v>1.06</v>
       </c>
       <c r="AT60">
-        <v>2.47</v>
+        <v>2.74</v>
       </c>
       <c r="AU60">
         <v>9</v>
@@ -13484,19 +13484,19 @@
         <v>0.8</v>
       </c>
       <c r="AO61">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="AQ61">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AR61">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AS61">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AT61">
         <v>2.35</v>
@@ -13687,25 +13687,25 @@
         <v>1.75</v>
       </c>
       <c r="AN62">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AO62">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AQ62">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="AR62">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AS62">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AT62">
-        <v>2.41</v>
+        <v>2.21</v>
       </c>
       <c r="AU62">
         <v>5</v>
@@ -13893,25 +13893,25 @@
         <v>1.18</v>
       </c>
       <c r="AN63">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AO63">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AP63">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ63">
-        <v>1.63</v>
+        <v>1.13</v>
       </c>
       <c r="AR63">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AS63">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="AT63">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
       <c r="AU63">
         <v>2</v>
@@ -14099,25 +14099,25 @@
         <v>1.16</v>
       </c>
       <c r="AN64">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AO64">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="AP64">
         <v>0.75</v>
       </c>
       <c r="AQ64">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR64">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AS64">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AT64">
-        <v>2.83</v>
+        <v>3.06</v>
       </c>
       <c r="AU64">
         <v>3</v>
@@ -14305,25 +14305,25 @@
         <v>1.45</v>
       </c>
       <c r="AN65">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AO65">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="AQ65">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AR65">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AS65">
-        <v>1.56</v>
+        <v>1.21</v>
       </c>
       <c r="AT65">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="AU65">
         <v>5</v>
@@ -14511,25 +14511,25 @@
         <v>1.6</v>
       </c>
       <c r="AN66">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="AO66">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AP66">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AQ66">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR66">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="AS66">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AT66">
-        <v>3.07</v>
+        <v>3.22</v>
       </c>
       <c r="AU66">
         <v>3</v>
@@ -14717,25 +14717,25 @@
         <v>4</v>
       </c>
       <c r="AN67">
-        <v>1.89</v>
+        <v>3</v>
       </c>
       <c r="AO67">
-        <v>0.45</v>
+        <v>0.33</v>
       </c>
       <c r="AP67">
-        <v>1.63</v>
+        <v>2.13</v>
       </c>
       <c r="AQ67">
         <v>0.75</v>
       </c>
       <c r="AR67">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AS67">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="AT67">
-        <v>2.96</v>
+        <v>3.32</v>
       </c>
       <c r="AU67">
         <v>5</v>
@@ -14923,25 +14923,25 @@
         <v>1.85</v>
       </c>
       <c r="AN68">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AO68">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="AQ68">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR68">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AS68">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AT68">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="AU68">
         <v>5</v>
@@ -15129,25 +15129,25 @@
         <v>1.47</v>
       </c>
       <c r="AN69">
-        <v>0.82</v>
+        <v>0.6</v>
       </c>
       <c r="AO69">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="AP69">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ69">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="AR69">
-        <v>0.98</v>
+        <v>0.89</v>
       </c>
       <c r="AS69">
-        <v>1.14</v>
+        <v>0.93</v>
       </c>
       <c r="AT69">
-        <v>2.12</v>
+        <v>1.82</v>
       </c>
       <c r="AU69">
         <v>5</v>
@@ -15335,25 +15335,25 @@
         <v>1.4</v>
       </c>
       <c r="AN70">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AO70">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AP70">
-        <v>0.9399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="AQ70">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AR70">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AS70">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AT70">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="AU70">
         <v>4</v>
@@ -15541,25 +15541,25 @@
         <v>2.1</v>
       </c>
       <c r="AN71">
-        <v>1.64</v>
+        <v>2.6</v>
       </c>
       <c r="AO71">
-        <v>1.27</v>
+        <v>0.83</v>
       </c>
       <c r="AP71">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="AQ71">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="AR71">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AS71">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AT71">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="AU71">
         <v>9</v>
@@ -15747,25 +15747,25 @@
         <v>1.51</v>
       </c>
       <c r="AN72">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AO72">
-        <v>1.75</v>
+        <v>0.83</v>
       </c>
       <c r="AP72">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ72">
-        <v>2.06</v>
+        <v>1.38</v>
       </c>
       <c r="AR72">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AS72">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="AT72">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="AU72">
         <v>7</v>
@@ -15953,7 +15953,7 @@
         <v>1.69</v>
       </c>
       <c r="AN73">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AO73">
         <v>1</v>
@@ -15962,16 +15962,16 @@
         <v>0.75</v>
       </c>
       <c r="AQ73">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR73">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AS73">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT73">
-        <v>2.24</v>
+        <v>2.49</v>
       </c>
       <c r="AU73">
         <v>5</v>
@@ -16159,25 +16159,25 @@
         <v>1.31</v>
       </c>
       <c r="AN74">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AO74">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AQ74">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AR74">
+        <v>1.16</v>
+      </c>
+      <c r="AS74">
         <v>1.18</v>
       </c>
-      <c r="AS74">
-        <v>1.49</v>
-      </c>
       <c r="AT74">
-        <v>2.67</v>
+        <v>2.34</v>
       </c>
       <c r="AU74">
         <v>5</v>
@@ -16365,25 +16365,25 @@
         <v>1.15</v>
       </c>
       <c r="AN75">
-        <v>1.17</v>
+        <v>1.8</v>
       </c>
       <c r="AO75">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AP75">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="AQ75">
-        <v>1.63</v>
+        <v>1.13</v>
       </c>
       <c r="AR75">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AS75">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AT75">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="AU75">
         <v>5</v>
@@ -16571,25 +16571,25 @@
         <v>1.3</v>
       </c>
       <c r="AN76">
+        <v>0.83</v>
+      </c>
+      <c r="AO76">
+        <v>1.4</v>
+      </c>
+      <c r="AP76">
         <v>0.75</v>
       </c>
-      <c r="AO76">
-        <v>1.17</v>
-      </c>
-      <c r="AP76">
-        <v>0.63</v>
-      </c>
       <c r="AQ76">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AR76">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AS76">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AT76">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AU76">
         <v>3</v>
@@ -16777,25 +16777,25 @@
         <v>2.9</v>
       </c>
       <c r="AN77">
-        <v>1.92</v>
+        <v>2.67</v>
       </c>
       <c r="AO77">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AQ77">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AR77">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AS77">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AT77">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="AU77">
         <v>7</v>
@@ -16983,25 +16983,25 @@
         <v>1.12</v>
       </c>
       <c r="AN78">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AO78">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="AP78">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ78">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR78">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="AS78">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AT78">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="AU78">
         <v>2</v>
@@ -17189,25 +17189,25 @@
         <v>2.2</v>
       </c>
       <c r="AN79">
-        <v>1.64</v>
+        <v>2.5</v>
       </c>
       <c r="AO79">
-        <v>1.31</v>
+        <v>1.67</v>
       </c>
       <c r="AP79">
+        <v>2.13</v>
+      </c>
+      <c r="AQ79">
         <v>1.63</v>
       </c>
-      <c r="AQ79">
-        <v>1.25</v>
-      </c>
       <c r="AR79">
-        <v>1.66</v>
+        <v>2.16</v>
       </c>
       <c r="AS79">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AT79">
-        <v>3.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU79">
         <v>4</v>
@@ -17395,25 +17395,25 @@
         <v>2.8</v>
       </c>
       <c r="AN80">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AO80">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AP80">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AQ80">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AR80">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="AS80">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AT80">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="AU80">
         <v>-1</v>
@@ -17601,25 +17601,25 @@
         <v>0</v>
       </c>
       <c r="AN81">
-        <v>1.31</v>
+        <v>2</v>
       </c>
       <c r="AO81">
-        <v>0.6899999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="AP81">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="AQ81">
         <v>0.75</v>
       </c>
       <c r="AR81">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AS81">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AT81">
-        <v>2.51</v>
+        <v>2.39</v>
       </c>
       <c r="AU81">
         <v>2</v>
@@ -17807,25 +17807,25 @@
         <v>0</v>
       </c>
       <c r="AN82">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AO82">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ82">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="AR82">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AS82">
-        <v>1.13</v>
+        <v>0.97</v>
       </c>
       <c r="AT82">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="AU82">
         <v>6</v>
@@ -18013,25 +18013,25 @@
         <v>1.85</v>
       </c>
       <c r="AN83">
-        <v>1.85</v>
+        <v>2.67</v>
       </c>
       <c r="AO83">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP83">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="AQ83">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR83">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AS83">
         <v>1.2</v>
       </c>
       <c r="AT83">
-        <v>2.69</v>
+        <v>2.96</v>
       </c>
       <c r="AU83">
         <v>6</v>
@@ -18219,25 +18219,25 @@
         <v>1.16</v>
       </c>
       <c r="AN84">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="AO84">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="AP84">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="AQ84">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AR84">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AS84">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="AT84">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AU84">
         <v>3</v>
@@ -18425,25 +18425,25 @@
         <v>1.47</v>
       </c>
       <c r="AN85">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AO85">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AP85">
         <v>0.75</v>
       </c>
       <c r="AQ85">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AR85">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AS85">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AT85">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="AU85">
         <v>7</v>
@@ -18631,25 +18631,25 @@
         <v>1.2</v>
       </c>
       <c r="AN86">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="AO86">
+        <v>1.14</v>
+      </c>
+      <c r="AP86">
         <v>1.5</v>
       </c>
-      <c r="AP86">
-        <v>1.25</v>
-      </c>
       <c r="AQ86">
-        <v>1.63</v>
+        <v>1.13</v>
       </c>
       <c r="AR86">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AS86">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="AT86">
-        <v>2.85</v>
+        <v>2.57</v>
       </c>
       <c r="AU86">
         <v>2</v>
@@ -18837,25 +18837,25 @@
         <v>1.72</v>
       </c>
       <c r="AN87">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AO87">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="AP87">
-        <v>0.9399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="AQ87">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR87">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AS87">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
       <c r="AT87">
-        <v>2.18</v>
+        <v>2.37</v>
       </c>
       <c r="AU87">
         <v>8</v>
@@ -19043,25 +19043,25 @@
         <v>2.65</v>
       </c>
       <c r="AN88">
-        <v>1.93</v>
+        <v>2.71</v>
       </c>
       <c r="AO88">
-        <v>1.21</v>
+        <v>0.71</v>
       </c>
       <c r="AP88">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AQ88">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="AR88">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AS88">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AT88">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="AU88">
         <v>6</v>
@@ -19249,25 +19249,25 @@
         <v>1.75</v>
       </c>
       <c r="AN89">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="AO89">
-        <v>1.93</v>
+        <v>1.14</v>
       </c>
       <c r="AP89">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="AQ89">
-        <v>2.06</v>
+        <v>1.38</v>
       </c>
       <c r="AR89">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AS89">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="AT89">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="AU89">
         <v>3</v>
@@ -19455,25 +19455,25 @@
         <v>3.2</v>
       </c>
       <c r="AN90">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AO90">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="AP90">
-        <v>1.63</v>
+        <v>2.13</v>
       </c>
       <c r="AQ90">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR90">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="AS90">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AT90">
-        <v>2.84</v>
+        <v>3.23</v>
       </c>
       <c r="AU90">
         <v>11</v>
@@ -19661,25 +19661,25 @@
         <v>1.47</v>
       </c>
       <c r="AN91">
+        <v>1.38</v>
+      </c>
+      <c r="AO91">
+        <v>1.86</v>
+      </c>
+      <c r="AP91">
+        <v>1.56</v>
+      </c>
+      <c r="AQ91">
+        <v>1.63</v>
+      </c>
+      <c r="AR91">
         <v>1.53</v>
       </c>
-      <c r="AO91">
-        <v>1.33</v>
-      </c>
-      <c r="AP91">
-        <v>1.63</v>
-      </c>
-      <c r="AQ91">
-        <v>1.25</v>
-      </c>
-      <c r="AR91">
-        <v>1.51</v>
-      </c>
       <c r="AS91">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AT91">
-        <v>2.79</v>
+        <v>2.68</v>
       </c>
       <c r="AU91">
         <v>3</v>
@@ -19867,25 +19867,25 @@
         <v>1.9</v>
       </c>
       <c r="AN92">
-        <v>1.57</v>
+        <v>2.17</v>
       </c>
       <c r="AO92">
-        <v>1.8</v>
+        <v>1.14</v>
       </c>
       <c r="AP92">
-        <v>1.63</v>
+        <v>2.13</v>
       </c>
       <c r="AQ92">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR92">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AS92">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AT92">
-        <v>3.24</v>
+        <v>3.39</v>
       </c>
       <c r="AU92">
         <v>9</v>
@@ -20073,25 +20073,25 @@
         <v>1.11</v>
       </c>
       <c r="AN93">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AO93">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AP93">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ93">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AR93">
-        <v>1.02</v>
+        <v>0.89</v>
       </c>
       <c r="AS93">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="AT93">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="AU93">
         <v>2</v>
@@ -20279,25 +20279,25 @@
         <v>1.8</v>
       </c>
       <c r="AN94">
+        <v>1.71</v>
+      </c>
+      <c r="AO94">
+        <v>1</v>
+      </c>
+      <c r="AP94">
+        <v>1.88</v>
+      </c>
+      <c r="AQ94">
+        <v>0.78</v>
+      </c>
+      <c r="AR94">
         <v>1.33</v>
       </c>
-      <c r="AO94">
-        <v>1.07</v>
-      </c>
-      <c r="AP94">
-        <v>1.44</v>
-      </c>
-      <c r="AQ94">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AR94">
-        <v>1.24</v>
-      </c>
       <c r="AS94">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AT94">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="AU94">
         <v>5</v>
@@ -20485,25 +20485,25 @@
         <v>1.36</v>
       </c>
       <c r="AN95">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AO95">
-        <v>1.13</v>
+        <v>0.71</v>
       </c>
       <c r="AP95">
         <v>0.75</v>
       </c>
       <c r="AQ95">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR95">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AS95">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AT95">
-        <v>2.37</v>
+        <v>2.53</v>
       </c>
       <c r="AU95">
         <v>2</v>
@@ -20691,25 +20691,25 @@
         <v>2.1</v>
       </c>
       <c r="AN96">
-        <v>2</v>
+        <v>2.71</v>
       </c>
       <c r="AO96">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AP96">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="AQ96">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="AR96">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="AS96">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="AT96">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="AU96">
         <v>4</v>
@@ -20897,25 +20897,25 @@
         <v>4.5</v>
       </c>
       <c r="AN97">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AO97">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP97">
-        <v>1.63</v>
+        <v>2.13</v>
       </c>
       <c r="AQ97">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AR97">
-        <v>1.76</v>
+        <v>2.11</v>
       </c>
       <c r="AS97">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AT97">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="AU97">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="210">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -487,6 +487,9 @@
     <t>['40', '44', '73']</t>
   </si>
   <si>
+    <t>['29', '60']</t>
+  </si>
+  <si>
     <t>['4', '6', '45+2']</t>
   </si>
   <si>
@@ -638,6 +641,9 @@
   </si>
   <si>
     <t>['36', '60', '84']</t>
+  </si>
+  <si>
+    <t>['37', '74']</t>
   </si>
 </sst>
 </file>
@@ -999,7 +1005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP97"/>
+  <dimension ref="A1:BP98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1255,7 +1261,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q2">
         <v>7</v>
@@ -1461,7 +1467,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1667,7 +1673,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2366,7 +2372,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ7">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2491,7 +2497,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q8">
         <v>2.1</v>
@@ -2903,7 +2909,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q10">
         <v>1.67</v>
@@ -3393,7 +3399,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ12">
         <v>1</v>
@@ -3727,7 +3733,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3933,7 +3939,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4139,7 +4145,7 @@
         <v>89</v>
       </c>
       <c r="P16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q16">
         <v>3.8</v>
@@ -4838,7 +4844,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ19">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR19">
         <v>1.09</v>
@@ -4963,7 +4969,7 @@
         <v>89</v>
       </c>
       <c r="P20" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5169,7 +5175,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q21">
         <v>2.03</v>
@@ -5247,7 +5253,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ21">
         <v>0.5</v>
@@ -5375,7 +5381,7 @@
         <v>99</v>
       </c>
       <c r="P22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q22">
         <v>2.4</v>
@@ -5581,7 +5587,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -6199,7 +6205,7 @@
         <v>103</v>
       </c>
       <c r="P26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6405,7 +6411,7 @@
         <v>104</v>
       </c>
       <c r="P27" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6483,7 +6489,7 @@
         <v>1.5</v>
       </c>
       <c r="AP27">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ27">
         <v>1.13</v>
@@ -6611,7 +6617,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -6898,7 +6904,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ29">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR29">
         <v>1.18</v>
@@ -7023,7 +7029,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7641,7 +7647,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -7847,7 +7853,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q34">
         <v>2.1</v>
@@ -8053,7 +8059,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8259,7 +8265,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8671,7 +8677,7 @@
         <v>89</v>
       </c>
       <c r="P38" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q38">
         <v>2.2</v>
@@ -8749,7 +8755,7 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ38">
         <v>1.71</v>
@@ -8877,7 +8883,7 @@
         <v>113</v>
       </c>
       <c r="P39" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -8958,7 +8964,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ39">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR39">
         <v>1.72</v>
@@ -9083,7 +9089,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q40">
         <v>3.6</v>
@@ -9495,7 +9501,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9701,7 +9707,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9988,7 +9994,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ44">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR44">
         <v>2.5</v>
@@ -10319,7 +10325,7 @@
         <v>120</v>
       </c>
       <c r="P46" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10525,7 +10531,7 @@
         <v>89</v>
       </c>
       <c r="P47" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10731,7 +10737,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11555,7 +11561,7 @@
         <v>89</v>
       </c>
       <c r="P52" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -11839,7 +11845,7 @@
         <v>1.75</v>
       </c>
       <c r="AP53">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ53">
         <v>1.13</v>
@@ -11967,7 +11973,7 @@
         <v>89</v>
       </c>
       <c r="P54" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12379,7 +12385,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q56">
         <v>1.95</v>
@@ -12457,7 +12463,7 @@
         <v>0.4</v>
       </c>
       <c r="AP56">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ56">
         <v>0.75</v>
@@ -12585,7 +12591,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12666,7 +12672,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ57">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR57">
         <v>1.44</v>
@@ -12791,7 +12797,7 @@
         <v>109</v>
       </c>
       <c r="P58" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q58">
         <v>4</v>
@@ -12997,7 +13003,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q59">
         <v>2.1</v>
@@ -13615,7 +13621,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -14233,7 +14239,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q65">
         <v>3.25</v>
@@ -14439,7 +14445,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q66">
         <v>2.88</v>
@@ -14517,7 +14523,7 @@
         <v>1.2</v>
       </c>
       <c r="AP66">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ66">
         <v>1.13</v>
@@ -14851,7 +14857,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q68">
         <v>2.5</v>
@@ -15675,7 +15681,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -15756,7 +15762,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ72">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR72">
         <v>1.52</v>
@@ -16087,7 +16093,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q74">
         <v>3.75</v>
@@ -16499,7 +16505,7 @@
         <v>142</v>
       </c>
       <c r="P76" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17117,7 +17123,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q79">
         <v>2.2</v>
@@ -17401,7 +17407,7 @@
         <v>1.17</v>
       </c>
       <c r="AP80">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ80">
         <v>0.78</v>
@@ -17529,7 +17535,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18147,7 +18153,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q84">
         <v>5.5</v>
@@ -18353,7 +18359,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q85">
         <v>3.4</v>
@@ -18559,7 +18565,7 @@
         <v>120</v>
       </c>
       <c r="P86" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18765,7 +18771,7 @@
         <v>89</v>
       </c>
       <c r="P87" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q87">
         <v>2.75</v>
@@ -19177,7 +19183,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19258,7 +19264,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ89">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR89">
         <v>1.4</v>
@@ -19589,7 +19595,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -19795,7 +19801,7 @@
         <v>153</v>
       </c>
       <c r="P92" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20001,7 +20007,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q93">
         <v>6</v>
@@ -20207,7 +20213,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q94">
         <v>2.6</v>
@@ -20413,7 +20419,7 @@
         <v>89</v>
       </c>
       <c r="P95" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20982,6 +20988,212 @@
       </c>
       <c r="BP97">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="98" spans="1:68">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>7482766</v>
+      </c>
+      <c r="C98" t="s">
+        <v>68</v>
+      </c>
+      <c r="D98" t="s">
+        <v>69</v>
+      </c>
+      <c r="E98" s="2">
+        <v>45695.6875</v>
+      </c>
+      <c r="F98">
+        <v>17</v>
+      </c>
+      <c r="G98" t="s">
+        <v>80</v>
+      </c>
+      <c r="H98" t="s">
+        <v>79</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98">
+        <v>1</v>
+      </c>
+      <c r="K98">
+        <v>2</v>
+      </c>
+      <c r="L98">
+        <v>2</v>
+      </c>
+      <c r="M98">
+        <v>2</v>
+      </c>
+      <c r="N98">
+        <v>4</v>
+      </c>
+      <c r="O98" t="s">
+        <v>157</v>
+      </c>
+      <c r="P98" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q98">
+        <v>2.5</v>
+      </c>
+      <c r="R98">
+        <v>2.25</v>
+      </c>
+      <c r="S98">
+        <v>4</v>
+      </c>
+      <c r="T98">
+        <v>1.33</v>
+      </c>
+      <c r="U98">
+        <v>3.25</v>
+      </c>
+      <c r="V98">
+        <v>2.63</v>
+      </c>
+      <c r="W98">
+        <v>1.44</v>
+      </c>
+      <c r="X98">
+        <v>6.5</v>
+      </c>
+      <c r="Y98">
+        <v>1.11</v>
+      </c>
+      <c r="Z98">
+        <v>1.91</v>
+      </c>
+      <c r="AA98">
+        <v>3.25</v>
+      </c>
+      <c r="AB98">
+        <v>3.9</v>
+      </c>
+      <c r="AC98">
+        <v>1.04</v>
+      </c>
+      <c r="AD98">
+        <v>12</v>
+      </c>
+      <c r="AE98">
+        <v>1.25</v>
+      </c>
+      <c r="AF98">
+        <v>4</v>
+      </c>
+      <c r="AG98">
+        <v>1.6</v>
+      </c>
+      <c r="AH98">
+        <v>2.1</v>
+      </c>
+      <c r="AI98">
+        <v>1.67</v>
+      </c>
+      <c r="AJ98">
+        <v>2.1</v>
+      </c>
+      <c r="AK98">
+        <v>1.24</v>
+      </c>
+      <c r="AL98">
+        <v>1.27</v>
+      </c>
+      <c r="AM98">
+        <v>1.9</v>
+      </c>
+      <c r="AN98">
+        <v>2.38</v>
+      </c>
+      <c r="AO98">
+        <v>1.38</v>
+      </c>
+      <c r="AP98">
+        <v>2.22</v>
+      </c>
+      <c r="AQ98">
+        <v>1.33</v>
+      </c>
+      <c r="AR98">
+        <v>1.71</v>
+      </c>
+      <c r="AS98">
+        <v>1.26</v>
+      </c>
+      <c r="AT98">
+        <v>2.97</v>
+      </c>
+      <c r="AU98">
+        <v>6</v>
+      </c>
+      <c r="AV98">
+        <v>4</v>
+      </c>
+      <c r="AW98">
+        <v>8</v>
+      </c>
+      <c r="AX98">
+        <v>6</v>
+      </c>
+      <c r="AY98">
+        <v>15</v>
+      </c>
+      <c r="AZ98">
+        <v>11</v>
+      </c>
+      <c r="BA98">
+        <v>3</v>
+      </c>
+      <c r="BB98">
+        <v>4</v>
+      </c>
+      <c r="BC98">
+        <v>7</v>
+      </c>
+      <c r="BD98">
+        <v>1.54</v>
+      </c>
+      <c r="BE98">
+        <v>6.75</v>
+      </c>
+      <c r="BF98">
+        <v>2.7</v>
+      </c>
+      <c r="BG98">
+        <v>1.29</v>
+      </c>
+      <c r="BH98">
+        <v>3.2</v>
+      </c>
+      <c r="BI98">
+        <v>1.49</v>
+      </c>
+      <c r="BJ98">
+        <v>2.4</v>
+      </c>
+      <c r="BK98">
+        <v>1.8</v>
+      </c>
+      <c r="BL98">
+        <v>1.89</v>
+      </c>
+      <c r="BM98">
+        <v>2.23</v>
+      </c>
+      <c r="BN98">
+        <v>1.56</v>
+      </c>
+      <c r="BO98">
+        <v>2.88</v>
+      </c>
+      <c r="BP98">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="214">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -490,6 +490,12 @@
     <t>['29', '60']</t>
   </si>
   <si>
+    <t>['81']</t>
+  </si>
+  <si>
+    <t>['38']</t>
+  </si>
+  <si>
     <t>['4', '6', '45+2']</t>
   </si>
   <si>
@@ -644,6 +650,12 @@
   </si>
   <si>
     <t>['37', '74']</t>
+  </si>
+  <si>
+    <t>['61', '75']</t>
+  </si>
+  <si>
+    <t>['73', '85', '90+3']</t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP98"/>
+  <dimension ref="A1:BP100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1261,7 +1273,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q2">
         <v>7</v>
@@ -1467,7 +1479,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1545,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ3">
         <v>1.13</v>
@@ -1673,7 +1685,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2163,7 +2175,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ6">
         <v>2.13</v>
@@ -2497,7 +2509,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q8">
         <v>2.1</v>
@@ -2784,7 +2796,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ9">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2909,7 +2921,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q10">
         <v>1.67</v>
@@ -3196,7 +3208,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ11">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3733,7 +3745,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3939,7 +3951,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4145,7 +4157,7 @@
         <v>89</v>
       </c>
       <c r="P16" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q16">
         <v>3.8</v>
@@ -4429,7 +4441,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ17">
         <v>1.13</v>
@@ -4635,10 +4647,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ18">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR18">
         <v>1.26</v>
@@ -4969,7 +4981,7 @@
         <v>89</v>
       </c>
       <c r="P20" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5175,7 +5187,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q21">
         <v>2.03</v>
@@ -5381,7 +5393,7 @@
         <v>99</v>
       </c>
       <c r="P22" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q22">
         <v>2.4</v>
@@ -5462,7 +5474,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ22">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5587,7 +5599,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -6080,7 +6092,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ25">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR25">
         <v>1.32</v>
@@ -6205,7 +6217,7 @@
         <v>103</v>
       </c>
       <c r="P26" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6411,7 +6423,7 @@
         <v>104</v>
       </c>
       <c r="P27" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6617,7 +6629,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -6695,7 +6707,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ28">
         <v>1.13</v>
@@ -6901,7 +6913,7 @@
         <v>0.5</v>
       </c>
       <c r="AP29">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ29">
         <v>1.33</v>
@@ -7029,7 +7041,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7110,7 +7122,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ30">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR30">
         <v>1.52</v>
@@ -7647,7 +7659,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -7853,7 +7865,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q34">
         <v>2.1</v>
@@ -7934,7 +7946,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ34">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR34">
         <v>1.35</v>
@@ -8059,7 +8071,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8265,7 +8277,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8343,7 +8355,7 @@
         <v>0.33</v>
       </c>
       <c r="AP36">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ36">
         <v>1</v>
@@ -8677,7 +8689,7 @@
         <v>89</v>
       </c>
       <c r="P38" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q38">
         <v>2.2</v>
@@ -8758,7 +8770,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ38">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR38">
         <v>1.97</v>
@@ -8883,7 +8895,7 @@
         <v>113</v>
       </c>
       <c r="P39" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -8961,7 +8973,7 @@
         <v>0.67</v>
       </c>
       <c r="AP39">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ39">
         <v>1.33</v>
@@ -9089,7 +9101,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q40">
         <v>3.6</v>
@@ -9501,7 +9513,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9707,7 +9719,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9785,7 +9797,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ43">
         <v>1.63</v>
@@ -10325,7 +10337,7 @@
         <v>120</v>
       </c>
       <c r="P46" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10531,7 +10543,7 @@
         <v>89</v>
       </c>
       <c r="P47" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10737,7 +10749,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11024,7 +11036,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ49">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR49">
         <v>1.83</v>
@@ -11561,7 +11573,7 @@
         <v>89</v>
       </c>
       <c r="P52" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -11639,7 +11651,7 @@
         <v>0.67</v>
       </c>
       <c r="AP52">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ52">
         <v>1.13</v>
@@ -11973,7 +11985,7 @@
         <v>89</v>
       </c>
       <c r="P54" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12054,7 +12066,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ54">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR54">
         <v>1.29</v>
@@ -12385,7 +12397,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q56">
         <v>1.95</v>
@@ -12466,7 +12478,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ56">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR56">
         <v>1.69</v>
@@ -12591,7 +12603,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12797,7 +12809,7 @@
         <v>109</v>
       </c>
       <c r="P58" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q58">
         <v>4</v>
@@ -13003,7 +13015,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q59">
         <v>2.1</v>
@@ -13081,7 +13093,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -13493,7 +13505,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ61">
         <v>0.78</v>
@@ -13621,7 +13633,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -14239,7 +14251,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q65">
         <v>3.25</v>
@@ -14445,7 +14457,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q66">
         <v>2.88</v>
@@ -14732,7 +14744,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ67">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR67">
         <v>2.3</v>
@@ -14857,7 +14869,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q68">
         <v>2.5</v>
@@ -15350,7 +15362,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ70">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR70">
         <v>1.35</v>
@@ -15681,7 +15693,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16093,7 +16105,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q74">
         <v>3.75</v>
@@ -16505,7 +16517,7 @@
         <v>142</v>
       </c>
       <c r="P76" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16583,7 +16595,7 @@
         <v>1.4</v>
       </c>
       <c r="AP76">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ76">
         <v>1.63</v>
@@ -16789,7 +16801,7 @@
         <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ77">
         <v>0.78</v>
@@ -17123,7 +17135,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q79">
         <v>2.2</v>
@@ -17535,7 +17547,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -17616,7 +17628,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ81">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR81">
         <v>1.31</v>
@@ -18153,7 +18165,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q84">
         <v>5.5</v>
@@ -18231,7 +18243,7 @@
         <v>2.17</v>
       </c>
       <c r="AP84">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ84">
         <v>2.13</v>
@@ -18359,7 +18371,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q85">
         <v>3.4</v>
@@ -18440,7 +18452,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ85">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR85">
         <v>1.46</v>
@@ -18565,7 +18577,7 @@
         <v>120</v>
       </c>
       <c r="P86" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18771,7 +18783,7 @@
         <v>89</v>
       </c>
       <c r="P87" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q87">
         <v>2.75</v>
@@ -19055,7 +19067,7 @@
         <v>0.71</v>
       </c>
       <c r="AP88">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ88">
         <v>1</v>
@@ -19183,7 +19195,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19595,7 +19607,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -19801,7 +19813,7 @@
         <v>153</v>
       </c>
       <c r="P92" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20007,7 +20019,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q93">
         <v>6</v>
@@ -20213,7 +20225,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q94">
         <v>2.6</v>
@@ -20419,7 +20431,7 @@
         <v>89</v>
       </c>
       <c r="P95" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -21037,7 +21049,7 @@
         <v>157</v>
       </c>
       <c r="P98" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q98">
         <v>2.5</v>
@@ -21193,6 +21205,418 @@
         <v>2.88</v>
       </c>
       <c r="BP98">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="99" spans="1:68">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>7482769</v>
+      </c>
+      <c r="C99" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" s="2">
+        <v>45696.54166666666</v>
+      </c>
+      <c r="F99">
+        <v>17</v>
+      </c>
+      <c r="G99" t="s">
+        <v>71</v>
+      </c>
+      <c r="H99" t="s">
+        <v>70</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>1</v>
+      </c>
+      <c r="M99">
+        <v>2</v>
+      </c>
+      <c r="N99">
+        <v>3</v>
+      </c>
+      <c r="O99" t="s">
+        <v>158</v>
+      </c>
+      <c r="P99" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q99">
+        <v>3.1</v>
+      </c>
+      <c r="R99">
+        <v>2.1</v>
+      </c>
+      <c r="S99">
+        <v>3.6</v>
+      </c>
+      <c r="T99">
+        <v>1.4</v>
+      </c>
+      <c r="U99">
+        <v>2.75</v>
+      </c>
+      <c r="V99">
+        <v>3</v>
+      </c>
+      <c r="W99">
+        <v>1.36</v>
+      </c>
+      <c r="X99">
+        <v>9</v>
+      </c>
+      <c r="Y99">
+        <v>1.07</v>
+      </c>
+      <c r="Z99">
+        <v>2.41</v>
+      </c>
+      <c r="AA99">
+        <v>3.17</v>
+      </c>
+      <c r="AB99">
+        <v>2.95</v>
+      </c>
+      <c r="AC99">
+        <v>1.06</v>
+      </c>
+      <c r="AD99">
+        <v>9.5</v>
+      </c>
+      <c r="AE99">
+        <v>1.33</v>
+      </c>
+      <c r="AF99">
+        <v>3.2</v>
+      </c>
+      <c r="AG99">
+        <v>1.96</v>
+      </c>
+      <c r="AH99">
+        <v>1.74</v>
+      </c>
+      <c r="AI99">
+        <v>1.8</v>
+      </c>
+      <c r="AJ99">
+        <v>1.95</v>
+      </c>
+      <c r="AK99">
+        <v>1.39</v>
+      </c>
+      <c r="AL99">
+        <v>1.3</v>
+      </c>
+      <c r="AM99">
+        <v>1.57</v>
+      </c>
+      <c r="AN99">
+        <v>0.75</v>
+      </c>
+      <c r="AO99">
+        <v>0.75</v>
+      </c>
+      <c r="AP99">
+        <v>0.67</v>
+      </c>
+      <c r="AQ99">
+        <v>1</v>
+      </c>
+      <c r="AR99">
+        <v>1.21</v>
+      </c>
+      <c r="AS99">
+        <v>1.09</v>
+      </c>
+      <c r="AT99">
+        <v>2.3</v>
+      </c>
+      <c r="AU99">
+        <v>6</v>
+      </c>
+      <c r="AV99">
+        <v>3</v>
+      </c>
+      <c r="AW99">
+        <v>5</v>
+      </c>
+      <c r="AX99">
+        <v>8</v>
+      </c>
+      <c r="AY99">
+        <v>11</v>
+      </c>
+      <c r="AZ99">
+        <v>11</v>
+      </c>
+      <c r="BA99">
+        <v>4</v>
+      </c>
+      <c r="BB99">
+        <v>3</v>
+      </c>
+      <c r="BC99">
+        <v>7</v>
+      </c>
+      <c r="BD99">
+        <v>0</v>
+      </c>
+      <c r="BE99">
+        <v>0</v>
+      </c>
+      <c r="BF99">
+        <v>0</v>
+      </c>
+      <c r="BG99">
+        <v>0</v>
+      </c>
+      <c r="BH99">
+        <v>0</v>
+      </c>
+      <c r="BI99">
+        <v>0</v>
+      </c>
+      <c r="BJ99">
+        <v>0</v>
+      </c>
+      <c r="BK99">
+        <v>1.98</v>
+      </c>
+      <c r="BL99">
+        <v>1.82</v>
+      </c>
+      <c r="BM99">
+        <v>0</v>
+      </c>
+      <c r="BN99">
+        <v>0</v>
+      </c>
+      <c r="BO99">
+        <v>0</v>
+      </c>
+      <c r="BP99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:68">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>7482768</v>
+      </c>
+      <c r="C100" t="s">
+        <v>68</v>
+      </c>
+      <c r="D100" t="s">
+        <v>69</v>
+      </c>
+      <c r="E100" s="2">
+        <v>45696.54166666666</v>
+      </c>
+      <c r="F100">
+        <v>17</v>
+      </c>
+      <c r="G100" t="s">
+        <v>74</v>
+      </c>
+      <c r="H100" t="s">
+        <v>73</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>1</v>
+      </c>
+      <c r="L100">
+        <v>1</v>
+      </c>
+      <c r="M100">
+        <v>3</v>
+      </c>
+      <c r="N100">
+        <v>4</v>
+      </c>
+      <c r="O100" t="s">
+        <v>159</v>
+      </c>
+      <c r="P100" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q100">
+        <v>2.3</v>
+      </c>
+      <c r="R100">
+        <v>2.3</v>
+      </c>
+      <c r="S100">
+        <v>4.75</v>
+      </c>
+      <c r="T100">
+        <v>1.33</v>
+      </c>
+      <c r="U100">
+        <v>3.25</v>
+      </c>
+      <c r="V100">
+        <v>2.63</v>
+      </c>
+      <c r="W100">
+        <v>1.44</v>
+      </c>
+      <c r="X100">
+        <v>6.5</v>
+      </c>
+      <c r="Y100">
+        <v>1.11</v>
+      </c>
+      <c r="Z100">
+        <v>1.77</v>
+      </c>
+      <c r="AA100">
+        <v>3.76</v>
+      </c>
+      <c r="AB100">
+        <v>4.2</v>
+      </c>
+      <c r="AC100">
+        <v>1.03</v>
+      </c>
+      <c r="AD100">
+        <v>13</v>
+      </c>
+      <c r="AE100">
+        <v>1.22</v>
+      </c>
+      <c r="AF100">
+        <v>4</v>
+      </c>
+      <c r="AG100">
+        <v>1.61</v>
+      </c>
+      <c r="AH100">
+        <v>2.05</v>
+      </c>
+      <c r="AI100">
+        <v>1.7</v>
+      </c>
+      <c r="AJ100">
+        <v>2.05</v>
+      </c>
+      <c r="AK100">
+        <v>1.22</v>
+      </c>
+      <c r="AL100">
+        <v>1.24</v>
+      </c>
+      <c r="AM100">
+        <v>2</v>
+      </c>
+      <c r="AN100">
+        <v>2.38</v>
+      </c>
+      <c r="AO100">
+        <v>1.71</v>
+      </c>
+      <c r="AP100">
+        <v>2.11</v>
+      </c>
+      <c r="AQ100">
+        <v>1.88</v>
+      </c>
+      <c r="AR100">
+        <v>1.69</v>
+      </c>
+      <c r="AS100">
+        <v>1.48</v>
+      </c>
+      <c r="AT100">
+        <v>3.17</v>
+      </c>
+      <c r="AU100">
+        <v>3</v>
+      </c>
+      <c r="AV100">
+        <v>4</v>
+      </c>
+      <c r="AW100">
+        <v>10</v>
+      </c>
+      <c r="AX100">
+        <v>7</v>
+      </c>
+      <c r="AY100">
+        <v>15</v>
+      </c>
+      <c r="AZ100">
+        <v>13</v>
+      </c>
+      <c r="BA100">
+        <v>3</v>
+      </c>
+      <c r="BB100">
+        <v>7</v>
+      </c>
+      <c r="BC100">
+        <v>10</v>
+      </c>
+      <c r="BD100">
+        <v>1.58</v>
+      </c>
+      <c r="BE100">
+        <v>6.75</v>
+      </c>
+      <c r="BF100">
+        <v>2.63</v>
+      </c>
+      <c r="BG100">
+        <v>1.29</v>
+      </c>
+      <c r="BH100">
+        <v>3.2</v>
+      </c>
+      <c r="BI100">
+        <v>1.49</v>
+      </c>
+      <c r="BJ100">
+        <v>2.4</v>
+      </c>
+      <c r="BK100">
+        <v>1.79</v>
+      </c>
+      <c r="BL100">
+        <v>1.9</v>
+      </c>
+      <c r="BM100">
+        <v>2.23</v>
+      </c>
+      <c r="BN100">
+        <v>1.57</v>
+      </c>
+      <c r="BO100">
+        <v>2.88</v>
+      </c>
+      <c r="BP100">
         <v>1.35</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="214">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1017,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP100"/>
+  <dimension ref="A1:BP103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1354,7 +1354,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ2">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ8">
         <v>0.5</v>
@@ -2793,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -3617,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ13">
         <v>1.13</v>
@@ -3823,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ14">
         <v>2.13</v>
@@ -4235,10 +4235,10 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ16">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR16">
         <v>1.73</v>
@@ -5059,7 +5059,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ20">
         <v>0.78</v>
@@ -6295,7 +6295,7 @@
         <v>0.5</v>
       </c>
       <c r="AP26">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ26">
         <v>1</v>
@@ -6710,7 +6710,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ28">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR28">
         <v>1.88</v>
@@ -7119,7 +7119,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ30">
         <v>1.88</v>
@@ -7943,7 +7943,7 @@
         <v>0.67</v>
       </c>
       <c r="AP34">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ34">
         <v>1</v>
@@ -8149,7 +8149,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -8561,10 +8561,10 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ37">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR37">
         <v>1</v>
@@ -11239,7 +11239,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -11445,7 +11445,7 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ51">
         <v>0.78</v>
@@ -11860,7 +11860,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ53">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR53">
         <v>1.83</v>
@@ -12681,7 +12681,7 @@
         <v>0.4</v>
       </c>
       <c r="AP57">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ57">
         <v>1.33</v>
@@ -12887,7 +12887,7 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ58">
         <v>1.63</v>
@@ -13920,7 +13920,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ63">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR63">
         <v>1.65</v>
@@ -14329,7 +14329,7 @@
         <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ65">
         <v>2.13</v>
@@ -14947,7 +14947,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ68">
         <v>1</v>
@@ -15153,7 +15153,7 @@
         <v>0.8</v>
       </c>
       <c r="AP69">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ69">
         <v>0.5</v>
@@ -15359,7 +15359,7 @@
         <v>1.8</v>
       </c>
       <c r="AP70">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ70">
         <v>1.88</v>
@@ -16392,7 +16392,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ75">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR75">
         <v>1.32</v>
@@ -17007,7 +17007,7 @@
         <v>1.17</v>
       </c>
       <c r="AP78">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ78">
         <v>1.13</v>
@@ -18658,7 +18658,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ86">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR86">
         <v>1.2</v>
@@ -18861,7 +18861,7 @@
         <v>0.86</v>
       </c>
       <c r="AP87">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ87">
         <v>1.13</v>
@@ -19273,7 +19273,7 @@
         <v>1.14</v>
       </c>
       <c r="AP89">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ89">
         <v>1.33</v>
@@ -20097,7 +20097,7 @@
         <v>2</v>
       </c>
       <c r="AP93">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ93">
         <v>2.13</v>
@@ -21618,6 +21618,624 @@
       </c>
       <c r="BP100">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="101" spans="1:68">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>7482767</v>
+      </c>
+      <c r="C101" t="s">
+        <v>68</v>
+      </c>
+      <c r="D101" t="s">
+        <v>69</v>
+      </c>
+      <c r="E101" s="2">
+        <v>45697.4375</v>
+      </c>
+      <c r="F101">
+        <v>17</v>
+      </c>
+      <c r="G101" t="s">
+        <v>81</v>
+      </c>
+      <c r="H101" t="s">
+        <v>78</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101" t="s">
+        <v>89</v>
+      </c>
+      <c r="P101" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q101">
+        <v>6.5</v>
+      </c>
+      <c r="R101">
+        <v>2.6</v>
+      </c>
+      <c r="S101">
+        <v>1.91</v>
+      </c>
+      <c r="T101">
+        <v>1.29</v>
+      </c>
+      <c r="U101">
+        <v>3.5</v>
+      </c>
+      <c r="V101">
+        <v>2.25</v>
+      </c>
+      <c r="W101">
+        <v>1.57</v>
+      </c>
+      <c r="X101">
+        <v>5.5</v>
+      </c>
+      <c r="Y101">
+        <v>1.14</v>
+      </c>
+      <c r="Z101">
+        <v>6.6</v>
+      </c>
+      <c r="AA101">
+        <v>5.1</v>
+      </c>
+      <c r="AB101">
+        <v>1.39</v>
+      </c>
+      <c r="AC101">
+        <v>1.01</v>
+      </c>
+      <c r="AD101">
+        <v>19</v>
+      </c>
+      <c r="AE101">
+        <v>1.17</v>
+      </c>
+      <c r="AF101">
+        <v>5</v>
+      </c>
+      <c r="AG101">
+        <v>1.45</v>
+      </c>
+      <c r="AH101">
+        <v>2.63</v>
+      </c>
+      <c r="AI101">
+        <v>1.75</v>
+      </c>
+      <c r="AJ101">
+        <v>2</v>
+      </c>
+      <c r="AK101">
+        <v>2.8</v>
+      </c>
+      <c r="AL101">
+        <v>1.17</v>
+      </c>
+      <c r="AM101">
+        <v>1.1</v>
+      </c>
+      <c r="AN101">
+        <v>1.14</v>
+      </c>
+      <c r="AO101">
+        <v>1.13</v>
+      </c>
+      <c r="AP101">
+        <v>1.13</v>
+      </c>
+      <c r="AQ101">
+        <v>1.11</v>
+      </c>
+      <c r="AR101">
+        <v>1.37</v>
+      </c>
+      <c r="AS101">
+        <v>1.46</v>
+      </c>
+      <c r="AT101">
+        <v>2.83</v>
+      </c>
+      <c r="AU101">
+        <v>3</v>
+      </c>
+      <c r="AV101">
+        <v>5</v>
+      </c>
+      <c r="AW101">
+        <v>5</v>
+      </c>
+      <c r="AX101">
+        <v>10</v>
+      </c>
+      <c r="AY101">
+        <v>13</v>
+      </c>
+      <c r="AZ101">
+        <v>20</v>
+      </c>
+      <c r="BA101">
+        <v>5</v>
+      </c>
+      <c r="BB101">
+        <v>10</v>
+      </c>
+      <c r="BC101">
+        <v>15</v>
+      </c>
+      <c r="BD101">
+        <v>5.2</v>
+      </c>
+      <c r="BE101">
+        <v>7.4</v>
+      </c>
+      <c r="BF101">
+        <v>1.25</v>
+      </c>
+      <c r="BG101">
+        <v>1.31</v>
+      </c>
+      <c r="BH101">
+        <v>3.1</v>
+      </c>
+      <c r="BI101">
+        <v>1.57</v>
+      </c>
+      <c r="BJ101">
+        <v>2.2</v>
+      </c>
+      <c r="BK101">
+        <v>2</v>
+      </c>
+      <c r="BL101">
+        <v>1.68</v>
+      </c>
+      <c r="BM101">
+        <v>2.7</v>
+      </c>
+      <c r="BN101">
+        <v>1.38</v>
+      </c>
+      <c r="BO101">
+        <v>3.8</v>
+      </c>
+      <c r="BP101">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="102" spans="1:68">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>7482770</v>
+      </c>
+      <c r="C102" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102" s="2">
+        <v>45697.4375</v>
+      </c>
+      <c r="F102">
+        <v>17</v>
+      </c>
+      <c r="G102" t="s">
+        <v>77</v>
+      </c>
+      <c r="H102" t="s">
+        <v>72</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>0</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102" t="s">
+        <v>89</v>
+      </c>
+      <c r="P102" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q102">
+        <v>3.75</v>
+      </c>
+      <c r="R102">
+        <v>2.1</v>
+      </c>
+      <c r="S102">
+        <v>3</v>
+      </c>
+      <c r="T102">
+        <v>1.44</v>
+      </c>
+      <c r="U102">
+        <v>2.63</v>
+      </c>
+      <c r="V102">
+        <v>3</v>
+      </c>
+      <c r="W102">
+        <v>1.36</v>
+      </c>
+      <c r="X102">
+        <v>9</v>
+      </c>
+      <c r="Y102">
+        <v>1.07</v>
+      </c>
+      <c r="Z102">
+        <v>3.21</v>
+      </c>
+      <c r="AA102">
+        <v>3.21</v>
+      </c>
+      <c r="AB102">
+        <v>2.24</v>
+      </c>
+      <c r="AC102">
+        <v>1.06</v>
+      </c>
+      <c r="AD102">
+        <v>10</v>
+      </c>
+      <c r="AE102">
+        <v>1.33</v>
+      </c>
+      <c r="AF102">
+        <v>3.25</v>
+      </c>
+      <c r="AG102">
+        <v>2.03</v>
+      </c>
+      <c r="AH102">
+        <v>1.72</v>
+      </c>
+      <c r="AI102">
+        <v>1.8</v>
+      </c>
+      <c r="AJ102">
+        <v>1.95</v>
+      </c>
+      <c r="AK102">
+        <v>1.61</v>
+      </c>
+      <c r="AL102">
+        <v>1.31</v>
+      </c>
+      <c r="AM102">
+        <v>1.35</v>
+      </c>
+      <c r="AN102">
+        <v>0.88</v>
+      </c>
+      <c r="AO102">
+        <v>1</v>
+      </c>
+      <c r="AP102">
+        <v>0.89</v>
+      </c>
+      <c r="AQ102">
+        <v>1</v>
+      </c>
+      <c r="AR102">
+        <v>0.9</v>
+      </c>
+      <c r="AS102">
+        <v>1.21</v>
+      </c>
+      <c r="AT102">
+        <v>2.11</v>
+      </c>
+      <c r="AU102">
+        <v>6</v>
+      </c>
+      <c r="AV102">
+        <v>2</v>
+      </c>
+      <c r="AW102">
+        <v>14</v>
+      </c>
+      <c r="AX102">
+        <v>2</v>
+      </c>
+      <c r="AY102">
+        <v>25</v>
+      </c>
+      <c r="AZ102">
+        <v>5</v>
+      </c>
+      <c r="BA102">
+        <v>4</v>
+      </c>
+      <c r="BB102">
+        <v>3</v>
+      </c>
+      <c r="BC102">
+        <v>7</v>
+      </c>
+      <c r="BD102">
+        <v>2.12</v>
+      </c>
+      <c r="BE102">
+        <v>5.8</v>
+      </c>
+      <c r="BF102">
+        <v>2.05</v>
+      </c>
+      <c r="BG102">
+        <v>1.27</v>
+      </c>
+      <c r="BH102">
+        <v>3.25</v>
+      </c>
+      <c r="BI102">
+        <v>1.51</v>
+      </c>
+      <c r="BJ102">
+        <v>2.3</v>
+      </c>
+      <c r="BK102">
+        <v>1.9</v>
+      </c>
+      <c r="BL102">
+        <v>1.75</v>
+      </c>
+      <c r="BM102">
+        <v>2.55</v>
+      </c>
+      <c r="BN102">
+        <v>1.43</v>
+      </c>
+      <c r="BO102">
+        <v>3.6</v>
+      </c>
+      <c r="BP102">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="103" spans="1:68">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>7482765</v>
+      </c>
+      <c r="C103" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45697.54166666666</v>
+      </c>
+      <c r="F103">
+        <v>17</v>
+      </c>
+      <c r="G103" t="s">
+        <v>76</v>
+      </c>
+      <c r="H103" t="s">
+        <v>75</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103" t="s">
+        <v>89</v>
+      </c>
+      <c r="P103" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q103">
+        <v>2.6</v>
+      </c>
+      <c r="R103">
+        <v>2.2</v>
+      </c>
+      <c r="S103">
+        <v>4.33</v>
+      </c>
+      <c r="T103">
+        <v>1.36</v>
+      </c>
+      <c r="U103">
+        <v>3</v>
+      </c>
+      <c r="V103">
+        <v>2.75</v>
+      </c>
+      <c r="W103">
+        <v>1.4</v>
+      </c>
+      <c r="X103">
+        <v>8</v>
+      </c>
+      <c r="Y103">
+        <v>1.08</v>
+      </c>
+      <c r="Z103">
+        <v>1.88</v>
+      </c>
+      <c r="AA103">
+        <v>3.26</v>
+      </c>
+      <c r="AB103">
+        <v>4.33</v>
+      </c>
+      <c r="AC103">
+        <v>1.05</v>
+      </c>
+      <c r="AD103">
+        <v>10</v>
+      </c>
+      <c r="AE103">
+        <v>1.3</v>
+      </c>
+      <c r="AF103">
+        <v>3.5</v>
+      </c>
+      <c r="AG103">
+        <v>1.85</v>
+      </c>
+      <c r="AH103">
+        <v>1.89</v>
+      </c>
+      <c r="AI103">
+        <v>1.7</v>
+      </c>
+      <c r="AJ103">
+        <v>2.05</v>
+      </c>
+      <c r="AK103">
+        <v>1.27</v>
+      </c>
+      <c r="AL103">
+        <v>1.29</v>
+      </c>
+      <c r="AM103">
+        <v>1.77</v>
+      </c>
+      <c r="AN103">
+        <v>0.88</v>
+      </c>
+      <c r="AO103">
+        <v>1</v>
+      </c>
+      <c r="AP103">
+        <v>0.89</v>
+      </c>
+      <c r="AQ103">
+        <v>1</v>
+      </c>
+      <c r="AR103">
+        <v>1.4</v>
+      </c>
+      <c r="AS103">
+        <v>1.17</v>
+      </c>
+      <c r="AT103">
+        <v>2.57</v>
+      </c>
+      <c r="AU103">
+        <v>5</v>
+      </c>
+      <c r="AV103">
+        <v>6</v>
+      </c>
+      <c r="AW103">
+        <v>11</v>
+      </c>
+      <c r="AX103">
+        <v>5</v>
+      </c>
+      <c r="AY103">
+        <v>19</v>
+      </c>
+      <c r="AZ103">
+        <v>14</v>
+      </c>
+      <c r="BA103">
+        <v>4</v>
+      </c>
+      <c r="BB103">
+        <v>4</v>
+      </c>
+      <c r="BC103">
+        <v>8</v>
+      </c>
+      <c r="BD103">
+        <v>1.46</v>
+      </c>
+      <c r="BE103">
+        <v>7.5</v>
+      </c>
+      <c r="BF103">
+        <v>3.2</v>
+      </c>
+      <c r="BG103">
+        <v>1.23</v>
+      </c>
+      <c r="BH103">
+        <v>3.6</v>
+      </c>
+      <c r="BI103">
+        <v>1.43</v>
+      </c>
+      <c r="BJ103">
+        <v>2.5</v>
+      </c>
+      <c r="BK103">
+        <v>1.77</v>
+      </c>
+      <c r="BL103">
+        <v>1.88</v>
+      </c>
+      <c r="BM103">
+        <v>2.3</v>
+      </c>
+      <c r="BN103">
+        <v>1.51</v>
+      </c>
+      <c r="BO103">
+        <v>3.2</v>
+      </c>
+      <c r="BP103">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="218">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -496,6 +496,12 @@
     <t>['38']</t>
   </si>
   <si>
+    <t>['53']</t>
+  </si>
+  <si>
+    <t>['17', '23', '83']</t>
+  </si>
+  <si>
     <t>['4', '6', '45+2']</t>
   </si>
   <si>
@@ -656,6 +662,12 @@
   </si>
   <si>
     <t>['73', '85', '90+3']</t>
+  </si>
+  <si>
+    <t>['2']</t>
+  </si>
+  <si>
+    <t>['49', '68', '72']</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP103"/>
+  <dimension ref="A1:BP106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1273,7 +1285,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q2">
         <v>7</v>
@@ -1479,7 +1491,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1560,7 +1572,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ3">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1685,7 +1697,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -1969,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ5">
         <v>0.78</v>
@@ -2178,7 +2190,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ6">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2381,7 +2393,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ7">
         <v>1.33</v>
@@ -2509,7 +2521,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q8">
         <v>2.1</v>
@@ -2590,7 +2602,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ8">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2921,7 +2933,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q10">
         <v>1.67</v>
@@ -2999,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3745,7 +3757,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3826,7 +3838,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ14">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR14">
         <v>0.52</v>
@@ -3951,7 +3963,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4157,7 +4169,7 @@
         <v>89</v>
       </c>
       <c r="P16" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q16">
         <v>3.8</v>
@@ -4444,7 +4456,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ17">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR17">
         <v>1.7</v>
@@ -4981,7 +4993,7 @@
         <v>89</v>
       </c>
       <c r="P20" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5187,7 +5199,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q21">
         <v>2.03</v>
@@ -5268,7 +5280,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ21">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR21">
         <v>2.09</v>
@@ -5393,7 +5405,7 @@
         <v>99</v>
       </c>
       <c r="P22" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q22">
         <v>2.4</v>
@@ -5471,7 +5483,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ22">
         <v>1</v>
@@ -5599,7 +5611,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5883,7 +5895,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ24">
         <v>1.13</v>
@@ -6217,7 +6229,7 @@
         <v>103</v>
       </c>
       <c r="P26" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6423,7 +6435,7 @@
         <v>104</v>
       </c>
       <c r="P27" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6504,7 +6516,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ27">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR27">
         <v>1.97</v>
@@ -6629,7 +6641,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7041,7 +7053,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7325,7 +7337,7 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ31">
         <v>1.13</v>
@@ -7531,7 +7543,7 @@
         <v>1.5</v>
       </c>
       <c r="AP32">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ32">
         <v>1.63</v>
@@ -7659,7 +7671,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -7740,7 +7752,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ33">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR33">
         <v>1.22</v>
@@ -7865,7 +7877,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q34">
         <v>2.1</v>
@@ -8071,7 +8083,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8277,7 +8289,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8689,7 +8701,7 @@
         <v>89</v>
       </c>
       <c r="P38" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q38">
         <v>2.2</v>
@@ -8895,7 +8907,7 @@
         <v>113</v>
       </c>
       <c r="P39" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9101,7 +9113,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q40">
         <v>3.6</v>
@@ -9182,7 +9194,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ40">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR40">
         <v>1.88</v>
@@ -9388,7 +9400,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ41">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR41">
         <v>1.23</v>
@@ -9513,7 +9525,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9591,10 +9603,10 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ42">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR42">
         <v>1.32</v>
@@ -9719,7 +9731,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10003,7 +10015,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ44">
         <v>1.33</v>
@@ -10212,7 +10224,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ45">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR45">
         <v>1.2</v>
@@ -10337,7 +10349,7 @@
         <v>120</v>
       </c>
       <c r="P46" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10415,10 +10427,10 @@
         <v>0.75</v>
       </c>
       <c r="AP46">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ46">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR46">
         <v>1.79</v>
@@ -10543,7 +10555,7 @@
         <v>89</v>
       </c>
       <c r="P47" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10749,7 +10761,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -10827,7 +10839,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -11573,7 +11585,7 @@
         <v>89</v>
       </c>
       <c r="P52" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -11985,7 +11997,7 @@
         <v>89</v>
       </c>
       <c r="P54" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12063,7 +12075,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ54">
         <v>1.88</v>
@@ -12269,10 +12281,10 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ55">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR55">
         <v>2.36</v>
@@ -12397,7 +12409,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q56">
         <v>1.95</v>
@@ -12603,7 +12615,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12809,7 +12821,7 @@
         <v>109</v>
       </c>
       <c r="P58" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q58">
         <v>4</v>
@@ -13015,7 +13027,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q59">
         <v>2.1</v>
@@ -13302,7 +13314,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ60">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR60">
         <v>1.68</v>
@@ -13633,7 +13645,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -13917,7 +13929,7 @@
         <v>1.4</v>
       </c>
       <c r="AP63">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ63">
         <v>1.11</v>
@@ -14251,7 +14263,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q65">
         <v>3.25</v>
@@ -14332,7 +14344,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ65">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -14457,7 +14469,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q66">
         <v>2.88</v>
@@ -14741,7 +14753,7 @@
         <v>0.33</v>
       </c>
       <c r="AP67">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ67">
         <v>1</v>
@@ -14869,7 +14881,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q68">
         <v>2.5</v>
@@ -15156,7 +15168,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ69">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR69">
         <v>0.89</v>
@@ -15693,7 +15705,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -15771,7 +15783,7 @@
         <v>0.83</v>
       </c>
       <c r="AP72">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ72">
         <v>1.33</v>
@@ -15980,7 +15992,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ73">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR73">
         <v>1.44</v>
@@ -16105,7 +16117,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q74">
         <v>3.75</v>
@@ -16186,7 +16198,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ74">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR74">
         <v>1.16</v>
@@ -16389,7 +16401,7 @@
         <v>1.33</v>
       </c>
       <c r="AP75">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ75">
         <v>1.11</v>
@@ -16517,7 +16529,7 @@
         <v>142</v>
       </c>
       <c r="P76" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17135,7 +17147,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q79">
         <v>2.2</v>
@@ -17213,7 +17225,7 @@
         <v>1.67</v>
       </c>
       <c r="AP79">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ79">
         <v>1.63</v>
@@ -17547,7 +17559,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -17625,7 +17637,7 @@
         <v>0.43</v>
       </c>
       <c r="AP81">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ81">
         <v>1</v>
@@ -17831,10 +17843,10 @@
         <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ82">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR82">
         <v>1.54</v>
@@ -18165,7 +18177,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q84">
         <v>5.5</v>
@@ -18246,7 +18258,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ84">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR84">
         <v>1.26</v>
@@ -18371,7 +18383,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q85">
         <v>3.4</v>
@@ -18577,7 +18589,7 @@
         <v>120</v>
       </c>
       <c r="P86" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18783,7 +18795,7 @@
         <v>89</v>
       </c>
       <c r="P87" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q87">
         <v>2.75</v>
@@ -18864,7 +18876,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ87">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR87">
         <v>1.29</v>
@@ -19195,7 +19207,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19479,7 +19491,7 @@
         <v>0.83</v>
       </c>
       <c r="AP90">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -19607,7 +19619,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -19685,7 +19697,7 @@
         <v>1.86</v>
       </c>
       <c r="AP91">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ91">
         <v>1.63</v>
@@ -19813,7 +19825,7 @@
         <v>153</v>
       </c>
       <c r="P92" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -19891,7 +19903,7 @@
         <v>1.14</v>
       </c>
       <c r="AP92">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ92">
         <v>1.13</v>
@@ -20019,7 +20031,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q93">
         <v>6</v>
@@ -20100,7 +20112,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ93">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR93">
         <v>0.89</v>
@@ -20225,7 +20237,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q94">
         <v>2.6</v>
@@ -20303,7 +20315,7 @@
         <v>1</v>
       </c>
       <c r="AP94">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ94">
         <v>0.78</v>
@@ -20431,7 +20443,7 @@
         <v>89</v>
       </c>
       <c r="P95" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20718,7 +20730,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ96">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR96">
         <v>1.72</v>
@@ -20921,7 +20933,7 @@
         <v>0.88</v>
       </c>
       <c r="AP97">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ97">
         <v>0.78</v>
@@ -21049,7 +21061,7 @@
         <v>157</v>
       </c>
       <c r="P98" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q98">
         <v>2.5</v>
@@ -21255,7 +21267,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21461,7 +21473,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q100">
         <v>2.3</v>
@@ -22236,6 +22248,624 @@
       </c>
       <c r="BP103">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="104" spans="1:68">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>7482771</v>
+      </c>
+      <c r="C104" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45703.54166666666</v>
+      </c>
+      <c r="F104">
+        <v>18</v>
+      </c>
+      <c r="G104" t="s">
+        <v>78</v>
+      </c>
+      <c r="H104" t="s">
+        <v>77</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>1</v>
+      </c>
+      <c r="K104">
+        <v>1</v>
+      </c>
+      <c r="L104">
+        <v>1</v>
+      </c>
+      <c r="M104">
+        <v>1</v>
+      </c>
+      <c r="N104">
+        <v>2</v>
+      </c>
+      <c r="O104" t="s">
+        <v>160</v>
+      </c>
+      <c r="P104" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q104">
+        <v>1.67</v>
+      </c>
+      <c r="R104">
+        <v>2.75</v>
+      </c>
+      <c r="S104">
+        <v>8.5</v>
+      </c>
+      <c r="T104">
+        <v>1.25</v>
+      </c>
+      <c r="U104">
+        <v>3.75</v>
+      </c>
+      <c r="V104">
+        <v>2.2</v>
+      </c>
+      <c r="W104">
+        <v>1.62</v>
+      </c>
+      <c r="X104">
+        <v>5</v>
+      </c>
+      <c r="Y104">
+        <v>1.17</v>
+      </c>
+      <c r="Z104">
+        <v>1.25</v>
+      </c>
+      <c r="AA104">
+        <v>6</v>
+      </c>
+      <c r="AB104">
+        <v>10</v>
+      </c>
+      <c r="AC104">
+        <v>1.01</v>
+      </c>
+      <c r="AD104">
+        <v>19</v>
+      </c>
+      <c r="AE104">
+        <v>1.14</v>
+      </c>
+      <c r="AF104">
+        <v>5.5</v>
+      </c>
+      <c r="AG104">
+        <v>1.58</v>
+      </c>
+      <c r="AH104">
+        <v>2.18</v>
+      </c>
+      <c r="AI104">
+        <v>1.95</v>
+      </c>
+      <c r="AJ104">
+        <v>1.8</v>
+      </c>
+      <c r="AK104">
+        <v>1.06</v>
+      </c>
+      <c r="AL104">
+        <v>1.12</v>
+      </c>
+      <c r="AM104">
+        <v>3.8</v>
+      </c>
+      <c r="AN104">
+        <v>2.13</v>
+      </c>
+      <c r="AO104">
+        <v>1.13</v>
+      </c>
+      <c r="AP104">
+        <v>2</v>
+      </c>
+      <c r="AQ104">
+        <v>1.11</v>
+      </c>
+      <c r="AR104">
+        <v>2.12</v>
+      </c>
+      <c r="AS104">
+        <v>1.13</v>
+      </c>
+      <c r="AT104">
+        <v>3.25</v>
+      </c>
+      <c r="AU104">
+        <v>5</v>
+      </c>
+      <c r="AV104">
+        <v>5</v>
+      </c>
+      <c r="AW104">
+        <v>21</v>
+      </c>
+      <c r="AX104">
+        <v>3</v>
+      </c>
+      <c r="AY104">
+        <v>34</v>
+      </c>
+      <c r="AZ104">
+        <v>11</v>
+      </c>
+      <c r="BA104">
+        <v>9</v>
+      </c>
+      <c r="BB104">
+        <v>2</v>
+      </c>
+      <c r="BC104">
+        <v>11</v>
+      </c>
+      <c r="BD104">
+        <v>1.26</v>
+      </c>
+      <c r="BE104">
+        <v>7.5</v>
+      </c>
+      <c r="BF104">
+        <v>4.3</v>
+      </c>
+      <c r="BG104">
+        <v>1.3</v>
+      </c>
+      <c r="BH104">
+        <v>3.05</v>
+      </c>
+      <c r="BI104">
+        <v>1.54</v>
+      </c>
+      <c r="BJ104">
+        <v>2.3</v>
+      </c>
+      <c r="BK104">
+        <v>1.86</v>
+      </c>
+      <c r="BL104">
+        <v>1.82</v>
+      </c>
+      <c r="BM104">
+        <v>2.33</v>
+      </c>
+      <c r="BN104">
+        <v>1.52</v>
+      </c>
+      <c r="BO104">
+        <v>2.95</v>
+      </c>
+      <c r="BP104">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="105" spans="1:68">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>7482772</v>
+      </c>
+      <c r="C105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45703.54166666666</v>
+      </c>
+      <c r="F105">
+        <v>18</v>
+      </c>
+      <c r="G105" t="s">
+        <v>73</v>
+      </c>
+      <c r="H105" t="s">
+        <v>80</v>
+      </c>
+      <c r="I105">
+        <v>2</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>2</v>
+      </c>
+      <c r="L105">
+        <v>3</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>3</v>
+      </c>
+      <c r="O105" t="s">
+        <v>161</v>
+      </c>
+      <c r="P105" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q105">
+        <v>3.5</v>
+      </c>
+      <c r="R105">
+        <v>2.1</v>
+      </c>
+      <c r="S105">
+        <v>3.1</v>
+      </c>
+      <c r="T105">
+        <v>1.4</v>
+      </c>
+      <c r="U105">
+        <v>2.75</v>
+      </c>
+      <c r="V105">
+        <v>3</v>
+      </c>
+      <c r="W105">
+        <v>1.36</v>
+      </c>
+      <c r="X105">
+        <v>8</v>
+      </c>
+      <c r="Y105">
+        <v>1.08</v>
+      </c>
+      <c r="Z105">
+        <v>3.01</v>
+      </c>
+      <c r="AA105">
+        <v>3.58</v>
+      </c>
+      <c r="AB105">
+        <v>2.18</v>
+      </c>
+      <c r="AC105">
+        <v>1.05</v>
+      </c>
+      <c r="AD105">
+        <v>11</v>
+      </c>
+      <c r="AE105">
+        <v>1.33</v>
+      </c>
+      <c r="AF105">
+        <v>3.3</v>
+      </c>
+      <c r="AG105">
+        <v>1.82</v>
+      </c>
+      <c r="AH105">
+        <v>1.92</v>
+      </c>
+      <c r="AI105">
+        <v>1.7</v>
+      </c>
+      <c r="AJ105">
+        <v>2.05</v>
+      </c>
+      <c r="AK105">
+        <v>1.58</v>
+      </c>
+      <c r="AL105">
+        <v>1.29</v>
+      </c>
+      <c r="AM105">
+        <v>1.39</v>
+      </c>
+      <c r="AN105">
+        <v>1.56</v>
+      </c>
+      <c r="AO105">
+        <v>2.13</v>
+      </c>
+      <c r="AP105">
+        <v>1.7</v>
+      </c>
+      <c r="AQ105">
+        <v>1.89</v>
+      </c>
+      <c r="AR105">
+        <v>1.48</v>
+      </c>
+      <c r="AS105">
+        <v>1.39</v>
+      </c>
+      <c r="AT105">
+        <v>2.87</v>
+      </c>
+      <c r="AU105">
+        <v>6</v>
+      </c>
+      <c r="AV105">
+        <v>0</v>
+      </c>
+      <c r="AW105">
+        <v>10</v>
+      </c>
+      <c r="AX105">
+        <v>9</v>
+      </c>
+      <c r="AY105">
+        <v>18</v>
+      </c>
+      <c r="AZ105">
+        <v>11</v>
+      </c>
+      <c r="BA105">
+        <v>3</v>
+      </c>
+      <c r="BB105">
+        <v>6</v>
+      </c>
+      <c r="BC105">
+        <v>9</v>
+      </c>
+      <c r="BD105">
+        <v>2.1</v>
+      </c>
+      <c r="BE105">
+        <v>6.4</v>
+      </c>
+      <c r="BF105">
+        <v>1.89</v>
+      </c>
+      <c r="BG105">
+        <v>1.38</v>
+      </c>
+      <c r="BH105">
+        <v>2.75</v>
+      </c>
+      <c r="BI105">
+        <v>1.65</v>
+      </c>
+      <c r="BJ105">
+        <v>2.08</v>
+      </c>
+      <c r="BK105">
+        <v>2.04</v>
+      </c>
+      <c r="BL105">
+        <v>1.67</v>
+      </c>
+      <c r="BM105">
+        <v>2.63</v>
+      </c>
+      <c r="BN105">
+        <v>1.41</v>
+      </c>
+      <c r="BO105">
+        <v>3.4</v>
+      </c>
+      <c r="BP105">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="106" spans="1:68">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>7482774</v>
+      </c>
+      <c r="C106" t="s">
+        <v>68</v>
+      </c>
+      <c r="D106" t="s">
+        <v>69</v>
+      </c>
+      <c r="E106" s="2">
+        <v>45703.54166666666</v>
+      </c>
+      <c r="F106">
+        <v>18</v>
+      </c>
+      <c r="G106" t="s">
+        <v>75</v>
+      </c>
+      <c r="H106" t="s">
+        <v>71</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <v>1</v>
+      </c>
+      <c r="M106">
+        <v>3</v>
+      </c>
+      <c r="N106">
+        <v>4</v>
+      </c>
+      <c r="O106" t="s">
+        <v>102</v>
+      </c>
+      <c r="P106" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q106">
+        <v>2.75</v>
+      </c>
+      <c r="R106">
+        <v>2</v>
+      </c>
+      <c r="S106">
+        <v>4.5</v>
+      </c>
+      <c r="T106">
+        <v>1.5</v>
+      </c>
+      <c r="U106">
+        <v>2.5</v>
+      </c>
+      <c r="V106">
+        <v>3.4</v>
+      </c>
+      <c r="W106">
+        <v>1.3</v>
+      </c>
+      <c r="X106">
+        <v>10</v>
+      </c>
+      <c r="Y106">
+        <v>1.06</v>
+      </c>
+      <c r="Z106">
+        <v>1.89</v>
+      </c>
+      <c r="AA106">
+        <v>3.38</v>
+      </c>
+      <c r="AB106">
+        <v>4.1</v>
+      </c>
+      <c r="AC106">
+        <v>1.08</v>
+      </c>
+      <c r="AD106">
+        <v>8</v>
+      </c>
+      <c r="AE106">
+        <v>1.44</v>
+      </c>
+      <c r="AF106">
+        <v>2.75</v>
+      </c>
+      <c r="AG106">
+        <v>1.95</v>
+      </c>
+      <c r="AH106">
+        <v>1.7</v>
+      </c>
+      <c r="AI106">
+        <v>2</v>
+      </c>
+      <c r="AJ106">
+        <v>1.75</v>
+      </c>
+      <c r="AK106">
+        <v>1.27</v>
+      </c>
+      <c r="AL106">
+        <v>1.31</v>
+      </c>
+      <c r="AM106">
+        <v>1.73</v>
+      </c>
+      <c r="AN106">
+        <v>1.88</v>
+      </c>
+      <c r="AO106">
+        <v>0.5</v>
+      </c>
+      <c r="AP106">
+        <v>1.67</v>
+      </c>
+      <c r="AQ106">
+        <v>0.78</v>
+      </c>
+      <c r="AR106">
+        <v>1.34</v>
+      </c>
+      <c r="AS106">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT106">
+        <v>2.28</v>
+      </c>
+      <c r="AU106">
+        <v>3</v>
+      </c>
+      <c r="AV106">
+        <v>4</v>
+      </c>
+      <c r="AW106">
+        <v>4</v>
+      </c>
+      <c r="AX106">
+        <v>7</v>
+      </c>
+      <c r="AY106">
+        <v>7</v>
+      </c>
+      <c r="AZ106">
+        <v>14</v>
+      </c>
+      <c r="BA106">
+        <v>2</v>
+      </c>
+      <c r="BB106">
+        <v>1</v>
+      </c>
+      <c r="BC106">
+        <v>3</v>
+      </c>
+      <c r="BD106">
+        <v>1.68</v>
+      </c>
+      <c r="BE106">
+        <v>6.4</v>
+      </c>
+      <c r="BF106">
+        <v>2.48</v>
+      </c>
+      <c r="BG106">
+        <v>1.49</v>
+      </c>
+      <c r="BH106">
+        <v>2.4</v>
+      </c>
+      <c r="BI106">
+        <v>1.82</v>
+      </c>
+      <c r="BJ106">
+        <v>1.86</v>
+      </c>
+      <c r="BK106">
+        <v>2.32</v>
+      </c>
+      <c r="BL106">
+        <v>1.53</v>
+      </c>
+      <c r="BM106">
+        <v>3.05</v>
+      </c>
+      <c r="BN106">
+        <v>1.32</v>
+      </c>
+      <c r="BO106">
+        <v>4.1</v>
+      </c>
+      <c r="BP106">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="220">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -502,6 +502,12 @@
     <t>['17', '23', '83']</t>
   </si>
   <si>
+    <t>['85']</t>
+  </si>
+  <si>
+    <t>['41', '47']</t>
+  </si>
+  <si>
     <t>['4', '6', '45+2']</t>
   </si>
   <si>
@@ -667,7 +673,7 @@
     <t>['2']</t>
   </si>
   <si>
-    <t>['49', '68', '72']</t>
+    <t>['49', '67', '72']</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP106"/>
+  <dimension ref="A1:BP109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1285,7 +1291,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q2">
         <v>7</v>
@@ -1363,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ2">
         <v>1.11</v>
@@ -1491,7 +1497,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1697,7 +1703,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -1775,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ4">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1984,7 +1990,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ5">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2521,7 +2527,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q8">
         <v>2.1</v>
@@ -2933,7 +2939,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q10">
         <v>1.67</v>
@@ -3217,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ11">
         <v>1.88</v>
@@ -3632,7 +3638,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ13">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3757,7 +3763,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3963,7 +3969,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4041,7 +4047,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4169,7 +4175,7 @@
         <v>89</v>
       </c>
       <c r="P16" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q16">
         <v>3.8</v>
@@ -4865,7 +4871,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ19">
         <v>1.33</v>
@@ -4993,7 +4999,7 @@
         <v>89</v>
       </c>
       <c r="P20" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5074,7 +5080,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ20">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR20">
         <v>0.78</v>
@@ -5199,7 +5205,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q21">
         <v>2.03</v>
@@ -5405,7 +5411,7 @@
         <v>99</v>
       </c>
       <c r="P22" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q22">
         <v>2.4</v>
@@ -5611,7 +5617,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5689,10 +5695,10 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ23">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR23">
         <v>1.73</v>
@@ -5898,7 +5904,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ24">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR24">
         <v>0.92</v>
@@ -6101,7 +6107,7 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -6229,7 +6235,7 @@
         <v>103</v>
       </c>
       <c r="P26" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6435,7 +6441,7 @@
         <v>104</v>
       </c>
       <c r="P27" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6641,7 +6647,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7053,7 +7059,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7340,7 +7346,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ31">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR31">
         <v>1.82</v>
@@ -7546,7 +7552,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ32">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR32">
         <v>1.09</v>
@@ -7671,7 +7677,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -7749,7 +7755,7 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ33">
         <v>0.78</v>
@@ -7877,7 +7883,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q34">
         <v>2.1</v>
@@ -8083,7 +8089,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8289,7 +8295,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8701,7 +8707,7 @@
         <v>89</v>
       </c>
       <c r="P38" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q38">
         <v>2.2</v>
@@ -8907,7 +8913,7 @@
         <v>113</v>
       </c>
       <c r="P39" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9113,7 +9119,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q40">
         <v>3.6</v>
@@ -9191,7 +9197,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ40">
         <v>1.89</v>
@@ -9397,7 +9403,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ41">
         <v>1.11</v>
@@ -9525,7 +9531,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9731,7 +9737,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9812,7 +9818,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ43">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR43">
         <v>1.82</v>
@@ -10221,7 +10227,7 @@
         <v>1.33</v>
       </c>
       <c r="AP45">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ45">
         <v>0.78</v>
@@ -10349,7 +10355,7 @@
         <v>120</v>
       </c>
       <c r="P46" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10555,7 +10561,7 @@
         <v>89</v>
       </c>
       <c r="P47" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10633,10 +10639,10 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ47">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR47">
         <v>1.52</v>
@@ -10761,7 +10767,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11045,7 +11051,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ49">
         <v>1</v>
@@ -11460,7 +11466,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ51">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR51">
         <v>1.44</v>
@@ -11585,7 +11591,7 @@
         <v>89</v>
       </c>
       <c r="P52" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -11666,7 +11672,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ52">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR52">
         <v>1.2</v>
@@ -11997,7 +12003,7 @@
         <v>89</v>
       </c>
       <c r="P54" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12409,7 +12415,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q56">
         <v>1.95</v>
@@ -12615,7 +12621,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12821,7 +12827,7 @@
         <v>109</v>
       </c>
       <c r="P58" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q58">
         <v>4</v>
@@ -12902,7 +12908,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ58">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR58">
         <v>1</v>
@@ -13027,7 +13033,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q59">
         <v>2.1</v>
@@ -13311,7 +13317,7 @@
         <v>1.2</v>
       </c>
       <c r="AP60">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ60">
         <v>1.11</v>
@@ -13520,7 +13526,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ61">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR61">
         <v>1.23</v>
@@ -13645,7 +13651,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -13723,7 +13729,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -14135,10 +14141,10 @@
         <v>1.25</v>
       </c>
       <c r="AP64">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ64">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR64">
         <v>1.56</v>
@@ -14263,7 +14269,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q65">
         <v>3.25</v>
@@ -14469,7 +14475,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q66">
         <v>2.88</v>
@@ -14550,7 +14556,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ66">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR66">
         <v>1.79</v>
@@ -14881,7 +14887,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q68">
         <v>2.5</v>
@@ -15577,7 +15583,7 @@
         <v>0.83</v>
       </c>
       <c r="AP71">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ71">
         <v>1</v>
@@ -15705,7 +15711,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -15989,7 +15995,7 @@
         <v>1</v>
       </c>
       <c r="AP73">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ73">
         <v>1.11</v>
@@ -16117,7 +16123,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q74">
         <v>3.75</v>
@@ -16195,7 +16201,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ74">
         <v>1.89</v>
@@ -16529,7 +16535,7 @@
         <v>142</v>
       </c>
       <c r="P76" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16610,7 +16616,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ76">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR76">
         <v>1.31</v>
@@ -16816,7 +16822,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ77">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR77">
         <v>1.67</v>
@@ -17022,7 +17028,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ78">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR78">
         <v>0.96</v>
@@ -17147,7 +17153,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q79">
         <v>2.2</v>
@@ -17228,7 +17234,7 @@
         <v>2</v>
       </c>
       <c r="AQ79">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR79">
         <v>2.16</v>
@@ -17434,7 +17440,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ80">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR80">
         <v>1.71</v>
@@ -17559,7 +17565,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18049,7 +18055,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ83">
         <v>1</v>
@@ -18177,7 +18183,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q84">
         <v>5.5</v>
@@ -18383,7 +18389,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q85">
         <v>3.4</v>
@@ -18461,7 +18467,7 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ85">
         <v>1.88</v>
@@ -18589,7 +18595,7 @@
         <v>120</v>
       </c>
       <c r="P86" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18667,7 +18673,7 @@
         <v>1.14</v>
       </c>
       <c r="AP86">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ86">
         <v>1.11</v>
@@ -18795,7 +18801,7 @@
         <v>89</v>
       </c>
       <c r="P87" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q87">
         <v>2.75</v>
@@ -19207,7 +19213,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19619,7 +19625,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -19700,7 +19706,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ91">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR91">
         <v>1.53</v>
@@ -19825,7 +19831,7 @@
         <v>153</v>
       </c>
       <c r="P92" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -19906,7 +19912,7 @@
         <v>2</v>
       </c>
       <c r="AQ92">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR92">
         <v>2.1</v>
@@ -20031,7 +20037,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q93">
         <v>6</v>
@@ -20237,7 +20243,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q94">
         <v>2.6</v>
@@ -20318,7 +20324,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ94">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR94">
         <v>1.33</v>
@@ -20443,7 +20449,7 @@
         <v>89</v>
       </c>
       <c r="P95" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20521,7 +20527,7 @@
         <v>0.71</v>
       </c>
       <c r="AP95">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ95">
         <v>1</v>
@@ -20727,7 +20733,7 @@
         <v>0.57</v>
       </c>
       <c r="AP96">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ96">
         <v>0.78</v>
@@ -20936,7 +20942,7 @@
         <v>2</v>
       </c>
       <c r="AQ97">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR97">
         <v>2.11</v>
@@ -21061,7 +21067,7 @@
         <v>157</v>
       </c>
       <c r="P98" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q98">
         <v>2.5</v>
@@ -21267,7 +21273,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21473,7 +21479,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q100">
         <v>2.3</v>
@@ -22297,7 +22303,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q104">
         <v>1.67</v>
@@ -22709,7 +22715,7 @@
         <v>102</v>
       </c>
       <c r="P106" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -22866,6 +22872,624 @@
       </c>
       <c r="BP106">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="107" spans="1:68">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>7482775</v>
+      </c>
+      <c r="C107" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45704.4375</v>
+      </c>
+      <c r="F107">
+        <v>18</v>
+      </c>
+      <c r="G107" t="s">
+        <v>70</v>
+      </c>
+      <c r="H107" t="s">
+        <v>76</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107" t="s">
+        <v>89</v>
+      </c>
+      <c r="P107" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q107">
+        <v>4</v>
+      </c>
+      <c r="R107">
+        <v>2.1</v>
+      </c>
+      <c r="S107">
+        <v>2.88</v>
+      </c>
+      <c r="T107">
+        <v>1.4</v>
+      </c>
+      <c r="U107">
+        <v>2.75</v>
+      </c>
+      <c r="V107">
+        <v>3</v>
+      </c>
+      <c r="W107">
+        <v>1.36</v>
+      </c>
+      <c r="X107">
+        <v>9</v>
+      </c>
+      <c r="Y107">
+        <v>1.07</v>
+      </c>
+      <c r="Z107">
+        <v>3</v>
+      </c>
+      <c r="AA107">
+        <v>3.45</v>
+      </c>
+      <c r="AB107">
+        <v>2.24</v>
+      </c>
+      <c r="AC107">
+        <v>1.05</v>
+      </c>
+      <c r="AD107">
+        <v>10</v>
+      </c>
+      <c r="AE107">
+        <v>1.33</v>
+      </c>
+      <c r="AF107">
+        <v>3.3</v>
+      </c>
+      <c r="AG107">
+        <v>1.79</v>
+      </c>
+      <c r="AH107">
+        <v>1.95</v>
+      </c>
+      <c r="AI107">
+        <v>1.75</v>
+      </c>
+      <c r="AJ107">
+        <v>2</v>
+      </c>
+      <c r="AK107">
+        <v>1.63</v>
+      </c>
+      <c r="AL107">
+        <v>1.29</v>
+      </c>
+      <c r="AM107">
+        <v>1.36</v>
+      </c>
+      <c r="AN107">
+        <v>0.75</v>
+      </c>
+      <c r="AO107">
+        <v>1.63</v>
+      </c>
+      <c r="AP107">
+        <v>0.78</v>
+      </c>
+      <c r="AQ107">
+        <v>1.56</v>
+      </c>
+      <c r="AR107">
+        <v>1.33</v>
+      </c>
+      <c r="AS107">
+        <v>1.09</v>
+      </c>
+      <c r="AT107">
+        <v>2.42</v>
+      </c>
+      <c r="AU107">
+        <v>4</v>
+      </c>
+      <c r="AV107">
+        <v>3</v>
+      </c>
+      <c r="AW107">
+        <v>9</v>
+      </c>
+      <c r="AX107">
+        <v>7</v>
+      </c>
+      <c r="AY107">
+        <v>16</v>
+      </c>
+      <c r="AZ107">
+        <v>11</v>
+      </c>
+      <c r="BA107">
+        <v>4</v>
+      </c>
+      <c r="BB107">
+        <v>4</v>
+      </c>
+      <c r="BC107">
+        <v>8</v>
+      </c>
+      <c r="BD107">
+        <v>2.23</v>
+      </c>
+      <c r="BE107">
+        <v>6.4</v>
+      </c>
+      <c r="BF107">
+        <v>1.79</v>
+      </c>
+      <c r="BG107">
+        <v>1.36</v>
+      </c>
+      <c r="BH107">
+        <v>2.8</v>
+      </c>
+      <c r="BI107">
+        <v>1.62</v>
+      </c>
+      <c r="BJ107">
+        <v>2.14</v>
+      </c>
+      <c r="BK107">
+        <v>2</v>
+      </c>
+      <c r="BL107">
+        <v>1.71</v>
+      </c>
+      <c r="BM107">
+        <v>2.55</v>
+      </c>
+      <c r="BN107">
+        <v>1.44</v>
+      </c>
+      <c r="BO107">
+        <v>3.3</v>
+      </c>
+      <c r="BP107">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="108" spans="1:68">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>7482776</v>
+      </c>
+      <c r="C108" t="s">
+        <v>68</v>
+      </c>
+      <c r="D108" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45704.4375</v>
+      </c>
+      <c r="F108">
+        <v>18</v>
+      </c>
+      <c r="G108" t="s">
+        <v>72</v>
+      </c>
+      <c r="H108" t="s">
+        <v>81</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>0</v>
+      </c>
+      <c r="L108">
+        <v>1</v>
+      </c>
+      <c r="M108">
+        <v>1</v>
+      </c>
+      <c r="N108">
+        <v>2</v>
+      </c>
+      <c r="O108" t="s">
+        <v>162</v>
+      </c>
+      <c r="P108" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q108">
+        <v>2.38</v>
+      </c>
+      <c r="R108">
+        <v>2.25</v>
+      </c>
+      <c r="S108">
+        <v>4.75</v>
+      </c>
+      <c r="T108">
+        <v>1.36</v>
+      </c>
+      <c r="U108">
+        <v>3</v>
+      </c>
+      <c r="V108">
+        <v>2.75</v>
+      </c>
+      <c r="W108">
+        <v>1.4</v>
+      </c>
+      <c r="X108">
+        <v>7</v>
+      </c>
+      <c r="Y108">
+        <v>1.1</v>
+      </c>
+      <c r="Z108">
+        <v>1.7</v>
+      </c>
+      <c r="AA108">
+        <v>3.82</v>
+      </c>
+      <c r="AB108">
+        <v>4.6</v>
+      </c>
+      <c r="AC108">
+        <v>1.03</v>
+      </c>
+      <c r="AD108">
+        <v>13</v>
+      </c>
+      <c r="AE108">
+        <v>1.22</v>
+      </c>
+      <c r="AF108">
+        <v>4</v>
+      </c>
+      <c r="AG108">
+        <v>1.8</v>
+      </c>
+      <c r="AH108">
+        <v>1.94</v>
+      </c>
+      <c r="AI108">
+        <v>1.75</v>
+      </c>
+      <c r="AJ108">
+        <v>2</v>
+      </c>
+      <c r="AK108">
+        <v>1.2</v>
+      </c>
+      <c r="AL108">
+        <v>1.24</v>
+      </c>
+      <c r="AM108">
+        <v>2.05</v>
+      </c>
+      <c r="AN108">
+        <v>1.5</v>
+      </c>
+      <c r="AO108">
+        <v>0.78</v>
+      </c>
+      <c r="AP108">
+        <v>1.44</v>
+      </c>
+      <c r="AQ108">
+        <v>0.8</v>
+      </c>
+      <c r="AR108">
+        <v>1.12</v>
+      </c>
+      <c r="AS108">
+        <v>0.97</v>
+      </c>
+      <c r="AT108">
+        <v>2.09</v>
+      </c>
+      <c r="AU108">
+        <v>5</v>
+      </c>
+      <c r="AV108">
+        <v>6</v>
+      </c>
+      <c r="AW108">
+        <v>12</v>
+      </c>
+      <c r="AX108">
+        <v>5</v>
+      </c>
+      <c r="AY108">
+        <v>21</v>
+      </c>
+      <c r="AZ108">
+        <v>11</v>
+      </c>
+      <c r="BA108">
+        <v>2</v>
+      </c>
+      <c r="BB108">
+        <v>3</v>
+      </c>
+      <c r="BC108">
+        <v>5</v>
+      </c>
+      <c r="BD108">
+        <v>1.63</v>
+      </c>
+      <c r="BE108">
+        <v>6.4</v>
+      </c>
+      <c r="BF108">
+        <v>2.55</v>
+      </c>
+      <c r="BG108">
+        <v>1.37</v>
+      </c>
+      <c r="BH108">
+        <v>2.8</v>
+      </c>
+      <c r="BI108">
+        <v>1.62</v>
+      </c>
+      <c r="BJ108">
+        <v>2.12</v>
+      </c>
+      <c r="BK108">
+        <v>2</v>
+      </c>
+      <c r="BL108">
+        <v>1.71</v>
+      </c>
+      <c r="BM108">
+        <v>2.55</v>
+      </c>
+      <c r="BN108">
+        <v>1.44</v>
+      </c>
+      <c r="BO108">
+        <v>3.3</v>
+      </c>
+      <c r="BP108">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="109" spans="1:68">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>7482773</v>
+      </c>
+      <c r="C109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45704.54166666666</v>
+      </c>
+      <c r="F109">
+        <v>18</v>
+      </c>
+      <c r="G109" t="s">
+        <v>79</v>
+      </c>
+      <c r="H109" t="s">
+        <v>74</v>
+      </c>
+      <c r="I109">
+        <v>1</v>
+      </c>
+      <c r="J109">
+        <v>1</v>
+      </c>
+      <c r="K109">
+        <v>2</v>
+      </c>
+      <c r="L109">
+        <v>2</v>
+      </c>
+      <c r="M109">
+        <v>1</v>
+      </c>
+      <c r="N109">
+        <v>3</v>
+      </c>
+      <c r="O109" t="s">
+        <v>163</v>
+      </c>
+      <c r="P109" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q109">
+        <v>3</v>
+      </c>
+      <c r="R109">
+        <v>2.2</v>
+      </c>
+      <c r="S109">
+        <v>3.4</v>
+      </c>
+      <c r="T109">
+        <v>1.4</v>
+      </c>
+      <c r="U109">
+        <v>2.75</v>
+      </c>
+      <c r="V109">
+        <v>2.75</v>
+      </c>
+      <c r="W109">
+        <v>1.4</v>
+      </c>
+      <c r="X109">
+        <v>8</v>
+      </c>
+      <c r="Y109">
+        <v>1.08</v>
+      </c>
+      <c r="Z109">
+        <v>2.41</v>
+      </c>
+      <c r="AA109">
+        <v>3.11</v>
+      </c>
+      <c r="AB109">
+        <v>3</v>
+      </c>
+      <c r="AC109">
+        <v>1.06</v>
+      </c>
+      <c r="AD109">
+        <v>10</v>
+      </c>
+      <c r="AE109">
+        <v>1.28</v>
+      </c>
+      <c r="AF109">
+        <v>3.6</v>
+      </c>
+      <c r="AG109">
+        <v>1.83</v>
+      </c>
+      <c r="AH109">
+        <v>1.91</v>
+      </c>
+      <c r="AI109">
+        <v>1.67</v>
+      </c>
+      <c r="AJ109">
+        <v>2.1</v>
+      </c>
+      <c r="AK109">
+        <v>1.4</v>
+      </c>
+      <c r="AL109">
+        <v>1.31</v>
+      </c>
+      <c r="AM109">
+        <v>1.55</v>
+      </c>
+      <c r="AN109">
+        <v>2.75</v>
+      </c>
+      <c r="AO109">
+        <v>1.13</v>
+      </c>
+      <c r="AP109">
+        <v>2.78</v>
+      </c>
+      <c r="AQ109">
+        <v>1</v>
+      </c>
+      <c r="AR109">
+        <v>1.67</v>
+      </c>
+      <c r="AS109">
+        <v>1.4</v>
+      </c>
+      <c r="AT109">
+        <v>3.07</v>
+      </c>
+      <c r="AU109">
+        <v>3</v>
+      </c>
+      <c r="AV109">
+        <v>6</v>
+      </c>
+      <c r="AW109">
+        <v>6</v>
+      </c>
+      <c r="AX109">
+        <v>8</v>
+      </c>
+      <c r="AY109">
+        <v>10</v>
+      </c>
+      <c r="AZ109">
+        <v>18</v>
+      </c>
+      <c r="BA109">
+        <v>2</v>
+      </c>
+      <c r="BB109">
+        <v>6</v>
+      </c>
+      <c r="BC109">
+        <v>8</v>
+      </c>
+      <c r="BD109">
+        <v>1.93</v>
+      </c>
+      <c r="BE109">
+        <v>6.4</v>
+      </c>
+      <c r="BF109">
+        <v>2.07</v>
+      </c>
+      <c r="BG109">
+        <v>1.32</v>
+      </c>
+      <c r="BH109">
+        <v>3.05</v>
+      </c>
+      <c r="BI109">
+        <v>1.55</v>
+      </c>
+      <c r="BJ109">
+        <v>2.28</v>
+      </c>
+      <c r="BK109">
+        <v>1.9</v>
+      </c>
+      <c r="BL109">
+        <v>1.79</v>
+      </c>
+      <c r="BM109">
+        <v>2.4</v>
+      </c>
+      <c r="BN109">
+        <v>1.5</v>
+      </c>
+      <c r="BO109">
+        <v>3.1</v>
+      </c>
+      <c r="BP109">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="AQ2">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1575,10 +1575,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="AQ3">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AQ4">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1987,10 +1987,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AQ5">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2193,10 +2193,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.11</v>
+        <v>1.56</v>
       </c>
       <c r="AQ6">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2399,10 +2399,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AQ7">
-        <v>1.33</v>
+        <v>2.06</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2599,25 +2599,25 @@
         <v>2.38</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="AQ8">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU8">
         <v>5</v>
@@ -2805,25 +2805,25 @@
         <v>1.58</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
+        <v>1</v>
+      </c>
+      <c r="AQ9">
         <v>0.89</v>
       </c>
-      <c r="AQ9">
-        <v>1</v>
-      </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU9">
         <v>2</v>
@@ -3011,25 +3011,25 @@
         <v>3.7</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP10">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AQ10">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AU10">
         <v>10</v>
@@ -3220,22 +3220,22 @@
         <v>0</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP11">
-        <v>2.78</v>
+        <v>2.06</v>
       </c>
       <c r="AQ11">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS11">
         <v>0</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AU11">
         <v>8</v>
@@ -3429,19 +3429,19 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AU12">
         <v>8</v>
@@ -3632,22 +3632,22 @@
         <v>0</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP13">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="AR13">
         <v>0</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AU13">
         <v>2</v>
@@ -3835,25 +3835,25 @@
         <v>1.13</v>
       </c>
       <c r="AN14">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP14">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ14">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AR14">
         <v>0.52</v>
       </c>
       <c r="AS14">
-        <v>0.84</v>
+        <v>1.47</v>
       </c>
       <c r="AT14">
-        <v>1.36</v>
+        <v>1.99</v>
       </c>
       <c r="AU14">
         <v>5</v>
@@ -4041,25 +4041,25 @@
         <v>1.54</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP15">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR15">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>0.55</v>
+        <v>0.73</v>
       </c>
       <c r="AT15">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AU15">
         <v>5</v>
@@ -4247,25 +4247,25 @@
         <v>1.33</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO16">
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="AQ16">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="AR16">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AS16">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="AT16">
-        <v>3.68</v>
+        <v>3.89</v>
       </c>
       <c r="AU16">
         <v>4</v>
@@ -4453,25 +4453,25 @@
         <v>2.6</v>
       </c>
       <c r="AN17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP17">
-        <v>2.11</v>
+        <v>1.56</v>
       </c>
       <c r="AQ17">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR17">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AS17">
-        <v>1.13</v>
+        <v>0.95</v>
       </c>
       <c r="AT17">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="AU17">
         <v>8</v>
@@ -4659,25 +4659,25 @@
         <v>1.48</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP18">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="AQ18">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR18">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="AS18">
         <v>1</v>
       </c>
       <c r="AT18">
-        <v>2.26</v>
+        <v>2.01</v>
       </c>
       <c r="AU18">
         <v>5</v>
@@ -4868,22 +4868,22 @@
         <v>0</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP19">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AQ19">
-        <v>1.33</v>
+        <v>2.06</v>
       </c>
       <c r="AR19">
-        <v>1.09</v>
+        <v>0.95</v>
       </c>
       <c r="AS19">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AT19">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="AU19">
         <v>8</v>
@@ -5071,25 +5071,25 @@
         <v>1.6</v>
       </c>
       <c r="AN20">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP20">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AQ20">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR20">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AT20">
-        <v>0.78</v>
+        <v>1.75</v>
       </c>
       <c r="AU20">
         <v>3</v>
@@ -5277,25 +5277,25 @@
         <v>2.53</v>
       </c>
       <c r="AN21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP21">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="AQ21">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="AR21">
-        <v>2.09</v>
+        <v>1.32</v>
       </c>
       <c r="AS21">
-        <v>0.76</v>
+        <v>1.04</v>
       </c>
       <c r="AT21">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="AU21">
         <v>7</v>
@@ -5483,25 +5483,25 @@
         <v>1.93</v>
       </c>
       <c r="AN22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO22">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP22">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AQ22">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS22">
-        <v>0.98</v>
+        <v>1.14</v>
       </c>
       <c r="AT22">
-        <v>0.98</v>
+        <v>2.25</v>
       </c>
       <c r="AU22">
         <v>9</v>
@@ -5689,25 +5689,25 @@
         <v>1.42</v>
       </c>
       <c r="AN23">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AO23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP23">
-        <v>2.78</v>
+        <v>2.06</v>
       </c>
       <c r="AQ23">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="AR23">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AS23">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AT23">
-        <v>3.33</v>
+        <v>3.05</v>
       </c>
       <c r="AU23">
         <v>7</v>
@@ -5895,25 +5895,25 @@
         <v>1.18</v>
       </c>
       <c r="AN24">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AO24">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AP24">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AQ24">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="AR24">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AS24">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AT24">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="AU24">
         <v>6</v>
@@ -6101,25 +6101,25 @@
         <v>1.8</v>
       </c>
       <c r="AN25">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AO25">
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR25">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AS25">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AT25">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6307,25 +6307,25 @@
         <v>1.68</v>
       </c>
       <c r="AN26">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO26">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP26">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR26">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="AS26">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT26">
-        <v>1.85</v>
+        <v>2.13</v>
       </c>
       <c r="AU26">
         <v>9</v>
@@ -6513,25 +6513,25 @@
         <v>3.3</v>
       </c>
       <c r="AN27">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AO27">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP27">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="AQ27">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR27">
-        <v>1.97</v>
+        <v>1.46</v>
       </c>
       <c r="AS27">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="AT27">
-        <v>2.94</v>
+        <v>2.45</v>
       </c>
       <c r="AU27">
         <v>7</v>
@@ -6719,25 +6719,25 @@
         <v>1.25</v>
       </c>
       <c r="AN28">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AO28">
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>2.11</v>
+        <v>1.56</v>
       </c>
       <c r="AQ28">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="AR28">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AS28">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AT28">
-        <v>3.73</v>
+        <v>3.85</v>
       </c>
       <c r="AU28">
         <v>7</v>
@@ -6928,22 +6928,22 @@
         <v>1.5</v>
       </c>
       <c r="AO29">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP29">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="AQ29">
-        <v>1.33</v>
+        <v>2.06</v>
       </c>
       <c r="AR29">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AS29">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AT29">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="AU29">
         <v>6</v>
@@ -7131,25 +7131,25 @@
         <v>2.05</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AO30">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP30">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="AQ30">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR30">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AS30">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AT30">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="AU30">
         <v>3</v>
@@ -7337,25 +7337,25 @@
         <v>1.33</v>
       </c>
       <c r="AN31">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AO31">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="AP31">
+        <v>1.78</v>
+      </c>
+      <c r="AQ31">
+        <v>1.56</v>
+      </c>
+      <c r="AR31">
+        <v>1.47</v>
+      </c>
+      <c r="AS31">
         <v>1.7</v>
       </c>
-      <c r="AQ31">
-        <v>1</v>
-      </c>
-      <c r="AR31">
-        <v>1.82</v>
-      </c>
-      <c r="AS31">
-        <v>1.68</v>
-      </c>
       <c r="AT31">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="AU31">
         <v>7</v>
@@ -7543,25 +7543,25 @@
         <v>1.34</v>
       </c>
       <c r="AN32">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="AO32">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP32">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AQ32">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="AR32">
-        <v>1.09</v>
+        <v>0.98</v>
       </c>
       <c r="AS32">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AT32">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AU32">
         <v>9</v>
@@ -7749,25 +7749,25 @@
         <v>1.45</v>
       </c>
       <c r="AN33">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AO33">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AP33">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="AQ33">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="AR33">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AS33">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AT33">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AU33">
         <v>8</v>
@@ -7955,25 +7955,25 @@
         <v>2.45</v>
       </c>
       <c r="AN34">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO34">
         <v>0.67</v>
       </c>
       <c r="AP34">
+        <v>1.22</v>
+      </c>
+      <c r="AQ34">
         <v>0.89</v>
       </c>
-      <c r="AQ34">
-        <v>1</v>
-      </c>
       <c r="AR34">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AS34">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="AT34">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="AU34">
         <v>8</v>
@@ -8161,25 +8161,25 @@
         <v>1.54</v>
       </c>
       <c r="AN35">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AO35">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR35">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AS35">
-        <v>0.8100000000000001</v>
+        <v>1.12</v>
       </c>
       <c r="AT35">
-        <v>2.01</v>
+        <v>2.42</v>
       </c>
       <c r="AU35">
         <v>9</v>
@@ -8370,22 +8370,22 @@
         <v>1.33</v>
       </c>
       <c r="AO36">
-        <v>0.33</v>
+        <v>1.67</v>
       </c>
       <c r="AP36">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="AQ36">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR36">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AS36">
-        <v>0.91</v>
+        <v>1.11</v>
       </c>
       <c r="AT36">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AU36">
         <v>3</v>
@@ -8573,25 +8573,25 @@
         <v>1.02</v>
       </c>
       <c r="AN37">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AO37">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AP37">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AQ37">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="AR37">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AS37">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AT37">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="AU37">
         <v>3</v>
@@ -8779,25 +8779,25 @@
         <v>2.3</v>
       </c>
       <c r="AN38">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AO38">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP38">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="AQ38">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR38">
-        <v>1.97</v>
+        <v>1.56</v>
       </c>
       <c r="AS38">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AT38">
-        <v>3.33</v>
+        <v>3.09</v>
       </c>
       <c r="AU38">
         <v>5</v>
@@ -8985,25 +8985,25 @@
         <v>1.83</v>
       </c>
       <c r="AN39">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="AO39">
-        <v>0.67</v>
+        <v>1.6</v>
       </c>
       <c r="AP39">
-        <v>2.11</v>
+        <v>1.56</v>
       </c>
       <c r="AQ39">
-        <v>1.33</v>
+        <v>2.06</v>
       </c>
       <c r="AR39">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AS39">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AT39">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="AU39">
         <v>11</v>
@@ -9191,25 +9191,25 @@
         <v>1.29</v>
       </c>
       <c r="AN40">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AO40">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.78</v>
+        <v>2.06</v>
       </c>
       <c r="AQ40">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AR40">
-        <v>1.88</v>
+        <v>1.59</v>
       </c>
       <c r="AS40">
-        <v>0.9399999999999999</v>
+        <v>1.54</v>
       </c>
       <c r="AT40">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="AU40">
         <v>6</v>
@@ -9397,25 +9397,25 @@
         <v>2.04</v>
       </c>
       <c r="AN41">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AO41">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AP41">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AQ41">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR41">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AS41">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AT41">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="AU41">
         <v>3</v>
@@ -9603,25 +9603,25 @@
         <v>1.28</v>
       </c>
       <c r="AN42">
-        <v>3</v>
+        <v>1.86</v>
       </c>
       <c r="AO42">
+        <v>1.86</v>
+      </c>
+      <c r="AP42">
         <v>1.33</v>
       </c>
-      <c r="AP42">
-        <v>1.67</v>
-      </c>
       <c r="AQ42">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AR42">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AS42">
-        <v>1.07</v>
+        <v>1.51</v>
       </c>
       <c r="AT42">
-        <v>2.39</v>
+        <v>2.65</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -9809,25 +9809,25 @@
         <v>1.95</v>
       </c>
       <c r="AN43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO43">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AP43">
-        <v>2.11</v>
+        <v>1.56</v>
       </c>
       <c r="AQ43">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="AR43">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AS43">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AT43">
-        <v>3.13</v>
+        <v>3.06</v>
       </c>
       <c r="AU43">
         <v>3</v>
@@ -10015,25 +10015,25 @@
         <v>3</v>
       </c>
       <c r="AN44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO44">
-        <v>0.5</v>
+        <v>1.29</v>
       </c>
       <c r="AP44">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AQ44">
-        <v>1.33</v>
+        <v>2.06</v>
       </c>
       <c r="AR44">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AS44">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="AT44">
-        <v>3.95</v>
+        <v>3.44</v>
       </c>
       <c r="AU44">
         <v>9</v>
@@ -10221,25 +10221,25 @@
         <v>1.68</v>
       </c>
       <c r="AN45">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO45">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AP45">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AQ45">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="AR45">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AS45">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AT45">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="AU45">
         <v>3</v>
@@ -10427,25 +10427,25 @@
         <v>2.25</v>
       </c>
       <c r="AN46">
-        <v>2.33</v>
+        <v>1.86</v>
       </c>
       <c r="AO46">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AP46">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AQ46">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR46">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="AS46">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AT46">
-        <v>2.84</v>
+        <v>2.44</v>
       </c>
       <c r="AU46">
         <v>6</v>
@@ -10633,25 +10633,25 @@
         <v>1.79</v>
       </c>
       <c r="AN47">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AO47">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP47">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="AQ47">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR47">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AS47">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AT47">
-        <v>3.09</v>
+        <v>2.72</v>
       </c>
       <c r="AU47">
         <v>5</v>
@@ -10839,25 +10839,25 @@
         <v>1.85</v>
       </c>
       <c r="AN48">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AO48">
-        <v>0.5</v>
+        <v>1.29</v>
       </c>
       <c r="AP48">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR48">
-        <v>1.74</v>
+        <v>1.45</v>
       </c>
       <c r="AS48">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AT48">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="AU48">
         <v>3</v>
@@ -11045,25 +11045,25 @@
         <v>2.22</v>
       </c>
       <c r="AN49">
-        <v>2.33</v>
+        <v>1.13</v>
       </c>
       <c r="AO49">
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>2.78</v>
+        <v>2.06</v>
       </c>
       <c r="AQ49">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR49">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="AS49">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="AT49">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="AU49">
         <v>3</v>
@@ -11251,25 +11251,25 @@
         <v>1.45</v>
       </c>
       <c r="AN50">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO50">
-        <v>1</v>
+        <v>1.63</v>
       </c>
       <c r="AP50">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AQ50">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR50">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="AS50">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AT50">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11457,25 +11457,25 @@
         <v>2.3</v>
       </c>
       <c r="AN51">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AO51">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AP51">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="AQ51">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR51">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AS51">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AT51">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="AU51">
         <v>7</v>
@@ -11666,22 +11666,22 @@
         <v>1</v>
       </c>
       <c r="AO52">
-        <v>0.67</v>
+        <v>1.88</v>
       </c>
       <c r="AP52">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="AQ52">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="AR52">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AS52">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AT52">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="AU52">
         <v>4</v>
@@ -11869,25 +11869,25 @@
         <v>1.41</v>
       </c>
       <c r="AN53">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AO53">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AP53">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="AQ53">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="AR53">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="AS53">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="AT53">
-        <v>3.49</v>
+        <v>3.41</v>
       </c>
       <c r="AU53">
         <v>3</v>
@@ -12075,25 +12075,25 @@
         <v>1.53</v>
       </c>
       <c r="AN54">
-        <v>2.25</v>
+        <v>1.56</v>
       </c>
       <c r="AO54">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AP54">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AQ54">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR54">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AS54">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AT54">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="AU54">
         <v>4</v>
@@ -12281,25 +12281,25 @@
         <v>3.75</v>
       </c>
       <c r="AN55">
-        <v>3</v>
+        <v>1.86</v>
       </c>
       <c r="AO55">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP55">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AQ55">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="AR55">
-        <v>2.36</v>
+        <v>1.7</v>
       </c>
       <c r="AS55">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AT55">
-        <v>3.36</v>
+        <v>2.83</v>
       </c>
       <c r="AU55">
         <v>11</v>
@@ -12487,25 +12487,25 @@
         <v>2.7</v>
       </c>
       <c r="AN56">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="AO56">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AP56">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="AQ56">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR56">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="AS56">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AT56">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AU56">
         <v>12</v>
@@ -12693,25 +12693,25 @@
         <v>1.35</v>
       </c>
       <c r="AN57">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AO57">
-        <v>0.4</v>
+        <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ57">
-        <v>1.33</v>
+        <v>2.06</v>
       </c>
       <c r="AR57">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AS57">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AT57">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AU57">
         <v>3</v>
@@ -12899,25 +12899,25 @@
         <v>1.28</v>
       </c>
       <c r="AN58">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO58">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AP58">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AQ58">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="AR58">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AS58">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AT58">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="AU58">
         <v>0</v>
@@ -13105,25 +13105,25 @@
         <v>2.4</v>
       </c>
       <c r="AN59">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AO59">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AP59">
-        <v>2.11</v>
+        <v>1.56</v>
       </c>
       <c r="AQ59">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR59">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AS59">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AT59">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="AU59">
         <v>4</v>
@@ -13311,25 +13311,25 @@
         <v>2.25</v>
       </c>
       <c r="AN60">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AO60">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="AP60">
-        <v>2.78</v>
+        <v>2.06</v>
       </c>
       <c r="AQ60">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR60">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AS60">
-        <v>1.06</v>
+        <v>0.98</v>
       </c>
       <c r="AT60">
-        <v>2.74</v>
+        <v>2.47</v>
       </c>
       <c r="AU60">
         <v>9</v>
@@ -13520,19 +13520,19 @@
         <v>0.8</v>
       </c>
       <c r="AO61">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AP61">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="AQ61">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR61">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AS61">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AT61">
         <v>2.35</v>
@@ -13723,25 +13723,25 @@
         <v>1.75</v>
       </c>
       <c r="AN62">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AO62">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AP62">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR62">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AS62">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AT62">
-        <v>2.21</v>
+        <v>2.41</v>
       </c>
       <c r="AU62">
         <v>5</v>
@@ -13929,25 +13929,25 @@
         <v>1.18</v>
       </c>
       <c r="AN63">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AO63">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AP63">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AQ63">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="AR63">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AS63">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="AT63">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="AU63">
         <v>2</v>
@@ -14135,25 +14135,25 @@
         <v>1.16</v>
       </c>
       <c r="AN64">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AO64">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="AP64">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="AQ64">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="AR64">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="AS64">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AT64">
-        <v>3.06</v>
+        <v>2.83</v>
       </c>
       <c r="AU64">
         <v>3</v>
@@ -14341,25 +14341,25 @@
         <v>1.45</v>
       </c>
       <c r="AN65">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AO65">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AP65">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="AQ65">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AR65">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AS65">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="AT65">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="AU65">
         <v>5</v>
@@ -14547,25 +14547,25 @@
         <v>1.6</v>
       </c>
       <c r="AN66">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AO66">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AP66">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="AQ66">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="AR66">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="AS66">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AT66">
-        <v>3.22</v>
+        <v>3.07</v>
       </c>
       <c r="AU66">
         <v>3</v>
@@ -14753,25 +14753,25 @@
         <v>4</v>
       </c>
       <c r="AN67">
-        <v>3</v>
+        <v>1.89</v>
       </c>
       <c r="AO67">
-        <v>0.33</v>
+        <v>0.45</v>
       </c>
       <c r="AP67">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR67">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AS67">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="AT67">
-        <v>3.32</v>
+        <v>2.96</v>
       </c>
       <c r="AU67">
         <v>5</v>
@@ -14959,25 +14959,25 @@
         <v>1.85</v>
       </c>
       <c r="AN68">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AO68">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP68">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="AQ68">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR68">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AS68">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AT68">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="AU68">
         <v>5</v>
@@ -15165,25 +15165,25 @@
         <v>1.47</v>
       </c>
       <c r="AN69">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AO69">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AP69">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AQ69">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="AR69">
-        <v>0.89</v>
+        <v>0.98</v>
       </c>
       <c r="AS69">
-        <v>0.93</v>
+        <v>1.14</v>
       </c>
       <c r="AT69">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AU69">
         <v>5</v>
@@ -15371,25 +15371,25 @@
         <v>1.4</v>
       </c>
       <c r="AN70">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AO70">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AP70">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ70">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR70">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AS70">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AT70">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="AU70">
         <v>4</v>
@@ -15577,25 +15577,25 @@
         <v>2.1</v>
       </c>
       <c r="AN71">
-        <v>2.6</v>
+        <v>1.64</v>
       </c>
       <c r="AO71">
-        <v>0.83</v>
+        <v>1.27</v>
       </c>
       <c r="AP71">
+        <v>2.06</v>
+      </c>
+      <c r="AQ71">
+        <v>1.33</v>
+      </c>
+      <c r="AR71">
+        <v>1.52</v>
+      </c>
+      <c r="AS71">
+        <v>1.26</v>
+      </c>
+      <c r="AT71">
         <v>2.78</v>
-      </c>
-      <c r="AQ71">
-        <v>1</v>
-      </c>
-      <c r="AR71">
-        <v>1.72</v>
-      </c>
-      <c r="AS71">
-        <v>1.2</v>
-      </c>
-      <c r="AT71">
-        <v>2.92</v>
       </c>
       <c r="AU71">
         <v>9</v>
@@ -15783,25 +15783,25 @@
         <v>1.51</v>
       </c>
       <c r="AN72">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AO72">
-        <v>0.83</v>
+        <v>1.75</v>
       </c>
       <c r="AP72">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AQ72">
-        <v>1.33</v>
+        <v>2.06</v>
       </c>
       <c r="AR72">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AS72">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="AT72">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="AU72">
         <v>7</v>
@@ -15989,25 +15989,25 @@
         <v>1.69</v>
       </c>
       <c r="AN73">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AO73">
         <v>1</v>
       </c>
       <c r="AP73">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="AQ73">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR73">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AS73">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AT73">
-        <v>2.49</v>
+        <v>2.24</v>
       </c>
       <c r="AU73">
         <v>5</v>
@@ -16195,25 +16195,25 @@
         <v>1.31</v>
       </c>
       <c r="AN74">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="AO74">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AP74">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AQ74">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AR74">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AS74">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="AT74">
-        <v>2.34</v>
+        <v>2.67</v>
       </c>
       <c r="AU74">
         <v>5</v>
@@ -16401,25 +16401,25 @@
         <v>1.15</v>
       </c>
       <c r="AN75">
+        <v>1.17</v>
+      </c>
+      <c r="AO75">
         <v>1.8</v>
       </c>
-      <c r="AO75">
+      <c r="AP75">
         <v>1.33</v>
       </c>
-      <c r="AP75">
-        <v>1.67</v>
-      </c>
       <c r="AQ75">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="AR75">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AS75">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="AT75">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="AU75">
         <v>5</v>
@@ -16607,25 +16607,25 @@
         <v>1.3</v>
       </c>
       <c r="AN76">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="AO76">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AP76">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="AQ76">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="AR76">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AS76">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AT76">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AU76">
         <v>3</v>
@@ -16813,25 +16813,25 @@
         <v>2.9</v>
       </c>
       <c r="AN77">
-        <v>2.67</v>
+        <v>1.92</v>
       </c>
       <c r="AO77">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AP77">
-        <v>2.11</v>
+        <v>1.56</v>
       </c>
       <c r="AQ77">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR77">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AS77">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AT77">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="AU77">
         <v>7</v>
@@ -17019,25 +17019,25 @@
         <v>1.12</v>
       </c>
       <c r="AN78">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AO78">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="AP78">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AQ78">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="AR78">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="AS78">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AT78">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="AU78">
         <v>2</v>
@@ -17225,25 +17225,25 @@
         <v>2.2</v>
       </c>
       <c r="AN79">
-        <v>2.5</v>
+        <v>1.64</v>
       </c>
       <c r="AO79">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="AP79">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AQ79">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="AR79">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="AS79">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AT79">
-        <v>3.45</v>
+        <v>3.01</v>
       </c>
       <c r="AU79">
         <v>4</v>
@@ -17431,25 +17431,25 @@
         <v>2.8</v>
       </c>
       <c r="AN80">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AO80">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AP80">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="AQ80">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR80">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="AS80">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AT80">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
       <c r="AU80">
         <v>-1</v>
@@ -17637,25 +17637,25 @@
         <v>0</v>
       </c>
       <c r="AN81">
-        <v>2</v>
+        <v>1.31</v>
       </c>
       <c r="AO81">
-        <v>0.43</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP81">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AQ81">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR81">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AS81">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AT81">
-        <v>2.39</v>
+        <v>2.51</v>
       </c>
       <c r="AU81">
         <v>2</v>
@@ -17843,25 +17843,25 @@
         <v>0</v>
       </c>
       <c r="AN82">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AO82">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP82">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AQ82">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="AR82">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AS82">
-        <v>0.97</v>
+        <v>1.13</v>
       </c>
       <c r="AT82">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="AU82">
         <v>6</v>
@@ -18049,25 +18049,25 @@
         <v>1.85</v>
       </c>
       <c r="AN83">
-        <v>2.67</v>
+        <v>1.85</v>
       </c>
       <c r="AO83">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP83">
-        <v>2.78</v>
+        <v>2.06</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR83">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="AS83">
         <v>1.2</v>
       </c>
       <c r="AT83">
-        <v>2.96</v>
+        <v>2.69</v>
       </c>
       <c r="AU83">
         <v>6</v>
@@ -18255,25 +18255,25 @@
         <v>1.16</v>
       </c>
       <c r="AN84">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="AO84">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AP84">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="AQ84">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AR84">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AS84">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="AT84">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AU84">
         <v>3</v>
@@ -18461,25 +18461,25 @@
         <v>1.47</v>
       </c>
       <c r="AN85">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AO85">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AP85">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="AQ85">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR85">
+        <v>1.25</v>
+      </c>
+      <c r="AS85">
         <v>1.46</v>
       </c>
-      <c r="AS85">
-        <v>1.38</v>
-      </c>
       <c r="AT85">
-        <v>2.84</v>
+        <v>2.71</v>
       </c>
       <c r="AU85">
         <v>7</v>
@@ -18667,25 +18667,25 @@
         <v>1.2</v>
       </c>
       <c r="AN86">
-        <v>1.57</v>
+        <v>1.23</v>
       </c>
       <c r="AO86">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AP86">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AQ86">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="AR86">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AS86">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="AT86">
-        <v>2.57</v>
+        <v>2.85</v>
       </c>
       <c r="AU86">
         <v>2</v>
@@ -18873,25 +18873,25 @@
         <v>1.72</v>
       </c>
       <c r="AN87">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AO87">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AP87">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ87">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR87">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AS87">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="AT87">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="AU87">
         <v>8</v>
@@ -19079,25 +19079,25 @@
         <v>2.65</v>
       </c>
       <c r="AN88">
-        <v>2.71</v>
+        <v>1.93</v>
       </c>
       <c r="AO88">
-        <v>0.71</v>
+        <v>1.21</v>
       </c>
       <c r="AP88">
-        <v>2.11</v>
+        <v>1.56</v>
       </c>
       <c r="AQ88">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR88">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AS88">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AT88">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="AU88">
         <v>6</v>
@@ -19285,25 +19285,25 @@
         <v>1.75</v>
       </c>
       <c r="AN89">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AO89">
-        <v>1.14</v>
+        <v>1.93</v>
       </c>
       <c r="AP89">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="AQ89">
-        <v>1.33</v>
+        <v>2.06</v>
       </c>
       <c r="AR89">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AS89">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="AT89">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="AU89">
         <v>3</v>
@@ -19491,25 +19491,25 @@
         <v>3.2</v>
       </c>
       <c r="AN90">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AO90">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="AP90">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR90">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="AS90">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AT90">
-        <v>3.23</v>
+        <v>2.84</v>
       </c>
       <c r="AU90">
         <v>11</v>
@@ -19697,25 +19697,25 @@
         <v>1.47</v>
       </c>
       <c r="AN91">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AO91">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AP91">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AQ91">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="AR91">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AS91">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AT91">
-        <v>2.68</v>
+        <v>2.79</v>
       </c>
       <c r="AU91">
         <v>3</v>
@@ -19903,25 +19903,25 @@
         <v>1.9</v>
       </c>
       <c r="AN92">
-        <v>2.17</v>
+        <v>1.57</v>
       </c>
       <c r="AO92">
-        <v>1.14</v>
+        <v>1.8</v>
       </c>
       <c r="AP92">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AQ92">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="AR92">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AS92">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AT92">
-        <v>3.39</v>
+        <v>3.24</v>
       </c>
       <c r="AU92">
         <v>9</v>
@@ -20109,25 +20109,25 @@
         <v>1.11</v>
       </c>
       <c r="AN93">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AO93">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AP93">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AQ93">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AR93">
-        <v>0.89</v>
+        <v>1.02</v>
       </c>
       <c r="AS93">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="AT93">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="AU93">
         <v>2</v>
@@ -20315,25 +20315,25 @@
         <v>1.8</v>
       </c>
       <c r="AN94">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="AO94">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AP94">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AQ94">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR94">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AS94">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AT94">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="AU94">
         <v>5</v>
@@ -20521,25 +20521,25 @@
         <v>1.36</v>
       </c>
       <c r="AN95">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AO95">
-        <v>0.71</v>
+        <v>1.13</v>
       </c>
       <c r="AP95">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="AQ95">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR95">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AS95">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AT95">
-        <v>2.53</v>
+        <v>2.37</v>
       </c>
       <c r="AU95">
         <v>2</v>
@@ -20727,25 +20727,25 @@
         <v>2.1</v>
       </c>
       <c r="AN96">
-        <v>2.71</v>
+        <v>2</v>
       </c>
       <c r="AO96">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="AP96">
-        <v>2.78</v>
+        <v>2.06</v>
       </c>
       <c r="AQ96">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="AR96">
-        <v>1.72</v>
+        <v>1.49</v>
       </c>
       <c r="AS96">
-        <v>0.96</v>
+        <v>1.09</v>
       </c>
       <c r="AT96">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="AU96">
         <v>4</v>
@@ -20933,25 +20933,25 @@
         <v>4.5</v>
       </c>
       <c r="AN97">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AO97">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AP97">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AQ97">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR97">
-        <v>2.11</v>
+        <v>1.76</v>
       </c>
       <c r="AS97">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AT97">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="AU97">
         <v>6</v>
@@ -21139,25 +21139,25 @@
         <v>1.9</v>
       </c>
       <c r="AN98">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AO98">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="AP98">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="AQ98">
-        <v>1.33</v>
+        <v>2.06</v>
       </c>
       <c r="AR98">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="AS98">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AT98">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="AU98">
         <v>6</v>
@@ -21345,25 +21345,25 @@
         <v>1.57</v>
       </c>
       <c r="AN99">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="AO99">
         <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="AQ99">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR99">
+        <v>1.08</v>
+      </c>
+      <c r="AS99">
         <v>1.21</v>
       </c>
-      <c r="AS99">
-        <v>1.09</v>
-      </c>
       <c r="AT99">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AU99">
         <v>6</v>
@@ -21551,25 +21551,25 @@
         <v>2</v>
       </c>
       <c r="AN100">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AO100">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AP100">
-        <v>2.11</v>
+        <v>1.56</v>
       </c>
       <c r="AQ100">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR100">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AS100">
         <v>1.48</v>
       </c>
       <c r="AT100">
-        <v>3.17</v>
+        <v>3.02</v>
       </c>
       <c r="AU100">
         <v>3</v>
@@ -21757,25 +21757,25 @@
         <v>1.1</v>
       </c>
       <c r="AN101">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AO101">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="AP101">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ101">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="AR101">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AS101">
-        <v>1.46</v>
+        <v>1.79</v>
       </c>
       <c r="AT101">
-        <v>2.83</v>
+        <v>2.96</v>
       </c>
       <c r="AU101">
         <v>3</v>
@@ -21963,25 +21963,25 @@
         <v>1.35</v>
       </c>
       <c r="AN102">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AO102">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AP102">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AQ102">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR102">
-        <v>0.9</v>
+        <v>1.02</v>
       </c>
       <c r="AS102">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AT102">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AU102">
         <v>6</v>
@@ -22169,25 +22169,25 @@
         <v>1.77</v>
       </c>
       <c r="AN103">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="AO103">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AP103">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="AQ103">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AR103">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AS103">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AT103">
-        <v>2.57</v>
+        <v>2.49</v>
       </c>
       <c r="AU103">
         <v>5</v>
@@ -22375,25 +22375,25 @@
         <v>3.8</v>
       </c>
       <c r="AN104">
-        <v>2.13</v>
+        <v>1.59</v>
       </c>
       <c r="AO104">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AP104">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AQ104">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR104">
-        <v>2.12</v>
+        <v>1.79</v>
       </c>
       <c r="AS104">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AT104">
-        <v>3.25</v>
+        <v>2.87</v>
       </c>
       <c r="AU104">
         <v>5</v>
@@ -22581,25 +22581,25 @@
         <v>1.39</v>
       </c>
       <c r="AN105">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AO105">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AP105">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AQ105">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AR105">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AS105">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AT105">
-        <v>2.87</v>
+        <v>3.01</v>
       </c>
       <c r="AU105">
         <v>6</v>
@@ -22787,25 +22787,25 @@
         <v>1.73</v>
       </c>
       <c r="AN106">
-        <v>1.88</v>
+        <v>1.41</v>
       </c>
       <c r="AO106">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="AP106">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AQ106">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="AR106">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AS106">
-        <v>0.9399999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="AT106">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="AU106">
         <v>3</v>
@@ -22993,25 +22993,25 @@
         <v>1.36</v>
       </c>
       <c r="AN107">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AO107">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="AP107">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="AQ107">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="AR107">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AS107">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="AT107">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="AU107">
         <v>4</v>
@@ -23199,25 +23199,25 @@
         <v>2.05</v>
       </c>
       <c r="AN108">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AO108">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP108">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AQ108">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR108">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AS108">
-        <v>0.97</v>
+        <v>1.16</v>
       </c>
       <c r="AT108">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="AU108">
         <v>5</v>
@@ -23405,25 +23405,25 @@
         <v>1.55</v>
       </c>
       <c r="AN109">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="AO109">
-        <v>1.13</v>
+        <v>1.65</v>
       </c>
       <c r="AP109">
-        <v>2.78</v>
+        <v>2.06</v>
       </c>
       <c r="AQ109">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="AR109">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AS109">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AT109">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="AU109">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="AQ2">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1575,10 +1575,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AQ4">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1987,10 +1987,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ5">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2193,10 +2193,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.56</v>
+        <v>2.11</v>
       </c>
       <c r="AQ6">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2399,10 +2399,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
+        <v>1.67</v>
+      </c>
+      <c r="AQ7">
         <v>1.33</v>
-      </c>
-      <c r="AQ7">
-        <v>2.06</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2599,25 +2599,25 @@
         <v>2.38</v>
       </c>
       <c r="AN8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="AQ8">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="AR8">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS8">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AT8">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU8">
         <v>5</v>
@@ -2805,25 +2805,25 @@
         <v>1.58</v>
       </c>
       <c r="AN9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ9">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AR9">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AU9">
         <v>2</v>
@@ -3011,25 +3011,25 @@
         <v>3.7</v>
       </c>
       <c r="AN10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AQ10">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR10">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AU10">
         <v>10</v>
@@ -3220,22 +3220,22 @@
         <v>0</v>
       </c>
       <c r="AO11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.06</v>
+        <v>2.78</v>
       </c>
       <c r="AQ11">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AR11">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AS11">
         <v>0</v>
       </c>
       <c r="AT11">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AU11">
         <v>8</v>
@@ -3429,19 +3429,19 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="AQ12">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AR12">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AU12">
         <v>8</v>
@@ -3632,22 +3632,22 @@
         <v>0</v>
       </c>
       <c r="AO13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP13">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AQ13">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>0</v>
       </c>
       <c r="AS13">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AU13">
         <v>2</v>
@@ -3835,25 +3835,25 @@
         <v>1.13</v>
       </c>
       <c r="AN14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO14">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AQ14">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AR14">
         <v>0.52</v>
       </c>
       <c r="AS14">
-        <v>1.47</v>
+        <v>0.84</v>
       </c>
       <c r="AT14">
-        <v>1.99</v>
+        <v>1.36</v>
       </c>
       <c r="AU14">
         <v>5</v>
@@ -4041,25 +4041,25 @@
         <v>1.54</v>
       </c>
       <c r="AN15">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO15">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="AQ15">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR15">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AS15">
-        <v>0.73</v>
+        <v>0.55</v>
       </c>
       <c r="AT15">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AU15">
         <v>5</v>
@@ -4247,25 +4247,25 @@
         <v>1.33</v>
       </c>
       <c r="AN16">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="AQ16">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="AR16">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AS16">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AT16">
-        <v>3.89</v>
+        <v>3.68</v>
       </c>
       <c r="AU16">
         <v>4</v>
@@ -4453,25 +4453,25 @@
         <v>2.6</v>
       </c>
       <c r="AN17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.56</v>
+        <v>2.11</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AR17">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AS17">
-        <v>0.95</v>
+        <v>1.13</v>
       </c>
       <c r="AT17">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="AU17">
         <v>8</v>
@@ -4659,25 +4659,25 @@
         <v>1.48</v>
       </c>
       <c r="AN18">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO18">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="AQ18">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AR18">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AS18">
         <v>1</v>
       </c>
       <c r="AT18">
-        <v>2.01</v>
+        <v>2.26</v>
       </c>
       <c r="AU18">
         <v>5</v>
@@ -4868,22 +4868,22 @@
         <v>0</v>
       </c>
       <c r="AO19">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AQ19">
-        <v>2.06</v>
+        <v>1.33</v>
       </c>
       <c r="AR19">
-        <v>0.95</v>
+        <v>1.09</v>
       </c>
       <c r="AS19">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AT19">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AU19">
         <v>8</v>
@@ -5071,25 +5071,25 @@
         <v>1.6</v>
       </c>
       <c r="AN20">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO20">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP20">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ20">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AR20">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="AS20">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="AT20">
-        <v>1.75</v>
+        <v>0.78</v>
       </c>
       <c r="AU20">
         <v>3</v>
@@ -5277,25 +5277,25 @@
         <v>2.53</v>
       </c>
       <c r="AN21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP21">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="AQ21">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="AR21">
-        <v>1.32</v>
+        <v>2.09</v>
       </c>
       <c r="AS21">
-        <v>1.04</v>
+        <v>0.76</v>
       </c>
       <c r="AT21">
-        <v>2.36</v>
+        <v>2.85</v>
       </c>
       <c r="AU21">
         <v>7</v>
@@ -5483,25 +5483,25 @@
         <v>1.93</v>
       </c>
       <c r="AN22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO22">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ22">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AR22">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AS22">
-        <v>1.14</v>
+        <v>0.98</v>
       </c>
       <c r="AT22">
-        <v>2.25</v>
+        <v>0.98</v>
       </c>
       <c r="AU22">
         <v>9</v>
@@ -5689,25 +5689,25 @@
         <v>1.42</v>
       </c>
       <c r="AN23">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AO23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP23">
-        <v>2.06</v>
+        <v>2.78</v>
       </c>
       <c r="AQ23">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="AR23">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AS23">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AT23">
-        <v>3.05</v>
+        <v>3.33</v>
       </c>
       <c r="AU23">
         <v>7</v>
@@ -5895,25 +5895,25 @@
         <v>1.18</v>
       </c>
       <c r="AN24">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AO24">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AQ24">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AR24">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="AS24">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AT24">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="AU24">
         <v>6</v>
@@ -6101,25 +6101,25 @@
         <v>1.8</v>
       </c>
       <c r="AN25">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AO25">
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AQ25">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AR25">
+        <v>1.32</v>
+      </c>
+      <c r="AS25">
         <v>1.15</v>
       </c>
-      <c r="AS25">
-        <v>1.19</v>
-      </c>
       <c r="AT25">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6307,25 +6307,25 @@
         <v>1.68</v>
       </c>
       <c r="AN26">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO26">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP26">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AQ26">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR26">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AS26">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AT26">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="AU26">
         <v>9</v>
@@ -6513,25 +6513,25 @@
         <v>3.3</v>
       </c>
       <c r="AN27">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AO27">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP27">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AR27">
-        <v>1.46</v>
+        <v>1.97</v>
       </c>
       <c r="AS27">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="AT27">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="AU27">
         <v>7</v>
@@ -6719,25 +6719,25 @@
         <v>1.25</v>
       </c>
       <c r="AN28">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="AO28">
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.56</v>
+        <v>2.11</v>
       </c>
       <c r="AQ28">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="AR28">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AS28">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AT28">
-        <v>3.85</v>
+        <v>3.73</v>
       </c>
       <c r="AU28">
         <v>7</v>
@@ -6928,22 +6928,22 @@
         <v>1.5</v>
       </c>
       <c r="AO29">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP29">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="AQ29">
-        <v>2.06</v>
+        <v>1.33</v>
       </c>
       <c r="AR29">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AS29">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="AT29">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="AU29">
         <v>6</v>
@@ -7131,25 +7131,25 @@
         <v>2.05</v>
       </c>
       <c r="AN30">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AO30">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="AQ30">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AR30">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AS30">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AT30">
-        <v>2.79</v>
+        <v>2.63</v>
       </c>
       <c r="AU30">
         <v>3</v>
@@ -7337,25 +7337,25 @@
         <v>1.33</v>
       </c>
       <c r="AN31">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AO31">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ31">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AR31">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="AS31">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AT31">
-        <v>3.17</v>
+        <v>3.5</v>
       </c>
       <c r="AU31">
         <v>7</v>
@@ -7543,25 +7543,25 @@
         <v>1.34</v>
       </c>
       <c r="AN32">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="AO32">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP32">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AQ32">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="AR32">
-        <v>0.98</v>
+        <v>1.09</v>
       </c>
       <c r="AS32">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AT32">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AU32">
         <v>9</v>
@@ -7749,25 +7749,25 @@
         <v>1.45</v>
       </c>
       <c r="AN33">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AO33">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="AQ33">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="AR33">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AS33">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="AT33">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="AU33">
         <v>8</v>
@@ -7955,25 +7955,25 @@
         <v>2.45</v>
       </c>
       <c r="AN34">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO34">
         <v>0.67</v>
       </c>
       <c r="AP34">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="AQ34">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AR34">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AS34">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AT34">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="AU34">
         <v>8</v>
@@ -8161,25 +8161,25 @@
         <v>1.54</v>
       </c>
       <c r="AN35">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AO35">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP35">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AQ35">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AR35">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AS35">
-        <v>1.12</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT35">
-        <v>2.42</v>
+        <v>2.01</v>
       </c>
       <c r="AU35">
         <v>9</v>
@@ -8370,22 +8370,22 @@
         <v>1.33</v>
       </c>
       <c r="AO36">
-        <v>1.67</v>
+        <v>0.33</v>
       </c>
       <c r="AP36">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="AQ36">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR36">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AS36">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
       <c r="AT36">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AU36">
         <v>3</v>
@@ -8573,25 +8573,25 @@
         <v>1.02</v>
       </c>
       <c r="AN37">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AO37">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AP37">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ37">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="AR37">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AS37">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="AT37">
-        <v>2.98</v>
+        <v>2.74</v>
       </c>
       <c r="AU37">
         <v>3</v>
@@ -8779,25 +8779,25 @@
         <v>2.3</v>
       </c>
       <c r="AN38">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AO38">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP38">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="AQ38">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AR38">
-        <v>1.56</v>
+        <v>1.97</v>
       </c>
       <c r="AS38">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AT38">
-        <v>3.09</v>
+        <v>3.33</v>
       </c>
       <c r="AU38">
         <v>5</v>
@@ -8985,25 +8985,25 @@
         <v>1.83</v>
       </c>
       <c r="AN39">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="AO39">
-        <v>1.6</v>
+        <v>0.67</v>
       </c>
       <c r="AP39">
-        <v>1.56</v>
+        <v>2.11</v>
       </c>
       <c r="AQ39">
-        <v>2.06</v>
+        <v>1.33</v>
       </c>
       <c r="AR39">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AS39">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AT39">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="AU39">
         <v>11</v>
@@ -9191,25 +9191,25 @@
         <v>1.29</v>
       </c>
       <c r="AN40">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AO40">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>2.06</v>
+        <v>2.78</v>
       </c>
       <c r="AQ40">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AR40">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="AS40">
-        <v>1.54</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT40">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="AU40">
         <v>6</v>
@@ -9397,25 +9397,25 @@
         <v>2.04</v>
       </c>
       <c r="AN41">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AO41">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AR41">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AS41">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AT41">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="AU41">
         <v>3</v>
@@ -9603,25 +9603,25 @@
         <v>1.28</v>
       </c>
       <c r="AN42">
-        <v>1.86</v>
+        <v>3</v>
       </c>
       <c r="AO42">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AQ42">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AR42">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AS42">
-        <v>1.51</v>
+        <v>1.07</v>
       </c>
       <c r="AT42">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -9809,25 +9809,25 @@
         <v>1.95</v>
       </c>
       <c r="AN43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO43">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AP43">
+        <v>2.11</v>
+      </c>
+      <c r="AQ43">
         <v>1.56</v>
       </c>
-      <c r="AQ43">
-        <v>1.22</v>
-      </c>
       <c r="AR43">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AS43">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AT43">
-        <v>3.06</v>
+        <v>3.13</v>
       </c>
       <c r="AU43">
         <v>3</v>
@@ -10015,25 +10015,25 @@
         <v>3</v>
       </c>
       <c r="AN44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO44">
-        <v>1.29</v>
+        <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AQ44">
-        <v>2.06</v>
+        <v>1.33</v>
       </c>
       <c r="AR44">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AS44">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AT44">
-        <v>3.44</v>
+        <v>3.95</v>
       </c>
       <c r="AU44">
         <v>9</v>
@@ -10221,25 +10221,25 @@
         <v>1.68</v>
       </c>
       <c r="AN45">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO45">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AP45">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AQ45">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="AR45">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AS45">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AT45">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AU45">
         <v>3</v>
@@ -10427,25 +10427,25 @@
         <v>2.25</v>
       </c>
       <c r="AN46">
-        <v>1.86</v>
+        <v>2.33</v>
       </c>
       <c r="AO46">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP46">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ46">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AR46">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AS46">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AT46">
-        <v>2.44</v>
+        <v>2.84</v>
       </c>
       <c r="AU46">
         <v>6</v>
@@ -10633,25 +10633,25 @@
         <v>1.79</v>
       </c>
       <c r="AN47">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="AO47">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="AQ47">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AR47">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AS47">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AT47">
-        <v>2.72</v>
+        <v>3.09</v>
       </c>
       <c r="AU47">
         <v>5</v>
@@ -10839,25 +10839,25 @@
         <v>1.85</v>
       </c>
       <c r="AN48">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AO48">
-        <v>1.29</v>
+        <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ48">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AR48">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="AS48">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AT48">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="AU48">
         <v>3</v>
@@ -11045,25 +11045,25 @@
         <v>2.22</v>
       </c>
       <c r="AN49">
-        <v>1.13</v>
+        <v>2.33</v>
       </c>
       <c r="AO49">
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>2.06</v>
+        <v>2.78</v>
       </c>
       <c r="AQ49">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AR49">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="AS49">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="AT49">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="AU49">
         <v>3</v>
@@ -11251,25 +11251,25 @@
         <v>1.45</v>
       </c>
       <c r="AN50">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO50">
-        <v>1.63</v>
+        <v>1</v>
       </c>
       <c r="AP50">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ50">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR50">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="AS50">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AT50">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11457,25 +11457,25 @@
         <v>2.3</v>
       </c>
       <c r="AN51">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="AO51">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AP51">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="AQ51">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AR51">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AS51">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AT51">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AU51">
         <v>7</v>
@@ -11666,22 +11666,22 @@
         <v>1</v>
       </c>
       <c r="AO52">
-        <v>1.88</v>
+        <v>0.67</v>
       </c>
       <c r="AP52">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="AQ52">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AR52">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AS52">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AT52">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="AU52">
         <v>4</v>
@@ -11869,25 +11869,25 @@
         <v>1.41</v>
       </c>
       <c r="AN53">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AO53">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AP53">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="AQ53">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="AR53">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="AS53">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="AT53">
-        <v>3.41</v>
+        <v>3.49</v>
       </c>
       <c r="AU53">
         <v>3</v>
@@ -12075,25 +12075,25 @@
         <v>1.53</v>
       </c>
       <c r="AN54">
-        <v>1.56</v>
+        <v>2.25</v>
       </c>
       <c r="AO54">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AQ54">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AR54">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AS54">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AT54">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="AU54">
         <v>4</v>
@@ -12281,25 +12281,25 @@
         <v>3.75</v>
       </c>
       <c r="AN55">
-        <v>1.86</v>
+        <v>3</v>
       </c>
       <c r="AO55">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AP55">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AQ55">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="AR55">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="AS55">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AT55">
-        <v>2.83</v>
+        <v>3.36</v>
       </c>
       <c r="AU55">
         <v>11</v>
@@ -12487,25 +12487,25 @@
         <v>2.7</v>
       </c>
       <c r="AN56">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="AO56">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AP56">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="AQ56">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AR56">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="AS56">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="AT56">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AU56">
         <v>12</v>
@@ -12693,25 +12693,25 @@
         <v>1.35</v>
       </c>
       <c r="AN57">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AO57">
+        <v>0.4</v>
+      </c>
+      <c r="AP57">
+        <v>1.13</v>
+      </c>
+      <c r="AQ57">
         <v>1.33</v>
       </c>
-      <c r="AP57">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AQ57">
-        <v>2.06</v>
-      </c>
       <c r="AR57">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AS57">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AT57">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AU57">
         <v>3</v>
@@ -12899,25 +12899,25 @@
         <v>1.28</v>
       </c>
       <c r="AN58">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO58">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP58">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ58">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="AR58">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AS58">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AT58">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="AU58">
         <v>0</v>
@@ -13105,25 +13105,25 @@
         <v>2.4</v>
       </c>
       <c r="AN59">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AO59">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.56</v>
+        <v>2.11</v>
       </c>
       <c r="AQ59">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AR59">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AS59">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AT59">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="AU59">
         <v>4</v>
@@ -13311,25 +13311,25 @@
         <v>2.25</v>
       </c>
       <c r="AN60">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="AO60">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="AP60">
-        <v>2.06</v>
+        <v>2.78</v>
       </c>
       <c r="AQ60">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AR60">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AS60">
-        <v>0.98</v>
+        <v>1.06</v>
       </c>
       <c r="AT60">
-        <v>2.47</v>
+        <v>2.74</v>
       </c>
       <c r="AU60">
         <v>9</v>
@@ -13520,19 +13520,19 @@
         <v>0.8</v>
       </c>
       <c r="AO61">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="AQ61">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AR61">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AS61">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AT61">
         <v>2.35</v>
@@ -13723,25 +13723,25 @@
         <v>1.75</v>
       </c>
       <c r="AN62">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AO62">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AQ62">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR62">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AS62">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AT62">
-        <v>2.41</v>
+        <v>2.21</v>
       </c>
       <c r="AU62">
         <v>5</v>
@@ -13929,25 +13929,25 @@
         <v>1.18</v>
       </c>
       <c r="AN63">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AO63">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AP63">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ63">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="AR63">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AS63">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="AT63">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
       <c r="AU63">
         <v>2</v>
@@ -14135,25 +14135,25 @@
         <v>1.16</v>
       </c>
       <c r="AN64">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AO64">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="AP64">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="AQ64">
+        <v>1</v>
+      </c>
+      <c r="AR64">
         <v>1.56</v>
       </c>
-      <c r="AR64">
-        <v>1.23</v>
-      </c>
       <c r="AS64">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AT64">
-        <v>2.83</v>
+        <v>3.06</v>
       </c>
       <c r="AU64">
         <v>3</v>
@@ -14341,25 +14341,25 @@
         <v>1.45</v>
       </c>
       <c r="AN65">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AO65">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="AQ65">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AR65">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AS65">
-        <v>1.56</v>
+        <v>1.21</v>
       </c>
       <c r="AT65">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="AU65">
         <v>5</v>
@@ -14547,25 +14547,25 @@
         <v>1.6</v>
       </c>
       <c r="AN66">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="AO66">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AP66">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="AQ66">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AR66">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="AS66">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AT66">
-        <v>3.07</v>
+        <v>3.22</v>
       </c>
       <c r="AU66">
         <v>3</v>
@@ -14753,25 +14753,25 @@
         <v>4</v>
       </c>
       <c r="AN67">
-        <v>1.89</v>
+        <v>3</v>
       </c>
       <c r="AO67">
-        <v>0.45</v>
+        <v>0.33</v>
       </c>
       <c r="AP67">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AQ67">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AR67">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AS67">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="AT67">
-        <v>2.96</v>
+        <v>3.32</v>
       </c>
       <c r="AU67">
         <v>5</v>
@@ -14959,25 +14959,25 @@
         <v>1.85</v>
       </c>
       <c r="AN68">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AO68">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="AQ68">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AR68">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AS68">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AT68">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="AU68">
         <v>5</v>
@@ -15165,25 +15165,25 @@
         <v>1.47</v>
       </c>
       <c r="AN69">
-        <v>0.82</v>
+        <v>0.6</v>
       </c>
       <c r="AO69">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="AP69">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ69">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="AR69">
-        <v>0.98</v>
+        <v>0.89</v>
       </c>
       <c r="AS69">
-        <v>1.14</v>
+        <v>0.93</v>
       </c>
       <c r="AT69">
-        <v>2.12</v>
+        <v>1.82</v>
       </c>
       <c r="AU69">
         <v>5</v>
@@ -15371,25 +15371,25 @@
         <v>1.4</v>
       </c>
       <c r="AN70">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AO70">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AP70">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AQ70">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AR70">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AS70">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AT70">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="AU70">
         <v>4</v>
@@ -15577,25 +15577,25 @@
         <v>2.1</v>
       </c>
       <c r="AN71">
-        <v>1.64</v>
+        <v>2.6</v>
       </c>
       <c r="AO71">
-        <v>1.27</v>
+        <v>0.83</v>
       </c>
       <c r="AP71">
-        <v>2.06</v>
+        <v>2.78</v>
       </c>
       <c r="AQ71">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR71">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AS71">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AT71">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="AU71">
         <v>9</v>
@@ -15783,25 +15783,25 @@
         <v>1.51</v>
       </c>
       <c r="AN72">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AO72">
-        <v>1.75</v>
+        <v>0.83</v>
       </c>
       <c r="AP72">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ72">
-        <v>2.06</v>
+        <v>1.33</v>
       </c>
       <c r="AR72">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AS72">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="AT72">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="AU72">
         <v>7</v>
@@ -15989,25 +15989,25 @@
         <v>1.69</v>
       </c>
       <c r="AN73">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AO73">
         <v>1</v>
       </c>
       <c r="AP73">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="AQ73">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AR73">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AS73">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT73">
-        <v>2.24</v>
+        <v>2.49</v>
       </c>
       <c r="AU73">
         <v>5</v>
@@ -16195,25 +16195,25 @@
         <v>1.31</v>
       </c>
       <c r="AN74">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AO74">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AQ74">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AR74">
+        <v>1.16</v>
+      </c>
+      <c r="AS74">
         <v>1.18</v>
       </c>
-      <c r="AS74">
-        <v>1.49</v>
-      </c>
       <c r="AT74">
-        <v>2.67</v>
+        <v>2.34</v>
       </c>
       <c r="AU74">
         <v>5</v>
@@ -16401,25 +16401,25 @@
         <v>1.15</v>
       </c>
       <c r="AN75">
-        <v>1.17</v>
+        <v>1.8</v>
       </c>
       <c r="AO75">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AP75">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AQ75">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="AR75">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AS75">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AT75">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="AU75">
         <v>5</v>
@@ -16607,25 +16607,25 @@
         <v>1.3</v>
       </c>
       <c r="AN76">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="AO76">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AP76">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="AQ76">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="AR76">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AS76">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AT76">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AU76">
         <v>3</v>
@@ -16813,25 +16813,25 @@
         <v>2.9</v>
       </c>
       <c r="AN77">
-        <v>1.92</v>
+        <v>2.67</v>
       </c>
       <c r="AO77">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>1.56</v>
+        <v>2.11</v>
       </c>
       <c r="AQ77">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AR77">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AS77">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AT77">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="AU77">
         <v>7</v>
@@ -17019,25 +17019,25 @@
         <v>1.12</v>
       </c>
       <c r="AN78">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AO78">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="AP78">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ78">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AR78">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="AS78">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AT78">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="AU78">
         <v>2</v>
@@ -17225,25 +17225,25 @@
         <v>2.2</v>
       </c>
       <c r="AN79">
-        <v>1.64</v>
+        <v>2.5</v>
       </c>
       <c r="AO79">
-        <v>1.31</v>
+        <v>1.67</v>
       </c>
       <c r="AP79">
+        <v>2</v>
+      </c>
+      <c r="AQ79">
         <v>1.56</v>
       </c>
-      <c r="AQ79">
-        <v>1.22</v>
-      </c>
       <c r="AR79">
-        <v>1.66</v>
+        <v>2.16</v>
       </c>
       <c r="AS79">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AT79">
-        <v>3.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU79">
         <v>4</v>
@@ -17431,25 +17431,25 @@
         <v>2.8</v>
       </c>
       <c r="AN80">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AO80">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AP80">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="AQ80">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AR80">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="AS80">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AT80">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="AU80">
         <v>-1</v>
@@ -17637,25 +17637,25 @@
         <v>0</v>
       </c>
       <c r="AN81">
+        <v>2</v>
+      </c>
+      <c r="AO81">
+        <v>0.43</v>
+      </c>
+      <c r="AP81">
+        <v>1.67</v>
+      </c>
+      <c r="AQ81">
+        <v>1</v>
+      </c>
+      <c r="AR81">
         <v>1.31</v>
       </c>
-      <c r="AO81">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AP81">
-        <v>1.33</v>
-      </c>
-      <c r="AQ81">
-        <v>0.89</v>
-      </c>
-      <c r="AR81">
-        <v>1.25</v>
-      </c>
       <c r="AS81">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AT81">
-        <v>2.51</v>
+        <v>2.39</v>
       </c>
       <c r="AU81">
         <v>2</v>
@@ -17843,25 +17843,25 @@
         <v>0</v>
       </c>
       <c r="AN82">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AO82">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ82">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="AR82">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AS82">
-        <v>1.13</v>
+        <v>0.97</v>
       </c>
       <c r="AT82">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="AU82">
         <v>6</v>
@@ -18049,25 +18049,25 @@
         <v>1.85</v>
       </c>
       <c r="AN83">
-        <v>1.85</v>
+        <v>2.67</v>
       </c>
       <c r="AO83">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP83">
-        <v>2.06</v>
+        <v>2.78</v>
       </c>
       <c r="AQ83">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AR83">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AS83">
         <v>1.2</v>
       </c>
       <c r="AT83">
-        <v>2.69</v>
+        <v>2.96</v>
       </c>
       <c r="AU83">
         <v>6</v>
@@ -18255,25 +18255,25 @@
         <v>1.16</v>
       </c>
       <c r="AN84">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="AO84">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="AP84">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="AQ84">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AR84">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AS84">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="AT84">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AU84">
         <v>3</v>
@@ -18461,25 +18461,25 @@
         <v>1.47</v>
       </c>
       <c r="AN85">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AO85">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="AQ85">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AR85">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AS85">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AT85">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="AU85">
         <v>7</v>
@@ -18667,25 +18667,25 @@
         <v>1.2</v>
       </c>
       <c r="AN86">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="AO86">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AP86">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AQ86">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="AR86">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AS86">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="AT86">
-        <v>2.85</v>
+        <v>2.57</v>
       </c>
       <c r="AU86">
         <v>2</v>
@@ -18873,25 +18873,25 @@
         <v>1.72</v>
       </c>
       <c r="AN87">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AO87">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="AP87">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AQ87">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AR87">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AS87">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
       <c r="AT87">
-        <v>2.18</v>
+        <v>2.37</v>
       </c>
       <c r="AU87">
         <v>8</v>
@@ -19079,25 +19079,25 @@
         <v>2.65</v>
       </c>
       <c r="AN88">
-        <v>1.93</v>
+        <v>2.71</v>
       </c>
       <c r="AO88">
-        <v>1.21</v>
+        <v>0.71</v>
       </c>
       <c r="AP88">
-        <v>1.56</v>
+        <v>2.11</v>
       </c>
       <c r="AQ88">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR88">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AS88">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AT88">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="AU88">
         <v>6</v>
@@ -19285,25 +19285,25 @@
         <v>1.75</v>
       </c>
       <c r="AN89">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="AO89">
-        <v>1.93</v>
+        <v>1.14</v>
       </c>
       <c r="AP89">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="AQ89">
-        <v>2.06</v>
+        <v>1.33</v>
       </c>
       <c r="AR89">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AS89">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="AT89">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="AU89">
         <v>3</v>
@@ -19491,25 +19491,25 @@
         <v>3.2</v>
       </c>
       <c r="AN90">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AO90">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="AP90">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AQ90">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AR90">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="AS90">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AT90">
-        <v>2.84</v>
+        <v>3.23</v>
       </c>
       <c r="AU90">
         <v>11</v>
@@ -19697,25 +19697,25 @@
         <v>1.47</v>
       </c>
       <c r="AN91">
+        <v>1.38</v>
+      </c>
+      <c r="AO91">
+        <v>1.86</v>
+      </c>
+      <c r="AP91">
+        <v>1.7</v>
+      </c>
+      <c r="AQ91">
+        <v>1.56</v>
+      </c>
+      <c r="AR91">
         <v>1.53</v>
       </c>
-      <c r="AO91">
-        <v>1.33</v>
-      </c>
-      <c r="AP91">
-        <v>1.78</v>
-      </c>
-      <c r="AQ91">
-        <v>1.22</v>
-      </c>
-      <c r="AR91">
-        <v>1.51</v>
-      </c>
       <c r="AS91">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AT91">
-        <v>2.79</v>
+        <v>2.68</v>
       </c>
       <c r="AU91">
         <v>3</v>
@@ -19903,25 +19903,25 @@
         <v>1.9</v>
       </c>
       <c r="AN92">
-        <v>1.57</v>
+        <v>2.17</v>
       </c>
       <c r="AO92">
-        <v>1.8</v>
+        <v>1.14</v>
       </c>
       <c r="AP92">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AQ92">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AR92">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AS92">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AT92">
-        <v>3.24</v>
+        <v>3.39</v>
       </c>
       <c r="AU92">
         <v>9</v>
@@ -20109,25 +20109,25 @@
         <v>1.11</v>
       </c>
       <c r="AN93">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AO93">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AP93">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ93">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AR93">
-        <v>1.02</v>
+        <v>0.89</v>
       </c>
       <c r="AS93">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="AT93">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="AU93">
         <v>2</v>
@@ -20315,25 +20315,25 @@
         <v>1.8</v>
       </c>
       <c r="AN94">
+        <v>1.71</v>
+      </c>
+      <c r="AO94">
+        <v>1</v>
+      </c>
+      <c r="AP94">
+        <v>1.67</v>
+      </c>
+      <c r="AQ94">
+        <v>0.8</v>
+      </c>
+      <c r="AR94">
         <v>1.33</v>
       </c>
-      <c r="AO94">
-        <v>1.07</v>
-      </c>
-      <c r="AP94">
-        <v>1.33</v>
-      </c>
-      <c r="AQ94">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AR94">
-        <v>1.24</v>
-      </c>
       <c r="AS94">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AT94">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="AU94">
         <v>5</v>
@@ -20521,25 +20521,25 @@
         <v>1.36</v>
       </c>
       <c r="AN95">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AO95">
-        <v>1.13</v>
+        <v>0.71</v>
       </c>
       <c r="AP95">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="AQ95">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AR95">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AS95">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AT95">
-        <v>2.37</v>
+        <v>2.53</v>
       </c>
       <c r="AU95">
         <v>2</v>
@@ -20727,25 +20727,25 @@
         <v>2.1</v>
       </c>
       <c r="AN96">
-        <v>2</v>
+        <v>2.71</v>
       </c>
       <c r="AO96">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AP96">
-        <v>2.06</v>
+        <v>2.78</v>
       </c>
       <c r="AQ96">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="AR96">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="AS96">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="AT96">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="AU96">
         <v>4</v>
@@ -20933,25 +20933,25 @@
         <v>4.5</v>
       </c>
       <c r="AN97">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AO97">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP97">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AQ97">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AR97">
-        <v>1.76</v>
+        <v>2.11</v>
       </c>
       <c r="AS97">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AT97">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="AU97">
         <v>6</v>
@@ -21139,25 +21139,25 @@
         <v>1.9</v>
       </c>
       <c r="AN98">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AO98">
-        <v>2.06</v>
+        <v>1.38</v>
       </c>
       <c r="AP98">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="AQ98">
-        <v>2.06</v>
+        <v>1.33</v>
       </c>
       <c r="AR98">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="AS98">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="AT98">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="AU98">
         <v>6</v>
@@ -21345,25 +21345,25 @@
         <v>1.57</v>
       </c>
       <c r="AN99">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="AO99">
         <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="AQ99">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AR99">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AS99">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AT99">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AU99">
         <v>6</v>
@@ -21551,25 +21551,25 @@
         <v>2</v>
       </c>
       <c r="AN100">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AO100">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AP100">
-        <v>1.56</v>
+        <v>2.11</v>
       </c>
       <c r="AQ100">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AR100">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AS100">
         <v>1.48</v>
       </c>
       <c r="AT100">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="AU100">
         <v>3</v>
@@ -21757,25 +21757,25 @@
         <v>1.1</v>
       </c>
       <c r="AN101">
-        <v>0.9399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="AO101">
-        <v>1.63</v>
+        <v>1.13</v>
       </c>
       <c r="AP101">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AQ101">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="AR101">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="AS101">
-        <v>1.79</v>
+        <v>1.46</v>
       </c>
       <c r="AT101">
-        <v>2.96</v>
+        <v>2.83</v>
       </c>
       <c r="AU101">
         <v>3</v>
@@ -21963,25 +21963,25 @@
         <v>1.35</v>
       </c>
       <c r="AN102">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AO102">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AP102">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ102">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AR102">
-        <v>1.02</v>
+        <v>0.9</v>
       </c>
       <c r="AS102">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AT102">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="AU102">
         <v>6</v>
@@ -22169,25 +22169,25 @@
         <v>1.77</v>
       </c>
       <c r="AN103">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="AO103">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="AP103">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="AQ103">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR103">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AS103">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AT103">
-        <v>2.49</v>
+        <v>2.57</v>
       </c>
       <c r="AU103">
         <v>5</v>
@@ -22375,25 +22375,25 @@
         <v>3.8</v>
       </c>
       <c r="AN104">
-        <v>1.59</v>
+        <v>2.13</v>
       </c>
       <c r="AO104">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AP104">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AQ104">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AR104">
-        <v>1.79</v>
+        <v>2.12</v>
       </c>
       <c r="AS104">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AT104">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="AU104">
         <v>5</v>
@@ -22581,25 +22581,25 @@
         <v>1.39</v>
       </c>
       <c r="AN105">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AO105">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="AP105">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ105">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AR105">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AS105">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AT105">
-        <v>3.01</v>
+        <v>2.87</v>
       </c>
       <c r="AU105">
         <v>6</v>
@@ -22787,25 +22787,25 @@
         <v>1.73</v>
       </c>
       <c r="AN106">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="AO106">
-        <v>0.59</v>
+        <v>0.5</v>
       </c>
       <c r="AP106">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AQ106">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="AR106">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AS106">
-        <v>1.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT106">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="AU106">
         <v>3</v>
@@ -22993,25 +22993,25 @@
         <v>1.36</v>
       </c>
       <c r="AN107">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="AO107">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="AP107">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="AQ107">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="AR107">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AS107">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="AT107">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="AU107">
         <v>4</v>
@@ -23199,25 +23199,25 @@
         <v>2.05</v>
       </c>
       <c r="AN108">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AO108">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AP108">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AQ108">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AR108">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AS108">
-        <v>1.16</v>
+        <v>0.97</v>
       </c>
       <c r="AT108">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AU108">
         <v>5</v>
@@ -23405,25 +23405,25 @@
         <v>1.55</v>
       </c>
       <c r="AN109">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AO109">
-        <v>1.65</v>
+        <v>1.13</v>
       </c>
       <c r="AP109">
-        <v>2.06</v>
+        <v>2.78</v>
       </c>
       <c r="AQ109">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AR109">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AS109">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AT109">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="AU109">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="225">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -508,6 +508,12 @@
     <t>['41', '47']</t>
   </si>
   <si>
+    <t>['12', '60', '78', '90+4']</t>
+  </si>
+  <si>
+    <t>['24', '84', '90+1']</t>
+  </si>
+  <si>
     <t>['4', '6', '45+2']</t>
   </si>
   <si>
@@ -674,6 +680,15 @@
   </si>
   <si>
     <t>['49', '67', '72']</t>
+  </si>
+  <si>
+    <t>['7']</t>
+  </si>
+  <si>
+    <t>['62', '73']</t>
+  </si>
+  <si>
+    <t>['9', '65', '90+9']</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP109"/>
+  <dimension ref="A1:BP112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1291,7 +1306,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q2">
         <v>7</v>
@@ -1372,7 +1387,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ2">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1497,7 +1512,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1703,7 +1718,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2527,7 +2542,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q8">
         <v>2.1</v>
@@ -2811,10 +2826,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ9">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2939,7 +2954,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q10">
         <v>1.67</v>
@@ -3223,10 +3238,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ11">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3635,7 +3650,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ13">
         <v>1</v>
@@ -3763,7 +3778,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3841,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ14">
         <v>1.89</v>
@@ -3969,7 +3984,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4175,7 +4190,7 @@
         <v>89</v>
       </c>
       <c r="P16" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q16">
         <v>3.8</v>
@@ -4256,7 +4271,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ16">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR16">
         <v>1.73</v>
@@ -4668,7 +4683,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ18">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR18">
         <v>1.26</v>
@@ -4999,7 +5014,7 @@
         <v>89</v>
       </c>
       <c r="P20" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5077,7 +5092,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ20">
         <v>0.8</v>
@@ -5205,7 +5220,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q21">
         <v>2.03</v>
@@ -5411,7 +5426,7 @@
         <v>99</v>
       </c>
       <c r="P22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q22">
         <v>2.4</v>
@@ -5492,7 +5507,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5617,7 +5632,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5695,7 +5710,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ23">
         <v>1.56</v>
@@ -6110,7 +6125,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR25">
         <v>1.32</v>
@@ -6235,7 +6250,7 @@
         <v>103</v>
       </c>
       <c r="P26" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6313,7 +6328,7 @@
         <v>0.5</v>
       </c>
       <c r="AP26">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ26">
         <v>1</v>
@@ -6441,7 +6456,7 @@
         <v>104</v>
       </c>
       <c r="P27" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6647,7 +6662,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -6728,7 +6743,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ28">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR28">
         <v>1.88</v>
@@ -7059,7 +7074,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7140,7 +7155,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ30">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR30">
         <v>1.52</v>
@@ -7677,7 +7692,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -7883,7 +7898,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q34">
         <v>2.1</v>
@@ -7964,7 +7979,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR34">
         <v>1.35</v>
@@ -8089,7 +8104,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8167,7 +8182,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -8295,7 +8310,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8579,10 +8594,10 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ37">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR37">
         <v>1</v>
@@ -8707,7 +8722,7 @@
         <v>89</v>
       </c>
       <c r="P38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q38">
         <v>2.2</v>
@@ -8788,7 +8803,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ38">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR38">
         <v>1.97</v>
@@ -8913,7 +8928,7 @@
         <v>113</v>
       </c>
       <c r="P39" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9119,7 +9134,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q40">
         <v>3.6</v>
@@ -9197,7 +9212,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ40">
         <v>1.89</v>
@@ -9531,7 +9546,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9737,7 +9752,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10355,7 +10370,7 @@
         <v>120</v>
       </c>
       <c r="P46" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10561,7 +10576,7 @@
         <v>89</v>
       </c>
       <c r="P47" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10767,7 +10782,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11051,10 +11066,10 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ49">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR49">
         <v>1.83</v>
@@ -11257,7 +11272,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -11591,7 +11606,7 @@
         <v>89</v>
       </c>
       <c r="P52" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -11878,7 +11893,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ53">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR53">
         <v>1.83</v>
@@ -12003,7 +12018,7 @@
         <v>89</v>
       </c>
       <c r="P54" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12084,7 +12099,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ54">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR54">
         <v>1.29</v>
@@ -12415,7 +12430,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q56">
         <v>1.95</v>
@@ -12496,7 +12511,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ56">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR56">
         <v>1.69</v>
@@ -12621,7 +12636,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12699,7 +12714,7 @@
         <v>0.4</v>
       </c>
       <c r="AP57">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ57">
         <v>1.33</v>
@@ -12827,7 +12842,7 @@
         <v>109</v>
       </c>
       <c r="P58" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q58">
         <v>4</v>
@@ -12905,7 +12920,7 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ58">
         <v>1.56</v>
@@ -13033,7 +13048,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q59">
         <v>2.1</v>
@@ -13317,7 +13332,7 @@
         <v>1.2</v>
       </c>
       <c r="AP60">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ60">
         <v>1.11</v>
@@ -13651,7 +13666,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -13938,7 +13953,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ63">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR63">
         <v>1.65</v>
@@ -14269,7 +14284,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q65">
         <v>3.25</v>
@@ -14475,7 +14490,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q66">
         <v>2.88</v>
@@ -14762,7 +14777,7 @@
         <v>2</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR67">
         <v>2.3</v>
@@ -14887,7 +14902,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q68">
         <v>2.5</v>
@@ -15171,7 +15186,7 @@
         <v>0.8</v>
       </c>
       <c r="AP69">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ69">
         <v>0.78</v>
@@ -15377,10 +15392,10 @@
         <v>1.8</v>
       </c>
       <c r="AP70">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ70">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR70">
         <v>1.35</v>
@@ -15583,7 +15598,7 @@
         <v>0.83</v>
       </c>
       <c r="AP71">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ71">
         <v>1</v>
@@ -15711,7 +15726,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16123,7 +16138,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q74">
         <v>3.75</v>
@@ -16410,7 +16425,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ75">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR75">
         <v>1.32</v>
@@ -16535,7 +16550,7 @@
         <v>142</v>
       </c>
       <c r="P76" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17025,7 +17040,7 @@
         <v>1.17</v>
       </c>
       <c r="AP78">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ78">
         <v>1</v>
@@ -17153,7 +17168,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q79">
         <v>2.2</v>
@@ -17565,7 +17580,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -17646,7 +17661,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ81">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR81">
         <v>1.31</v>
@@ -18055,7 +18070,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ83">
         <v>1</v>
@@ -18183,7 +18198,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q84">
         <v>5.5</v>
@@ -18389,7 +18404,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q85">
         <v>3.4</v>
@@ -18470,7 +18485,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ85">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR85">
         <v>1.46</v>
@@ -18595,7 +18610,7 @@
         <v>120</v>
       </c>
       <c r="P86" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18676,7 +18691,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ86">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR86">
         <v>1.2</v>
@@ -18801,7 +18816,7 @@
         <v>89</v>
       </c>
       <c r="P87" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q87">
         <v>2.75</v>
@@ -18879,7 +18894,7 @@
         <v>0.86</v>
       </c>
       <c r="AP87">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ87">
         <v>1.11</v>
@@ -19213,7 +19228,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19625,7 +19640,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -19831,7 +19846,7 @@
         <v>153</v>
       </c>
       <c r="P92" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20037,7 +20052,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q93">
         <v>6</v>
@@ -20115,7 +20130,7 @@
         <v>2</v>
       </c>
       <c r="AP93">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ93">
         <v>1.89</v>
@@ -20243,7 +20258,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q94">
         <v>2.6</v>
@@ -20449,7 +20464,7 @@
         <v>89</v>
       </c>
       <c r="P95" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20733,7 +20748,7 @@
         <v>0.57</v>
       </c>
       <c r="AP96">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ96">
         <v>0.78</v>
@@ -21067,7 +21082,7 @@
         <v>157</v>
       </c>
       <c r="P98" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q98">
         <v>2.5</v>
@@ -21273,7 +21288,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21354,7 +21369,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ99">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR99">
         <v>1.21</v>
@@ -21479,7 +21494,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q100">
         <v>2.3</v>
@@ -21560,7 +21575,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ100">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR100">
         <v>1.69</v>
@@ -21763,10 +21778,10 @@
         <v>1.13</v>
       </c>
       <c r="AP101">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ101">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR101">
         <v>1.37</v>
@@ -21969,7 +21984,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ102">
         <v>1</v>
@@ -22303,7 +22318,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q104">
         <v>1.67</v>
@@ -22715,7 +22730,7 @@
         <v>102</v>
       </c>
       <c r="P106" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23411,7 +23426,7 @@
         <v>1.13</v>
       </c>
       <c r="AP109">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ109">
         <v>1</v>
@@ -23489,6 +23504,624 @@
         <v>3.1</v>
       </c>
       <c r="BP109">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7482778</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45710.54166666666</v>
+      </c>
+      <c r="F110">
+        <v>19</v>
+      </c>
+      <c r="G110" t="s">
+        <v>79</v>
+      </c>
+      <c r="H110" t="s">
+        <v>78</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>1</v>
+      </c>
+      <c r="K110">
+        <v>1</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>1</v>
+      </c>
+      <c r="N110">
+        <v>1</v>
+      </c>
+      <c r="O110" t="s">
+        <v>89</v>
+      </c>
+      <c r="P110" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q110">
+        <v>3.4</v>
+      </c>
+      <c r="R110">
+        <v>2.2</v>
+      </c>
+      <c r="S110">
+        <v>3.1</v>
+      </c>
+      <c r="T110">
+        <v>1.36</v>
+      </c>
+      <c r="U110">
+        <v>3</v>
+      </c>
+      <c r="V110">
+        <v>2.75</v>
+      </c>
+      <c r="W110">
+        <v>1.4</v>
+      </c>
+      <c r="X110">
+        <v>7</v>
+      </c>
+      <c r="Y110">
+        <v>1.1</v>
+      </c>
+      <c r="Z110">
+        <v>2.79</v>
+      </c>
+      <c r="AA110">
+        <v>3.39</v>
+      </c>
+      <c r="AB110">
+        <v>2.4</v>
+      </c>
+      <c r="AC110">
+        <v>1.05</v>
+      </c>
+      <c r="AD110">
+        <v>9.5</v>
+      </c>
+      <c r="AE110">
+        <v>1.25</v>
+      </c>
+      <c r="AF110">
+        <v>3.9</v>
+      </c>
+      <c r="AG110">
+        <v>1.53</v>
+      </c>
+      <c r="AH110">
+        <v>2.25</v>
+      </c>
+      <c r="AI110">
+        <v>1.62</v>
+      </c>
+      <c r="AJ110">
+        <v>2.2</v>
+      </c>
+      <c r="AK110">
+        <v>1.52</v>
+      </c>
+      <c r="AL110">
+        <v>1.3</v>
+      </c>
+      <c r="AM110">
+        <v>1.42</v>
+      </c>
+      <c r="AN110">
+        <v>2.78</v>
+      </c>
+      <c r="AO110">
+        <v>1.11</v>
+      </c>
+      <c r="AP110">
+        <v>2.5</v>
+      </c>
+      <c r="AQ110">
+        <v>1.3</v>
+      </c>
+      <c r="AR110">
+        <v>1.61</v>
+      </c>
+      <c r="AS110">
+        <v>1.49</v>
+      </c>
+      <c r="AT110">
+        <v>3.1</v>
+      </c>
+      <c r="AU110">
+        <v>3</v>
+      </c>
+      <c r="AV110">
+        <v>5</v>
+      </c>
+      <c r="AW110">
+        <v>8</v>
+      </c>
+      <c r="AX110">
+        <v>12</v>
+      </c>
+      <c r="AY110">
+        <v>11</v>
+      </c>
+      <c r="AZ110">
+        <v>19</v>
+      </c>
+      <c r="BA110">
+        <v>6</v>
+      </c>
+      <c r="BB110">
+        <v>5</v>
+      </c>
+      <c r="BC110">
+        <v>11</v>
+      </c>
+      <c r="BD110">
+        <v>2.07</v>
+      </c>
+      <c r="BE110">
+        <v>6.4</v>
+      </c>
+      <c r="BF110">
+        <v>1.93</v>
+      </c>
+      <c r="BG110">
+        <v>1.34</v>
+      </c>
+      <c r="BH110">
+        <v>2.9</v>
+      </c>
+      <c r="BI110">
+        <v>1.58</v>
+      </c>
+      <c r="BJ110">
+        <v>2.2</v>
+      </c>
+      <c r="BK110">
+        <v>2</v>
+      </c>
+      <c r="BL110">
+        <v>1.8</v>
+      </c>
+      <c r="BM110">
+        <v>2.43</v>
+      </c>
+      <c r="BN110">
+        <v>1.47</v>
+      </c>
+      <c r="BO110">
+        <v>3.15</v>
+      </c>
+      <c r="BP110">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7482780</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45710.54166666666</v>
+      </c>
+      <c r="F111">
+        <v>19</v>
+      </c>
+      <c r="G111" t="s">
+        <v>81</v>
+      </c>
+      <c r="H111" t="s">
+        <v>70</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>1</v>
+      </c>
+      <c r="L111">
+        <v>4</v>
+      </c>
+      <c r="M111">
+        <v>2</v>
+      </c>
+      <c r="N111">
+        <v>6</v>
+      </c>
+      <c r="O111" t="s">
+        <v>164</v>
+      </c>
+      <c r="P111" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q111">
+        <v>3.1</v>
+      </c>
+      <c r="R111">
+        <v>2.2</v>
+      </c>
+      <c r="S111">
+        <v>3.4</v>
+      </c>
+      <c r="T111">
+        <v>1.4</v>
+      </c>
+      <c r="U111">
+        <v>2.75</v>
+      </c>
+      <c r="V111">
+        <v>2.75</v>
+      </c>
+      <c r="W111">
+        <v>1.4</v>
+      </c>
+      <c r="X111">
+        <v>8</v>
+      </c>
+      <c r="Y111">
+        <v>1.08</v>
+      </c>
+      <c r="Z111">
+        <v>2.68</v>
+      </c>
+      <c r="AA111">
+        <v>3.29</v>
+      </c>
+      <c r="AB111">
+        <v>2.55</v>
+      </c>
+      <c r="AC111">
+        <v>1.05</v>
+      </c>
+      <c r="AD111">
+        <v>9</v>
+      </c>
+      <c r="AE111">
+        <v>1.3</v>
+      </c>
+      <c r="AF111">
+        <v>3.45</v>
+      </c>
+      <c r="AG111">
+        <v>1.87</v>
+      </c>
+      <c r="AH111">
+        <v>1.87</v>
+      </c>
+      <c r="AI111">
+        <v>1.7</v>
+      </c>
+      <c r="AJ111">
+        <v>2.05</v>
+      </c>
+      <c r="AK111">
+        <v>1.42</v>
+      </c>
+      <c r="AL111">
+        <v>1.29</v>
+      </c>
+      <c r="AM111">
+        <v>1.55</v>
+      </c>
+      <c r="AN111">
+        <v>1.13</v>
+      </c>
+      <c r="AO111">
+        <v>1</v>
+      </c>
+      <c r="AP111">
+        <v>1.33</v>
+      </c>
+      <c r="AQ111">
+        <v>0.9</v>
+      </c>
+      <c r="AR111">
+        <v>1.32</v>
+      </c>
+      <c r="AS111">
+        <v>1.1</v>
+      </c>
+      <c r="AT111">
+        <v>2.42</v>
+      </c>
+      <c r="AU111">
+        <v>10</v>
+      </c>
+      <c r="AV111">
+        <v>5</v>
+      </c>
+      <c r="AW111">
+        <v>5</v>
+      </c>
+      <c r="AX111">
+        <v>8</v>
+      </c>
+      <c r="AY111">
+        <v>15</v>
+      </c>
+      <c r="AZ111">
+        <v>15</v>
+      </c>
+      <c r="BA111">
+        <v>5</v>
+      </c>
+      <c r="BB111">
+        <v>7</v>
+      </c>
+      <c r="BC111">
+        <v>12</v>
+      </c>
+      <c r="BD111">
+        <v>1.98</v>
+      </c>
+      <c r="BE111">
+        <v>6.5</v>
+      </c>
+      <c r="BF111">
+        <v>2</v>
+      </c>
+      <c r="BG111">
+        <v>1.3</v>
+      </c>
+      <c r="BH111">
+        <v>3.15</v>
+      </c>
+      <c r="BI111">
+        <v>1.52</v>
+      </c>
+      <c r="BJ111">
+        <v>2.33</v>
+      </c>
+      <c r="BK111">
+        <v>1.95</v>
+      </c>
+      <c r="BL111">
+        <v>1.85</v>
+      </c>
+      <c r="BM111">
+        <v>2.33</v>
+      </c>
+      <c r="BN111">
+        <v>1.52</v>
+      </c>
+      <c r="BO111">
+        <v>2.95</v>
+      </c>
+      <c r="BP111">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7482782</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45710.54166666666</v>
+      </c>
+      <c r="F112">
+        <v>19</v>
+      </c>
+      <c r="G112" t="s">
+        <v>77</v>
+      </c>
+      <c r="H112" t="s">
+        <v>73</v>
+      </c>
+      <c r="I112">
+        <v>1</v>
+      </c>
+      <c r="J112">
+        <v>1</v>
+      </c>
+      <c r="K112">
+        <v>2</v>
+      </c>
+      <c r="L112">
+        <v>3</v>
+      </c>
+      <c r="M112">
+        <v>3</v>
+      </c>
+      <c r="N112">
+        <v>6</v>
+      </c>
+      <c r="O112" t="s">
+        <v>165</v>
+      </c>
+      <c r="P112" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q112">
+        <v>4.53</v>
+      </c>
+      <c r="R112">
+        <v>2.28</v>
+      </c>
+      <c r="S112">
+        <v>2.52</v>
+      </c>
+      <c r="T112">
+        <v>1.38</v>
+      </c>
+      <c r="U112">
+        <v>3.05</v>
+      </c>
+      <c r="V112">
+        <v>2.88</v>
+      </c>
+      <c r="W112">
+        <v>1.41</v>
+      </c>
+      <c r="X112">
+        <v>7.1</v>
+      </c>
+      <c r="Y112">
+        <v>1.04</v>
+      </c>
+      <c r="Z112">
+        <v>4</v>
+      </c>
+      <c r="AA112">
+        <v>3.5</v>
+      </c>
+      <c r="AB112">
+        <v>1.87</v>
+      </c>
+      <c r="AC112">
+        <v>1.06</v>
+      </c>
+      <c r="AD112">
+        <v>8.5</v>
+      </c>
+      <c r="AE112">
+        <v>1.3</v>
+      </c>
+      <c r="AF112">
+        <v>3.4</v>
+      </c>
+      <c r="AG112">
+        <v>1.91</v>
+      </c>
+      <c r="AH112">
+        <v>1.83</v>
+      </c>
+      <c r="AI112">
+        <v>1.75</v>
+      </c>
+      <c r="AJ112">
+        <v>1.93</v>
+      </c>
+      <c r="AK112">
+        <v>1.83</v>
+      </c>
+      <c r="AL112">
+        <v>1.25</v>
+      </c>
+      <c r="AM112">
+        <v>1.25</v>
+      </c>
+      <c r="AN112">
+        <v>0.89</v>
+      </c>
+      <c r="AO112">
+        <v>1.88</v>
+      </c>
+      <c r="AP112">
+        <v>0.9</v>
+      </c>
+      <c r="AQ112">
+        <v>1.78</v>
+      </c>
+      <c r="AR112">
+        <v>1.03</v>
+      </c>
+      <c r="AS112">
+        <v>1.45</v>
+      </c>
+      <c r="AT112">
+        <v>2.48</v>
+      </c>
+      <c r="AU112">
+        <v>5</v>
+      </c>
+      <c r="AV112">
+        <v>8</v>
+      </c>
+      <c r="AW112">
+        <v>4</v>
+      </c>
+      <c r="AX112">
+        <v>8</v>
+      </c>
+      <c r="AY112">
+        <v>11</v>
+      </c>
+      <c r="AZ112">
+        <v>17</v>
+      </c>
+      <c r="BA112">
+        <v>3</v>
+      </c>
+      <c r="BB112">
+        <v>4</v>
+      </c>
+      <c r="BC112">
+        <v>7</v>
+      </c>
+      <c r="BD112">
+        <v>2.55</v>
+      </c>
+      <c r="BE112">
+        <v>6.4</v>
+      </c>
+      <c r="BF112">
+        <v>1.64</v>
+      </c>
+      <c r="BG112">
+        <v>1.33</v>
+      </c>
+      <c r="BH112">
+        <v>2.95</v>
+      </c>
+      <c r="BI112">
+        <v>1.55</v>
+      </c>
+      <c r="BJ112">
+        <v>2.25</v>
+      </c>
+      <c r="BK112">
+        <v>1.85</v>
+      </c>
+      <c r="BL112">
+        <v>1.95</v>
+      </c>
+      <c r="BM112">
+        <v>2.4</v>
+      </c>
+      <c r="BN112">
+        <v>1.49</v>
+      </c>
+      <c r="BO112">
+        <v>3.05</v>
+      </c>
+      <c r="BP112">
         <v>1.3</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="227">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -508,10 +508,16 @@
     <t>['41', '47']</t>
   </si>
   <si>
-    <t>['12', '60', '78', '90+4']</t>
+    <t>['12', '60', '78', '90+5']</t>
   </si>
   <si>
     <t>['24', '84', '90+1']</t>
+  </si>
+  <si>
+    <t>['18', '43']</t>
+  </si>
+  <si>
+    <t>['31', '78']</t>
   </si>
   <si>
     <t>['4', '6', '45+2']</t>
@@ -1050,7 +1056,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP112"/>
+  <dimension ref="A1:BP115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1306,7 +1312,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q2">
         <v>7</v>
@@ -1512,7 +1518,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1590,7 +1596,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AQ3">
         <v>1.11</v>
@@ -1718,7 +1724,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2542,7 +2548,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q8">
         <v>2.1</v>
@@ -2620,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ8">
         <v>0.78</v>
@@ -2954,7 +2960,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q10">
         <v>1.67</v>
@@ -3035,7 +3041,7 @@
         <v>2</v>
       </c>
       <c r="AQ10">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3444,7 +3450,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ12">
         <v>1</v>
@@ -3653,7 +3659,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3778,7 +3784,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3984,7 +3990,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4065,7 +4071,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR15">
         <v>1.07</v>
@@ -4190,7 +4196,7 @@
         <v>89</v>
       </c>
       <c r="P16" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q16">
         <v>3.8</v>
@@ -4268,7 +4274,7 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ16">
         <v>1.3</v>
@@ -4680,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AQ18">
         <v>1.78</v>
@@ -5014,7 +5020,7 @@
         <v>89</v>
       </c>
       <c r="P20" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5220,7 +5226,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q21">
         <v>2.03</v>
@@ -5298,7 +5304,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ21">
         <v>0.78</v>
@@ -5426,7 +5432,7 @@
         <v>99</v>
       </c>
       <c r="P22" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q22">
         <v>2.4</v>
@@ -5632,7 +5638,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5919,7 +5925,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ24">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR24">
         <v>0.92</v>
@@ -6250,7 +6256,7 @@
         <v>103</v>
       </c>
       <c r="P26" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6331,7 +6337,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR26">
         <v>0.84</v>
@@ -6456,7 +6462,7 @@
         <v>104</v>
       </c>
       <c r="P27" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6534,7 +6540,7 @@
         <v>1.5</v>
       </c>
       <c r="AP27">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ27">
         <v>1.11</v>
@@ -6662,7 +6668,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -6946,7 +6952,7 @@
         <v>0.5</v>
       </c>
       <c r="AP29">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AQ29">
         <v>1.33</v>
@@ -7074,7 +7080,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7152,7 +7158,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ30">
         <v>1.78</v>
@@ -7361,7 +7367,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ31">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR31">
         <v>1.82</v>
@@ -7692,7 +7698,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -7898,7 +7904,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q34">
         <v>2.1</v>
@@ -7976,7 +7982,7 @@
         <v>0.67</v>
       </c>
       <c r="AP34">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ34">
         <v>0.9</v>
@@ -8104,7 +8110,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8310,7 +8316,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8388,10 +8394,10 @@
         <v>0.33</v>
       </c>
       <c r="AP36">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AQ36">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR36">
         <v>1.26</v>
@@ -8722,7 +8728,7 @@
         <v>89</v>
       </c>
       <c r="P38" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q38">
         <v>2.2</v>
@@ -8800,7 +8806,7 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ38">
         <v>1.78</v>
@@ -8928,7 +8934,7 @@
         <v>113</v>
       </c>
       <c r="P39" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9134,7 +9140,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q40">
         <v>3.6</v>
@@ -9546,7 +9552,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9752,7 +9758,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10370,7 +10376,7 @@
         <v>120</v>
       </c>
       <c r="P46" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10576,7 +10582,7 @@
         <v>89</v>
       </c>
       <c r="P47" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10782,7 +10788,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11275,7 +11281,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ50">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR50">
         <v>0.98</v>
@@ -11478,7 +11484,7 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ51">
         <v>0.8</v>
@@ -11606,7 +11612,7 @@
         <v>89</v>
       </c>
       <c r="P52" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -11684,10 +11690,10 @@
         <v>0.67</v>
       </c>
       <c r="AP52">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AQ52">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR52">
         <v>1.2</v>
@@ -11890,7 +11896,7 @@
         <v>1.75</v>
       </c>
       <c r="AP53">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ53">
         <v>1.3</v>
@@ -12018,7 +12024,7 @@
         <v>89</v>
       </c>
       <c r="P54" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12430,7 +12436,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q56">
         <v>1.95</v>
@@ -12508,7 +12514,7 @@
         <v>0.4</v>
       </c>
       <c r="AP56">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ56">
         <v>0.9</v>
@@ -12636,7 +12642,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12842,7 +12848,7 @@
         <v>109</v>
       </c>
       <c r="P58" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q58">
         <v>4</v>
@@ -13048,7 +13054,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q59">
         <v>2.1</v>
@@ -13538,7 +13544,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AQ61">
         <v>0.8</v>
@@ -13666,7 +13672,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -13747,7 +13753,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR62">
         <v>1.17</v>
@@ -14159,7 +14165,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ64">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR64">
         <v>1.56</v>
@@ -14284,7 +14290,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q65">
         <v>3.25</v>
@@ -14362,7 +14368,7 @@
         <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ65">
         <v>1.89</v>
@@ -14490,7 +14496,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q66">
         <v>2.88</v>
@@ -14568,10 +14574,10 @@
         <v>1.2</v>
       </c>
       <c r="AP66">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ66">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR66">
         <v>1.79</v>
@@ -14902,7 +14908,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q68">
         <v>2.5</v>
@@ -14980,7 +14986,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ68">
         <v>1</v>
@@ -15601,7 +15607,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ71">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR71">
         <v>1.72</v>
@@ -15726,7 +15732,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16138,7 +16144,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q74">
         <v>3.75</v>
@@ -16550,7 +16556,7 @@
         <v>142</v>
       </c>
       <c r="P76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16628,7 +16634,7 @@
         <v>1.4</v>
       </c>
       <c r="AP76">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AQ76">
         <v>1.56</v>
@@ -17043,7 +17049,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ78">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR78">
         <v>0.96</v>
@@ -17168,7 +17174,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q79">
         <v>2.2</v>
@@ -17452,7 +17458,7 @@
         <v>1.17</v>
       </c>
       <c r="AP80">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ80">
         <v>0.8</v>
@@ -17580,7 +17586,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18198,7 +18204,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q84">
         <v>5.5</v>
@@ -18276,7 +18282,7 @@
         <v>2.17</v>
       </c>
       <c r="AP84">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AQ84">
         <v>1.89</v>
@@ -18404,7 +18410,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q85">
         <v>3.4</v>
@@ -18610,7 +18616,7 @@
         <v>120</v>
       </c>
       <c r="P86" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18816,7 +18822,7 @@
         <v>89</v>
       </c>
       <c r="P87" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q87">
         <v>2.75</v>
@@ -19103,7 +19109,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ88">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR88">
         <v>1.65</v>
@@ -19228,7 +19234,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19306,7 +19312,7 @@
         <v>1.14</v>
       </c>
       <c r="AP89">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ89">
         <v>1.33</v>
@@ -19640,7 +19646,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -19846,7 +19852,7 @@
         <v>153</v>
       </c>
       <c r="P92" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -19927,7 +19933,7 @@
         <v>2</v>
       </c>
       <c r="AQ92">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR92">
         <v>2.1</v>
@@ -20052,7 +20058,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q93">
         <v>6</v>
@@ -20258,7 +20264,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q94">
         <v>2.6</v>
@@ -20464,7 +20470,7 @@
         <v>89</v>
       </c>
       <c r="P95" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -21082,7 +21088,7 @@
         <v>157</v>
       </c>
       <c r="P98" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q98">
         <v>2.5</v>
@@ -21160,7 +21166,7 @@
         <v>1.38</v>
       </c>
       <c r="AP98">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ98">
         <v>1.33</v>
@@ -21288,7 +21294,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21366,7 +21372,7 @@
         <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AQ99">
         <v>0.9</v>
@@ -21494,7 +21500,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q100">
         <v>2.3</v>
@@ -22190,10 +22196,10 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ103">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR103">
         <v>1.4</v>
@@ -22318,7 +22324,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q104">
         <v>1.67</v>
@@ -22730,7 +22736,7 @@
         <v>102</v>
       </c>
       <c r="P106" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23429,7 +23435,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ109">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR109">
         <v>1.67</v>
@@ -23554,7 +23560,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23760,7 +23766,7 @@
         <v>164</v>
       </c>
       <c r="P111" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q111">
         <v>3.1</v>
@@ -23966,7 +23972,7 @@
         <v>165</v>
       </c>
       <c r="P112" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q112">
         <v>4.53</v>
@@ -24123,6 +24129,624 @@
       </c>
       <c r="BP112">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7482779</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45711.4375</v>
+      </c>
+      <c r="F113">
+        <v>19</v>
+      </c>
+      <c r="G113" t="s">
+        <v>80</v>
+      </c>
+      <c r="H113" t="s">
+        <v>75</v>
+      </c>
+      <c r="I113">
+        <v>2</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>2</v>
+      </c>
+      <c r="L113">
+        <v>2</v>
+      </c>
+      <c r="M113">
+        <v>1</v>
+      </c>
+      <c r="N113">
+        <v>3</v>
+      </c>
+      <c r="O113" t="s">
+        <v>166</v>
+      </c>
+      <c r="P113" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q113">
+        <v>2.3</v>
+      </c>
+      <c r="R113">
+        <v>2.2</v>
+      </c>
+      <c r="S113">
+        <v>5</v>
+      </c>
+      <c r="T113">
+        <v>1.4</v>
+      </c>
+      <c r="U113">
+        <v>2.75</v>
+      </c>
+      <c r="V113">
+        <v>2.75</v>
+      </c>
+      <c r="W113">
+        <v>1.4</v>
+      </c>
+      <c r="X113">
+        <v>8</v>
+      </c>
+      <c r="Y113">
+        <v>1.08</v>
+      </c>
+      <c r="Z113">
+        <v>1.6</v>
+      </c>
+      <c r="AA113">
+        <v>3.94</v>
+      </c>
+      <c r="AB113">
+        <v>5.3</v>
+      </c>
+      <c r="AC113">
+        <v>1.05</v>
+      </c>
+      <c r="AD113">
+        <v>9.5</v>
+      </c>
+      <c r="AE113">
+        <v>1.28</v>
+      </c>
+      <c r="AF113">
+        <v>3.5</v>
+      </c>
+      <c r="AG113">
+        <v>1.87</v>
+      </c>
+      <c r="AH113">
+        <v>1.87</v>
+      </c>
+      <c r="AI113">
+        <v>1.91</v>
+      </c>
+      <c r="AJ113">
+        <v>1.91</v>
+      </c>
+      <c r="AK113">
+        <v>1.17</v>
+      </c>
+      <c r="AL113">
+        <v>1.2</v>
+      </c>
+      <c r="AM113">
+        <v>2.15</v>
+      </c>
+      <c r="AN113">
+        <v>2.22</v>
+      </c>
+      <c r="AO113">
+        <v>1</v>
+      </c>
+      <c r="AP113">
+        <v>2.3</v>
+      </c>
+      <c r="AQ113">
+        <v>0.9</v>
+      </c>
+      <c r="AR113">
+        <v>1.71</v>
+      </c>
+      <c r="AS113">
+        <v>1.19</v>
+      </c>
+      <c r="AT113">
+        <v>2.9</v>
+      </c>
+      <c r="AU113">
+        <v>5</v>
+      </c>
+      <c r="AV113">
+        <v>4</v>
+      </c>
+      <c r="AW113">
+        <v>12</v>
+      </c>
+      <c r="AX113">
+        <v>5</v>
+      </c>
+      <c r="AY113">
+        <v>25</v>
+      </c>
+      <c r="AZ113">
+        <v>13</v>
+      </c>
+      <c r="BA113">
+        <v>2</v>
+      </c>
+      <c r="BB113">
+        <v>2</v>
+      </c>
+      <c r="BC113">
+        <v>4</v>
+      </c>
+      <c r="BD113">
+        <v>1.45</v>
+      </c>
+      <c r="BE113">
+        <v>6.75</v>
+      </c>
+      <c r="BF113">
+        <v>3.05</v>
+      </c>
+      <c r="BG113">
+        <v>1.34</v>
+      </c>
+      <c r="BH113">
+        <v>2.9</v>
+      </c>
+      <c r="BI113">
+        <v>1.57</v>
+      </c>
+      <c r="BJ113">
+        <v>2.2</v>
+      </c>
+      <c r="BK113">
+        <v>1.95</v>
+      </c>
+      <c r="BL113">
+        <v>1.75</v>
+      </c>
+      <c r="BM113">
+        <v>2.45</v>
+      </c>
+      <c r="BN113">
+        <v>1.48</v>
+      </c>
+      <c r="BO113">
+        <v>3.15</v>
+      </c>
+      <c r="BP113">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7482781</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45711.4375</v>
+      </c>
+      <c r="F114">
+        <v>19</v>
+      </c>
+      <c r="G114" t="s">
+        <v>71</v>
+      </c>
+      <c r="H114" t="s">
+        <v>72</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>0</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>0</v>
+      </c>
+      <c r="O114" t="s">
+        <v>89</v>
+      </c>
+      <c r="P114" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q114">
+        <v>3.5</v>
+      </c>
+      <c r="R114">
+        <v>2</v>
+      </c>
+      <c r="S114">
+        <v>3.5</v>
+      </c>
+      <c r="T114">
+        <v>1.5</v>
+      </c>
+      <c r="U114">
+        <v>2.5</v>
+      </c>
+      <c r="V114">
+        <v>3.5</v>
+      </c>
+      <c r="W114">
+        <v>1.29</v>
+      </c>
+      <c r="X114">
+        <v>11</v>
+      </c>
+      <c r="Y114">
+        <v>1.05</v>
+      </c>
+      <c r="Z114">
+        <v>2.68</v>
+      </c>
+      <c r="AA114">
+        <v>3.07</v>
+      </c>
+      <c r="AB114">
+        <v>2.69</v>
+      </c>
+      <c r="AC114">
+        <v>1.08</v>
+      </c>
+      <c r="AD114">
+        <v>7.5</v>
+      </c>
+      <c r="AE114">
+        <v>1.42</v>
+      </c>
+      <c r="AF114">
+        <v>2.8</v>
+      </c>
+      <c r="AG114">
+        <v>2.15</v>
+      </c>
+      <c r="AH114">
+        <v>1.57</v>
+      </c>
+      <c r="AI114">
+        <v>1.95</v>
+      </c>
+      <c r="AJ114">
+        <v>1.8</v>
+      </c>
+      <c r="AK114">
+        <v>1.44</v>
+      </c>
+      <c r="AL114">
+        <v>1.3</v>
+      </c>
+      <c r="AM114">
+        <v>1.45</v>
+      </c>
+      <c r="AN114">
+        <v>0.67</v>
+      </c>
+      <c r="AO114">
+        <v>1</v>
+      </c>
+      <c r="AP114">
+        <v>0.7</v>
+      </c>
+      <c r="AQ114">
+        <v>1</v>
+      </c>
+      <c r="AR114">
+        <v>1.24</v>
+      </c>
+      <c r="AS114">
+        <v>1.16</v>
+      </c>
+      <c r="AT114">
+        <v>2.4</v>
+      </c>
+      <c r="AU114">
+        <v>5</v>
+      </c>
+      <c r="AV114">
+        <v>3</v>
+      </c>
+      <c r="AW114">
+        <v>10</v>
+      </c>
+      <c r="AX114">
+        <v>6</v>
+      </c>
+      <c r="AY114">
+        <v>18</v>
+      </c>
+      <c r="AZ114">
+        <v>10</v>
+      </c>
+      <c r="BA114">
+        <v>6</v>
+      </c>
+      <c r="BB114">
+        <v>7</v>
+      </c>
+      <c r="BC114">
+        <v>13</v>
+      </c>
+      <c r="BD114">
+        <v>1.94</v>
+      </c>
+      <c r="BE114">
+        <v>6.4</v>
+      </c>
+      <c r="BF114">
+        <v>2.07</v>
+      </c>
+      <c r="BG114">
+        <v>1.36</v>
+      </c>
+      <c r="BH114">
+        <v>2.8</v>
+      </c>
+      <c r="BI114">
+        <v>1.61</v>
+      </c>
+      <c r="BJ114">
+        <v>2.15</v>
+      </c>
+      <c r="BK114">
+        <v>1.98</v>
+      </c>
+      <c r="BL114">
+        <v>1.72</v>
+      </c>
+      <c r="BM114">
+        <v>2.55</v>
+      </c>
+      <c r="BN114">
+        <v>1.44</v>
+      </c>
+      <c r="BO114">
+        <v>3.3</v>
+      </c>
+      <c r="BP114">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7482777</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45711.54166666666</v>
+      </c>
+      <c r="F115">
+        <v>19</v>
+      </c>
+      <c r="G115" t="s">
+        <v>76</v>
+      </c>
+      <c r="H115" t="s">
+        <v>74</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>1</v>
+      </c>
+      <c r="L115">
+        <v>2</v>
+      </c>
+      <c r="M115">
+        <v>1</v>
+      </c>
+      <c r="N115">
+        <v>3</v>
+      </c>
+      <c r="O115" t="s">
+        <v>167</v>
+      </c>
+      <c r="P115" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q115">
+        <v>3.6</v>
+      </c>
+      <c r="R115">
+        <v>2.2</v>
+      </c>
+      <c r="S115">
+        <v>3</v>
+      </c>
+      <c r="T115">
+        <v>1.4</v>
+      </c>
+      <c r="U115">
+        <v>2.75</v>
+      </c>
+      <c r="V115">
+        <v>2.75</v>
+      </c>
+      <c r="W115">
+        <v>1.4</v>
+      </c>
+      <c r="X115">
+        <v>8</v>
+      </c>
+      <c r="Y115">
+        <v>1.08</v>
+      </c>
+      <c r="Z115">
+        <v>2.99</v>
+      </c>
+      <c r="AA115">
+        <v>3.35</v>
+      </c>
+      <c r="AB115">
+        <v>2.29</v>
+      </c>
+      <c r="AC115">
+        <v>1.05</v>
+      </c>
+      <c r="AD115">
+        <v>9</v>
+      </c>
+      <c r="AE115">
+        <v>1.28</v>
+      </c>
+      <c r="AF115">
+        <v>3.5</v>
+      </c>
+      <c r="AG115">
+        <v>1.83</v>
+      </c>
+      <c r="AH115">
+        <v>1.91</v>
+      </c>
+      <c r="AI115">
+        <v>1.7</v>
+      </c>
+      <c r="AJ115">
+        <v>2.05</v>
+      </c>
+      <c r="AK115">
+        <v>1.6</v>
+      </c>
+      <c r="AL115">
+        <v>1.25</v>
+      </c>
+      <c r="AM115">
+        <v>1.38</v>
+      </c>
+      <c r="AN115">
+        <v>0.89</v>
+      </c>
+      <c r="AO115">
+        <v>1</v>
+      </c>
+      <c r="AP115">
+        <v>1.1</v>
+      </c>
+      <c r="AQ115">
+        <v>0.9</v>
+      </c>
+      <c r="AR115">
+        <v>1.44</v>
+      </c>
+      <c r="AS115">
+        <v>1.44</v>
+      </c>
+      <c r="AT115">
+        <v>2.88</v>
+      </c>
+      <c r="AU115">
+        <v>7</v>
+      </c>
+      <c r="AV115">
+        <v>10</v>
+      </c>
+      <c r="AW115">
+        <v>10</v>
+      </c>
+      <c r="AX115">
+        <v>13</v>
+      </c>
+      <c r="AY115">
+        <v>18</v>
+      </c>
+      <c r="AZ115">
+        <v>23</v>
+      </c>
+      <c r="BA115">
+        <v>4</v>
+      </c>
+      <c r="BB115">
+        <v>8</v>
+      </c>
+      <c r="BC115">
+        <v>12</v>
+      </c>
+      <c r="BD115">
+        <v>2.18</v>
+      </c>
+      <c r="BE115">
+        <v>6.4</v>
+      </c>
+      <c r="BF115">
+        <v>1.84</v>
+      </c>
+      <c r="BG115">
+        <v>1.3</v>
+      </c>
+      <c r="BH115">
+        <v>3.15</v>
+      </c>
+      <c r="BI115">
+        <v>1.52</v>
+      </c>
+      <c r="BJ115">
+        <v>2.33</v>
+      </c>
+      <c r="BK115">
+        <v>1.84</v>
+      </c>
+      <c r="BL115">
+        <v>1.84</v>
+      </c>
+      <c r="BM115">
+        <v>2.3</v>
+      </c>
+      <c r="BN115">
+        <v>1.53</v>
+      </c>
+      <c r="BO115">
+        <v>2.95</v>
+      </c>
+      <c r="BP115">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="231">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -520,6 +520,12 @@
     <t>['31', '78']</t>
   </si>
   <si>
+    <t>['90+1']</t>
+  </si>
+  <si>
+    <t>['8', '56', '68', '78', '90+5']</t>
+  </si>
+  <si>
     <t>['4', '6', '45+2']</t>
   </si>
   <si>
@@ -695,6 +701,12 @@
   </si>
   <si>
     <t>['9', '65', '90+9']</t>
+  </si>
+  <si>
+    <t>['16', '77', '90+5']</t>
+  </si>
+  <si>
+    <t>['56', '62']</t>
   </si>
 </sst>
 </file>
@@ -1056,7 +1068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP115"/>
+  <dimension ref="A1:BP118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1312,7 +1324,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q2">
         <v>7</v>
@@ -1390,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ2">
         <v>1.3</v>
@@ -1518,7 +1530,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1724,7 +1736,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -1802,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ4">
         <v>1.56</v>
@@ -2214,7 +2226,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ6">
         <v>1.89</v>
@@ -2423,7 +2435,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ7">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2548,7 +2560,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q8">
         <v>2.1</v>
@@ -2629,7 +2641,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ8">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2960,7 +2972,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q10">
         <v>1.67</v>
@@ -3247,7 +3259,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ11">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3784,7 +3796,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3990,7 +4002,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4068,7 +4080,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ15">
         <v>0.9</v>
@@ -4196,7 +4208,7 @@
         <v>89</v>
       </c>
       <c r="P16" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q16">
         <v>3.8</v>
@@ -4480,7 +4492,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ17">
         <v>1.11</v>
@@ -4689,7 +4701,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ18">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR18">
         <v>1.26</v>
@@ -4892,10 +4904,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ19">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR19">
         <v>1.09</v>
@@ -5020,7 +5032,7 @@
         <v>89</v>
       </c>
       <c r="P20" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5226,7 +5238,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q21">
         <v>2.03</v>
@@ -5307,7 +5319,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ21">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR21">
         <v>2.09</v>
@@ -5432,7 +5444,7 @@
         <v>99</v>
       </c>
       <c r="P22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q22">
         <v>2.4</v>
@@ -5638,7 +5650,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -6128,7 +6140,7 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ25">
         <v>0.9</v>
@@ -6256,7 +6268,7 @@
         <v>103</v>
       </c>
       <c r="P26" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6462,7 +6474,7 @@
         <v>104</v>
       </c>
       <c r="P27" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6668,7 +6680,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -6746,7 +6758,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ28">
         <v>1.3</v>
@@ -6955,7 +6967,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ29">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR29">
         <v>1.18</v>
@@ -7080,7 +7092,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7161,7 +7173,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ30">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR30">
         <v>1.52</v>
@@ -7698,7 +7710,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -7776,10 +7788,10 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ33">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR33">
         <v>1.22</v>
@@ -7904,7 +7916,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q34">
         <v>2.1</v>
@@ -8110,7 +8122,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8316,7 +8328,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8728,7 +8740,7 @@
         <v>89</v>
       </c>
       <c r="P38" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q38">
         <v>2.2</v>
@@ -8809,7 +8821,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ38">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR38">
         <v>1.97</v>
@@ -8934,7 +8946,7 @@
         <v>113</v>
       </c>
       <c r="P39" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9012,10 +9024,10 @@
         <v>0.67</v>
       </c>
       <c r="AP39">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ39">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR39">
         <v>1.72</v>
@@ -9140,7 +9152,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q40">
         <v>3.6</v>
@@ -9424,7 +9436,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ41">
         <v>1.11</v>
@@ -9552,7 +9564,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9758,7 +9770,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9836,7 +9848,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ43">
         <v>1.56</v>
@@ -10045,7 +10057,7 @@
         <v>2</v>
       </c>
       <c r="AQ44">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR44">
         <v>2.5</v>
@@ -10248,10 +10260,10 @@
         <v>1.33</v>
       </c>
       <c r="AP45">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ45">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR45">
         <v>1.2</v>
@@ -10376,7 +10388,7 @@
         <v>120</v>
       </c>
       <c r="P46" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10582,7 +10594,7 @@
         <v>89</v>
       </c>
       <c r="P47" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10660,7 +10672,7 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ47">
         <v>0.8</v>
@@ -10788,7 +10800,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11612,7 +11624,7 @@
         <v>89</v>
       </c>
       <c r="P52" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12024,7 +12036,7 @@
         <v>89</v>
       </c>
       <c r="P54" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12105,7 +12117,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ54">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR54">
         <v>1.29</v>
@@ -12311,7 +12323,7 @@
         <v>2</v>
       </c>
       <c r="AQ55">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR55">
         <v>2.36</v>
@@ -12436,7 +12448,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q56">
         <v>1.95</v>
@@ -12642,7 +12654,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12723,7 +12735,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ57">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR57">
         <v>1.44</v>
@@ -12848,7 +12860,7 @@
         <v>109</v>
       </c>
       <c r="P58" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q58">
         <v>4</v>
@@ -13054,7 +13066,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q59">
         <v>2.1</v>
@@ -13132,7 +13144,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -13672,7 +13684,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -13750,7 +13762,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ62">
         <v>0.9</v>
@@ -14162,7 +14174,7 @@
         <v>1.25</v>
       </c>
       <c r="AP64">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ64">
         <v>0.9</v>
@@ -14290,7 +14302,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q65">
         <v>3.25</v>
@@ -14496,7 +14508,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q66">
         <v>2.88</v>
@@ -14908,7 +14920,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q68">
         <v>2.5</v>
@@ -15195,7 +15207,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ69">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR69">
         <v>0.89</v>
@@ -15401,7 +15413,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ70">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR70">
         <v>1.35</v>
@@ -15732,7 +15744,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -15813,7 +15825,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ72">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR72">
         <v>1.52</v>
@@ -16016,7 +16028,7 @@
         <v>1</v>
       </c>
       <c r="AP73">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ73">
         <v>1.11</v>
@@ -16144,7 +16156,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q74">
         <v>3.75</v>
@@ -16222,7 +16234,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ74">
         <v>1.89</v>
@@ -16556,7 +16568,7 @@
         <v>142</v>
       </c>
       <c r="P76" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16840,7 +16852,7 @@
         <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ77">
         <v>0.8</v>
@@ -17174,7 +17186,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q79">
         <v>2.2</v>
@@ -17586,7 +17598,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -17873,7 +17885,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ82">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR82">
         <v>1.54</v>
@@ -18204,7 +18216,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q84">
         <v>5.5</v>
@@ -18410,7 +18422,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q85">
         <v>3.4</v>
@@ -18488,10 +18500,10 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ85">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR85">
         <v>1.46</v>
@@ -18616,7 +18628,7 @@
         <v>120</v>
       </c>
       <c r="P86" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18694,7 +18706,7 @@
         <v>1.14</v>
       </c>
       <c r="AP86">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ86">
         <v>1.3</v>
@@ -18822,7 +18834,7 @@
         <v>89</v>
       </c>
       <c r="P87" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q87">
         <v>2.75</v>
@@ -19106,7 +19118,7 @@
         <v>0.71</v>
       </c>
       <c r="AP88">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ88">
         <v>0.9</v>
@@ -19234,7 +19246,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19315,7 +19327,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ89">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR89">
         <v>1.4</v>
@@ -19646,7 +19658,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -19852,7 +19864,7 @@
         <v>153</v>
       </c>
       <c r="P92" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -20058,7 +20070,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q93">
         <v>6</v>
@@ -20264,7 +20276,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q94">
         <v>2.6</v>
@@ -20470,7 +20482,7 @@
         <v>89</v>
       </c>
       <c r="P95" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20548,7 +20560,7 @@
         <v>0.71</v>
       </c>
       <c r="AP95">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ95">
         <v>1</v>
@@ -20757,7 +20769,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ96">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR96">
         <v>1.72</v>
@@ -21088,7 +21100,7 @@
         <v>157</v>
       </c>
       <c r="P98" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q98">
         <v>2.5</v>
@@ -21169,7 +21181,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ98">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR98">
         <v>1.71</v>
@@ -21294,7 +21306,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21500,7 +21512,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q100">
         <v>2.3</v>
@@ -21578,10 +21590,10 @@
         <v>1.71</v>
       </c>
       <c r="AP100">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ100">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR100">
         <v>1.69</v>
@@ -22324,7 +22336,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q104">
         <v>1.67</v>
@@ -22736,7 +22748,7 @@
         <v>102</v>
       </c>
       <c r="P106" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -22817,7 +22829,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ106">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR106">
         <v>1.34</v>
@@ -23020,7 +23032,7 @@
         <v>1.63</v>
       </c>
       <c r="AP107">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ107">
         <v>1.56</v>
@@ -23226,7 +23238,7 @@
         <v>0.78</v>
       </c>
       <c r="AP108">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ108">
         <v>0.8</v>
@@ -23560,7 +23572,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23766,7 +23778,7 @@
         <v>164</v>
       </c>
       <c r="P111" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q111">
         <v>3.1</v>
@@ -23972,7 +23984,7 @@
         <v>165</v>
       </c>
       <c r="P112" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q112">
         <v>4.53</v>
@@ -24053,7 +24065,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ112">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR112">
         <v>1.03</v>
@@ -24590,7 +24602,7 @@
         <v>167</v>
       </c>
       <c r="P115" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -24747,6 +24759,624 @@
       </c>
       <c r="BP115">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7482788</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45717.54166666666</v>
+      </c>
+      <c r="F116">
+        <v>20</v>
+      </c>
+      <c r="G116" t="s">
+        <v>72</v>
+      </c>
+      <c r="H116" t="s">
+        <v>73</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>1</v>
+      </c>
+      <c r="K116">
+        <v>1</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>3</v>
+      </c>
+      <c r="N116">
+        <v>3</v>
+      </c>
+      <c r="O116" t="s">
+        <v>89</v>
+      </c>
+      <c r="P116" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q116">
+        <v>3.4</v>
+      </c>
+      <c r="R116">
+        <v>2.1</v>
+      </c>
+      <c r="S116">
+        <v>3.2</v>
+      </c>
+      <c r="T116">
+        <v>1.4</v>
+      </c>
+      <c r="U116">
+        <v>2.75</v>
+      </c>
+      <c r="V116">
+        <v>3</v>
+      </c>
+      <c r="W116">
+        <v>1.36</v>
+      </c>
+      <c r="X116">
+        <v>8</v>
+      </c>
+      <c r="Y116">
+        <v>1.08</v>
+      </c>
+      <c r="Z116">
+        <v>2.58</v>
+      </c>
+      <c r="AA116">
+        <v>3.38</v>
+      </c>
+      <c r="AB116">
+        <v>2.58</v>
+      </c>
+      <c r="AC116">
+        <v>1.05</v>
+      </c>
+      <c r="AD116">
+        <v>9.5</v>
+      </c>
+      <c r="AE116">
+        <v>1.25</v>
+      </c>
+      <c r="AF116">
+        <v>3.75</v>
+      </c>
+      <c r="AG116">
+        <v>1.77</v>
+      </c>
+      <c r="AH116">
+        <v>1.98</v>
+      </c>
+      <c r="AI116">
+        <v>1.7</v>
+      </c>
+      <c r="AJ116">
+        <v>2.05</v>
+      </c>
+      <c r="AK116">
+        <v>1.57</v>
+      </c>
+      <c r="AL116">
+        <v>1.25</v>
+      </c>
+      <c r="AM116">
+        <v>1.38</v>
+      </c>
+      <c r="AN116">
+        <v>1.44</v>
+      </c>
+      <c r="AO116">
+        <v>1.78</v>
+      </c>
+      <c r="AP116">
+        <v>1.3</v>
+      </c>
+      <c r="AQ116">
+        <v>1.9</v>
+      </c>
+      <c r="AR116">
+        <v>1.19</v>
+      </c>
+      <c r="AS116">
+        <v>1.5</v>
+      </c>
+      <c r="AT116">
+        <v>2.69</v>
+      </c>
+      <c r="AU116">
+        <v>3</v>
+      </c>
+      <c r="AV116">
+        <v>9</v>
+      </c>
+      <c r="AW116">
+        <v>4</v>
+      </c>
+      <c r="AX116">
+        <v>6</v>
+      </c>
+      <c r="AY116">
+        <v>7</v>
+      </c>
+      <c r="AZ116">
+        <v>18</v>
+      </c>
+      <c r="BA116">
+        <v>3</v>
+      </c>
+      <c r="BB116">
+        <v>4</v>
+      </c>
+      <c r="BC116">
+        <v>7</v>
+      </c>
+      <c r="BD116">
+        <v>2.02</v>
+      </c>
+      <c r="BE116">
+        <v>6.25</v>
+      </c>
+      <c r="BF116">
+        <v>1.98</v>
+      </c>
+      <c r="BG116">
+        <v>1.4</v>
+      </c>
+      <c r="BH116">
+        <v>2.65</v>
+      </c>
+      <c r="BI116">
+        <v>1.67</v>
+      </c>
+      <c r="BJ116">
+        <v>2.05</v>
+      </c>
+      <c r="BK116">
+        <v>2.06</v>
+      </c>
+      <c r="BL116">
+        <v>1.66</v>
+      </c>
+      <c r="BM116">
+        <v>2.65</v>
+      </c>
+      <c r="BN116">
+        <v>1.41</v>
+      </c>
+      <c r="BO116">
+        <v>3.45</v>
+      </c>
+      <c r="BP116">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7482787</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45717.54166666666</v>
+      </c>
+      <c r="F117">
+        <v>20</v>
+      </c>
+      <c r="G117" t="s">
+        <v>70</v>
+      </c>
+      <c r="H117" t="s">
+        <v>79</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>1</v>
+      </c>
+      <c r="M117">
+        <v>2</v>
+      </c>
+      <c r="N117">
+        <v>3</v>
+      </c>
+      <c r="O117" t="s">
+        <v>168</v>
+      </c>
+      <c r="P117" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q117">
+        <v>4</v>
+      </c>
+      <c r="R117">
+        <v>2.2</v>
+      </c>
+      <c r="S117">
+        <v>2.65</v>
+      </c>
+      <c r="T117">
+        <v>1.36</v>
+      </c>
+      <c r="U117">
+        <v>2.9</v>
+      </c>
+      <c r="V117">
+        <v>2.8</v>
+      </c>
+      <c r="W117">
+        <v>1.39</v>
+      </c>
+      <c r="X117">
+        <v>6.95</v>
+      </c>
+      <c r="Y117">
+        <v>1.07</v>
+      </c>
+      <c r="Z117">
+        <v>3.69</v>
+      </c>
+      <c r="AA117">
+        <v>3.6</v>
+      </c>
+      <c r="AB117">
+        <v>1.92</v>
+      </c>
+      <c r="AC117">
+        <v>1.04</v>
+      </c>
+      <c r="AD117">
+        <v>11</v>
+      </c>
+      <c r="AE117">
+        <v>1.3</v>
+      </c>
+      <c r="AF117">
+        <v>3.5</v>
+      </c>
+      <c r="AG117">
+        <v>1.87</v>
+      </c>
+      <c r="AH117">
+        <v>1.87</v>
+      </c>
+      <c r="AI117">
+        <v>1.75</v>
+      </c>
+      <c r="AJ117">
+        <v>2</v>
+      </c>
+      <c r="AK117">
+        <v>1.83</v>
+      </c>
+      <c r="AL117">
+        <v>1.25</v>
+      </c>
+      <c r="AM117">
+        <v>1.3</v>
+      </c>
+      <c r="AN117">
+        <v>0.78</v>
+      </c>
+      <c r="AO117">
+        <v>1.33</v>
+      </c>
+      <c r="AP117">
+        <v>0.7</v>
+      </c>
+      <c r="AQ117">
+        <v>1.5</v>
+      </c>
+      <c r="AR117">
+        <v>1.34</v>
+      </c>
+      <c r="AS117">
+        <v>1.25</v>
+      </c>
+      <c r="AT117">
+        <v>2.59</v>
+      </c>
+      <c r="AU117">
+        <v>4</v>
+      </c>
+      <c r="AV117">
+        <v>5</v>
+      </c>
+      <c r="AW117">
+        <v>7</v>
+      </c>
+      <c r="AX117">
+        <v>6</v>
+      </c>
+      <c r="AY117">
+        <v>12</v>
+      </c>
+      <c r="AZ117">
+        <v>11</v>
+      </c>
+      <c r="BA117">
+        <v>4</v>
+      </c>
+      <c r="BB117">
+        <v>3</v>
+      </c>
+      <c r="BC117">
+        <v>7</v>
+      </c>
+      <c r="BD117">
+        <v>2.4</v>
+      </c>
+      <c r="BE117">
+        <v>6.5</v>
+      </c>
+      <c r="BF117">
+        <v>1.68</v>
+      </c>
+      <c r="BG117">
+        <v>1.38</v>
+      </c>
+      <c r="BH117">
+        <v>2.7</v>
+      </c>
+      <c r="BI117">
+        <v>1.66</v>
+      </c>
+      <c r="BJ117">
+        <v>2.07</v>
+      </c>
+      <c r="BK117">
+        <v>2.05</v>
+      </c>
+      <c r="BL117">
+        <v>1.67</v>
+      </c>
+      <c r="BM117">
+        <v>2.65</v>
+      </c>
+      <c r="BN117">
+        <v>1.41</v>
+      </c>
+      <c r="BO117">
+        <v>3.45</v>
+      </c>
+      <c r="BP117">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7482785</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45717.54166666666</v>
+      </c>
+      <c r="F118">
+        <v>20</v>
+      </c>
+      <c r="G118" t="s">
+        <v>74</v>
+      </c>
+      <c r="H118" t="s">
+        <v>71</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>1</v>
+      </c>
+      <c r="L118">
+        <v>5</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <v>5</v>
+      </c>
+      <c r="O118" t="s">
+        <v>169</v>
+      </c>
+      <c r="P118" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q118">
+        <v>2.1</v>
+      </c>
+      <c r="R118">
+        <v>2.25</v>
+      </c>
+      <c r="S118">
+        <v>6.5</v>
+      </c>
+      <c r="T118">
+        <v>1.4</v>
+      </c>
+      <c r="U118">
+        <v>2.75</v>
+      </c>
+      <c r="V118">
+        <v>2.75</v>
+      </c>
+      <c r="W118">
+        <v>1.4</v>
+      </c>
+      <c r="X118">
+        <v>8</v>
+      </c>
+      <c r="Y118">
+        <v>1.08</v>
+      </c>
+      <c r="Z118">
+        <v>1.49</v>
+      </c>
+      <c r="AA118">
+        <v>4.7</v>
+      </c>
+      <c r="AB118">
+        <v>5.4</v>
+      </c>
+      <c r="AC118">
+        <v>1.05</v>
+      </c>
+      <c r="AD118">
+        <v>9.5</v>
+      </c>
+      <c r="AE118">
+        <v>1.3</v>
+      </c>
+      <c r="AF118">
+        <v>3.45</v>
+      </c>
+      <c r="AG118">
+        <v>1.98</v>
+      </c>
+      <c r="AH118">
+        <v>1.77</v>
+      </c>
+      <c r="AI118">
+        <v>2</v>
+      </c>
+      <c r="AJ118">
+        <v>1.75</v>
+      </c>
+      <c r="AK118">
+        <v>1.12</v>
+      </c>
+      <c r="AL118">
+        <v>1.17</v>
+      </c>
+      <c r="AM118">
+        <v>2.5</v>
+      </c>
+      <c r="AN118">
+        <v>2.11</v>
+      </c>
+      <c r="AO118">
+        <v>0.78</v>
+      </c>
+      <c r="AP118">
+        <v>2.2</v>
+      </c>
+      <c r="AQ118">
+        <v>0.7</v>
+      </c>
+      <c r="AR118">
+        <v>1.66</v>
+      </c>
+      <c r="AS118">
+        <v>0.98</v>
+      </c>
+      <c r="AT118">
+        <v>2.64</v>
+      </c>
+      <c r="AU118">
+        <v>10</v>
+      </c>
+      <c r="AV118">
+        <v>3</v>
+      </c>
+      <c r="AW118">
+        <v>6</v>
+      </c>
+      <c r="AX118">
+        <v>6</v>
+      </c>
+      <c r="AY118">
+        <v>17</v>
+      </c>
+      <c r="AZ118">
+        <v>11</v>
+      </c>
+      <c r="BA118">
+        <v>5</v>
+      </c>
+      <c r="BB118">
+        <v>2</v>
+      </c>
+      <c r="BC118">
+        <v>7</v>
+      </c>
+      <c r="BD118">
+        <v>1.45</v>
+      </c>
+      <c r="BE118">
+        <v>6.75</v>
+      </c>
+      <c r="BF118">
+        <v>3.15</v>
+      </c>
+      <c r="BG118">
+        <v>1.44</v>
+      </c>
+      <c r="BH118">
+        <v>2.55</v>
+      </c>
+      <c r="BI118">
+        <v>1.73</v>
+      </c>
+      <c r="BJ118">
+        <v>1.96</v>
+      </c>
+      <c r="BK118">
+        <v>2.18</v>
+      </c>
+      <c r="BL118">
+        <v>1.58</v>
+      </c>
+      <c r="BM118">
+        <v>2.8</v>
+      </c>
+      <c r="BN118">
+        <v>1.36</v>
+      </c>
+      <c r="BO118">
+        <v>3.8</v>
+      </c>
+      <c r="BP118">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="235">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -526,6 +526,12 @@
     <t>['8', '56', '68', '78', '90+5']</t>
   </si>
   <si>
+    <t>['1', '90+2']</t>
+  </si>
+  <si>
+    <t>['72', '84', '87']</t>
+  </si>
+  <si>
     <t>['4', '6', '45+2']</t>
   </si>
   <si>
@@ -707,6 +713,12 @@
   </si>
   <si>
     <t>['56', '62']</t>
+  </si>
+  <si>
+    <t>['14', '61']</t>
+  </si>
+  <si>
+    <t>['10']</t>
   </si>
 </sst>
 </file>
@@ -1068,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP118"/>
+  <dimension ref="A1:BP121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1324,7 +1336,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q2">
         <v>7</v>
@@ -1530,7 +1542,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1611,7 +1623,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ3">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1736,7 +1748,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -1817,7 +1829,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ4">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2229,7 +2241,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ6">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2432,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ7">
         <v>1.5</v>
@@ -2560,7 +2572,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q8">
         <v>2.1</v>
@@ -2972,7 +2984,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q10">
         <v>1.67</v>
@@ -3050,7 +3062,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ10">
         <v>0.9</v>
@@ -3668,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ13">
         <v>0.9</v>
@@ -3796,7 +3808,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3874,10 +3886,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ14">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR14">
         <v>0.52</v>
@@ -4002,7 +4014,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4208,7 +4220,7 @@
         <v>89</v>
       </c>
       <c r="P16" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q16">
         <v>3.8</v>
@@ -4495,7 +4507,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ17">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR17">
         <v>1.7</v>
@@ -5032,7 +5044,7 @@
         <v>89</v>
       </c>
       <c r="P20" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5238,7 +5250,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q21">
         <v>2.03</v>
@@ -5444,7 +5456,7 @@
         <v>99</v>
       </c>
       <c r="P22" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q22">
         <v>2.4</v>
@@ -5650,7 +5662,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5731,7 +5743,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ23">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR23">
         <v>1.73</v>
@@ -5934,7 +5946,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ24">
         <v>0.9</v>
@@ -6268,7 +6280,7 @@
         <v>103</v>
       </c>
       <c r="P26" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6346,7 +6358,7 @@
         <v>0.5</v>
       </c>
       <c r="AP26">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ26">
         <v>0.9</v>
@@ -6474,7 +6486,7 @@
         <v>104</v>
       </c>
       <c r="P27" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6555,7 +6567,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ27">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR27">
         <v>1.97</v>
@@ -6680,7 +6692,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7092,7 +7104,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7582,10 +7594,10 @@
         <v>1.5</v>
       </c>
       <c r="AP32">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ32">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR32">
         <v>1.09</v>
@@ -7710,7 +7722,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -7916,7 +7928,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q34">
         <v>2.1</v>
@@ -8122,7 +8134,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8200,7 +8212,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -8328,7 +8340,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8740,7 +8752,7 @@
         <v>89</v>
       </c>
       <c r="P38" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q38">
         <v>2.2</v>
@@ -8946,7 +8958,7 @@
         <v>113</v>
       </c>
       <c r="P39" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9152,7 +9164,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q40">
         <v>3.6</v>
@@ -9233,7 +9245,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ40">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR40">
         <v>1.88</v>
@@ -9439,7 +9451,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ41">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR41">
         <v>1.23</v>
@@ -9564,7 +9576,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9642,10 +9654,10 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ42">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR42">
         <v>1.32</v>
@@ -9770,7 +9782,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9851,7 +9863,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ43">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR43">
         <v>1.82</v>
@@ -10054,7 +10066,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ44">
         <v>1.5</v>
@@ -10388,7 +10400,7 @@
         <v>120</v>
       </c>
       <c r="P46" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10469,7 +10481,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ46">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR46">
         <v>1.79</v>
@@ -10594,7 +10606,7 @@
         <v>89</v>
       </c>
       <c r="P47" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10800,7 +10812,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11624,7 +11636,7 @@
         <v>89</v>
       </c>
       <c r="P52" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12036,7 +12048,7 @@
         <v>89</v>
       </c>
       <c r="P54" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12114,7 +12126,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ54">
         <v>1.9</v>
@@ -12320,7 +12332,7 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ55">
         <v>0.7</v>
@@ -12448,7 +12460,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q56">
         <v>1.95</v>
@@ -12654,7 +12666,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12732,7 +12744,7 @@
         <v>0.4</v>
       </c>
       <c r="AP57">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ57">
         <v>1.5</v>
@@ -12860,7 +12872,7 @@
         <v>109</v>
       </c>
       <c r="P58" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q58">
         <v>4</v>
@@ -12941,7 +12953,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ58">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR58">
         <v>1</v>
@@ -13066,7 +13078,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q59">
         <v>2.1</v>
@@ -13353,7 +13365,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ60">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR60">
         <v>1.68</v>
@@ -13684,7 +13696,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -14302,7 +14314,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q65">
         <v>3.25</v>
@@ -14383,7 +14395,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ65">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -14508,7 +14520,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q66">
         <v>2.88</v>
@@ -14792,7 +14804,7 @@
         <v>0.33</v>
       </c>
       <c r="AP67">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ67">
         <v>0.9</v>
@@ -14920,7 +14932,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q68">
         <v>2.5</v>
@@ -15410,7 +15422,7 @@
         <v>1.8</v>
       </c>
       <c r="AP70">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ70">
         <v>1.9</v>
@@ -15744,7 +15756,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16031,7 +16043,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ73">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR73">
         <v>1.44</v>
@@ -16156,7 +16168,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q74">
         <v>3.75</v>
@@ -16237,7 +16249,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ74">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR74">
         <v>1.16</v>
@@ -16440,7 +16452,7 @@
         <v>1.33</v>
       </c>
       <c r="AP75">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ75">
         <v>1.3</v>
@@ -16568,7 +16580,7 @@
         <v>142</v>
       </c>
       <c r="P76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16649,7 +16661,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ76">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR76">
         <v>1.31</v>
@@ -17186,7 +17198,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q79">
         <v>2.2</v>
@@ -17264,10 +17276,10 @@
         <v>1.67</v>
       </c>
       <c r="AP79">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ79">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR79">
         <v>2.16</v>
@@ -17598,7 +17610,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -17676,7 +17688,7 @@
         <v>0.43</v>
       </c>
       <c r="AP81">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ81">
         <v>0.9</v>
@@ -18216,7 +18228,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q84">
         <v>5.5</v>
@@ -18297,7 +18309,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ84">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR84">
         <v>1.26</v>
@@ -18422,7 +18434,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q85">
         <v>3.4</v>
@@ -18628,7 +18640,7 @@
         <v>120</v>
       </c>
       <c r="P86" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18834,7 +18846,7 @@
         <v>89</v>
       </c>
       <c r="P87" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q87">
         <v>2.75</v>
@@ -18912,10 +18924,10 @@
         <v>0.86</v>
       </c>
       <c r="AP87">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ87">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR87">
         <v>1.29</v>
@@ -19246,7 +19258,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19530,7 +19542,7 @@
         <v>0.83</v>
       </c>
       <c r="AP90">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -19658,7 +19670,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -19739,7 +19751,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ91">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR91">
         <v>1.53</v>
@@ -19864,7 +19876,7 @@
         <v>153</v>
       </c>
       <c r="P92" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -19942,7 +19954,7 @@
         <v>1.14</v>
       </c>
       <c r="AP92">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ92">
         <v>0.9</v>
@@ -20070,7 +20082,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q93">
         <v>6</v>
@@ -20151,7 +20163,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ93">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR93">
         <v>0.89</v>
@@ -20276,7 +20288,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q94">
         <v>2.6</v>
@@ -20354,7 +20366,7 @@
         <v>1</v>
       </c>
       <c r="AP94">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ94">
         <v>0.8</v>
@@ -20482,7 +20494,7 @@
         <v>89</v>
       </c>
       <c r="P95" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20972,7 +20984,7 @@
         <v>0.88</v>
       </c>
       <c r="AP97">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ97">
         <v>0.8</v>
@@ -21100,7 +21112,7 @@
         <v>157</v>
       </c>
       <c r="P98" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q98">
         <v>2.5</v>
@@ -21306,7 +21318,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21512,7 +21524,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q100">
         <v>2.3</v>
@@ -21796,7 +21808,7 @@
         <v>1.13</v>
       </c>
       <c r="AP101">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ101">
         <v>1.3</v>
@@ -22336,7 +22348,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q104">
         <v>1.67</v>
@@ -22414,10 +22426,10 @@
         <v>1.13</v>
       </c>
       <c r="AP104">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ104">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR104">
         <v>2.12</v>
@@ -22623,7 +22635,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ105">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR105">
         <v>1.48</v>
@@ -22748,7 +22760,7 @@
         <v>102</v>
       </c>
       <c r="P106" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -22826,7 +22838,7 @@
         <v>0.5</v>
       </c>
       <c r="AP106">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ106">
         <v>0.7</v>
@@ -23035,7 +23047,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ107">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR107">
         <v>1.33</v>
@@ -23572,7 +23584,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23778,7 +23790,7 @@
         <v>164</v>
       </c>
       <c r="P111" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q111">
         <v>3.1</v>
@@ -23856,7 +23868,7 @@
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ111">
         <v>0.9</v>
@@ -23984,7 +23996,7 @@
         <v>165</v>
       </c>
       <c r="P112" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q112">
         <v>4.53</v>
@@ -24602,7 +24614,7 @@
         <v>167</v>
       </c>
       <c r="P115" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -24808,7 +24820,7 @@
         <v>89</v>
       </c>
       <c r="P116" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25014,7 +25026,7 @@
         <v>168</v>
       </c>
       <c r="P117" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25377,6 +25389,624 @@
       </c>
       <c r="BP118">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7482786</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45718.4375</v>
+      </c>
+      <c r="F119">
+        <v>20</v>
+      </c>
+      <c r="G119" t="s">
+        <v>75</v>
+      </c>
+      <c r="H119" t="s">
+        <v>77</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="J119">
+        <v>1</v>
+      </c>
+      <c r="K119">
+        <v>2</v>
+      </c>
+      <c r="L119">
+        <v>2</v>
+      </c>
+      <c r="M119">
+        <v>1</v>
+      </c>
+      <c r="N119">
+        <v>3</v>
+      </c>
+      <c r="O119" t="s">
+        <v>170</v>
+      </c>
+      <c r="P119" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q119">
+        <v>2.6</v>
+      </c>
+      <c r="R119">
+        <v>2.05</v>
+      </c>
+      <c r="S119">
+        <v>4.75</v>
+      </c>
+      <c r="T119">
+        <v>1.44</v>
+      </c>
+      <c r="U119">
+        <v>2.63</v>
+      </c>
+      <c r="V119">
+        <v>3.4</v>
+      </c>
+      <c r="W119">
+        <v>1.3</v>
+      </c>
+      <c r="X119">
+        <v>10</v>
+      </c>
+      <c r="Y119">
+        <v>1.06</v>
+      </c>
+      <c r="Z119">
+        <v>1.83</v>
+      </c>
+      <c r="AA119">
+        <v>3.16</v>
+      </c>
+      <c r="AB119">
+        <v>4.8</v>
+      </c>
+      <c r="AC119">
+        <v>1.09</v>
+      </c>
+      <c r="AD119">
+        <v>8</v>
+      </c>
+      <c r="AE119">
+        <v>1.4</v>
+      </c>
+      <c r="AF119">
+        <v>2.95</v>
+      </c>
+      <c r="AG119">
+        <v>2.05</v>
+      </c>
+      <c r="AH119">
+        <v>1.65</v>
+      </c>
+      <c r="AI119">
+        <v>2</v>
+      </c>
+      <c r="AJ119">
+        <v>1.75</v>
+      </c>
+      <c r="AK119">
+        <v>1.2</v>
+      </c>
+      <c r="AL119">
+        <v>1.31</v>
+      </c>
+      <c r="AM119">
+        <v>1.9</v>
+      </c>
+      <c r="AN119">
+        <v>1.67</v>
+      </c>
+      <c r="AO119">
+        <v>1.11</v>
+      </c>
+      <c r="AP119">
+        <v>1.8</v>
+      </c>
+      <c r="AQ119">
+        <v>1</v>
+      </c>
+      <c r="AR119">
+        <v>1.3</v>
+      </c>
+      <c r="AS119">
+        <v>1.13</v>
+      </c>
+      <c r="AT119">
+        <v>2.43</v>
+      </c>
+      <c r="AU119">
+        <v>7</v>
+      </c>
+      <c r="AV119">
+        <v>5</v>
+      </c>
+      <c r="AW119">
+        <v>19</v>
+      </c>
+      <c r="AX119">
+        <v>4</v>
+      </c>
+      <c r="AY119">
+        <v>33</v>
+      </c>
+      <c r="AZ119">
+        <v>10</v>
+      </c>
+      <c r="BA119">
+        <v>4</v>
+      </c>
+      <c r="BB119">
+        <v>3</v>
+      </c>
+      <c r="BC119">
+        <v>7</v>
+      </c>
+      <c r="BD119">
+        <v>1.58</v>
+      </c>
+      <c r="BE119">
+        <v>6.4</v>
+      </c>
+      <c r="BF119">
+        <v>2.65</v>
+      </c>
+      <c r="BG119">
+        <v>1.44</v>
+      </c>
+      <c r="BH119">
+        <v>2.55</v>
+      </c>
+      <c r="BI119">
+        <v>1.73</v>
+      </c>
+      <c r="BJ119">
+        <v>1.96</v>
+      </c>
+      <c r="BK119">
+        <v>2.17</v>
+      </c>
+      <c r="BL119">
+        <v>1.58</v>
+      </c>
+      <c r="BM119">
+        <v>2.8</v>
+      </c>
+      <c r="BN119">
+        <v>1.36</v>
+      </c>
+      <c r="BO119">
+        <v>3.7</v>
+      </c>
+      <c r="BP119">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="120" spans="1:68">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7482784</v>
+      </c>
+      <c r="C120" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45718.4375</v>
+      </c>
+      <c r="F120">
+        <v>20</v>
+      </c>
+      <c r="G120" t="s">
+        <v>81</v>
+      </c>
+      <c r="H120" t="s">
+        <v>76</v>
+      </c>
+      <c r="I120">
+        <v>1</v>
+      </c>
+      <c r="J120">
+        <v>1</v>
+      </c>
+      <c r="K120">
+        <v>2</v>
+      </c>
+      <c r="L120">
+        <v>1</v>
+      </c>
+      <c r="M120">
+        <v>2</v>
+      </c>
+      <c r="N120">
+        <v>3</v>
+      </c>
+      <c r="O120" t="s">
+        <v>93</v>
+      </c>
+      <c r="P120" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q120">
+        <v>4.33</v>
+      </c>
+      <c r="R120">
+        <v>2.1</v>
+      </c>
+      <c r="S120">
+        <v>2.63</v>
+      </c>
+      <c r="T120">
+        <v>1.4</v>
+      </c>
+      <c r="U120">
+        <v>2.75</v>
+      </c>
+      <c r="V120">
+        <v>3</v>
+      </c>
+      <c r="W120">
+        <v>1.36</v>
+      </c>
+      <c r="X120">
+        <v>8</v>
+      </c>
+      <c r="Y120">
+        <v>1.08</v>
+      </c>
+      <c r="Z120">
+        <v>3.8</v>
+      </c>
+      <c r="AA120">
+        <v>3.38</v>
+      </c>
+      <c r="AB120">
+        <v>1.96</v>
+      </c>
+      <c r="AC120">
+        <v>1.05</v>
+      </c>
+      <c r="AD120">
+        <v>10</v>
+      </c>
+      <c r="AE120">
+        <v>1.33</v>
+      </c>
+      <c r="AF120">
+        <v>3.3</v>
+      </c>
+      <c r="AG120">
+        <v>1.95</v>
+      </c>
+      <c r="AH120">
+        <v>1.79</v>
+      </c>
+      <c r="AI120">
+        <v>1.8</v>
+      </c>
+      <c r="AJ120">
+        <v>1.95</v>
+      </c>
+      <c r="AK120">
+        <v>1.78</v>
+      </c>
+      <c r="AL120">
+        <v>1.3</v>
+      </c>
+      <c r="AM120">
+        <v>1.26</v>
+      </c>
+      <c r="AN120">
+        <v>1.33</v>
+      </c>
+      <c r="AO120">
+        <v>1.56</v>
+      </c>
+      <c r="AP120">
+        <v>1.2</v>
+      </c>
+      <c r="AQ120">
+        <v>1.7</v>
+      </c>
+      <c r="AR120">
+        <v>1.39</v>
+      </c>
+      <c r="AS120">
+        <v>1.11</v>
+      </c>
+      <c r="AT120">
+        <v>2.5</v>
+      </c>
+      <c r="AU120">
+        <v>3</v>
+      </c>
+      <c r="AV120">
+        <v>5</v>
+      </c>
+      <c r="AW120">
+        <v>5</v>
+      </c>
+      <c r="AX120">
+        <v>9</v>
+      </c>
+      <c r="AY120">
+        <v>9</v>
+      </c>
+      <c r="AZ120">
+        <v>16</v>
+      </c>
+      <c r="BA120">
+        <v>2</v>
+      </c>
+      <c r="BB120">
+        <v>4</v>
+      </c>
+      <c r="BC120">
+        <v>6</v>
+      </c>
+      <c r="BD120">
+        <v>2.45</v>
+      </c>
+      <c r="BE120">
+        <v>6.25</v>
+      </c>
+      <c r="BF120">
+        <v>1.68</v>
+      </c>
+      <c r="BG120">
+        <v>1.4</v>
+      </c>
+      <c r="BH120">
+        <v>2.65</v>
+      </c>
+      <c r="BI120">
+        <v>1.68</v>
+      </c>
+      <c r="BJ120">
+        <v>2.04</v>
+      </c>
+      <c r="BK120">
+        <v>2.08</v>
+      </c>
+      <c r="BL120">
+        <v>1.65</v>
+      </c>
+      <c r="BM120">
+        <v>2.65</v>
+      </c>
+      <c r="BN120">
+        <v>1.41</v>
+      </c>
+      <c r="BO120">
+        <v>3.55</v>
+      </c>
+      <c r="BP120">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7482783</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45718.54166666666</v>
+      </c>
+      <c r="F121">
+        <v>20</v>
+      </c>
+      <c r="G121" t="s">
+        <v>78</v>
+      </c>
+      <c r="H121" t="s">
+        <v>80</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>1</v>
+      </c>
+      <c r="K121">
+        <v>1</v>
+      </c>
+      <c r="L121">
+        <v>3</v>
+      </c>
+      <c r="M121">
+        <v>1</v>
+      </c>
+      <c r="N121">
+        <v>4</v>
+      </c>
+      <c r="O121" t="s">
+        <v>171</v>
+      </c>
+      <c r="P121" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q121">
+        <v>2.6</v>
+      </c>
+      <c r="R121">
+        <v>2.25</v>
+      </c>
+      <c r="S121">
+        <v>4</v>
+      </c>
+      <c r="T121">
+        <v>1.33</v>
+      </c>
+      <c r="U121">
+        <v>3.25</v>
+      </c>
+      <c r="V121">
+        <v>2.63</v>
+      </c>
+      <c r="W121">
+        <v>1.44</v>
+      </c>
+      <c r="X121">
+        <v>6.5</v>
+      </c>
+      <c r="Y121">
+        <v>1.11</v>
+      </c>
+      <c r="Z121">
+        <v>1.98</v>
+      </c>
+      <c r="AA121">
+        <v>3.51</v>
+      </c>
+      <c r="AB121">
+        <v>3.58</v>
+      </c>
+      <c r="AC121">
+        <v>1.03</v>
+      </c>
+      <c r="AD121">
+        <v>13</v>
+      </c>
+      <c r="AE121">
+        <v>1.22</v>
+      </c>
+      <c r="AF121">
+        <v>4.2</v>
+      </c>
+      <c r="AG121">
+        <v>1.67</v>
+      </c>
+      <c r="AH121">
+        <v>2</v>
+      </c>
+      <c r="AI121">
+        <v>1.62</v>
+      </c>
+      <c r="AJ121">
+        <v>2.2</v>
+      </c>
+      <c r="AK121">
+        <v>1.3</v>
+      </c>
+      <c r="AL121">
+        <v>1.28</v>
+      </c>
+      <c r="AM121">
+        <v>1.75</v>
+      </c>
+      <c r="AN121">
+        <v>2</v>
+      </c>
+      <c r="AO121">
+        <v>1.89</v>
+      </c>
+      <c r="AP121">
+        <v>2.1</v>
+      </c>
+      <c r="AQ121">
+        <v>1.7</v>
+      </c>
+      <c r="AR121">
+        <v>2.18</v>
+      </c>
+      <c r="AS121">
+        <v>1.34</v>
+      </c>
+      <c r="AT121">
+        <v>3.52</v>
+      </c>
+      <c r="AU121">
+        <v>8</v>
+      </c>
+      <c r="AV121">
+        <v>6</v>
+      </c>
+      <c r="AW121">
+        <v>18</v>
+      </c>
+      <c r="AX121">
+        <v>10</v>
+      </c>
+      <c r="AY121">
+        <v>34</v>
+      </c>
+      <c r="AZ121">
+        <v>21</v>
+      </c>
+      <c r="BA121">
+        <v>3</v>
+      </c>
+      <c r="BB121">
+        <v>5</v>
+      </c>
+      <c r="BC121">
+        <v>8</v>
+      </c>
+      <c r="BD121">
+        <v>1.74</v>
+      </c>
+      <c r="BE121">
+        <v>6.4</v>
+      </c>
+      <c r="BF121">
+        <v>2.3</v>
+      </c>
+      <c r="BG121">
+        <v>1.35</v>
+      </c>
+      <c r="BH121">
+        <v>2.9</v>
+      </c>
+      <c r="BI121">
+        <v>1.61</v>
+      </c>
+      <c r="BJ121">
+        <v>2.15</v>
+      </c>
+      <c r="BK121">
+        <v>1.98</v>
+      </c>
+      <c r="BL121">
+        <v>1.72</v>
+      </c>
+      <c r="BM121">
+        <v>2.5</v>
+      </c>
+      <c r="BN121">
+        <v>1.46</v>
+      </c>
+      <c r="BO121">
+        <v>3.3</v>
+      </c>
+      <c r="BP121">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="244">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -532,6 +532,21 @@
     <t>['72', '84', '87']</t>
   </si>
   <si>
+    <t>['42', '90+4']</t>
+  </si>
+  <si>
+    <t>['71']</t>
+  </si>
+  <si>
+    <t>['15', '20']</t>
+  </si>
+  <si>
+    <t>['80']</t>
+  </si>
+  <si>
+    <t>['49', '74']</t>
+  </si>
+  <si>
     <t>['4', '6', '45+2']</t>
   </si>
   <si>
@@ -719,6 +734,18 @@
   </si>
   <si>
     <t>['10']</t>
+  </si>
+  <si>
+    <t>['36', '87']</t>
+  </si>
+  <si>
+    <t>['11']</t>
+  </si>
+  <si>
+    <t>['86', '90+2']</t>
+  </si>
+  <si>
+    <t>['84']</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP121"/>
+  <dimension ref="A1:BP127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1336,7 +1363,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Q2">
         <v>7</v>
@@ -1414,10 +1441,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ2">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1542,7 +1569,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1620,10 +1647,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1748,7 +1775,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -1826,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ4">
         <v>1.7</v>
@@ -2032,10 +2059,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ5">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2241,7 +2268,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ6">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2572,7 +2599,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="Q8">
         <v>2.1</v>
@@ -2650,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ8">
         <v>0.7</v>
@@ -2984,7 +3011,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="Q10">
         <v>1.67</v>
@@ -3065,7 +3092,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ10">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3268,7 +3295,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ11">
         <v>1.9</v>
@@ -3683,7 +3710,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ13">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3808,7 +3835,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3889,7 +3916,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ14">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR14">
         <v>0.52</v>
@@ -4014,7 +4041,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4092,10 +4119,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ15">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR15">
         <v>1.07</v>
@@ -4220,7 +4247,7 @@
         <v>89</v>
       </c>
       <c r="P16" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="Q16">
         <v>3.8</v>
@@ -4298,10 +4325,10 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ16">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR16">
         <v>1.73</v>
@@ -4507,7 +4534,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR17">
         <v>1.7</v>
@@ -4710,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ18">
         <v>1.9</v>
@@ -4916,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ19">
         <v>1.5</v>
@@ -5044,7 +5071,7 @@
         <v>89</v>
       </c>
       <c r="P20" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5125,7 +5152,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ20">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR20">
         <v>0.78</v>
@@ -5250,7 +5277,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="Q21">
         <v>2.03</v>
@@ -5456,7 +5483,7 @@
         <v>99</v>
       </c>
       <c r="P22" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="Q22">
         <v>2.4</v>
@@ -5534,7 +5561,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ22">
         <v>0.9</v>
@@ -5662,7 +5689,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5740,7 +5767,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ23">
         <v>1.7</v>
@@ -5949,7 +5976,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ24">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR24">
         <v>0.92</v>
@@ -6152,7 +6179,7 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ25">
         <v>0.9</v>
@@ -6280,7 +6307,7 @@
         <v>103</v>
       </c>
       <c r="P26" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6361,7 +6388,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ26">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR26">
         <v>0.84</v>
@@ -6486,7 +6513,7 @@
         <v>104</v>
       </c>
       <c r="P27" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6567,7 +6594,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR27">
         <v>1.97</v>
@@ -6692,7 +6719,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -6773,7 +6800,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ28">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR28">
         <v>1.88</v>
@@ -6976,7 +7003,7 @@
         <v>0.5</v>
       </c>
       <c r="AP29">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ29">
         <v>1.5</v>
@@ -7104,7 +7131,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7182,7 +7209,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ30">
         <v>1.9</v>
@@ -7388,10 +7415,10 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ31">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR31">
         <v>1.82</v>
@@ -7722,7 +7749,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -7800,7 +7827,7 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ33">
         <v>0.7</v>
@@ -7928,7 +7955,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Q34">
         <v>2.1</v>
@@ -8006,7 +8033,7 @@
         <v>0.67</v>
       </c>
       <c r="AP34">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ34">
         <v>0.9</v>
@@ -8134,7 +8161,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8340,7 +8367,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8418,10 +8445,10 @@
         <v>0.33</v>
       </c>
       <c r="AP36">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ36">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR36">
         <v>1.26</v>
@@ -8627,7 +8654,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ37">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR37">
         <v>1</v>
@@ -8752,7 +8779,7 @@
         <v>89</v>
       </c>
       <c r="P38" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="Q38">
         <v>2.2</v>
@@ -8958,7 +8985,7 @@
         <v>113</v>
       </c>
       <c r="P39" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9164,7 +9191,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="Q40">
         <v>3.6</v>
@@ -9242,10 +9269,10 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ40">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR40">
         <v>1.88</v>
@@ -9448,10 +9475,10 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR41">
         <v>1.23</v>
@@ -9576,7 +9603,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9657,7 +9684,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ42">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR42">
         <v>1.32</v>
@@ -9782,7 +9809,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10272,7 +10299,7 @@
         <v>1.33</v>
       </c>
       <c r="AP45">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ45">
         <v>0.7</v>
@@ -10400,7 +10427,7 @@
         <v>120</v>
       </c>
       <c r="P46" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10478,10 +10505,10 @@
         <v>0.75</v>
       </c>
       <c r="AP46">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ46">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR46">
         <v>1.79</v>
@@ -10606,7 +10633,7 @@
         <v>89</v>
       </c>
       <c r="P47" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10684,10 +10711,10 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ47">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR47">
         <v>1.52</v>
@@ -10812,7 +10839,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -10890,7 +10917,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -11096,7 +11123,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ49">
         <v>0.9</v>
@@ -11305,7 +11332,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ50">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR50">
         <v>0.98</v>
@@ -11508,10 +11535,10 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ51">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR51">
         <v>1.44</v>
@@ -11636,7 +11663,7 @@
         <v>89</v>
       </c>
       <c r="P52" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -11714,10 +11741,10 @@
         <v>0.67</v>
       </c>
       <c r="AP52">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ52">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR52">
         <v>1.2</v>
@@ -11923,7 +11950,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ53">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR53">
         <v>1.83</v>
@@ -12048,7 +12075,7 @@
         <v>89</v>
       </c>
       <c r="P54" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12460,7 +12487,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="Q56">
         <v>1.95</v>
@@ -12666,7 +12693,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12872,7 +12899,7 @@
         <v>109</v>
       </c>
       <c r="P58" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="Q58">
         <v>4</v>
@@ -13078,7 +13105,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="Q59">
         <v>2.1</v>
@@ -13362,10 +13389,10 @@
         <v>1.2</v>
       </c>
       <c r="AP60">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ60">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR60">
         <v>1.68</v>
@@ -13568,10 +13595,10 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ61">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR61">
         <v>1.23</v>
@@ -13696,7 +13723,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -13774,10 +13801,10 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ62">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR62">
         <v>1.17</v>
@@ -13980,10 +14007,10 @@
         <v>1.4</v>
       </c>
       <c r="AP63">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ63">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR63">
         <v>1.65</v>
@@ -14186,10 +14213,10 @@
         <v>1.25</v>
       </c>
       <c r="AP64">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ64">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR64">
         <v>1.56</v>
@@ -14314,7 +14341,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="Q65">
         <v>3.25</v>
@@ -14392,10 +14419,10 @@
         <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ65">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -14520,7 +14547,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="Q66">
         <v>2.88</v>
@@ -14601,7 +14628,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ66">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR66">
         <v>1.79</v>
@@ -14932,7 +14959,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="Q68">
         <v>2.5</v>
@@ -15010,7 +15037,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ68">
         <v>1</v>
@@ -15628,10 +15655,10 @@
         <v>0.83</v>
       </c>
       <c r="AP71">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ71">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR71">
         <v>1.72</v>
@@ -15756,7 +15783,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -15834,7 +15861,7 @@
         <v>0.83</v>
       </c>
       <c r="AP72">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ72">
         <v>1.5</v>
@@ -16040,10 +16067,10 @@
         <v>1</v>
       </c>
       <c r="AP73">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ73">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR73">
         <v>1.44</v>
@@ -16168,7 +16195,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="Q74">
         <v>3.75</v>
@@ -16246,10 +16273,10 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ74">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR74">
         <v>1.16</v>
@@ -16455,7 +16482,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ75">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR75">
         <v>1.32</v>
@@ -16580,7 +16607,7 @@
         <v>142</v>
       </c>
       <c r="P76" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16658,7 +16685,7 @@
         <v>1.4</v>
       </c>
       <c r="AP76">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ76">
         <v>1.7</v>
@@ -16867,7 +16894,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ77">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR77">
         <v>1.67</v>
@@ -17073,7 +17100,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ78">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR78">
         <v>0.96</v>
@@ -17198,7 +17225,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="Q79">
         <v>2.2</v>
@@ -17485,7 +17512,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ80">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR80">
         <v>1.71</v>
@@ -17610,7 +17637,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -17894,7 +17921,7 @@
         <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ82">
         <v>0.7</v>
@@ -18100,7 +18127,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ83">
         <v>1</v>
@@ -18228,7 +18255,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="Q84">
         <v>5.5</v>
@@ -18306,10 +18333,10 @@
         <v>2.17</v>
       </c>
       <c r="AP84">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ84">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR84">
         <v>1.26</v>
@@ -18434,7 +18461,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="Q85">
         <v>3.4</v>
@@ -18512,7 +18539,7 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ85">
         <v>1.9</v>
@@ -18640,7 +18667,7 @@
         <v>120</v>
       </c>
       <c r="P86" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18718,10 +18745,10 @@
         <v>1.14</v>
       </c>
       <c r="AP86">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ86">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR86">
         <v>1.2</v>
@@ -18846,7 +18873,7 @@
         <v>89</v>
       </c>
       <c r="P87" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="Q87">
         <v>2.75</v>
@@ -18927,7 +18954,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ87">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR87">
         <v>1.29</v>
@@ -19133,7 +19160,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ88">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR88">
         <v>1.65</v>
@@ -19258,7 +19285,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19336,7 +19363,7 @@
         <v>1.14</v>
       </c>
       <c r="AP89">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ89">
         <v>1.5</v>
@@ -19670,7 +19697,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -19748,7 +19775,7 @@
         <v>1.86</v>
       </c>
       <c r="AP91">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ91">
         <v>1.7</v>
@@ -19876,7 +19903,7 @@
         <v>153</v>
       </c>
       <c r="P92" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -19957,7 +19984,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ92">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR92">
         <v>2.1</v>
@@ -20082,7 +20109,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="Q93">
         <v>6</v>
@@ -20163,7 +20190,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ93">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR93">
         <v>0.89</v>
@@ -20288,7 +20315,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="Q94">
         <v>2.6</v>
@@ -20369,7 +20396,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ94">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR94">
         <v>1.33</v>
@@ -20494,7 +20521,7 @@
         <v>89</v>
       </c>
       <c r="P95" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20572,7 +20599,7 @@
         <v>0.71</v>
       </c>
       <c r="AP95">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ95">
         <v>1</v>
@@ -20778,7 +20805,7 @@
         <v>0.57</v>
       </c>
       <c r="AP96">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ96">
         <v>0.7</v>
@@ -20987,7 +21014,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ97">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR97">
         <v>2.11</v>
@@ -21112,7 +21139,7 @@
         <v>157</v>
       </c>
       <c r="P98" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="Q98">
         <v>2.5</v>
@@ -21318,7 +21345,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21396,7 +21423,7 @@
         <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ99">
         <v>0.9</v>
@@ -21524,7 +21551,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Q100">
         <v>2.3</v>
@@ -21811,7 +21838,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ101">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR101">
         <v>1.37</v>
@@ -22220,10 +22247,10 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ103">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR103">
         <v>1.4</v>
@@ -22348,7 +22375,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="Q104">
         <v>1.67</v>
@@ -22429,7 +22456,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ104">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR104">
         <v>2.12</v>
@@ -22632,10 +22659,10 @@
         <v>2.13</v>
       </c>
       <c r="AP105">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ105">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR105">
         <v>1.48</v>
@@ -22760,7 +22787,7 @@
         <v>102</v>
       </c>
       <c r="P106" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -23044,7 +23071,7 @@
         <v>1.63</v>
       </c>
       <c r="AP107">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ107">
         <v>1.7</v>
@@ -23250,10 +23277,10 @@
         <v>0.78</v>
       </c>
       <c r="AP108">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ108">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR108">
         <v>1.12</v>
@@ -23456,10 +23483,10 @@
         <v>1.13</v>
       </c>
       <c r="AP109">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ109">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR109">
         <v>1.67</v>
@@ -23584,7 +23611,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23662,10 +23689,10 @@
         <v>1.11</v>
       </c>
       <c r="AP110">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ110">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR110">
         <v>1.61</v>
@@ -23790,7 +23817,7 @@
         <v>164</v>
       </c>
       <c r="P111" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="Q111">
         <v>3.1</v>
@@ -23996,7 +24023,7 @@
         <v>165</v>
       </c>
       <c r="P112" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="Q112">
         <v>4.53</v>
@@ -24283,7 +24310,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ113">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR113">
         <v>1.71</v>
@@ -24486,7 +24513,7 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AQ114">
         <v>1</v>
@@ -24614,7 +24641,7 @@
         <v>167</v>
       </c>
       <c r="P115" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -24692,10 +24719,10 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ115">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR115">
         <v>1.44</v>
@@ -24820,7 +24847,7 @@
         <v>89</v>
       </c>
       <c r="P116" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -24898,7 +24925,7 @@
         <v>1.78</v>
       </c>
       <c r="AP116">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ116">
         <v>1.9</v>
@@ -25026,7 +25053,7 @@
         <v>168</v>
       </c>
       <c r="P117" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25104,7 +25131,7 @@
         <v>1.33</v>
       </c>
       <c r="AP117">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ117">
         <v>1.5</v>
@@ -25519,7 +25546,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ119">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR119">
         <v>1.3</v>
@@ -25644,7 +25671,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="Q120">
         <v>4.33</v>
@@ -25850,7 +25877,7 @@
         <v>171</v>
       </c>
       <c r="P121" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Q121">
         <v>2.6</v>
@@ -25931,7 +25958,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ121">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR121">
         <v>2.18</v>
@@ -26007,6 +26034,1242 @@
       </c>
       <c r="BP121">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7482789</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45725.54166666666</v>
+      </c>
+      <c r="F122">
+        <v>21</v>
+      </c>
+      <c r="G122" t="s">
+        <v>76</v>
+      </c>
+      <c r="H122" t="s">
+        <v>77</v>
+      </c>
+      <c r="I122">
+        <v>1</v>
+      </c>
+      <c r="J122">
+        <v>1</v>
+      </c>
+      <c r="K122">
+        <v>2</v>
+      </c>
+      <c r="L122">
+        <v>2</v>
+      </c>
+      <c r="M122">
+        <v>1</v>
+      </c>
+      <c r="N122">
+        <v>3</v>
+      </c>
+      <c r="O122" t="s">
+        <v>172</v>
+      </c>
+      <c r="P122" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q122">
+        <v>2.38</v>
+      </c>
+      <c r="R122">
+        <v>2.1</v>
+      </c>
+      <c r="S122">
+        <v>5.5</v>
+      </c>
+      <c r="T122">
+        <v>1.44</v>
+      </c>
+      <c r="U122">
+        <v>2.63</v>
+      </c>
+      <c r="V122">
+        <v>3.25</v>
+      </c>
+      <c r="W122">
+        <v>1.33</v>
+      </c>
+      <c r="X122">
+        <v>9</v>
+      </c>
+      <c r="Y122">
+        <v>1.07</v>
+      </c>
+      <c r="Z122">
+        <v>1.76</v>
+      </c>
+      <c r="AA122">
+        <v>3.68</v>
+      </c>
+      <c r="AB122">
+        <v>4.33</v>
+      </c>
+      <c r="AC122">
+        <v>1.06</v>
+      </c>
+      <c r="AD122">
+        <v>8.5</v>
+      </c>
+      <c r="AE122">
+        <v>1.33</v>
+      </c>
+      <c r="AF122">
+        <v>3.25</v>
+      </c>
+      <c r="AG122">
+        <v>1.94</v>
+      </c>
+      <c r="AH122">
+        <v>1.8</v>
+      </c>
+      <c r="AI122">
+        <v>1.95</v>
+      </c>
+      <c r="AJ122">
+        <v>1.8</v>
+      </c>
+      <c r="AK122">
+        <v>1.2</v>
+      </c>
+      <c r="AL122">
+        <v>1.22</v>
+      </c>
+      <c r="AM122">
+        <v>1.95</v>
+      </c>
+      <c r="AN122">
+        <v>1.1</v>
+      </c>
+      <c r="AO122">
+        <v>1</v>
+      </c>
+      <c r="AP122">
+        <v>1.27</v>
+      </c>
+      <c r="AQ122">
+        <v>0.91</v>
+      </c>
+      <c r="AR122">
+        <v>1.49</v>
+      </c>
+      <c r="AS122">
+        <v>1.13</v>
+      </c>
+      <c r="AT122">
+        <v>2.62</v>
+      </c>
+      <c r="AU122">
+        <v>12</v>
+      </c>
+      <c r="AV122">
+        <v>4</v>
+      </c>
+      <c r="AW122">
+        <v>15</v>
+      </c>
+      <c r="AX122">
+        <v>1</v>
+      </c>
+      <c r="AY122">
+        <v>30</v>
+      </c>
+      <c r="AZ122">
+        <v>5</v>
+      </c>
+      <c r="BA122">
+        <v>12</v>
+      </c>
+      <c r="BB122">
+        <v>0</v>
+      </c>
+      <c r="BC122">
+        <v>12</v>
+      </c>
+      <c r="BD122">
+        <v>1.52</v>
+      </c>
+      <c r="BE122">
+        <v>6.5</v>
+      </c>
+      <c r="BF122">
+        <v>2.8</v>
+      </c>
+      <c r="BG122">
+        <v>1.43</v>
+      </c>
+      <c r="BH122">
+        <v>2.6</v>
+      </c>
+      <c r="BI122">
+        <v>1.71</v>
+      </c>
+      <c r="BJ122">
+        <v>2</v>
+      </c>
+      <c r="BK122">
+        <v>2.12</v>
+      </c>
+      <c r="BL122">
+        <v>1.63</v>
+      </c>
+      <c r="BM122">
+        <v>2.7</v>
+      </c>
+      <c r="BN122">
+        <v>1.38</v>
+      </c>
+      <c r="BO122">
+        <v>3.65</v>
+      </c>
+      <c r="BP122">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7482790</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45725.54166666666</v>
+      </c>
+      <c r="F123">
+        <v>21</v>
+      </c>
+      <c r="G123" t="s">
+        <v>73</v>
+      </c>
+      <c r="H123" t="s">
+        <v>75</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>1</v>
+      </c>
+      <c r="K123">
+        <v>1</v>
+      </c>
+      <c r="L123">
+        <v>1</v>
+      </c>
+      <c r="M123">
+        <v>2</v>
+      </c>
+      <c r="N123">
+        <v>3</v>
+      </c>
+      <c r="O123" t="s">
+        <v>173</v>
+      </c>
+      <c r="P123" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q123">
+        <v>2.6</v>
+      </c>
+      <c r="R123">
+        <v>2.2</v>
+      </c>
+      <c r="S123">
+        <v>4.5</v>
+      </c>
+      <c r="T123">
+        <v>1.4</v>
+      </c>
+      <c r="U123">
+        <v>2.75</v>
+      </c>
+      <c r="V123">
+        <v>3</v>
+      </c>
+      <c r="W123">
+        <v>1.36</v>
+      </c>
+      <c r="X123">
+        <v>8</v>
+      </c>
+      <c r="Y123">
+        <v>1.08</v>
+      </c>
+      <c r="Z123">
+        <v>1.98</v>
+      </c>
+      <c r="AA123">
+        <v>3.38</v>
+      </c>
+      <c r="AB123">
+        <v>3.71</v>
+      </c>
+      <c r="AC123">
+        <v>1.06</v>
+      </c>
+      <c r="AD123">
+        <v>8.5</v>
+      </c>
+      <c r="AE123">
+        <v>1.33</v>
+      </c>
+      <c r="AF123">
+        <v>3.3</v>
+      </c>
+      <c r="AG123">
+        <v>1.94</v>
+      </c>
+      <c r="AH123">
+        <v>1.8</v>
+      </c>
+      <c r="AI123">
+        <v>1.8</v>
+      </c>
+      <c r="AJ123">
+        <v>1.95</v>
+      </c>
+      <c r="AK123">
+        <v>1.25</v>
+      </c>
+      <c r="AL123">
+        <v>1.25</v>
+      </c>
+      <c r="AM123">
+        <v>1.77</v>
+      </c>
+      <c r="AN123">
+        <v>1.7</v>
+      </c>
+      <c r="AO123">
+        <v>0.9</v>
+      </c>
+      <c r="AP123">
+        <v>1.55</v>
+      </c>
+      <c r="AQ123">
+        <v>1.09</v>
+      </c>
+      <c r="AR123">
+        <v>1.5</v>
+      </c>
+      <c r="AS123">
+        <v>1.19</v>
+      </c>
+      <c r="AT123">
+        <v>2.69</v>
+      </c>
+      <c r="AU123">
+        <v>5</v>
+      </c>
+      <c r="AV123">
+        <v>6</v>
+      </c>
+      <c r="AW123">
+        <v>12</v>
+      </c>
+      <c r="AX123">
+        <v>5</v>
+      </c>
+      <c r="AY123">
+        <v>19</v>
+      </c>
+      <c r="AZ123">
+        <v>12</v>
+      </c>
+      <c r="BA123">
+        <v>5</v>
+      </c>
+      <c r="BB123">
+        <v>2</v>
+      </c>
+      <c r="BC123">
+        <v>7</v>
+      </c>
+      <c r="BD123">
+        <v>1.44</v>
+      </c>
+      <c r="BE123">
+        <v>9</v>
+      </c>
+      <c r="BF123">
+        <v>3</v>
+      </c>
+      <c r="BG123">
+        <v>1.24</v>
+      </c>
+      <c r="BH123">
+        <v>3.5</v>
+      </c>
+      <c r="BI123">
+        <v>1.46</v>
+      </c>
+      <c r="BJ123">
+        <v>2.45</v>
+      </c>
+      <c r="BK123">
+        <v>1.8</v>
+      </c>
+      <c r="BL123">
+        <v>1.83</v>
+      </c>
+      <c r="BM123">
+        <v>2.37</v>
+      </c>
+      <c r="BN123">
+        <v>1.47</v>
+      </c>
+      <c r="BO123">
+        <v>3.3</v>
+      </c>
+      <c r="BP123">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="124" spans="1:68">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7482791</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45725.54166666666</v>
+      </c>
+      <c r="F124">
+        <v>21</v>
+      </c>
+      <c r="G124" t="s">
+        <v>79</v>
+      </c>
+      <c r="H124" t="s">
+        <v>81</v>
+      </c>
+      <c r="I124">
+        <v>2</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>2</v>
+      </c>
+      <c r="L124">
+        <v>2</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>2</v>
+      </c>
+      <c r="O124" t="s">
+        <v>174</v>
+      </c>
+      <c r="P124" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q124">
+        <v>2.05</v>
+      </c>
+      <c r="R124">
+        <v>2.38</v>
+      </c>
+      <c r="S124">
+        <v>6</v>
+      </c>
+      <c r="T124">
+        <v>1.33</v>
+      </c>
+      <c r="U124">
+        <v>3.25</v>
+      </c>
+      <c r="V124">
+        <v>2.63</v>
+      </c>
+      <c r="W124">
+        <v>1.44</v>
+      </c>
+      <c r="X124">
+        <v>6.5</v>
+      </c>
+      <c r="Y124">
+        <v>1.11</v>
+      </c>
+      <c r="Z124">
+        <v>1.51</v>
+      </c>
+      <c r="AA124">
+        <v>4.2</v>
+      </c>
+      <c r="AB124">
+        <v>5.8</v>
+      </c>
+      <c r="AC124">
+        <v>1.04</v>
+      </c>
+      <c r="AD124">
+        <v>10</v>
+      </c>
+      <c r="AE124">
+        <v>1.22</v>
+      </c>
+      <c r="AF124">
+        <v>4</v>
+      </c>
+      <c r="AG124">
+        <v>1.67</v>
+      </c>
+      <c r="AH124">
+        <v>2</v>
+      </c>
+      <c r="AI124">
+        <v>1.8</v>
+      </c>
+      <c r="AJ124">
+        <v>1.95</v>
+      </c>
+      <c r="AK124">
+        <v>1.11</v>
+      </c>
+      <c r="AL124">
+        <v>1.17</v>
+      </c>
+      <c r="AM124">
+        <v>2.55</v>
+      </c>
+      <c r="AN124">
+        <v>2.5</v>
+      </c>
+      <c r="AO124">
+        <v>0.8</v>
+      </c>
+      <c r="AP124">
+        <v>2.55</v>
+      </c>
+      <c r="AQ124">
+        <v>0.73</v>
+      </c>
+      <c r="AR124">
+        <v>1.58</v>
+      </c>
+      <c r="AS124">
+        <v>1.02</v>
+      </c>
+      <c r="AT124">
+        <v>2.6</v>
+      </c>
+      <c r="AU124">
+        <v>15</v>
+      </c>
+      <c r="AV124">
+        <v>3</v>
+      </c>
+      <c r="AW124">
+        <v>15</v>
+      </c>
+      <c r="AX124">
+        <v>2</v>
+      </c>
+      <c r="AY124">
+        <v>31</v>
+      </c>
+      <c r="AZ124">
+        <v>5</v>
+      </c>
+      <c r="BA124">
+        <v>12</v>
+      </c>
+      <c r="BB124">
+        <v>1</v>
+      </c>
+      <c r="BC124">
+        <v>13</v>
+      </c>
+      <c r="BD124">
+        <v>1.42</v>
+      </c>
+      <c r="BE124">
+        <v>6.75</v>
+      </c>
+      <c r="BF124">
+        <v>3.2</v>
+      </c>
+      <c r="BG124">
+        <v>1.4</v>
+      </c>
+      <c r="BH124">
+        <v>2.65</v>
+      </c>
+      <c r="BI124">
+        <v>1.66</v>
+      </c>
+      <c r="BJ124">
+        <v>2.06</v>
+      </c>
+      <c r="BK124">
+        <v>2.07</v>
+      </c>
+      <c r="BL124">
+        <v>1.66</v>
+      </c>
+      <c r="BM124">
+        <v>2.65</v>
+      </c>
+      <c r="BN124">
+        <v>1.41</v>
+      </c>
+      <c r="BO124">
+        <v>3.45</v>
+      </c>
+      <c r="BP124">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="125" spans="1:68">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>7482792</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45725.54166666666</v>
+      </c>
+      <c r="F125">
+        <v>21</v>
+      </c>
+      <c r="G125" t="s">
+        <v>71</v>
+      </c>
+      <c r="H125" t="s">
+        <v>78</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>1</v>
+      </c>
+      <c r="K125">
+        <v>1</v>
+      </c>
+      <c r="L125">
+        <v>1</v>
+      </c>
+      <c r="M125">
+        <v>1</v>
+      </c>
+      <c r="N125">
+        <v>2</v>
+      </c>
+      <c r="O125" t="s">
+        <v>175</v>
+      </c>
+      <c r="P125" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q125">
+        <v>5.5</v>
+      </c>
+      <c r="R125">
+        <v>2.3</v>
+      </c>
+      <c r="S125">
+        <v>2.2</v>
+      </c>
+      <c r="T125">
+        <v>1.36</v>
+      </c>
+      <c r="U125">
+        <v>3</v>
+      </c>
+      <c r="V125">
+        <v>2.63</v>
+      </c>
+      <c r="W125">
+        <v>1.44</v>
+      </c>
+      <c r="X125">
+        <v>7</v>
+      </c>
+      <c r="Y125">
+        <v>1.1</v>
+      </c>
+      <c r="Z125">
+        <v>5.1</v>
+      </c>
+      <c r="AA125">
+        <v>3.91</v>
+      </c>
+      <c r="AB125">
+        <v>1.62</v>
+      </c>
+      <c r="AC125">
+        <v>1.05</v>
+      </c>
+      <c r="AD125">
+        <v>9.5</v>
+      </c>
+      <c r="AE125">
+        <v>1.28</v>
+      </c>
+      <c r="AF125">
+        <v>3.55</v>
+      </c>
+      <c r="AG125">
+        <v>1.85</v>
+      </c>
+      <c r="AH125">
+        <v>1.89</v>
+      </c>
+      <c r="AI125">
+        <v>1.8</v>
+      </c>
+      <c r="AJ125">
+        <v>1.95</v>
+      </c>
+      <c r="AK125">
+        <v>2.15</v>
+      </c>
+      <c r="AL125">
+        <v>1.22</v>
+      </c>
+      <c r="AM125">
+        <v>1.15</v>
+      </c>
+      <c r="AN125">
+        <v>0.7</v>
+      </c>
+      <c r="AO125">
+        <v>1.3</v>
+      </c>
+      <c r="AP125">
+        <v>0.73</v>
+      </c>
+      <c r="AQ125">
+        <v>1.27</v>
+      </c>
+      <c r="AR125">
+        <v>1.29</v>
+      </c>
+      <c r="AS125">
+        <v>1.52</v>
+      </c>
+      <c r="AT125">
+        <v>2.81</v>
+      </c>
+      <c r="AU125">
+        <v>3</v>
+      </c>
+      <c r="AV125">
+        <v>6</v>
+      </c>
+      <c r="AW125">
+        <v>6</v>
+      </c>
+      <c r="AX125">
+        <v>12</v>
+      </c>
+      <c r="AY125">
+        <v>10</v>
+      </c>
+      <c r="AZ125">
+        <v>23</v>
+      </c>
+      <c r="BA125">
+        <v>0</v>
+      </c>
+      <c r="BB125">
+        <v>5</v>
+      </c>
+      <c r="BC125">
+        <v>5</v>
+      </c>
+      <c r="BD125">
+        <v>2.95</v>
+      </c>
+      <c r="BE125">
+        <v>6.75</v>
+      </c>
+      <c r="BF125">
+        <v>1.49</v>
+      </c>
+      <c r="BG125">
+        <v>1.37</v>
+      </c>
+      <c r="BH125">
+        <v>2.8</v>
+      </c>
+      <c r="BI125">
+        <v>1.64</v>
+      </c>
+      <c r="BJ125">
+        <v>2.1</v>
+      </c>
+      <c r="BK125">
+        <v>2.02</v>
+      </c>
+      <c r="BL125">
+        <v>1.7</v>
+      </c>
+      <c r="BM125">
+        <v>2.55</v>
+      </c>
+      <c r="BN125">
+        <v>1.44</v>
+      </c>
+      <c r="BO125">
+        <v>3.4</v>
+      </c>
+      <c r="BP125">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="126" spans="1:68">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>7482793</v>
+      </c>
+      <c r="C126" t="s">
+        <v>68</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45725.54166666666</v>
+      </c>
+      <c r="F126">
+        <v>21</v>
+      </c>
+      <c r="G126" t="s">
+        <v>70</v>
+      </c>
+      <c r="H126" t="s">
+        <v>80</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>1</v>
+      </c>
+      <c r="M126">
+        <v>2</v>
+      </c>
+      <c r="N126">
+        <v>3</v>
+      </c>
+      <c r="O126" t="s">
+        <v>87</v>
+      </c>
+      <c r="P126" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q126">
+        <v>5</v>
+      </c>
+      <c r="R126">
+        <v>2.38</v>
+      </c>
+      <c r="S126">
+        <v>2.2</v>
+      </c>
+      <c r="T126">
+        <v>1.33</v>
+      </c>
+      <c r="U126">
+        <v>3.25</v>
+      </c>
+      <c r="V126">
+        <v>2.5</v>
+      </c>
+      <c r="W126">
+        <v>1.5</v>
+      </c>
+      <c r="X126">
+        <v>6.5</v>
+      </c>
+      <c r="Y126">
+        <v>1.11</v>
+      </c>
+      <c r="Z126">
+        <v>5</v>
+      </c>
+      <c r="AA126">
+        <v>4</v>
+      </c>
+      <c r="AB126">
+        <v>1.61</v>
+      </c>
+      <c r="AC126">
+        <v>1.04</v>
+      </c>
+      <c r="AD126">
+        <v>10</v>
+      </c>
+      <c r="AE126">
+        <v>1.2</v>
+      </c>
+      <c r="AF126">
+        <v>4.33</v>
+      </c>
+      <c r="AG126">
+        <v>1.6</v>
+      </c>
+      <c r="AH126">
+        <v>2.15</v>
+      </c>
+      <c r="AI126">
+        <v>1.75</v>
+      </c>
+      <c r="AJ126">
+        <v>2</v>
+      </c>
+      <c r="AK126">
+        <v>2.3</v>
+      </c>
+      <c r="AL126">
+        <v>1.18</v>
+      </c>
+      <c r="AM126">
+        <v>1.15</v>
+      </c>
+      <c r="AN126">
+        <v>0.7</v>
+      </c>
+      <c r="AO126">
+        <v>1.7</v>
+      </c>
+      <c r="AP126">
+        <v>0.64</v>
+      </c>
+      <c r="AQ126">
+        <v>1.82</v>
+      </c>
+      <c r="AR126">
+        <v>1.33</v>
+      </c>
+      <c r="AS126">
+        <v>1.38</v>
+      </c>
+      <c r="AT126">
+        <v>2.71</v>
+      </c>
+      <c r="AU126">
+        <v>4</v>
+      </c>
+      <c r="AV126">
+        <v>5</v>
+      </c>
+      <c r="AW126">
+        <v>6</v>
+      </c>
+      <c r="AX126">
+        <v>7</v>
+      </c>
+      <c r="AY126">
+        <v>11</v>
+      </c>
+      <c r="AZ126">
+        <v>13</v>
+      </c>
+      <c r="BA126">
+        <v>3</v>
+      </c>
+      <c r="BB126">
+        <v>6</v>
+      </c>
+      <c r="BC126">
+        <v>9</v>
+      </c>
+      <c r="BD126">
+        <v>2.95</v>
+      </c>
+      <c r="BE126">
+        <v>6.75</v>
+      </c>
+      <c r="BF126">
+        <v>1.48</v>
+      </c>
+      <c r="BG126">
+        <v>1.34</v>
+      </c>
+      <c r="BH126">
+        <v>2.9</v>
+      </c>
+      <c r="BI126">
+        <v>1.58</v>
+      </c>
+      <c r="BJ126">
+        <v>2.2</v>
+      </c>
+      <c r="BK126">
+        <v>1.94</v>
+      </c>
+      <c r="BL126">
+        <v>1.76</v>
+      </c>
+      <c r="BM126">
+        <v>2.45</v>
+      </c>
+      <c r="BN126">
+        <v>1.48</v>
+      </c>
+      <c r="BO126">
+        <v>3.2</v>
+      </c>
+      <c r="BP126">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7482794</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45725.57291666666</v>
+      </c>
+      <c r="F127">
+        <v>21</v>
+      </c>
+      <c r="G127" t="s">
+        <v>72</v>
+      </c>
+      <c r="H127" t="s">
+        <v>74</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>2</v>
+      </c>
+      <c r="M127">
+        <v>1</v>
+      </c>
+      <c r="N127">
+        <v>3</v>
+      </c>
+      <c r="O127" t="s">
+        <v>176</v>
+      </c>
+      <c r="P127" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q127">
+        <v>4.5</v>
+      </c>
+      <c r="R127">
+        <v>2.3</v>
+      </c>
+      <c r="S127">
+        <v>2.38</v>
+      </c>
+      <c r="T127">
+        <v>1.33</v>
+      </c>
+      <c r="U127">
+        <v>3.25</v>
+      </c>
+      <c r="V127">
+        <v>2.63</v>
+      </c>
+      <c r="W127">
+        <v>1.44</v>
+      </c>
+      <c r="X127">
+        <v>6.5</v>
+      </c>
+      <c r="Y127">
+        <v>1.11</v>
+      </c>
+      <c r="Z127">
+        <v>4.33</v>
+      </c>
+      <c r="AA127">
+        <v>3.74</v>
+      </c>
+      <c r="AB127">
+        <v>1.75</v>
+      </c>
+      <c r="AC127">
+        <v>1.05</v>
+      </c>
+      <c r="AD127">
+        <v>9.5</v>
+      </c>
+      <c r="AE127">
+        <v>1.25</v>
+      </c>
+      <c r="AF127">
+        <v>3.85</v>
+      </c>
+      <c r="AG127">
+        <v>1.7</v>
+      </c>
+      <c r="AH127">
+        <v>1.95</v>
+      </c>
+      <c r="AI127">
+        <v>1.7</v>
+      </c>
+      <c r="AJ127">
+        <v>2.05</v>
+      </c>
+      <c r="AK127">
+        <v>2</v>
+      </c>
+      <c r="AL127">
+        <v>1.22</v>
+      </c>
+      <c r="AM127">
+        <v>1.2</v>
+      </c>
+      <c r="AN127">
+        <v>1.3</v>
+      </c>
+      <c r="AO127">
+        <v>0.9</v>
+      </c>
+      <c r="AP127">
+        <v>1.45</v>
+      </c>
+      <c r="AQ127">
+        <v>0.82</v>
+      </c>
+      <c r="AR127">
+        <v>1.17</v>
+      </c>
+      <c r="AS127">
+        <v>1.56</v>
+      </c>
+      <c r="AT127">
+        <v>2.73</v>
+      </c>
+      <c r="AU127">
+        <v>4</v>
+      </c>
+      <c r="AV127">
+        <v>4</v>
+      </c>
+      <c r="AW127">
+        <v>3</v>
+      </c>
+      <c r="AX127">
+        <v>5</v>
+      </c>
+      <c r="AY127">
+        <v>8</v>
+      </c>
+      <c r="AZ127">
+        <v>11</v>
+      </c>
+      <c r="BA127">
+        <v>6</v>
+      </c>
+      <c r="BB127">
+        <v>3</v>
+      </c>
+      <c r="BC127">
+        <v>9</v>
+      </c>
+      <c r="BD127">
+        <v>2.65</v>
+      </c>
+      <c r="BE127">
+        <v>6.75</v>
+      </c>
+      <c r="BF127">
+        <v>1.57</v>
+      </c>
+      <c r="BG127">
+        <v>1.36</v>
+      </c>
+      <c r="BH127">
+        <v>2.8</v>
+      </c>
+      <c r="BI127">
+        <v>1.62</v>
+      </c>
+      <c r="BJ127">
+        <v>2.12</v>
+      </c>
+      <c r="BK127">
+        <v>2</v>
+      </c>
+      <c r="BL127">
+        <v>1.71</v>
+      </c>
+      <c r="BM127">
+        <v>2.55</v>
+      </c>
+      <c r="BN127">
+        <v>1.44</v>
+      </c>
+      <c r="BO127">
+        <v>3.4</v>
+      </c>
+      <c r="BP127">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -26815,10 +26815,10 @@
         <v>0</v>
       </c>
       <c r="BB125">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC125">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD125">
         <v>2.95</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="251">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -547,6 +547,21 @@
     <t>['49', '74']</t>
   </si>
   <si>
+    <t>['13']</t>
+  </si>
+  <si>
+    <t>['31', '50', '83', '90+6']</t>
+  </si>
+  <si>
+    <t>['5', '90+5']</t>
+  </si>
+  <si>
+    <t>['23', '32', '44']</t>
+  </si>
+  <si>
+    <t>['16', '48', '70', '86']</t>
+  </si>
+  <si>
     <t>['4', '6', '45+2']</t>
   </si>
   <si>
@@ -746,6 +761,12 @@
   </si>
   <si>
     <t>['84']</t>
+  </si>
+  <si>
+    <t>['77', '85']</t>
+  </si>
+  <si>
+    <t>['11', '14']</t>
   </si>
 </sst>
 </file>
@@ -1107,7 +1128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP127"/>
+  <dimension ref="A1:BP132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1363,7 +1384,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="Q2">
         <v>7</v>
@@ -1569,7 +1590,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1775,7 +1796,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -1856,7 +1877,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ4">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2265,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ6">
         <v>1.82</v>
@@ -2471,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ7">
         <v>1.5</v>
@@ -2599,7 +2620,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="Q8">
         <v>2.1</v>
@@ -2680,7 +2701,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ8">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2886,7 +2907,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ9">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3011,7 +3032,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="Q10">
         <v>1.67</v>
@@ -3089,7 +3110,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ10">
         <v>1.09</v>
@@ -3298,7 +3319,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ11">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3501,10 +3522,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3707,7 +3728,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ13">
         <v>0.82</v>
@@ -3835,7 +3856,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3913,7 +3934,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ14">
         <v>1.82</v>
@@ -4041,7 +4062,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4247,7 +4268,7 @@
         <v>89</v>
       </c>
       <c r="P16" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="Q16">
         <v>3.8</v>
@@ -4531,7 +4552,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ17">
         <v>0.91</v>
@@ -4740,7 +4761,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ18">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR18">
         <v>1.26</v>
@@ -5071,7 +5092,7 @@
         <v>89</v>
       </c>
       <c r="P20" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5277,7 +5298,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="Q21">
         <v>2.03</v>
@@ -5355,10 +5376,10 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ21">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR21">
         <v>2.09</v>
@@ -5483,7 +5504,7 @@
         <v>99</v>
       </c>
       <c r="P22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="Q22">
         <v>2.4</v>
@@ -5564,7 +5585,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ22">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5689,7 +5710,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5770,7 +5791,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ23">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR23">
         <v>1.73</v>
@@ -5973,7 +5994,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ24">
         <v>0.82</v>
@@ -6182,7 +6203,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ25">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR25">
         <v>1.32</v>
@@ -6307,7 +6328,7 @@
         <v>103</v>
       </c>
       <c r="P26" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6385,7 +6406,7 @@
         <v>0.5</v>
       </c>
       <c r="AP26">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ26">
         <v>1.09</v>
@@ -6513,7 +6534,7 @@
         <v>104</v>
       </c>
       <c r="P27" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6591,7 +6612,7 @@
         <v>1.5</v>
       </c>
       <c r="AP27">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ27">
         <v>0.91</v>
@@ -6719,7 +6740,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -6797,7 +6818,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ28">
         <v>1.27</v>
@@ -7131,7 +7152,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="Q30">
         <v>2.3</v>
@@ -7212,7 +7233,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ30">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR30">
         <v>1.52</v>
@@ -7621,10 +7642,10 @@
         <v>1.5</v>
       </c>
       <c r="AP32">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ32">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR32">
         <v>1.09</v>
@@ -7749,7 +7770,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -7830,7 +7851,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ33">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR33">
         <v>1.22</v>
@@ -7955,7 +7976,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="Q34">
         <v>2.1</v>
@@ -8036,7 +8057,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ34">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR34">
         <v>1.35</v>
@@ -8161,7 +8182,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8239,10 +8260,10 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR35">
         <v>1.2</v>
@@ -8367,7 +8388,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="Q36">
         <v>2.75</v>
@@ -8779,7 +8800,7 @@
         <v>89</v>
       </c>
       <c r="P38" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="Q38">
         <v>2.2</v>
@@ -8857,10 +8878,10 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ38">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR38">
         <v>1.97</v>
@@ -8985,7 +9006,7 @@
         <v>113</v>
       </c>
       <c r="P39" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9063,7 +9084,7 @@
         <v>0.67</v>
       </c>
       <c r="AP39">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ39">
         <v>1.5</v>
@@ -9191,7 +9212,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="Q40">
         <v>3.6</v>
@@ -9603,7 +9624,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9681,7 +9702,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ42">
         <v>1.82</v>
@@ -9809,7 +9830,7 @@
         <v>117</v>
       </c>
       <c r="P43" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -9887,10 +9908,10 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ43">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR43">
         <v>1.82</v>
@@ -10093,7 +10114,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ44">
         <v>1.5</v>
@@ -10302,7 +10323,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ45">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR45">
         <v>1.2</v>
@@ -10427,7 +10448,7 @@
         <v>120</v>
       </c>
       <c r="P46" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10633,7 +10654,7 @@
         <v>89</v>
       </c>
       <c r="P47" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10839,7 +10860,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -10920,7 +10941,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR48">
         <v>1.74</v>
@@ -11126,7 +11147,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ49">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR49">
         <v>1.83</v>
@@ -11663,7 +11684,7 @@
         <v>89</v>
       </c>
       <c r="P52" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -11947,7 +11968,7 @@
         <v>1.75</v>
       </c>
       <c r="AP53">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ53">
         <v>1.27</v>
@@ -12075,7 +12096,7 @@
         <v>89</v>
       </c>
       <c r="P54" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12153,10 +12174,10 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ54">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR54">
         <v>1.29</v>
@@ -12359,10 +12380,10 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ55">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR55">
         <v>2.36</v>
@@ -12487,7 +12508,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="Q56">
         <v>1.95</v>
@@ -12565,10 +12586,10 @@
         <v>0.4</v>
       </c>
       <c r="AP56">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ56">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR56">
         <v>1.69</v>
@@ -12693,7 +12714,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12771,7 +12792,7 @@
         <v>0.4</v>
       </c>
       <c r="AP57">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ57">
         <v>1.5</v>
@@ -12899,7 +12920,7 @@
         <v>109</v>
       </c>
       <c r="P58" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="Q58">
         <v>4</v>
@@ -12980,7 +13001,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ58">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR58">
         <v>1</v>
@@ -13105,7 +13126,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="Q59">
         <v>2.1</v>
@@ -13183,10 +13204,10 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ59">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR59">
         <v>1.71</v>
@@ -13723,7 +13744,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -14341,7 +14362,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="Q65">
         <v>3.25</v>
@@ -14547,7 +14568,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="Q66">
         <v>2.88</v>
@@ -14625,7 +14646,7 @@
         <v>1.2</v>
       </c>
       <c r="AP66">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ66">
         <v>0.82</v>
@@ -14831,10 +14852,10 @@
         <v>0.33</v>
       </c>
       <c r="AP67">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ67">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR67">
         <v>2.3</v>
@@ -14959,7 +14980,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="Q68">
         <v>2.5</v>
@@ -15040,7 +15061,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ68">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR68">
         <v>1.38</v>
@@ -15246,7 +15267,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ69">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR69">
         <v>0.89</v>
@@ -15449,10 +15470,10 @@
         <v>1.8</v>
       </c>
       <c r="AP70">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ70">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR70">
         <v>1.35</v>
@@ -15783,7 +15804,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16195,7 +16216,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="Q74">
         <v>3.75</v>
@@ -16479,7 +16500,7 @@
         <v>1.33</v>
       </c>
       <c r="AP75">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ75">
         <v>1.27</v>
@@ -16607,7 +16628,7 @@
         <v>142</v>
       </c>
       <c r="P76" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16688,7 +16709,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ76">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR76">
         <v>1.31</v>
@@ -16891,7 +16912,7 @@
         <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ77">
         <v>0.73</v>
@@ -17225,7 +17246,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="Q79">
         <v>2.2</v>
@@ -17303,10 +17324,10 @@
         <v>1.67</v>
       </c>
       <c r="AP79">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ79">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR79">
         <v>2.16</v>
@@ -17509,7 +17530,7 @@
         <v>1.17</v>
       </c>
       <c r="AP80">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ80">
         <v>0.73</v>
@@ -17637,7 +17658,7 @@
         <v>146</v>
       </c>
       <c r="P81" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -17715,10 +17736,10 @@
         <v>0.43</v>
       </c>
       <c r="AP81">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ81">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR81">
         <v>1.31</v>
@@ -17924,7 +17945,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ82">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR82">
         <v>1.54</v>
@@ -18130,7 +18151,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR83">
         <v>1.76</v>
@@ -18255,7 +18276,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="Q84">
         <v>5.5</v>
@@ -18461,7 +18482,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="Q85">
         <v>3.4</v>
@@ -18542,7 +18563,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ85">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR85">
         <v>1.46</v>
@@ -18667,7 +18688,7 @@
         <v>120</v>
       </c>
       <c r="P86" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="Q86">
         <v>4.75</v>
@@ -18873,7 +18894,7 @@
         <v>89</v>
       </c>
       <c r="P87" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="Q87">
         <v>2.75</v>
@@ -18951,7 +18972,7 @@
         <v>0.86</v>
       </c>
       <c r="AP87">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ87">
         <v>0.91</v>
@@ -19157,7 +19178,7 @@
         <v>0.71</v>
       </c>
       <c r="AP88">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ88">
         <v>1.09</v>
@@ -19285,7 +19306,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19569,10 +19590,10 @@
         <v>0.83</v>
       </c>
       <c r="AP90">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR90">
         <v>2.08</v>
@@ -19697,7 +19718,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -19778,7 +19799,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ91">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR91">
         <v>1.53</v>
@@ -19903,7 +19924,7 @@
         <v>153</v>
       </c>
       <c r="P92" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="Q92">
         <v>2.4</v>
@@ -19981,7 +20002,7 @@
         <v>1.14</v>
       </c>
       <c r="AP92">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ92">
         <v>0.82</v>
@@ -20109,7 +20130,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Q93">
         <v>6</v>
@@ -20315,7 +20336,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="Q94">
         <v>2.6</v>
@@ -20393,7 +20414,7 @@
         <v>1</v>
       </c>
       <c r="AP94">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ94">
         <v>0.73</v>
@@ -20521,7 +20542,7 @@
         <v>89</v>
       </c>
       <c r="P95" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20602,7 +20623,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ95">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR95">
         <v>1.42</v>
@@ -20808,7 +20829,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ96">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR96">
         <v>1.72</v>
@@ -21011,7 +21032,7 @@
         <v>0.88</v>
       </c>
       <c r="AP97">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ97">
         <v>0.73</v>
@@ -21139,7 +21160,7 @@
         <v>157</v>
       </c>
       <c r="P98" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="Q98">
         <v>2.5</v>
@@ -21217,7 +21238,7 @@
         <v>1.38</v>
       </c>
       <c r="AP98">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ98">
         <v>1.5</v>
@@ -21345,7 +21366,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="Q99">
         <v>3.1</v>
@@ -21426,7 +21447,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ99">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR99">
         <v>1.21</v>
@@ -21551,7 +21572,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="Q100">
         <v>2.3</v>
@@ -21629,10 +21650,10 @@
         <v>1.71</v>
       </c>
       <c r="AP100">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ100">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR100">
         <v>1.69</v>
@@ -21835,7 +21856,7 @@
         <v>1.13</v>
       </c>
       <c r="AP101">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ101">
         <v>1.27</v>
@@ -22044,7 +22065,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ102">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR102">
         <v>0.9</v>
@@ -22375,7 +22396,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Q104">
         <v>1.67</v>
@@ -22453,7 +22474,7 @@
         <v>1.13</v>
       </c>
       <c r="AP104">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ104">
         <v>0.91</v>
@@ -22787,7 +22808,7 @@
         <v>102</v>
       </c>
       <c r="P106" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="Q106">
         <v>2.75</v>
@@ -22865,10 +22886,10 @@
         <v>0.5</v>
       </c>
       <c r="AP106">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ106">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR106">
         <v>1.34</v>
@@ -23074,7 +23095,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ107">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR107">
         <v>1.33</v>
@@ -23611,7 +23632,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23817,7 +23838,7 @@
         <v>164</v>
       </c>
       <c r="P111" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Q111">
         <v>3.1</v>
@@ -23895,10 +23916,10 @@
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ111">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR111">
         <v>1.32</v>
@@ -24023,7 +24044,7 @@
         <v>165</v>
       </c>
       <c r="P112" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="Q112">
         <v>4.53</v>
@@ -24104,7 +24125,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ112">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR112">
         <v>1.03</v>
@@ -24307,7 +24328,7 @@
         <v>1</v>
       </c>
       <c r="AP113">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ113">
         <v>1.09</v>
@@ -24516,7 +24537,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ114">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR114">
         <v>1.24</v>
@@ -24641,7 +24662,7 @@
         <v>167</v>
       </c>
       <c r="P115" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -24847,7 +24868,7 @@
         <v>89</v>
       </c>
       <c r="P116" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -24928,7 +24949,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ116">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR116">
         <v>1.19</v>
@@ -25053,7 +25074,7 @@
         <v>168</v>
       </c>
       <c r="P117" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25337,10 +25358,10 @@
         <v>0.78</v>
       </c>
       <c r="AP118">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ118">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR118">
         <v>1.66</v>
@@ -25543,7 +25564,7 @@
         <v>1.11</v>
       </c>
       <c r="AP119">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ119">
         <v>0.91</v>
@@ -25671,7 +25692,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="Q120">
         <v>4.33</v>
@@ -25749,10 +25770,10 @@
         <v>1.56</v>
       </c>
       <c r="AP120">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ120">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR120">
         <v>1.39</v>
@@ -25877,7 +25898,7 @@
         <v>171</v>
       </c>
       <c r="P121" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="Q121">
         <v>2.6</v>
@@ -25955,7 +25976,7 @@
         <v>1.89</v>
       </c>
       <c r="AP121">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ121">
         <v>1.82</v>
@@ -26083,7 +26104,7 @@
         <v>172</v>
       </c>
       <c r="P122" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="Q122">
         <v>2.38</v>
@@ -26289,7 +26310,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="Q123">
         <v>2.6</v>
@@ -26701,7 +26722,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="Q125">
         <v>5.5</v>
@@ -26907,7 +26928,7 @@
         <v>87</v>
       </c>
       <c r="P126" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27113,7 +27134,7 @@
         <v>176</v>
       </c>
       <c r="P127" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="Q127">
         <v>4.5</v>
@@ -27270,6 +27291,1036 @@
       </c>
       <c r="BP127">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7482795</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45732.54166666666</v>
+      </c>
+      <c r="F128">
+        <v>22</v>
+      </c>
+      <c r="G128" t="s">
+        <v>78</v>
+      </c>
+      <c r="H128" t="s">
+        <v>73</v>
+      </c>
+      <c r="I128">
+        <v>1</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>1</v>
+      </c>
+      <c r="L128">
+        <v>1</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>1</v>
+      </c>
+      <c r="O128" t="s">
+        <v>177</v>
+      </c>
+      <c r="P128" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q128">
+        <v>2.1</v>
+      </c>
+      <c r="R128">
+        <v>2.38</v>
+      </c>
+      <c r="S128">
+        <v>5.5</v>
+      </c>
+      <c r="T128">
+        <v>1.33</v>
+      </c>
+      <c r="U128">
+        <v>3.25</v>
+      </c>
+      <c r="V128">
+        <v>2.5</v>
+      </c>
+      <c r="W128">
+        <v>1.5</v>
+      </c>
+      <c r="X128">
+        <v>6.5</v>
+      </c>
+      <c r="Y128">
+        <v>1.11</v>
+      </c>
+      <c r="Z128">
+        <v>1.66</v>
+      </c>
+      <c r="AA128">
+        <v>3.98</v>
+      </c>
+      <c r="AB128">
+        <v>4.6</v>
+      </c>
+      <c r="AC128">
+        <v>1.01</v>
+      </c>
+      <c r="AD128">
+        <v>13.5</v>
+      </c>
+      <c r="AE128">
+        <v>1.21</v>
+      </c>
+      <c r="AF128">
+        <v>4.43</v>
+      </c>
+      <c r="AG128">
+        <v>1.61</v>
+      </c>
+      <c r="AH128">
+        <v>2.05</v>
+      </c>
+      <c r="AI128">
+        <v>1.75</v>
+      </c>
+      <c r="AJ128">
+        <v>2</v>
+      </c>
+      <c r="AK128">
+        <v>1.17</v>
+      </c>
+      <c r="AL128">
+        <v>1.22</v>
+      </c>
+      <c r="AM128">
+        <v>2.3</v>
+      </c>
+      <c r="AN128">
+        <v>2.1</v>
+      </c>
+      <c r="AO128">
+        <v>1.9</v>
+      </c>
+      <c r="AP128">
+        <v>2.18</v>
+      </c>
+      <c r="AQ128">
+        <v>1.73</v>
+      </c>
+      <c r="AR128">
+        <v>2.23</v>
+      </c>
+      <c r="AS128">
+        <v>1.54</v>
+      </c>
+      <c r="AT128">
+        <v>3.77</v>
+      </c>
+      <c r="AU128">
+        <v>4</v>
+      </c>
+      <c r="AV128">
+        <v>2</v>
+      </c>
+      <c r="AW128">
+        <v>5</v>
+      </c>
+      <c r="AX128">
+        <v>0</v>
+      </c>
+      <c r="AY128">
+        <v>9</v>
+      </c>
+      <c r="AZ128">
+        <v>2</v>
+      </c>
+      <c r="BA128">
+        <v>4</v>
+      </c>
+      <c r="BB128">
+        <v>5</v>
+      </c>
+      <c r="BC128">
+        <v>9</v>
+      </c>
+      <c r="BD128">
+        <v>1.39</v>
+      </c>
+      <c r="BE128">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF128">
+        <v>3.78</v>
+      </c>
+      <c r="BG128">
+        <v>1.18</v>
+      </c>
+      <c r="BH128">
+        <v>3.84</v>
+      </c>
+      <c r="BI128">
+        <v>1.38</v>
+      </c>
+      <c r="BJ128">
+        <v>2.71</v>
+      </c>
+      <c r="BK128">
+        <v>1.7</v>
+      </c>
+      <c r="BL128">
+        <v>2.12</v>
+      </c>
+      <c r="BM128">
+        <v>2.13</v>
+      </c>
+      <c r="BN128">
+        <v>1.69</v>
+      </c>
+      <c r="BO128">
+        <v>2.74</v>
+      </c>
+      <c r="BP128">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7482796</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45732.54166666666</v>
+      </c>
+      <c r="F129">
+        <v>22</v>
+      </c>
+      <c r="G129" t="s">
+        <v>80</v>
+      </c>
+      <c r="H129" t="s">
+        <v>76</v>
+      </c>
+      <c r="I129">
+        <v>1</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>1</v>
+      </c>
+      <c r="L129">
+        <v>4</v>
+      </c>
+      <c r="M129">
+        <v>2</v>
+      </c>
+      <c r="N129">
+        <v>6</v>
+      </c>
+      <c r="O129" t="s">
+        <v>178</v>
+      </c>
+      <c r="P129" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q129">
+        <v>2.6</v>
+      </c>
+      <c r="R129">
+        <v>2.2</v>
+      </c>
+      <c r="S129">
+        <v>4.33</v>
+      </c>
+      <c r="T129">
+        <v>1.36</v>
+      </c>
+      <c r="U129">
+        <v>3</v>
+      </c>
+      <c r="V129">
+        <v>2.75</v>
+      </c>
+      <c r="W129">
+        <v>1.4</v>
+      </c>
+      <c r="X129">
+        <v>8</v>
+      </c>
+      <c r="Y129">
+        <v>1.08</v>
+      </c>
+      <c r="Z129">
+        <v>1.86</v>
+      </c>
+      <c r="AA129">
+        <v>3.55</v>
+      </c>
+      <c r="AB129">
+        <v>3.98</v>
+      </c>
+      <c r="AC129">
+        <v>1.01</v>
+      </c>
+      <c r="AD129">
+        <v>12</v>
+      </c>
+      <c r="AE129">
+        <v>1.26</v>
+      </c>
+      <c r="AF129">
+        <v>3.79</v>
+      </c>
+      <c r="AG129">
+        <v>1.85</v>
+      </c>
+      <c r="AH129">
+        <v>1.89</v>
+      </c>
+      <c r="AI129">
+        <v>1.75</v>
+      </c>
+      <c r="AJ129">
+        <v>2</v>
+      </c>
+      <c r="AK129">
+        <v>1.29</v>
+      </c>
+      <c r="AL129">
+        <v>1.3</v>
+      </c>
+      <c r="AM129">
+        <v>1.75</v>
+      </c>
+      <c r="AN129">
+        <v>2.3</v>
+      </c>
+      <c r="AO129">
+        <v>1.7</v>
+      </c>
+      <c r="AP129">
+        <v>2.36</v>
+      </c>
+      <c r="AQ129">
+        <v>1.55</v>
+      </c>
+      <c r="AR129">
+        <v>1.73</v>
+      </c>
+      <c r="AS129">
+        <v>1.16</v>
+      </c>
+      <c r="AT129">
+        <v>2.89</v>
+      </c>
+      <c r="AU129">
+        <v>9</v>
+      </c>
+      <c r="AV129">
+        <v>5</v>
+      </c>
+      <c r="AW129">
+        <v>11</v>
+      </c>
+      <c r="AX129">
+        <v>3</v>
+      </c>
+      <c r="AY129">
+        <v>24</v>
+      </c>
+      <c r="AZ129">
+        <v>9</v>
+      </c>
+      <c r="BA129">
+        <v>9</v>
+      </c>
+      <c r="BB129">
+        <v>4</v>
+      </c>
+      <c r="BC129">
+        <v>13</v>
+      </c>
+      <c r="BD129">
+        <v>1.51</v>
+      </c>
+      <c r="BE129">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF129">
+        <v>3.24</v>
+      </c>
+      <c r="BG129">
+        <v>1.28</v>
+      </c>
+      <c r="BH129">
+        <v>3.08</v>
+      </c>
+      <c r="BI129">
+        <v>1.57</v>
+      </c>
+      <c r="BJ129">
+        <v>2.34</v>
+      </c>
+      <c r="BK129">
+        <v>1.95</v>
+      </c>
+      <c r="BL129">
+        <v>1.84</v>
+      </c>
+      <c r="BM129">
+        <v>2.49</v>
+      </c>
+      <c r="BN129">
+        <v>1.5</v>
+      </c>
+      <c r="BO129">
+        <v>3.42</v>
+      </c>
+      <c r="BP129">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7482797</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45732.54166666666</v>
+      </c>
+      <c r="F130">
+        <v>22</v>
+      </c>
+      <c r="G130" t="s">
+        <v>81</v>
+      </c>
+      <c r="H130" t="s">
+        <v>71</v>
+      </c>
+      <c r="I130">
+        <v>1</v>
+      </c>
+      <c r="J130">
+        <v>2</v>
+      </c>
+      <c r="K130">
+        <v>3</v>
+      </c>
+      <c r="L130">
+        <v>2</v>
+      </c>
+      <c r="M130">
+        <v>2</v>
+      </c>
+      <c r="N130">
+        <v>4</v>
+      </c>
+      <c r="O130" t="s">
+        <v>179</v>
+      </c>
+      <c r="P130" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q130">
+        <v>3.5</v>
+      </c>
+      <c r="R130">
+        <v>2.05</v>
+      </c>
+      <c r="S130">
+        <v>3.25</v>
+      </c>
+      <c r="T130">
+        <v>1.5</v>
+      </c>
+      <c r="U130">
+        <v>2.5</v>
+      </c>
+      <c r="V130">
+        <v>3.4</v>
+      </c>
+      <c r="W130">
+        <v>1.3</v>
+      </c>
+      <c r="X130">
+        <v>10</v>
+      </c>
+      <c r="Y130">
+        <v>1.06</v>
+      </c>
+      <c r="Z130">
+        <v>2.63</v>
+      </c>
+      <c r="AA130">
+        <v>3.21</v>
+      </c>
+      <c r="AB130">
+        <v>2.64</v>
+      </c>
+      <c r="AC130">
+        <v>1.03</v>
+      </c>
+      <c r="AD130">
+        <v>7.2</v>
+      </c>
+      <c r="AE130">
+        <v>1.38</v>
+      </c>
+      <c r="AF130">
+        <v>3.02</v>
+      </c>
+      <c r="AG130">
+        <v>2</v>
+      </c>
+      <c r="AH130">
+        <v>1.65</v>
+      </c>
+      <c r="AI130">
+        <v>1.95</v>
+      </c>
+      <c r="AJ130">
+        <v>1.8</v>
+      </c>
+      <c r="AK130">
+        <v>1.49</v>
+      </c>
+      <c r="AL130">
+        <v>1.32</v>
+      </c>
+      <c r="AM130">
+        <v>1.43</v>
+      </c>
+      <c r="AN130">
+        <v>1.2</v>
+      </c>
+      <c r="AO130">
+        <v>0.7</v>
+      </c>
+      <c r="AP130">
+        <v>1.18</v>
+      </c>
+      <c r="AQ130">
+        <v>0.73</v>
+      </c>
+      <c r="AR130">
+        <v>1.34</v>
+      </c>
+      <c r="AS130">
+        <v>0.98</v>
+      </c>
+      <c r="AT130">
+        <v>2.32</v>
+      </c>
+      <c r="AU130">
+        <v>7</v>
+      </c>
+      <c r="AV130">
+        <v>5</v>
+      </c>
+      <c r="AW130">
+        <v>4</v>
+      </c>
+      <c r="AX130">
+        <v>5</v>
+      </c>
+      <c r="AY130">
+        <v>15</v>
+      </c>
+      <c r="AZ130">
+        <v>12</v>
+      </c>
+      <c r="BA130">
+        <v>6</v>
+      </c>
+      <c r="BB130">
+        <v>6</v>
+      </c>
+      <c r="BC130">
+        <v>12</v>
+      </c>
+      <c r="BD130">
+        <v>2.05</v>
+      </c>
+      <c r="BE130">
+        <v>6.35</v>
+      </c>
+      <c r="BF130">
+        <v>2.23</v>
+      </c>
+      <c r="BG130">
+        <v>1.31</v>
+      </c>
+      <c r="BH130">
+        <v>2.92</v>
+      </c>
+      <c r="BI130">
+        <v>1.65</v>
+      </c>
+      <c r="BJ130">
+        <v>2.2</v>
+      </c>
+      <c r="BK130">
+        <v>2.06</v>
+      </c>
+      <c r="BL130">
+        <v>1.74</v>
+      </c>
+      <c r="BM130">
+        <v>2.67</v>
+      </c>
+      <c r="BN130">
+        <v>1.39</v>
+      </c>
+      <c r="BO130">
+        <v>3.68</v>
+      </c>
+      <c r="BP130">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7482798</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45732.54166666666</v>
+      </c>
+      <c r="F131">
+        <v>22</v>
+      </c>
+      <c r="G131" t="s">
+        <v>74</v>
+      </c>
+      <c r="H131" t="s">
+        <v>70</v>
+      </c>
+      <c r="I131">
+        <v>3</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>3</v>
+      </c>
+      <c r="L131">
+        <v>3</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>3</v>
+      </c>
+      <c r="O131" t="s">
+        <v>180</v>
+      </c>
+      <c r="P131" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q131">
+        <v>1.83</v>
+      </c>
+      <c r="R131">
+        <v>2.5</v>
+      </c>
+      <c r="S131">
+        <v>7.5</v>
+      </c>
+      <c r="T131">
+        <v>1.3</v>
+      </c>
+      <c r="U131">
+        <v>3.4</v>
+      </c>
+      <c r="V131">
+        <v>2.5</v>
+      </c>
+      <c r="W131">
+        <v>1.5</v>
+      </c>
+      <c r="X131">
+        <v>6</v>
+      </c>
+      <c r="Y131">
+        <v>1.13</v>
+      </c>
+      <c r="Z131">
+        <v>1.32</v>
+      </c>
+      <c r="AA131">
+        <v>5.1</v>
+      </c>
+      <c r="AB131">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AC131">
+        <v>1.02</v>
+      </c>
+      <c r="AD131">
+        <v>15.5</v>
+      </c>
+      <c r="AE131">
+        <v>1.2</v>
+      </c>
+      <c r="AF131">
+        <v>4.45</v>
+      </c>
+      <c r="AG131">
+        <v>1.6</v>
+      </c>
+      <c r="AH131">
+        <v>2.15</v>
+      </c>
+      <c r="AI131">
+        <v>1.95</v>
+      </c>
+      <c r="AJ131">
+        <v>1.8</v>
+      </c>
+      <c r="AK131">
+        <v>1.09</v>
+      </c>
+      <c r="AL131">
+        <v>1.16</v>
+      </c>
+      <c r="AM131">
+        <v>3</v>
+      </c>
+      <c r="AN131">
+        <v>2.2</v>
+      </c>
+      <c r="AO131">
+        <v>0.9</v>
+      </c>
+      <c r="AP131">
+        <v>2.27</v>
+      </c>
+      <c r="AQ131">
+        <v>0.82</v>
+      </c>
+      <c r="AR131">
+        <v>1.71</v>
+      </c>
+      <c r="AS131">
+        <v>1.13</v>
+      </c>
+      <c r="AT131">
+        <v>2.84</v>
+      </c>
+      <c r="AU131">
+        <v>6</v>
+      </c>
+      <c r="AV131">
+        <v>3</v>
+      </c>
+      <c r="AW131">
+        <v>9</v>
+      </c>
+      <c r="AX131">
+        <v>2</v>
+      </c>
+      <c r="AY131">
+        <v>19</v>
+      </c>
+      <c r="AZ131">
+        <v>6</v>
+      </c>
+      <c r="BA131">
+        <v>12</v>
+      </c>
+      <c r="BB131">
+        <v>4</v>
+      </c>
+      <c r="BC131">
+        <v>16</v>
+      </c>
+      <c r="BD131">
+        <v>1.16</v>
+      </c>
+      <c r="BE131">
+        <v>12.7</v>
+      </c>
+      <c r="BF131">
+        <v>6.87</v>
+      </c>
+      <c r="BG131">
+        <v>1.19</v>
+      </c>
+      <c r="BH131">
+        <v>3.75</v>
+      </c>
+      <c r="BI131">
+        <v>1.4</v>
+      </c>
+      <c r="BJ131">
+        <v>2.64</v>
+      </c>
+      <c r="BK131">
+        <v>1.73</v>
+      </c>
+      <c r="BL131">
+        <v>2.06</v>
+      </c>
+      <c r="BM131">
+        <v>2.16</v>
+      </c>
+      <c r="BN131">
+        <v>1.66</v>
+      </c>
+      <c r="BO131">
+        <v>2.78</v>
+      </c>
+      <c r="BP131">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7482799</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45732.54166666666</v>
+      </c>
+      <c r="F132">
+        <v>22</v>
+      </c>
+      <c r="G132" t="s">
+        <v>75</v>
+      </c>
+      <c r="H132" t="s">
+        <v>72</v>
+      </c>
+      <c r="I132">
+        <v>1</v>
+      </c>
+      <c r="J132">
+        <v>1</v>
+      </c>
+      <c r="K132">
+        <v>2</v>
+      </c>
+      <c r="L132">
+        <v>4</v>
+      </c>
+      <c r="M132">
+        <v>1</v>
+      </c>
+      <c r="N132">
+        <v>5</v>
+      </c>
+      <c r="O132" t="s">
+        <v>181</v>
+      </c>
+      <c r="P132" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q132">
+        <v>2.75</v>
+      </c>
+      <c r="R132">
+        <v>2.1</v>
+      </c>
+      <c r="S132">
+        <v>4</v>
+      </c>
+      <c r="T132">
+        <v>1.4</v>
+      </c>
+      <c r="U132">
+        <v>2.75</v>
+      </c>
+      <c r="V132">
+        <v>3</v>
+      </c>
+      <c r="W132">
+        <v>1.36</v>
+      </c>
+      <c r="X132">
+        <v>9</v>
+      </c>
+      <c r="Y132">
+        <v>1.07</v>
+      </c>
+      <c r="Z132">
+        <v>2.16</v>
+      </c>
+      <c r="AA132">
+        <v>3.45</v>
+      </c>
+      <c r="AB132">
+        <v>3.17</v>
+      </c>
+      <c r="AC132">
+        <v>1.02</v>
+      </c>
+      <c r="AD132">
+        <v>10.9</v>
+      </c>
+      <c r="AE132">
+        <v>1.32</v>
+      </c>
+      <c r="AF132">
+        <v>3.38</v>
+      </c>
+      <c r="AG132">
+        <v>1.94</v>
+      </c>
+      <c r="AH132">
+        <v>1.8</v>
+      </c>
+      <c r="AI132">
+        <v>1.8</v>
+      </c>
+      <c r="AJ132">
+        <v>1.95</v>
+      </c>
+      <c r="AK132">
+        <v>1.31</v>
+      </c>
+      <c r="AL132">
+        <v>1.3</v>
+      </c>
+      <c r="AM132">
+        <v>1.68</v>
+      </c>
+      <c r="AN132">
+        <v>1.8</v>
+      </c>
+      <c r="AO132">
+        <v>1</v>
+      </c>
+      <c r="AP132">
+        <v>1.91</v>
+      </c>
+      <c r="AQ132">
+        <v>0.91</v>
+      </c>
+      <c r="AR132">
+        <v>1.42</v>
+      </c>
+      <c r="AS132">
+        <v>1.15</v>
+      </c>
+      <c r="AT132">
+        <v>2.57</v>
+      </c>
+      <c r="AU132">
+        <v>10</v>
+      </c>
+      <c r="AV132">
+        <v>5</v>
+      </c>
+      <c r="AW132">
+        <v>8</v>
+      </c>
+      <c r="AX132">
+        <v>1</v>
+      </c>
+      <c r="AY132">
+        <v>21</v>
+      </c>
+      <c r="AZ132">
+        <v>7</v>
+      </c>
+      <c r="BA132">
+        <v>7</v>
+      </c>
+      <c r="BB132">
+        <v>2</v>
+      </c>
+      <c r="BC132">
+        <v>9</v>
+      </c>
+      <c r="BD132">
+        <v>2.03</v>
+      </c>
+      <c r="BE132">
+        <v>6.4</v>
+      </c>
+      <c r="BF132">
+        <v>2.25</v>
+      </c>
+      <c r="BG132">
+        <v>1.3</v>
+      </c>
+      <c r="BH132">
+        <v>2.97</v>
+      </c>
+      <c r="BI132">
+        <v>1.61</v>
+      </c>
+      <c r="BJ132">
+        <v>2.24</v>
+      </c>
+      <c r="BK132">
+        <v>2.01</v>
+      </c>
+      <c r="BL132">
+        <v>1.77</v>
+      </c>
+      <c r="BM132">
+        <v>2.55</v>
+      </c>
+      <c r="BN132">
+        <v>1.47</v>
+      </c>
+      <c r="BO132">
+        <v>3.58</v>
+      </c>
+      <c r="BP132">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="252">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -768,6 +768,9 @@
   <si>
     <t>['11', '14']</t>
   </si>
+  <si>
+    <t>['57', '81']</t>
+  </si>
 </sst>
 </file>
 
@@ -1128,7 +1131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP132"/>
+  <dimension ref="A1:BP133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2495,7 +2498,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2904,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ9">
         <v>0.82</v>
@@ -4967,7 +4970,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ19">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR19">
         <v>1.09</v>
@@ -5170,7 +5173,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ20">
         <v>0.73</v>
@@ -7027,7 +7030,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ29">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR29">
         <v>1.18</v>
@@ -8672,7 +8675,7 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ37">
         <v>1.27</v>
@@ -9087,7 +9090,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ39">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR39">
         <v>1.72</v>
@@ -10117,7 +10120,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ44">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR44">
         <v>2.5</v>
@@ -11350,7 +11353,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ50">
         <v>1.09</v>
@@ -12795,7 +12798,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ57">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR57">
         <v>1.44</v>
@@ -12998,7 +13001,7 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ58">
         <v>1.55</v>
@@ -15264,7 +15267,7 @@
         <v>0.8</v>
       </c>
       <c r="AP69">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ69">
         <v>0.73</v>
@@ -15885,7 +15888,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ72">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR72">
         <v>1.52</v>
@@ -17118,7 +17121,7 @@
         <v>1.17</v>
       </c>
       <c r="AP78">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ78">
         <v>0.82</v>
@@ -19387,7 +19390,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ89">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR89">
         <v>1.4</v>
@@ -20208,7 +20211,7 @@
         <v>2</v>
       </c>
       <c r="AP93">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ93">
         <v>1.82</v>
@@ -21241,7 +21244,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ98">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR98">
         <v>1.71</v>
@@ -22062,7 +22065,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ102">
         <v>0.91</v>
@@ -24122,7 +24125,7 @@
         <v>1.88</v>
       </c>
       <c r="AP112">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ112">
         <v>1.73</v>
@@ -25155,7 +25158,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ117">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR117">
         <v>1.34</v>
@@ -28321,6 +28324,212 @@
       </c>
       <c r="BP132">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7482800</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45732.54166666666</v>
+      </c>
+      <c r="F133">
+        <v>22</v>
+      </c>
+      <c r="G133" t="s">
+        <v>77</v>
+      </c>
+      <c r="H133" t="s">
+        <v>79</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>2</v>
+      </c>
+      <c r="N133">
+        <v>2</v>
+      </c>
+      <c r="O133" t="s">
+        <v>89</v>
+      </c>
+      <c r="P133" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q133">
+        <v>5.5</v>
+      </c>
+      <c r="R133">
+        <v>2.2</v>
+      </c>
+      <c r="S133">
+        <v>2.3</v>
+      </c>
+      <c r="T133">
+        <v>1.4</v>
+      </c>
+      <c r="U133">
+        <v>2.75</v>
+      </c>
+      <c r="V133">
+        <v>3</v>
+      </c>
+      <c r="W133">
+        <v>1.36</v>
+      </c>
+      <c r="X133">
+        <v>8</v>
+      </c>
+      <c r="Y133">
+        <v>1.08</v>
+      </c>
+      <c r="Z133">
+        <v>4.2</v>
+      </c>
+      <c r="AA133">
+        <v>3.58</v>
+      </c>
+      <c r="AB133">
+        <v>1.8</v>
+      </c>
+      <c r="AC133">
+        <v>1.01</v>
+      </c>
+      <c r="AD133">
+        <v>8.5</v>
+      </c>
+      <c r="AE133">
+        <v>1.31</v>
+      </c>
+      <c r="AF133">
+        <v>3.43</v>
+      </c>
+      <c r="AG133">
+        <v>1.91</v>
+      </c>
+      <c r="AH133">
+        <v>1.83</v>
+      </c>
+      <c r="AI133">
+        <v>1.95</v>
+      </c>
+      <c r="AJ133">
+        <v>1.8</v>
+      </c>
+      <c r="AK133">
+        <v>2</v>
+      </c>
+      <c r="AL133">
+        <v>1.27</v>
+      </c>
+      <c r="AM133">
+        <v>1.19</v>
+      </c>
+      <c r="AN133">
+        <v>0.9</v>
+      </c>
+      <c r="AO133">
+        <v>1.5</v>
+      </c>
+      <c r="AP133">
+        <v>0.82</v>
+      </c>
+      <c r="AQ133">
+        <v>1.64</v>
+      </c>
+      <c r="AR133">
+        <v>1.05</v>
+      </c>
+      <c r="AS133">
+        <v>1.26</v>
+      </c>
+      <c r="AT133">
+        <v>2.31</v>
+      </c>
+      <c r="AU133">
+        <v>4</v>
+      </c>
+      <c r="AV133">
+        <v>4</v>
+      </c>
+      <c r="AW133">
+        <v>10</v>
+      </c>
+      <c r="AX133">
+        <v>8</v>
+      </c>
+      <c r="AY133">
+        <v>18</v>
+      </c>
+      <c r="AZ133">
+        <v>16</v>
+      </c>
+      <c r="BA133">
+        <v>3</v>
+      </c>
+      <c r="BB133">
+        <v>11</v>
+      </c>
+      <c r="BC133">
+        <v>14</v>
+      </c>
+      <c r="BD133">
+        <v>3.44</v>
+      </c>
+      <c r="BE133">
+        <v>7.1</v>
+      </c>
+      <c r="BF133">
+        <v>1.53</v>
+      </c>
+      <c r="BG133">
+        <v>1.27</v>
+      </c>
+      <c r="BH133">
+        <v>3.14</v>
+      </c>
+      <c r="BI133">
+        <v>1.56</v>
+      </c>
+      <c r="BJ133">
+        <v>2.32</v>
+      </c>
+      <c r="BK133">
+        <v>1.93</v>
+      </c>
+      <c r="BL133">
+        <v>1.86</v>
+      </c>
+      <c r="BM133">
+        <v>2.43</v>
+      </c>
+      <c r="BN133">
+        <v>1.52</v>
+      </c>
+      <c r="BO133">
+        <v>3.34</v>
+      </c>
+      <c r="BP133">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="252">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -496,10 +496,10 @@
     <t>['81']</t>
   </si>
   <si>
-    <t>['53']</t>
+    <t>['17', '23', '83']</t>
   </si>
   <si>
-    <t>['17', '23', '83']</t>
+    <t>['53']</t>
   </si>
   <si>
     <t>['85']</t>
@@ -520,10 +520,10 @@
     <t>['31', '78']</t>
   </si>
   <si>
-    <t>['8', '56', '68', '78', '90+5']</t>
+    <t>['90+1']</t>
   </si>
   <si>
-    <t>['90+1']</t>
+    <t>['8', '56', '68', '78', '90+5']</t>
   </si>
   <si>
     <t>['1', '90+2']</t>
@@ -547,19 +547,19 @@
     <t>['49', '74']</t>
   </si>
   <si>
+    <t>['5', '90+5']</t>
+  </si>
+  <si>
     <t>['16', '48', '70', '86']</t>
   </si>
   <si>
-    <t>['5', '90+5']</t>
-  </si>
-  <si>
-    <t>['23', '32', '44']</t>
+    <t>['31', '50', '83', '90+6']</t>
   </si>
   <si>
     <t>['13']</t>
   </si>
   <si>
-    <t>['31', '50', '83', '90+6']</t>
+    <t>['23', '32', '44']</t>
   </si>
   <si>
     <t>['4', '6', '45+2']</t>
@@ -724,10 +724,10 @@
     <t>['61', '75']</t>
   </si>
   <si>
-    <t>['2']</t>
+    <t>['49', '67', '72']</t>
   </si>
   <si>
-    <t>['49', '67', '72']</t>
+    <t>['2']</t>
   </si>
   <si>
     <t>['7']</t>
@@ -764,6 +764,9 @@
   </si>
   <si>
     <t>['11', '14']</t>
+  </si>
+  <si>
+    <t>['57', '81']</t>
   </si>
   <si>
     <t>['77', '85']</t>
@@ -1128,7 +1131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP132"/>
+  <dimension ref="A1:BP133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2495,7 +2498,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2904,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ9">
         <v>0.82</v>
@@ -4555,7 +4558,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ17">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR17">
         <v>1.09</v>
@@ -5170,7 +5173,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ20">
         <v>0.73</v>
@@ -7233,7 +7236,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ30">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR30">
         <v>1.18</v>
@@ -8878,7 +8881,7 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ38">
         <v>1.27</v>
@@ -9087,7 +9090,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ39">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR39">
         <v>1.72</v>
@@ -9911,7 +9914,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ43">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR43">
         <v>2.5</v>
@@ -11350,7 +11353,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ50">
         <v>1.09</v>
@@ -12795,7 +12798,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ57">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR57">
         <v>1.44</v>
@@ -12998,7 +13001,7 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ58">
         <v>1.55</v>
@@ -15470,7 +15473,7 @@
         <v>0.8</v>
       </c>
       <c r="AP70">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ70">
         <v>0.73</v>
@@ -15885,7 +15888,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ72">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR72">
         <v>1.52</v>
@@ -17324,7 +17327,7 @@
         <v>1.17</v>
       </c>
       <c r="AP79">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ79">
         <v>0.82</v>
@@ -19387,7 +19390,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ89">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR89">
         <v>1.4</v>
@@ -20002,7 +20005,7 @@
         <v>2</v>
       </c>
       <c r="AP92">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ92">
         <v>1.82</v>
@@ -21241,7 +21244,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ98">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR98">
         <v>1.71</v>
@@ -22062,7 +22065,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ102">
         <v>0.91</v>
@@ -22354,7 +22357,7 @@
         <v>103</v>
       </c>
       <c r="B104">
-        <v>7482771</v>
+        <v>7482774</v>
       </c>
       <c r="C104" t="s">
         <v>68</v>
@@ -22369,190 +22372,190 @@
         <v>18</v>
       </c>
       <c r="G104" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H104" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I104">
         <v>0</v>
       </c>
       <c r="J104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104">
         <v>1</v>
       </c>
       <c r="M104">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N104">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O104" t="s">
-        <v>160</v>
+        <v>103</v>
       </c>
       <c r="P104" t="s">
         <v>236</v>
       </c>
       <c r="Q104">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="R104">
+        <v>2</v>
+      </c>
+      <c r="S104">
+        <v>4.5</v>
+      </c>
+      <c r="T104">
+        <v>1.5</v>
+      </c>
+      <c r="U104">
+        <v>2.5</v>
+      </c>
+      <c r="V104">
+        <v>3.4</v>
+      </c>
+      <c r="W104">
+        <v>1.3</v>
+      </c>
+      <c r="X104">
+        <v>10</v>
+      </c>
+      <c r="Y104">
+        <v>1.06</v>
+      </c>
+      <c r="Z104">
+        <v>1.89</v>
+      </c>
+      <c r="AA104">
+        <v>3.38</v>
+      </c>
+      <c r="AB104">
+        <v>4.1</v>
+      </c>
+      <c r="AC104">
+        <v>1.08</v>
+      </c>
+      <c r="AD104">
+        <v>8</v>
+      </c>
+      <c r="AE104">
+        <v>1.44</v>
+      </c>
+      <c r="AF104">
         <v>2.75</v>
       </c>
-      <c r="S104">
-        <v>8.5</v>
-      </c>
-      <c r="T104">
-        <v>1.25</v>
-      </c>
-      <c r="U104">
-        <v>3.75</v>
-      </c>
-      <c r="V104">
-        <v>2.2</v>
-      </c>
-      <c r="W104">
-        <v>1.62</v>
-      </c>
-      <c r="X104">
-        <v>5</v>
-      </c>
-      <c r="Y104">
-        <v>1.17</v>
-      </c>
-      <c r="Z104">
-        <v>1.25</v>
-      </c>
-      <c r="AA104">
-        <v>6</v>
-      </c>
-      <c r="AB104">
-        <v>10</v>
-      </c>
-      <c r="AC104">
-        <v>1.01</v>
-      </c>
-      <c r="AD104">
-        <v>19</v>
-      </c>
-      <c r="AE104">
-        <v>1.14</v>
-      </c>
-      <c r="AF104">
-        <v>5.5</v>
-      </c>
       <c r="AG104">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AH104">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="AI104">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AJ104">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AK104">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="AL104">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="AM104">
-        <v>3.8</v>
+        <v>1.73</v>
       </c>
       <c r="AN104">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="AO104">
-        <v>1.13</v>
+        <v>0.5</v>
       </c>
       <c r="AP104">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AQ104">
-        <v>0.91</v>
+        <v>0.73</v>
       </c>
       <c r="AR104">
-        <v>2.12</v>
+        <v>1.34</v>
       </c>
       <c r="AS104">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT104">
-        <v>3.25</v>
+        <v>2.28</v>
       </c>
       <c r="AU104">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV104">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW104">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AX104">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY104">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="AZ104">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BA104">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="BB104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC104">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="BD104">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
       <c r="BE104">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF104">
-        <v>4.3</v>
+        <v>2.48</v>
       </c>
       <c r="BG104">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="BH104">
+        <v>2.4</v>
+      </c>
+      <c r="BI104">
+        <v>1.82</v>
+      </c>
+      <c r="BJ104">
+        <v>1.86</v>
+      </c>
+      <c r="BK104">
+        <v>2.32</v>
+      </c>
+      <c r="BL104">
+        <v>1.53</v>
+      </c>
+      <c r="BM104">
         <v>3.05</v>
       </c>
-      <c r="BI104">
-        <v>1.54</v>
-      </c>
-      <c r="BJ104">
-        <v>2.3</v>
-      </c>
-      <c r="BK104">
-        <v>1.86</v>
-      </c>
-      <c r="BL104">
-        <v>1.82</v>
-      </c>
-      <c r="BM104">
-        <v>2.33</v>
-      </c>
       <c r="BN104">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="BO104">
-        <v>2.95</v>
+        <v>4.1</v>
       </c>
       <c r="BP104">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="105" spans="1:68">
@@ -22599,7 +22602,7 @@
         <v>3</v>
       </c>
       <c r="O105" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P105" t="s">
         <v>89</v>
@@ -22766,7 +22769,7 @@
         <v>105</v>
       </c>
       <c r="B106">
-        <v>7482774</v>
+        <v>7482771</v>
       </c>
       <c r="C106" t="s">
         <v>68</v>
@@ -22781,190 +22784,190 @@
         <v>18</v>
       </c>
       <c r="G106" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H106" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="I106">
         <v>0</v>
       </c>
       <c r="J106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106">
         <v>1</v>
       </c>
       <c r="M106">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N106">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O106" t="s">
-        <v>103</v>
+        <v>161</v>
       </c>
       <c r="P106" t="s">
         <v>237</v>
       </c>
       <c r="Q106">
+        <v>1.67</v>
+      </c>
+      <c r="R106">
         <v>2.75</v>
       </c>
-      <c r="R106">
-        <v>2</v>
-      </c>
       <c r="S106">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="T106">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="U106">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="V106">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="W106">
+        <v>1.62</v>
+      </c>
+      <c r="X106">
+        <v>5</v>
+      </c>
+      <c r="Y106">
+        <v>1.17</v>
+      </c>
+      <c r="Z106">
+        <v>1.25</v>
+      </c>
+      <c r="AA106">
+        <v>6</v>
+      </c>
+      <c r="AB106">
+        <v>10</v>
+      </c>
+      <c r="AC106">
+        <v>1.01</v>
+      </c>
+      <c r="AD106">
+        <v>19</v>
+      </c>
+      <c r="AE106">
+        <v>1.14</v>
+      </c>
+      <c r="AF106">
+        <v>5.5</v>
+      </c>
+      <c r="AG106">
+        <v>1.58</v>
+      </c>
+      <c r="AH106">
+        <v>2.18</v>
+      </c>
+      <c r="AI106">
+        <v>1.95</v>
+      </c>
+      <c r="AJ106">
+        <v>1.8</v>
+      </c>
+      <c r="AK106">
+        <v>1.06</v>
+      </c>
+      <c r="AL106">
+        <v>1.12</v>
+      </c>
+      <c r="AM106">
+        <v>3.8</v>
+      </c>
+      <c r="AN106">
+        <v>2.13</v>
+      </c>
+      <c r="AO106">
+        <v>1.13</v>
+      </c>
+      <c r="AP106">
+        <v>2.18</v>
+      </c>
+      <c r="AQ106">
+        <v>0.91</v>
+      </c>
+      <c r="AR106">
+        <v>2.12</v>
+      </c>
+      <c r="AS106">
+        <v>1.13</v>
+      </c>
+      <c r="AT106">
+        <v>3.25</v>
+      </c>
+      <c r="AU106">
+        <v>5</v>
+      </c>
+      <c r="AV106">
+        <v>5</v>
+      </c>
+      <c r="AW106">
+        <v>21</v>
+      </c>
+      <c r="AX106">
+        <v>3</v>
+      </c>
+      <c r="AY106">
+        <v>34</v>
+      </c>
+      <c r="AZ106">
+        <v>11</v>
+      </c>
+      <c r="BA106">
+        <v>9</v>
+      </c>
+      <c r="BB106">
+        <v>2</v>
+      </c>
+      <c r="BC106">
+        <v>11</v>
+      </c>
+      <c r="BD106">
+        <v>1.26</v>
+      </c>
+      <c r="BE106">
+        <v>7.5</v>
+      </c>
+      <c r="BF106">
+        <v>4.3</v>
+      </c>
+      <c r="BG106">
         <v>1.3</v>
       </c>
-      <c r="X106">
-        <v>10</v>
-      </c>
-      <c r="Y106">
-        <v>1.06</v>
-      </c>
-      <c r="Z106">
-        <v>1.89</v>
-      </c>
-      <c r="AA106">
-        <v>3.38</v>
-      </c>
-      <c r="AB106">
-        <v>4.1</v>
-      </c>
-      <c r="AC106">
-        <v>1.08</v>
-      </c>
-      <c r="AD106">
-        <v>8</v>
-      </c>
-      <c r="AE106">
-        <v>1.44</v>
-      </c>
-      <c r="AF106">
-        <v>2.75</v>
-      </c>
-      <c r="AG106">
-        <v>1.95</v>
-      </c>
-      <c r="AH106">
-        <v>1.7</v>
-      </c>
-      <c r="AI106">
-        <v>2</v>
-      </c>
-      <c r="AJ106">
-        <v>1.75</v>
-      </c>
-      <c r="AK106">
-        <v>1.27</v>
-      </c>
-      <c r="AL106">
-        <v>1.31</v>
-      </c>
-      <c r="AM106">
-        <v>1.73</v>
-      </c>
-      <c r="AN106">
-        <v>1.88</v>
-      </c>
-      <c r="AO106">
-        <v>0.5</v>
-      </c>
-      <c r="AP106">
-        <v>1.91</v>
-      </c>
-      <c r="AQ106">
-        <v>0.73</v>
-      </c>
-      <c r="AR106">
-        <v>1.34</v>
-      </c>
-      <c r="AS106">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AT106">
-        <v>2.28</v>
-      </c>
-      <c r="AU106">
-        <v>3</v>
-      </c>
-      <c r="AV106">
-        <v>4</v>
-      </c>
-      <c r="AW106">
-        <v>4</v>
-      </c>
-      <c r="AX106">
-        <v>7</v>
-      </c>
-      <c r="AY106">
-        <v>7</v>
-      </c>
-      <c r="AZ106">
-        <v>14</v>
-      </c>
-      <c r="BA106">
-        <v>2</v>
-      </c>
-      <c r="BB106">
-        <v>1</v>
-      </c>
-      <c r="BC106">
-        <v>3</v>
-      </c>
-      <c r="BD106">
-        <v>1.68</v>
-      </c>
-      <c r="BE106">
-        <v>6.4</v>
-      </c>
-      <c r="BF106">
-        <v>2.48</v>
-      </c>
-      <c r="BG106">
-        <v>1.49</v>
-      </c>
       <c r="BH106">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="BI106">
+        <v>1.54</v>
+      </c>
+      <c r="BJ106">
+        <v>2.3</v>
+      </c>
+      <c r="BK106">
+        <v>1.86</v>
+      </c>
+      <c r="BL106">
         <v>1.82</v>
       </c>
-      <c r="BJ106">
-        <v>1.86</v>
-      </c>
-      <c r="BK106">
-        <v>2.32</v>
-      </c>
-      <c r="BL106">
-        <v>1.53</v>
-      </c>
       <c r="BM106">
-        <v>3.05</v>
+        <v>2.33</v>
       </c>
       <c r="BN106">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="BO106">
-        <v>4.1</v>
+        <v>2.95</v>
       </c>
       <c r="BP106">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="107" spans="1:68">
@@ -22972,7 +22975,7 @@
         <v>106</v>
       </c>
       <c r="B107">
-        <v>7482776</v>
+        <v>7482775</v>
       </c>
       <c r="C107" t="s">
         <v>68</v>
@@ -22987,10 +22990,10 @@
         <v>18</v>
       </c>
       <c r="G107" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H107" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I107">
         <v>0</v>
@@ -23002,73 +23005,73 @@
         <v>0</v>
       </c>
       <c r="L107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N107">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O107" t="s">
-        <v>162</v>
+        <v>89</v>
       </c>
       <c r="P107" t="s">
-        <v>132</v>
+        <v>89</v>
       </c>
       <c r="Q107">
-        <v>2.38</v>
+        <v>4</v>
       </c>
       <c r="R107">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S107">
-        <v>4.75</v>
+        <v>2.88</v>
       </c>
       <c r="T107">
+        <v>1.4</v>
+      </c>
+      <c r="U107">
+        <v>2.75</v>
+      </c>
+      <c r="V107">
+        <v>3</v>
+      </c>
+      <c r="W107">
         <v>1.36</v>
       </c>
-      <c r="U107">
-        <v>3</v>
-      </c>
-      <c r="V107">
-        <v>2.75</v>
-      </c>
-      <c r="W107">
-        <v>1.4</v>
-      </c>
       <c r="X107">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y107">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z107">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="AA107">
-        <v>3.82</v>
+        <v>3.45</v>
       </c>
       <c r="AB107">
-        <v>4.6</v>
+        <v>2.24</v>
       </c>
       <c r="AC107">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AD107">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE107">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AF107">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AG107">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH107">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AI107">
         <v>1.75</v>
@@ -23077,73 +23080,73 @@
         <v>2</v>
       </c>
       <c r="AK107">
-        <v>1.2</v>
+        <v>1.63</v>
       </c>
       <c r="AL107">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AM107">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AN107">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="AO107">
-        <v>0.78</v>
+        <v>1.63</v>
       </c>
       <c r="AP107">
-        <v>1.45</v>
+        <v>0.64</v>
       </c>
       <c r="AQ107">
-        <v>0.73</v>
+        <v>1.55</v>
       </c>
       <c r="AR107">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AS107">
-        <v>0.97</v>
+        <v>1.09</v>
       </c>
       <c r="AT107">
-        <v>2.09</v>
+        <v>2.42</v>
       </c>
       <c r="AU107">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV107">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AW107">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AX107">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY107">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ107">
         <v>11</v>
       </c>
       <c r="BA107">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BB107">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC107">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BD107">
-        <v>1.63</v>
+        <v>2.23</v>
       </c>
       <c r="BE107">
         <v>6.4</v>
       </c>
       <c r="BF107">
-        <v>2.55</v>
+        <v>1.79</v>
       </c>
       <c r="BG107">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="BH107">
         <v>2.8</v>
@@ -23152,7 +23155,7 @@
         <v>1.62</v>
       </c>
       <c r="BJ107">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BK107">
         <v>2</v>
@@ -23178,7 +23181,7 @@
         <v>107</v>
       </c>
       <c r="B108">
-        <v>7482775</v>
+        <v>7482776</v>
       </c>
       <c r="C108" t="s">
         <v>68</v>
@@ -23193,10 +23196,10 @@
         <v>18</v>
       </c>
       <c r="G108" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H108" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -23208,73 +23211,73 @@
         <v>0</v>
       </c>
       <c r="L108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O108" t="s">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="P108" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="Q108">
+        <v>2.38</v>
+      </c>
+      <c r="R108">
+        <v>2.25</v>
+      </c>
+      <c r="S108">
+        <v>4.75</v>
+      </c>
+      <c r="T108">
+        <v>1.36</v>
+      </c>
+      <c r="U108">
+        <v>3</v>
+      </c>
+      <c r="V108">
+        <v>2.75</v>
+      </c>
+      <c r="W108">
+        <v>1.4</v>
+      </c>
+      <c r="X108">
+        <v>7</v>
+      </c>
+      <c r="Y108">
+        <v>1.1</v>
+      </c>
+      <c r="Z108">
+        <v>1.7</v>
+      </c>
+      <c r="AA108">
+        <v>3.82</v>
+      </c>
+      <c r="AB108">
+        <v>4.6</v>
+      </c>
+      <c r="AC108">
+        <v>1.03</v>
+      </c>
+      <c r="AD108">
+        <v>13</v>
+      </c>
+      <c r="AE108">
+        <v>1.22</v>
+      </c>
+      <c r="AF108">
         <v>4</v>
       </c>
-      <c r="R108">
-        <v>2.1</v>
-      </c>
-      <c r="S108">
-        <v>2.88</v>
-      </c>
-      <c r="T108">
-        <v>1.4</v>
-      </c>
-      <c r="U108">
-        <v>2.75</v>
-      </c>
-      <c r="V108">
-        <v>3</v>
-      </c>
-      <c r="W108">
-        <v>1.36</v>
-      </c>
-      <c r="X108">
-        <v>9</v>
-      </c>
-      <c r="Y108">
-        <v>1.07</v>
-      </c>
-      <c r="Z108">
-        <v>3</v>
-      </c>
-      <c r="AA108">
-        <v>3.45</v>
-      </c>
-      <c r="AB108">
-        <v>2.24</v>
-      </c>
-      <c r="AC108">
-        <v>1.05</v>
-      </c>
-      <c r="AD108">
-        <v>10</v>
-      </c>
-      <c r="AE108">
-        <v>1.33</v>
-      </c>
-      <c r="AF108">
-        <v>3.3</v>
-      </c>
       <c r="AG108">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH108">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AI108">
         <v>1.75</v>
@@ -23283,73 +23286,73 @@
         <v>2</v>
       </c>
       <c r="AK108">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="AL108">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AM108">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AN108">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="AO108">
-        <v>1.63</v>
+        <v>0.78</v>
       </c>
       <c r="AP108">
-        <v>0.64</v>
+        <v>1.45</v>
       </c>
       <c r="AQ108">
-        <v>1.55</v>
+        <v>0.73</v>
       </c>
       <c r="AR108">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AS108">
-        <v>1.09</v>
+        <v>0.97</v>
       </c>
       <c r="AT108">
-        <v>2.42</v>
+        <v>2.09</v>
       </c>
       <c r="AU108">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV108">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW108">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX108">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY108">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AZ108">
         <v>11</v>
       </c>
       <c r="BA108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB108">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC108">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BD108">
-        <v>2.23</v>
+        <v>1.63</v>
       </c>
       <c r="BE108">
         <v>6.4</v>
       </c>
       <c r="BF108">
-        <v>1.79</v>
+        <v>2.55</v>
       </c>
       <c r="BG108">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="BH108">
         <v>2.8</v>
@@ -23358,7 +23361,7 @@
         <v>1.62</v>
       </c>
       <c r="BJ108">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BK108">
         <v>2</v>
@@ -24122,7 +24125,7 @@
         <v>1.88</v>
       </c>
       <c r="AP112">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ112">
         <v>1.73</v>
@@ -25032,7 +25035,7 @@
         <v>116</v>
       </c>
       <c r="B117">
-        <v>7482785</v>
+        <v>7482787</v>
       </c>
       <c r="C117" t="s">
         <v>68</v>
@@ -25047,190 +25050,190 @@
         <v>20</v>
       </c>
       <c r="G117" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H117" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="I117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J117">
         <v>0</v>
       </c>
       <c r="K117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M117">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N117">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O117" t="s">
         <v>168</v>
       </c>
       <c r="P117" t="s">
-        <v>89</v>
+        <v>242</v>
       </c>
       <c r="Q117">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="R117">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S117">
-        <v>6.5</v>
+        <v>2.65</v>
       </c>
       <c r="T117">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U117">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="V117">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="W117">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X117">
-        <v>8</v>
+        <v>6.95</v>
       </c>
       <c r="Y117">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z117">
-        <v>1.49</v>
+        <v>3.69</v>
       </c>
       <c r="AA117">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="AB117">
-        <v>5.4</v>
+        <v>1.92</v>
       </c>
       <c r="AC117">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AD117">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="AE117">
         <v>1.3</v>
       </c>
       <c r="AF117">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AG117">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AH117">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AI117">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AJ117">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AK117">
-        <v>1.12</v>
+        <v>1.83</v>
       </c>
       <c r="AL117">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AM117">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="AN117">
-        <v>2.11</v>
+        <v>0.78</v>
       </c>
       <c r="AO117">
-        <v>0.78</v>
+        <v>1.33</v>
       </c>
       <c r="AP117">
-        <v>2.27</v>
+        <v>0.64</v>
       </c>
       <c r="AQ117">
-        <v>0.73</v>
+        <v>1.64</v>
       </c>
       <c r="AR117">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="AS117">
-        <v>0.98</v>
+        <v>1.25</v>
       </c>
       <c r="AT117">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="AU117">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AV117">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW117">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX117">
         <v>6</v>
       </c>
       <c r="AY117">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ117">
         <v>11</v>
       </c>
       <c r="BA117">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB117">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC117">
         <v>7</v>
       </c>
       <c r="BD117">
-        <v>1.45</v>
+        <v>2.4</v>
       </c>
       <c r="BE117">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="BF117">
-        <v>3.15</v>
+        <v>1.68</v>
       </c>
       <c r="BG117">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="BH117">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="BI117">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="BJ117">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="BK117">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="BL117">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="BM117">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="BN117">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="BO117">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="BP117">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="118" spans="1:68">
@@ -25238,7 +25241,7 @@
         <v>117</v>
       </c>
       <c r="B118">
-        <v>7482787</v>
+        <v>7482785</v>
       </c>
       <c r="C118" t="s">
         <v>68</v>
@@ -25253,190 +25256,190 @@
         <v>20</v>
       </c>
       <c r="G118" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H118" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="I118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J118">
         <v>0</v>
       </c>
       <c r="K118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M118">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N118">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O118" t="s">
         <v>169</v>
       </c>
       <c r="P118" t="s">
-        <v>242</v>
+        <v>89</v>
       </c>
       <c r="Q118">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="R118">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S118">
-        <v>2.65</v>
+        <v>6.5</v>
       </c>
       <c r="T118">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="U118">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="V118">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="W118">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X118">
-        <v>6.95</v>
+        <v>8</v>
       </c>
       <c r="Y118">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z118">
-        <v>3.69</v>
+        <v>1.49</v>
       </c>
       <c r="AA118">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="AB118">
-        <v>1.92</v>
+        <v>5.4</v>
       </c>
       <c r="AC118">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AD118">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="AE118">
         <v>1.3</v>
       </c>
       <c r="AF118">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AG118">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AH118">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AI118">
+        <v>2</v>
+      </c>
+      <c r="AJ118">
         <v>1.75</v>
       </c>
-      <c r="AJ118">
-        <v>2</v>
-      </c>
       <c r="AK118">
-        <v>1.83</v>
+        <v>1.12</v>
       </c>
       <c r="AL118">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AM118">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="AN118">
+        <v>2.11</v>
+      </c>
+      <c r="AO118">
         <v>0.78</v>
       </c>
-      <c r="AO118">
-        <v>1.33</v>
-      </c>
       <c r="AP118">
-        <v>0.64</v>
+        <v>2.27</v>
       </c>
       <c r="AQ118">
-        <v>1.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR118">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="AS118">
-        <v>1.25</v>
+        <v>0.98</v>
       </c>
       <c r="AT118">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="AU118">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AV118">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW118">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX118">
         <v>6</v>
       </c>
       <c r="AY118">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AZ118">
         <v>11</v>
       </c>
       <c r="BA118">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC118">
         <v>7</v>
       </c>
       <c r="BD118">
-        <v>2.4</v>
+        <v>1.45</v>
       </c>
       <c r="BE118">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="BF118">
-        <v>1.68</v>
+        <v>3.15</v>
       </c>
       <c r="BG118">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BH118">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="BI118">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="BJ118">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="BK118">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="BL118">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="BM118">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="BN118">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="BO118">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="BP118">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="119" spans="1:68">
@@ -27298,7 +27301,7 @@
         <v>127</v>
       </c>
       <c r="B128">
-        <v>7482799</v>
+        <v>7482797</v>
       </c>
       <c r="C128" t="s">
         <v>68</v>
@@ -27313,190 +27316,190 @@
         <v>22</v>
       </c>
       <c r="G128" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H128" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I128">
         <v>1</v>
       </c>
       <c r="J128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K128">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L128">
+        <v>2</v>
+      </c>
+      <c r="M128">
+        <v>2</v>
+      </c>
+      <c r="N128">
         <v>4</v>
-      </c>
-      <c r="M128">
-        <v>1</v>
-      </c>
-      <c r="N128">
-        <v>5</v>
       </c>
       <c r="O128" t="s">
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>137</v>
+        <v>249</v>
       </c>
       <c r="Q128">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="R128">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S128">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="T128">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="U128">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V128">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="W128">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="X128">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y128">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z128">
-        <v>2.16</v>
+        <v>2.63</v>
       </c>
       <c r="AA128">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="AB128">
-        <v>3.17</v>
+        <v>2.64</v>
       </c>
       <c r="AC128">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AD128">
-        <v>10.9</v>
+        <v>7.2</v>
       </c>
       <c r="AE128">
+        <v>1.38</v>
+      </c>
+      <c r="AF128">
+        <v>3.02</v>
+      </c>
+      <c r="AG128">
+        <v>2</v>
+      </c>
+      <c r="AH128">
+        <v>1.65</v>
+      </c>
+      <c r="AI128">
+        <v>1.95</v>
+      </c>
+      <c r="AJ128">
+        <v>1.8</v>
+      </c>
+      <c r="AK128">
+        <v>1.49</v>
+      </c>
+      <c r="AL128">
         <v>1.32</v>
       </c>
-      <c r="AF128">
-        <v>3.38</v>
-      </c>
-      <c r="AG128">
-        <v>1.94</v>
-      </c>
-      <c r="AH128">
-        <v>1.8</v>
-      </c>
-      <c r="AI128">
-        <v>1.8</v>
-      </c>
-      <c r="AJ128">
-        <v>1.95</v>
-      </c>
-      <c r="AK128">
-        <v>1.31</v>
-      </c>
-      <c r="AL128">
-        <v>1.3</v>
-      </c>
       <c r="AM128">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="AN128">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AO128">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AP128">
-        <v>1.91</v>
+        <v>1.18</v>
       </c>
       <c r="AQ128">
-        <v>0.91</v>
+        <v>0.73</v>
       </c>
       <c r="AR128">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AS128">
-        <v>1.15</v>
+        <v>0.98</v>
       </c>
       <c r="AT128">
-        <v>2.57</v>
+        <v>2.32</v>
       </c>
       <c r="AU128">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AV128">
         <v>5</v>
       </c>
       <c r="AW128">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AX128">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AY128">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ128">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BA128">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB128">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BC128">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BD128">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="BE128">
-        <v>6.4</v>
+        <v>6.35</v>
       </c>
       <c r="BF128">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BG128">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BH128">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="BI128">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="BJ128">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="BK128">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="BL128">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="BM128">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="BN128">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="BO128">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="BP128">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="129" spans="1:68">
@@ -27504,7 +27507,7 @@
         <v>128</v>
       </c>
       <c r="B129">
-        <v>7482797</v>
+        <v>7482800</v>
       </c>
       <c r="C129" t="s">
         <v>68</v>
@@ -27519,88 +27522,88 @@
         <v>22</v>
       </c>
       <c r="G129" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H129" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="I129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K129">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L129">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M129">
         <v>2</v>
       </c>
       <c r="N129">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O129" t="s">
-        <v>178</v>
+        <v>89</v>
       </c>
       <c r="P129" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q129">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="R129">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S129">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="T129">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="U129">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V129">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="W129">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X129">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y129">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z129">
-        <v>2.63</v>
+        <v>4.2</v>
       </c>
       <c r="AA129">
-        <v>3.21</v>
+        <v>3.58</v>
       </c>
       <c r="AB129">
-        <v>2.64</v>
+        <v>1.8</v>
       </c>
       <c r="AC129">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AD129">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="AE129">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AF129">
-        <v>3.02</v>
+        <v>3.43</v>
       </c>
       <c r="AG129">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH129">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AI129">
         <v>1.95</v>
@@ -27609,100 +27612,100 @@
         <v>1.8</v>
       </c>
       <c r="AK129">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="AL129">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AM129">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="AN129">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="AO129">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="AP129">
-        <v>1.18</v>
+        <v>0.82</v>
       </c>
       <c r="AQ129">
-        <v>0.73</v>
+        <v>1.64</v>
       </c>
       <c r="AR129">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="AS129">
-        <v>0.98</v>
+        <v>1.26</v>
       </c>
       <c r="AT129">
+        <v>2.31</v>
+      </c>
+      <c r="AU129">
+        <v>4</v>
+      </c>
+      <c r="AV129">
+        <v>4</v>
+      </c>
+      <c r="AW129">
+        <v>10</v>
+      </c>
+      <c r="AX129">
+        <v>8</v>
+      </c>
+      <c r="AY129">
+        <v>18</v>
+      </c>
+      <c r="AZ129">
+        <v>16</v>
+      </c>
+      <c r="BA129">
+        <v>3</v>
+      </c>
+      <c r="BB129">
+        <v>11</v>
+      </c>
+      <c r="BC129">
+        <v>14</v>
+      </c>
+      <c r="BD129">
+        <v>3.44</v>
+      </c>
+      <c r="BE129">
+        <v>7.1</v>
+      </c>
+      <c r="BF129">
+        <v>1.53</v>
+      </c>
+      <c r="BG129">
+        <v>1.27</v>
+      </c>
+      <c r="BH129">
+        <v>3.14</v>
+      </c>
+      <c r="BI129">
+        <v>1.56</v>
+      </c>
+      <c r="BJ129">
         <v>2.32</v>
       </c>
-      <c r="AU129">
-        <v>7</v>
-      </c>
-      <c r="AV129">
-        <v>5</v>
-      </c>
-      <c r="AW129">
-        <v>4</v>
-      </c>
-      <c r="AX129">
-        <v>5</v>
-      </c>
-      <c r="AY129">
-        <v>15</v>
-      </c>
-      <c r="AZ129">
-        <v>12</v>
-      </c>
-      <c r="BA129">
-        <v>6</v>
-      </c>
-      <c r="BB129">
-        <v>6</v>
-      </c>
-      <c r="BC129">
-        <v>12</v>
-      </c>
-      <c r="BD129">
-        <v>2.05</v>
-      </c>
-      <c r="BE129">
-        <v>6.35</v>
-      </c>
-      <c r="BF129">
-        <v>2.23</v>
-      </c>
-      <c r="BG129">
-        <v>1.31</v>
-      </c>
-      <c r="BH129">
-        <v>2.92</v>
-      </c>
-      <c r="BI129">
-        <v>1.65</v>
-      </c>
-      <c r="BJ129">
-        <v>2.2</v>
-      </c>
       <c r="BK129">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="BL129">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="BM129">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="BN129">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="BO129">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="BP129">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="130" spans="1:68">
@@ -27710,7 +27713,7 @@
         <v>129</v>
       </c>
       <c r="B130">
-        <v>7482798</v>
+        <v>7482799</v>
       </c>
       <c r="C130" t="s">
         <v>68</v>
@@ -27725,190 +27728,190 @@
         <v>22</v>
       </c>
       <c r="G130" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H130" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I130">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L130">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N130">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O130" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P130" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="Q130">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="R130">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S130">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="T130">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="U130">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="V130">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="W130">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="X130">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y130">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z130">
-        <v>1.32</v>
+        <v>2.16</v>
       </c>
       <c r="AA130">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="AB130">
-        <v>8.699999999999999</v>
+        <v>3.17</v>
       </c>
       <c r="AC130">
         <v>1.02</v>
       </c>
       <c r="AD130">
-        <v>15.5</v>
+        <v>10.9</v>
       </c>
       <c r="AE130">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AF130">
-        <v>4.45</v>
+        <v>3.38</v>
       </c>
       <c r="AG130">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AH130">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AI130">
+        <v>1.8</v>
+      </c>
+      <c r="AJ130">
         <v>1.95</v>
       </c>
-      <c r="AJ130">
+      <c r="AK130">
+        <v>1.31</v>
+      </c>
+      <c r="AL130">
+        <v>1.3</v>
+      </c>
+      <c r="AM130">
+        <v>1.68</v>
+      </c>
+      <c r="AN130">
         <v>1.8</v>
       </c>
-      <c r="AK130">
-        <v>1.09</v>
-      </c>
-      <c r="AL130">
-        <v>1.16</v>
-      </c>
-      <c r="AM130">
-        <v>3</v>
-      </c>
-      <c r="AN130">
-        <v>2.2</v>
-      </c>
       <c r="AO130">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AP130">
-        <v>2.27</v>
+        <v>1.91</v>
       </c>
       <c r="AQ130">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AR130">
-        <v>1.71</v>
+        <v>1.42</v>
       </c>
       <c r="AS130">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AT130">
-        <v>2.84</v>
+        <v>2.57</v>
       </c>
       <c r="AU130">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AV130">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW130">
+        <v>8</v>
+      </c>
+      <c r="AX130">
+        <v>1</v>
+      </c>
+      <c r="AY130">
+        <v>21</v>
+      </c>
+      <c r="AZ130">
+        <v>7</v>
+      </c>
+      <c r="BA130">
+        <v>7</v>
+      </c>
+      <c r="BB130">
+        <v>2</v>
+      </c>
+      <c r="BC130">
         <v>9</v>
       </c>
-      <c r="AX130">
-        <v>2</v>
-      </c>
-      <c r="AY130">
-        <v>19</v>
-      </c>
-      <c r="AZ130">
-        <v>6</v>
-      </c>
-      <c r="BA130">
-        <v>12</v>
-      </c>
-      <c r="BB130">
-        <v>4</v>
-      </c>
-      <c r="BC130">
-        <v>16</v>
-      </c>
       <c r="BD130">
-        <v>1.16</v>
+        <v>2.03</v>
       </c>
       <c r="BE130">
-        <v>12.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF130">
-        <v>6.87</v>
+        <v>2.25</v>
       </c>
       <c r="BG130">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="BH130">
-        <v>3.75</v>
+        <v>2.97</v>
       </c>
       <c r="BI130">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="BJ130">
-        <v>2.64</v>
+        <v>2.24</v>
       </c>
       <c r="BK130">
-        <v>1.73</v>
+        <v>2.01</v>
       </c>
       <c r="BL130">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="BM130">
-        <v>2.16</v>
+        <v>2.55</v>
       </c>
       <c r="BN130">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="BO130">
-        <v>2.78</v>
+        <v>3.58</v>
       </c>
       <c r="BP130">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="131" spans="1:68">
@@ -27916,7 +27919,7 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>7482795</v>
+        <v>7482796</v>
       </c>
       <c r="C131" t="s">
         <v>68</v>
@@ -27931,10 +27934,10 @@
         <v>22</v>
       </c>
       <c r="G131" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H131" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I131">
         <v>1</v>
@@ -27946,73 +27949,73 @@
         <v>1</v>
       </c>
       <c r="L131">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M131">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N131">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O131" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P131" t="s">
-        <v>89</v>
+        <v>251</v>
       </c>
       <c r="Q131">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="R131">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S131">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="T131">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="U131">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="V131">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="W131">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="X131">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Y131">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z131">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AA131">
+        <v>3.55</v>
+      </c>
+      <c r="AB131">
         <v>3.98</v>
-      </c>
-      <c r="AB131">
-        <v>4.6</v>
       </c>
       <c r="AC131">
         <v>1.01</v>
       </c>
       <c r="AD131">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE131">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AF131">
-        <v>4.43</v>
+        <v>3.79</v>
       </c>
       <c r="AG131">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AH131">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AI131">
         <v>1.75</v>
@@ -28021,100 +28024,100 @@
         <v>2</v>
       </c>
       <c r="AK131">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AL131">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AM131">
+        <v>1.75</v>
+      </c>
+      <c r="AN131">
         <v>2.3</v>
       </c>
-      <c r="AN131">
-        <v>2.1</v>
-      </c>
       <c r="AO131">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AP131">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="AQ131">
+        <v>1.55</v>
+      </c>
+      <c r="AR131">
         <v>1.73</v>
       </c>
-      <c r="AR131">
-        <v>2.23</v>
-      </c>
       <c r="AS131">
-        <v>1.54</v>
+        <v>1.16</v>
       </c>
       <c r="AT131">
-        <v>3.77</v>
+        <v>2.89</v>
       </c>
       <c r="AU131">
+        <v>9</v>
+      </c>
+      <c r="AV131">
+        <v>5</v>
+      </c>
+      <c r="AW131">
+        <v>11</v>
+      </c>
+      <c r="AX131">
+        <v>3</v>
+      </c>
+      <c r="AY131">
+        <v>24</v>
+      </c>
+      <c r="AZ131">
+        <v>9</v>
+      </c>
+      <c r="BA131">
+        <v>9</v>
+      </c>
+      <c r="BB131">
         <v>4</v>
       </c>
-      <c r="AV131">
-        <v>2</v>
-      </c>
-      <c r="AW131">
-        <v>5</v>
-      </c>
-      <c r="AX131">
-        <v>0</v>
-      </c>
-      <c r="AY131">
-        <v>9</v>
-      </c>
-      <c r="AZ131">
-        <v>2</v>
-      </c>
-      <c r="BA131">
-        <v>4</v>
-      </c>
-      <c r="BB131">
-        <v>5</v>
-      </c>
       <c r="BC131">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BD131">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="BE131">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF131">
-        <v>3.78</v>
+        <v>3.24</v>
       </c>
       <c r="BG131">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="BH131">
-        <v>3.84</v>
+        <v>3.08</v>
       </c>
       <c r="BI131">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="BJ131">
-        <v>2.71</v>
+        <v>2.34</v>
       </c>
       <c r="BK131">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="BL131">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="BM131">
-        <v>2.13</v>
+        <v>2.49</v>
       </c>
       <c r="BN131">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="BO131">
-        <v>2.74</v>
+        <v>3.42</v>
       </c>
       <c r="BP131">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="132" spans="1:68">
@@ -28122,7 +28125,7 @@
         <v>131</v>
       </c>
       <c r="B132">
-        <v>7482796</v>
+        <v>7482795</v>
       </c>
       <c r="C132" t="s">
         <v>68</v>
@@ -28137,10 +28140,10 @@
         <v>22</v>
       </c>
       <c r="G132" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H132" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I132">
         <v>1</v>
@@ -28152,73 +28155,73 @@
         <v>1</v>
       </c>
       <c r="L132">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M132">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N132">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O132" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P132" t="s">
-        <v>250</v>
+        <v>89</v>
       </c>
       <c r="Q132">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="R132">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S132">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="T132">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="U132">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V132">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="W132">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="X132">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="Y132">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z132">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="AA132">
-        <v>3.55</v>
+        <v>3.98</v>
       </c>
       <c r="AB132">
-        <v>3.98</v>
+        <v>4.6</v>
       </c>
       <c r="AC132">
         <v>1.01</v>
       </c>
       <c r="AD132">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AE132">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AF132">
-        <v>3.79</v>
+        <v>4.43</v>
       </c>
       <c r="AG132">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AH132">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AI132">
         <v>1.75</v>
@@ -28227,100 +28230,306 @@
         <v>2</v>
       </c>
       <c r="AK132">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AL132">
+        <v>1.22</v>
+      </c>
+      <c r="AM132">
+        <v>2.3</v>
+      </c>
+      <c r="AN132">
+        <v>2.1</v>
+      </c>
+      <c r="AO132">
+        <v>1.9</v>
+      </c>
+      <c r="AP132">
+        <v>2.18</v>
+      </c>
+      <c r="AQ132">
+        <v>1.73</v>
+      </c>
+      <c r="AR132">
+        <v>2.23</v>
+      </c>
+      <c r="AS132">
+        <v>1.54</v>
+      </c>
+      <c r="AT132">
+        <v>3.77</v>
+      </c>
+      <c r="AU132">
+        <v>4</v>
+      </c>
+      <c r="AV132">
+        <v>2</v>
+      </c>
+      <c r="AW132">
+        <v>5</v>
+      </c>
+      <c r="AX132">
+        <v>0</v>
+      </c>
+      <c r="AY132">
+        <v>9</v>
+      </c>
+      <c r="AZ132">
+        <v>2</v>
+      </c>
+      <c r="BA132">
+        <v>4</v>
+      </c>
+      <c r="BB132">
+        <v>5</v>
+      </c>
+      <c r="BC132">
+        <v>9</v>
+      </c>
+      <c r="BD132">
+        <v>1.39</v>
+      </c>
+      <c r="BE132">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF132">
+        <v>3.78</v>
+      </c>
+      <c r="BG132">
+        <v>1.18</v>
+      </c>
+      <c r="BH132">
+        <v>3.84</v>
+      </c>
+      <c r="BI132">
+        <v>1.38</v>
+      </c>
+      <c r="BJ132">
+        <v>2.71</v>
+      </c>
+      <c r="BK132">
+        <v>1.7</v>
+      </c>
+      <c r="BL132">
+        <v>2.12</v>
+      </c>
+      <c r="BM132">
+        <v>2.13</v>
+      </c>
+      <c r="BN132">
+        <v>1.69</v>
+      </c>
+      <c r="BO132">
+        <v>2.74</v>
+      </c>
+      <c r="BP132">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7482798</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45732.54166666666</v>
+      </c>
+      <c r="F133">
+        <v>22</v>
+      </c>
+      <c r="G133" t="s">
+        <v>74</v>
+      </c>
+      <c r="H133" t="s">
+        <v>70</v>
+      </c>
+      <c r="I133">
+        <v>3</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>3</v>
+      </c>
+      <c r="L133">
+        <v>3</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>3</v>
+      </c>
+      <c r="O133" t="s">
+        <v>181</v>
+      </c>
+      <c r="P133" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q133">
+        <v>1.83</v>
+      </c>
+      <c r="R133">
+        <v>2.5</v>
+      </c>
+      <c r="S133">
+        <v>7.5</v>
+      </c>
+      <c r="T133">
         <v>1.3</v>
       </c>
-      <c r="AM132">
-        <v>1.75</v>
-      </c>
-      <c r="AN132">
-        <v>2.3</v>
-      </c>
-      <c r="AO132">
-        <v>1.7</v>
-      </c>
-      <c r="AP132">
-        <v>2.36</v>
-      </c>
-      <c r="AQ132">
-        <v>1.55</v>
-      </c>
-      <c r="AR132">
+      <c r="U133">
+        <v>3.4</v>
+      </c>
+      <c r="V133">
+        <v>2.5</v>
+      </c>
+      <c r="W133">
+        <v>1.5</v>
+      </c>
+      <c r="X133">
+        <v>6</v>
+      </c>
+      <c r="Y133">
+        <v>1.13</v>
+      </c>
+      <c r="Z133">
+        <v>1.32</v>
+      </c>
+      <c r="AA133">
+        <v>5.1</v>
+      </c>
+      <c r="AB133">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AC133">
+        <v>1.02</v>
+      </c>
+      <c r="AD133">
+        <v>15.5</v>
+      </c>
+      <c r="AE133">
+        <v>1.2</v>
+      </c>
+      <c r="AF133">
+        <v>4.45</v>
+      </c>
+      <c r="AG133">
+        <v>1.6</v>
+      </c>
+      <c r="AH133">
+        <v>2.15</v>
+      </c>
+      <c r="AI133">
+        <v>1.95</v>
+      </c>
+      <c r="AJ133">
+        <v>1.8</v>
+      </c>
+      <c r="AK133">
+        <v>1.09</v>
+      </c>
+      <c r="AL133">
+        <v>1.16</v>
+      </c>
+      <c r="AM133">
+        <v>3</v>
+      </c>
+      <c r="AN133">
+        <v>2.2</v>
+      </c>
+      <c r="AO133">
+        <v>0.9</v>
+      </c>
+      <c r="AP133">
+        <v>2.27</v>
+      </c>
+      <c r="AQ133">
+        <v>0.82</v>
+      </c>
+      <c r="AR133">
+        <v>1.71</v>
+      </c>
+      <c r="AS133">
+        <v>1.13</v>
+      </c>
+      <c r="AT133">
+        <v>2.84</v>
+      </c>
+      <c r="AU133">
+        <v>6</v>
+      </c>
+      <c r="AV133">
+        <v>3</v>
+      </c>
+      <c r="AW133">
+        <v>9</v>
+      </c>
+      <c r="AX133">
+        <v>2</v>
+      </c>
+      <c r="AY133">
+        <v>19</v>
+      </c>
+      <c r="AZ133">
+        <v>6</v>
+      </c>
+      <c r="BA133">
+        <v>12</v>
+      </c>
+      <c r="BB133">
+        <v>4</v>
+      </c>
+      <c r="BC133">
+        <v>16</v>
+      </c>
+      <c r="BD133">
+        <v>1.16</v>
+      </c>
+      <c r="BE133">
+        <v>12.7</v>
+      </c>
+      <c r="BF133">
+        <v>6.87</v>
+      </c>
+      <c r="BG133">
+        <v>1.19</v>
+      </c>
+      <c r="BH133">
+        <v>3.75</v>
+      </c>
+      <c r="BI133">
+        <v>1.4</v>
+      </c>
+      <c r="BJ133">
+        <v>2.64</v>
+      </c>
+      <c r="BK133">
         <v>1.73</v>
       </c>
-      <c r="AS132">
-        <v>1.16</v>
-      </c>
-      <c r="AT132">
-        <v>2.89</v>
-      </c>
-      <c r="AU132">
-        <v>9</v>
-      </c>
-      <c r="AV132">
-        <v>5</v>
-      </c>
-      <c r="AW132">
-        <v>11</v>
-      </c>
-      <c r="AX132">
-        <v>3</v>
-      </c>
-      <c r="AY132">
-        <v>24</v>
-      </c>
-      <c r="AZ132">
-        <v>9</v>
-      </c>
-      <c r="BA132">
-        <v>9</v>
-      </c>
-      <c r="BB132">
-        <v>4</v>
-      </c>
-      <c r="BC132">
-        <v>13</v>
-      </c>
-      <c r="BD132">
-        <v>1.51</v>
-      </c>
-      <c r="BE132">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF132">
-        <v>3.24</v>
-      </c>
-      <c r="BG132">
-        <v>1.28</v>
-      </c>
-      <c r="BH132">
-        <v>3.08</v>
-      </c>
-      <c r="BI132">
-        <v>1.57</v>
-      </c>
-      <c r="BJ132">
-        <v>2.34</v>
-      </c>
-      <c r="BK132">
-        <v>1.95</v>
-      </c>
-      <c r="BL132">
-        <v>1.84</v>
-      </c>
-      <c r="BM132">
-        <v>2.49</v>
-      </c>
-      <c r="BN132">
-        <v>1.5</v>
-      </c>
-      <c r="BO132">
-        <v>3.42</v>
-      </c>
-      <c r="BP132">
-        <v>1.23</v>
+      <c r="BL133">
+        <v>2.06</v>
+      </c>
+      <c r="BM133">
+        <v>2.16</v>
+      </c>
+      <c r="BN133">
+        <v>1.66</v>
+      </c>
+      <c r="BO133">
+        <v>2.78</v>
+      </c>
+      <c r="BP133">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="253">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -771,6 +771,9 @@
   <si>
     <t>['77', '85']</t>
   </si>
+  <si>
+    <t>['28', '59']</t>
+  </si>
 </sst>
 </file>
 
@@ -1131,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP133"/>
+  <dimension ref="A1:BP134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1671,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ3">
         <v>0.91</v>
@@ -1880,7 +1883,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ4">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -4967,7 +4970,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ19">
         <v>1.73</v>
@@ -5794,7 +5797,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ23">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR23">
         <v>1.73</v>
@@ -7233,7 +7236,7 @@
         <v>0.5</v>
       </c>
       <c r="AP30">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ30">
         <v>1.64</v>
@@ -7648,7 +7651,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ32">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR32">
         <v>1.09</v>
@@ -8057,7 +8060,7 @@
         <v>0.33</v>
       </c>
       <c r="AP34">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ34">
         <v>1.09</v>
@@ -10120,7 +10123,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ44">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR44">
         <v>1.82</v>
@@ -11765,7 +11768,7 @@
         <v>0.67</v>
       </c>
       <c r="AP52">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ52">
         <v>0.82</v>
@@ -13004,7 +13007,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ58">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR58">
         <v>1</v>
@@ -13619,7 +13622,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ61">
         <v>0.73</v>
@@ -16709,10 +16712,10 @@
         <v>1.4</v>
       </c>
       <c r="AP76">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ76">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR76">
         <v>1.31</v>
@@ -17124,7 +17127,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ78">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR78">
         <v>2.16</v>
@@ -18357,7 +18360,7 @@
         <v>2.17</v>
       </c>
       <c r="AP84">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ84">
         <v>1.82</v>
@@ -19802,7 +19805,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ91">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR91">
         <v>1.53</v>
@@ -21653,7 +21656,7 @@
         <v>0.75</v>
       </c>
       <c r="AP100">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ100">
         <v>0.82</v>
@@ -23098,7 +23101,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ107">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR107">
         <v>1.33</v>
@@ -24537,7 +24540,7 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ114">
         <v>0.91</v>
@@ -25570,7 +25573,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ119">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR119">
         <v>1.39</v>
@@ -26803,7 +26806,7 @@
         <v>1.3</v>
       </c>
       <c r="AP125">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ125">
         <v>1.27</v>
@@ -28042,7 +28045,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ131">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR131">
         <v>1.73</v>
@@ -28530,6 +28533,212 @@
       </c>
       <c r="BP133">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7859403</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45744.64583333334</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+      <c r="G134" t="s">
+        <v>71</v>
+      </c>
+      <c r="H134" t="s">
+        <v>76</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>1</v>
+      </c>
+      <c r="K134">
+        <v>1</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>2</v>
+      </c>
+      <c r="N134">
+        <v>2</v>
+      </c>
+      <c r="O134" t="s">
+        <v>89</v>
+      </c>
+      <c r="P134" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q134">
+        <v>3.75</v>
+      </c>
+      <c r="R134">
+        <v>2.1</v>
+      </c>
+      <c r="S134">
+        <v>3</v>
+      </c>
+      <c r="T134">
+        <v>1.44</v>
+      </c>
+      <c r="U134">
+        <v>2.63</v>
+      </c>
+      <c r="V134">
+        <v>3.25</v>
+      </c>
+      <c r="W134">
+        <v>1.33</v>
+      </c>
+      <c r="X134">
+        <v>9</v>
+      </c>
+      <c r="Y134">
+        <v>1.07</v>
+      </c>
+      <c r="Z134">
+        <v>3.09</v>
+      </c>
+      <c r="AA134">
+        <v>3.39</v>
+      </c>
+      <c r="AB134">
+        <v>2.21</v>
+      </c>
+      <c r="AC134">
+        <v>1.06</v>
+      </c>
+      <c r="AD134">
+        <v>8.5</v>
+      </c>
+      <c r="AE134">
+        <v>1.33</v>
+      </c>
+      <c r="AF134">
+        <v>3.27</v>
+      </c>
+      <c r="AG134">
+        <v>1.98</v>
+      </c>
+      <c r="AH134">
+        <v>1.77</v>
+      </c>
+      <c r="AI134">
+        <v>1.8</v>
+      </c>
+      <c r="AJ134">
+        <v>1.95</v>
+      </c>
+      <c r="AK134">
+        <v>1.62</v>
+      </c>
+      <c r="AL134">
+        <v>1.31</v>
+      </c>
+      <c r="AM134">
+        <v>1.35</v>
+      </c>
+      <c r="AN134">
+        <v>0.73</v>
+      </c>
+      <c r="AO134">
+        <v>1.55</v>
+      </c>
+      <c r="AP134">
+        <v>0.67</v>
+      </c>
+      <c r="AQ134">
+        <v>1.67</v>
+      </c>
+      <c r="AR134">
+        <v>1.26</v>
+      </c>
+      <c r="AS134">
+        <v>1.15</v>
+      </c>
+      <c r="AT134">
+        <v>2.41</v>
+      </c>
+      <c r="AU134">
+        <v>6</v>
+      </c>
+      <c r="AV134">
+        <v>4</v>
+      </c>
+      <c r="AW134">
+        <v>8</v>
+      </c>
+      <c r="AX134">
+        <v>3</v>
+      </c>
+      <c r="AY134">
+        <v>15</v>
+      </c>
+      <c r="AZ134">
+        <v>8</v>
+      </c>
+      <c r="BA134">
+        <v>7</v>
+      </c>
+      <c r="BB134">
+        <v>1</v>
+      </c>
+      <c r="BC134">
+        <v>8</v>
+      </c>
+      <c r="BD134">
+        <v>2</v>
+      </c>
+      <c r="BE134">
+        <v>6.3</v>
+      </c>
+      <c r="BF134">
+        <v>2.3</v>
+      </c>
+      <c r="BG134">
+        <v>1.31</v>
+      </c>
+      <c r="BH134">
+        <v>2.92</v>
+      </c>
+      <c r="BI134">
+        <v>1.59</v>
+      </c>
+      <c r="BJ134">
+        <v>2.16</v>
+      </c>
+      <c r="BK134">
+        <v>1.95</v>
+      </c>
+      <c r="BL134">
+        <v>1.77</v>
+      </c>
+      <c r="BM134">
+        <v>2.67</v>
+      </c>
+      <c r="BN134">
+        <v>1.39</v>
+      </c>
+      <c r="BO134">
+        <v>3.58</v>
+      </c>
+      <c r="BP134">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="257">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -562,6 +562,9 @@
     <t>['23', '32', '44']</t>
   </si>
   <si>
+    <t>['12', '71']</t>
+  </si>
+  <si>
     <t>['4', '6', '45+2']</t>
   </si>
   <si>
@@ -773,6 +776,15 @@
   </si>
   <si>
     <t>['28', '59']</t>
+  </si>
+  <si>
+    <t>['45+2', '63', '84']</t>
+  </si>
+  <si>
+    <t>['2', '17']</t>
+  </si>
+  <si>
+    <t>['37', '48']</t>
   </si>
 </sst>
 </file>
@@ -1134,7 +1146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP134"/>
+  <dimension ref="A1:BP139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1390,7 +1402,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q2">
         <v>7</v>
@@ -1468,10 +1480,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ2">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1596,7 +1608,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1677,7 +1689,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ3">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1802,7 +1814,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -1880,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4">
         <v>1.67</v>
@@ -2086,10 +2098,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2292,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ6">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2498,10 +2510,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ7">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2626,7 +2638,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q8">
         <v>2.1</v>
@@ -3038,7 +3050,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q10">
         <v>1.67</v>
@@ -3862,7 +3874,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3940,7 +3952,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ14">
         <v>1.09</v>
@@ -4068,7 +4080,7 @@
         <v>89</v>
       </c>
       <c r="P15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q15">
         <v>5.5</v>
@@ -4149,7 +4161,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ15">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR15">
         <v>0.52</v>
@@ -4274,7 +4286,7 @@
         <v>89</v>
       </c>
       <c r="P16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q16">
         <v>3.8</v>
@@ -4355,7 +4367,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ16">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR16">
         <v>1.73</v>
@@ -4558,10 +4570,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ17">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR17">
         <v>1.09</v>
@@ -4764,10 +4776,10 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ18">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR18">
         <v>1.7</v>
@@ -5098,7 +5110,7 @@
         <v>89</v>
       </c>
       <c r="P20" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5179,7 +5191,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ20">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR20">
         <v>0.78</v>
@@ -5304,7 +5316,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q21">
         <v>2.03</v>
@@ -5510,7 +5522,7 @@
         <v>99</v>
       </c>
       <c r="P22" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q22">
         <v>2.4</v>
@@ -5588,7 +5600,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ22">
         <v>0.82</v>
@@ -5716,7 +5728,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -6000,7 +6012,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ24">
         <v>0.82</v>
@@ -6128,7 +6140,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6412,7 +6424,7 @@
         <v>0.5</v>
       </c>
       <c r="AP26">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ26">
         <v>0.82</v>
@@ -6540,7 +6552,7 @@
         <v>104</v>
       </c>
       <c r="P27" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6621,7 +6633,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ27">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR27">
         <v>1.97</v>
@@ -6746,7 +6758,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -6952,7 +6964,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q29">
         <v>4.33</v>
@@ -7030,10 +7042,10 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ29">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR29">
         <v>1.88</v>
@@ -7239,7 +7251,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ30">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR30">
         <v>1.18</v>
@@ -7442,7 +7454,7 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ31">
         <v>0.82</v>
@@ -7648,7 +7660,7 @@
         <v>1.5</v>
       </c>
       <c r="AP32">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ32">
         <v>1.67</v>
@@ -7776,7 +7788,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -7854,7 +7866,7 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ33">
         <v>0.73</v>
@@ -7982,7 +7994,7 @@
         <v>89</v>
       </c>
       <c r="P34" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8188,7 +8200,7 @@
         <v>111</v>
       </c>
       <c r="P35" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8394,7 +8406,7 @@
         <v>112</v>
       </c>
       <c r="P36" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q36">
         <v>2.1</v>
@@ -8600,7 +8612,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q37">
         <v>2.2</v>
@@ -8887,7 +8899,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ38">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR38">
         <v>1</v>
@@ -9012,7 +9024,7 @@
         <v>113</v>
       </c>
       <c r="P39" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9090,10 +9102,10 @@
         <v>0.67</v>
       </c>
       <c r="AP39">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ39">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR39">
         <v>1.72</v>
@@ -9218,7 +9230,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q40">
         <v>3.6</v>
@@ -9299,7 +9311,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ40">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR40">
         <v>1.88</v>
@@ -9502,10 +9514,10 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ41">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR41">
         <v>1.23</v>
@@ -9630,7 +9642,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9708,10 +9720,10 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ42">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR42">
         <v>1.32</v>
@@ -9917,7 +9929,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ43">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR43">
         <v>2.5</v>
@@ -10042,7 +10054,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q44">
         <v>2.4</v>
@@ -10120,7 +10132,7 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ44">
         <v>1.67</v>
@@ -10248,7 +10260,7 @@
         <v>119</v>
       </c>
       <c r="P45" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q45">
         <v>2.2</v>
@@ -10326,10 +10338,10 @@
         <v>0.75</v>
       </c>
       <c r="AP45">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ45">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR45">
         <v>1.79</v>
@@ -10532,7 +10544,7 @@
         <v>1.33</v>
       </c>
       <c r="AP46">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ46">
         <v>0.73</v>
@@ -10660,7 +10672,7 @@
         <v>89</v>
       </c>
       <c r="P47" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10738,10 +10750,10 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ47">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR47">
         <v>1.52</v>
@@ -10866,7 +10878,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -10944,7 +10956,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ48">
         <v>0.91</v>
@@ -11565,7 +11577,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ51">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR51">
         <v>1.44</v>
@@ -11690,7 +11702,7 @@
         <v>89</v>
       </c>
       <c r="P52" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -11977,7 +11989,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ53">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR53">
         <v>1.83</v>
@@ -12102,7 +12114,7 @@
         <v>89</v>
       </c>
       <c r="P54" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12180,7 +12192,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ54">
         <v>1.73</v>
@@ -12308,7 +12320,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q55">
         <v>1.95</v>
@@ -12720,7 +12732,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12801,7 +12813,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ57">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR57">
         <v>1.44</v>
@@ -12926,7 +12938,7 @@
         <v>109</v>
       </c>
       <c r="P58" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q58">
         <v>4</v>
@@ -13132,7 +13144,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q59">
         <v>2.1</v>
@@ -13210,7 +13222,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ59">
         <v>0.91</v>
@@ -13419,7 +13431,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ60">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR60">
         <v>1.68</v>
@@ -13625,7 +13637,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ61">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR61">
         <v>1.23</v>
@@ -13750,7 +13762,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -13828,7 +13840,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ62">
         <v>1.09</v>
@@ -14034,10 +14046,10 @@
         <v>1.4</v>
       </c>
       <c r="AP63">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ63">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR63">
         <v>1.65</v>
@@ -14240,7 +14252,7 @@
         <v>1.25</v>
       </c>
       <c r="AP64">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ64">
         <v>0.82</v>
@@ -14368,7 +14380,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q65">
         <v>3.25</v>
@@ -14449,7 +14461,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ65">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -14574,7 +14586,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14780,7 +14792,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q67">
         <v>2.88</v>
@@ -15810,7 +15822,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -15888,10 +15900,10 @@
         <v>0.83</v>
       </c>
       <c r="AP72">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ72">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR72">
         <v>1.52</v>
@@ -16094,10 +16106,10 @@
         <v>1</v>
       </c>
       <c r="AP73">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ73">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR73">
         <v>1.44</v>
@@ -16222,7 +16234,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q74">
         <v>3.75</v>
@@ -16300,10 +16312,10 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ74">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR74">
         <v>1.16</v>
@@ -16506,10 +16518,10 @@
         <v>1.33</v>
       </c>
       <c r="AP75">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ75">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR75">
         <v>1.32</v>
@@ -16634,7 +16646,7 @@
         <v>142</v>
       </c>
       <c r="P76" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16918,10 +16930,10 @@
         <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ77">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR77">
         <v>1.67</v>
@@ -17046,7 +17058,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q78">
         <v>2.2</v>
@@ -17539,7 +17551,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ80">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR80">
         <v>1.71</v>
@@ -17742,7 +17754,7 @@
         <v>0.67</v>
       </c>
       <c r="AP81">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81">
         <v>0.73</v>
@@ -17870,7 +17882,7 @@
         <v>147</v>
       </c>
       <c r="P82" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q82">
         <v>2.88</v>
@@ -17948,7 +17960,7 @@
         <v>0.43</v>
       </c>
       <c r="AP82">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ82">
         <v>0.82</v>
@@ -18282,7 +18294,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q84">
         <v>5.5</v>
@@ -18363,7 +18375,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ84">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR84">
         <v>1.26</v>
@@ -18488,7 +18500,7 @@
         <v>119</v>
       </c>
       <c r="P85" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18566,10 +18578,10 @@
         <v>1.14</v>
       </c>
       <c r="AP85">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ85">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR85">
         <v>1.2</v>
@@ -18694,7 +18706,7 @@
         <v>149</v>
       </c>
       <c r="P86" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q86">
         <v>3.4</v>
@@ -18772,7 +18784,7 @@
         <v>1.5</v>
       </c>
       <c r="AP86">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ86">
         <v>1.73</v>
@@ -18900,7 +18912,7 @@
         <v>89</v>
       </c>
       <c r="P87" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q87">
         <v>2.75</v>
@@ -18981,7 +18993,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ87">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR87">
         <v>1.29</v>
@@ -19184,7 +19196,7 @@
         <v>0.71</v>
       </c>
       <c r="AP88">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ88">
         <v>1.09</v>
@@ -19312,7 +19324,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19393,7 +19405,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ89">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR89">
         <v>1.4</v>
@@ -19724,7 +19736,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -19802,7 +19814,7 @@
         <v>1.86</v>
       </c>
       <c r="AP91">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ91">
         <v>1.67</v>
@@ -19930,7 +19942,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q92">
         <v>6</v>
@@ -20011,7 +20023,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ92">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR92">
         <v>0.89</v>
@@ -20136,7 +20148,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q93">
         <v>2.4</v>
@@ -20342,7 +20354,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q94">
         <v>2.6</v>
@@ -20420,10 +20432,10 @@
         <v>1</v>
       </c>
       <c r="AP94">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ94">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR94">
         <v>1.33</v>
@@ -20548,7 +20560,7 @@
         <v>89</v>
       </c>
       <c r="P95" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20626,7 +20638,7 @@
         <v>0.71</v>
       </c>
       <c r="AP95">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ95">
         <v>0.91</v>
@@ -21041,7 +21053,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ97">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR97">
         <v>2.11</v>
@@ -21166,7 +21178,7 @@
         <v>157</v>
       </c>
       <c r="P98" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q98">
         <v>2.5</v>
@@ -21247,7 +21259,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ98">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR98">
         <v>1.71</v>
@@ -21372,7 +21384,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q99">
         <v>2.3</v>
@@ -21450,7 +21462,7 @@
         <v>1.71</v>
       </c>
       <c r="AP99">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ99">
         <v>1.73</v>
@@ -21578,7 +21590,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21865,7 +21877,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ101">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR101">
         <v>1.37</v>
@@ -22402,7 +22414,7 @@
         <v>103</v>
       </c>
       <c r="P104" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q104">
         <v>2.75</v>
@@ -22480,7 +22492,7 @@
         <v>0.5</v>
       </c>
       <c r="AP104">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ104">
         <v>0.73</v>
@@ -22686,10 +22698,10 @@
         <v>2.13</v>
       </c>
       <c r="AP105">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ105">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR105">
         <v>1.48</v>
@@ -22814,7 +22826,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q106">
         <v>1.67</v>
@@ -22895,7 +22907,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ106">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR106">
         <v>2.12</v>
@@ -23098,7 +23110,7 @@
         <v>1.63</v>
       </c>
       <c r="AP107">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ107">
         <v>1.67</v>
@@ -23304,10 +23316,10 @@
         <v>0.78</v>
       </c>
       <c r="AP108">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ108">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR108">
         <v>1.12</v>
@@ -23638,7 +23650,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23719,7 +23731,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ110">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR110">
         <v>1.61</v>
@@ -23844,7 +23856,7 @@
         <v>164</v>
       </c>
       <c r="P111" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q111">
         <v>3.1</v>
@@ -24050,7 +24062,7 @@
         <v>165</v>
       </c>
       <c r="P112" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q112">
         <v>4.53</v>
@@ -24668,7 +24680,7 @@
         <v>167</v>
       </c>
       <c r="P115" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -24874,7 +24886,7 @@
         <v>89</v>
       </c>
       <c r="P116" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -24952,7 +24964,7 @@
         <v>1.78</v>
       </c>
       <c r="AP116">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ116">
         <v>1.73</v>
@@ -25080,7 +25092,7 @@
         <v>168</v>
       </c>
       <c r="P117" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25158,10 +25170,10 @@
         <v>1.33</v>
       </c>
       <c r="AP117">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ117">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR117">
         <v>1.34</v>
@@ -25364,7 +25376,7 @@
         <v>0.78</v>
       </c>
       <c r="AP118">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ118">
         <v>0.73</v>
@@ -25492,7 +25504,7 @@
         <v>91</v>
       </c>
       <c r="P119" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q119">
         <v>4.33</v>
@@ -25776,10 +25788,10 @@
         <v>1.11</v>
       </c>
       <c r="AP120">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ120">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR120">
         <v>1.3</v>
@@ -25904,7 +25916,7 @@
         <v>171</v>
       </c>
       <c r="P121" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q121">
         <v>2.6</v>
@@ -25985,7 +25997,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ121">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR121">
         <v>2.18</v>
@@ -26110,7 +26122,7 @@
         <v>172</v>
       </c>
       <c r="P122" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q122">
         <v>2.38</v>
@@ -26191,7 +26203,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ122">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR122">
         <v>1.49</v>
@@ -26316,7 +26328,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q123">
         <v>2.6</v>
@@ -26394,7 +26406,7 @@
         <v>0.9</v>
       </c>
       <c r="AP123">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ123">
         <v>1.09</v>
@@ -26603,7 +26615,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ124">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR124">
         <v>1.58</v>
@@ -26728,7 +26740,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q125">
         <v>5.5</v>
@@ -26809,7 +26821,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ125">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR125">
         <v>1.29</v>
@@ -26934,7 +26946,7 @@
         <v>87</v>
       </c>
       <c r="P126" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27012,10 +27024,10 @@
         <v>1.7</v>
       </c>
       <c r="AP126">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ126">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR126">
         <v>1.33</v>
@@ -27140,7 +27152,7 @@
         <v>176</v>
       </c>
       <c r="P127" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q127">
         <v>4.5</v>
@@ -27218,7 +27230,7 @@
         <v>0.9</v>
       </c>
       <c r="AP127">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ127">
         <v>0.82</v>
@@ -27346,7 +27358,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q128">
         <v>3.5</v>
@@ -27552,7 +27564,7 @@
         <v>89</v>
       </c>
       <c r="P129" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q129">
         <v>5.5</v>
@@ -27633,7 +27645,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ129">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR129">
         <v>1.05</v>
@@ -27836,7 +27848,7 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ130">
         <v>0.91</v>
@@ -27964,7 +27976,7 @@
         <v>179</v>
       </c>
       <c r="P131" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q131">
         <v>2.6</v>
@@ -28454,7 +28466,7 @@
         <v>0.9</v>
       </c>
       <c r="AP133">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ133">
         <v>0.82</v>
@@ -28582,7 +28594,7 @@
         <v>89</v>
       </c>
       <c r="P134" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28739,6 +28751,1036 @@
       </c>
       <c r="BP134">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7859404</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45745.54166666666</v>
+      </c>
+      <c r="F135">
+        <v>1</v>
+      </c>
+      <c r="G135" t="s">
+        <v>70</v>
+      </c>
+      <c r="H135" t="s">
+        <v>77</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135" t="s">
+        <v>89</v>
+      </c>
+      <c r="P135" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q135">
+        <v>3</v>
+      </c>
+      <c r="R135">
+        <v>2.1</v>
+      </c>
+      <c r="S135">
+        <v>3.75</v>
+      </c>
+      <c r="T135">
+        <v>1.44</v>
+      </c>
+      <c r="U135">
+        <v>2.63</v>
+      </c>
+      <c r="V135">
+        <v>3.25</v>
+      </c>
+      <c r="W135">
+        <v>1.33</v>
+      </c>
+      <c r="X135">
+        <v>9</v>
+      </c>
+      <c r="Y135">
+        <v>1.07</v>
+      </c>
+      <c r="Z135">
+        <v>2.31</v>
+      </c>
+      <c r="AA135">
+        <v>3.17</v>
+      </c>
+      <c r="AB135">
+        <v>3.1</v>
+      </c>
+      <c r="AC135">
+        <v>1.06</v>
+      </c>
+      <c r="AD135">
+        <v>8.25</v>
+      </c>
+      <c r="AE135">
+        <v>1.38</v>
+      </c>
+      <c r="AF135">
+        <v>3</v>
+      </c>
+      <c r="AG135">
+        <v>1.91</v>
+      </c>
+      <c r="AH135">
+        <v>1.73</v>
+      </c>
+      <c r="AI135">
+        <v>1.8</v>
+      </c>
+      <c r="AJ135">
+        <v>1.95</v>
+      </c>
+      <c r="AK135">
+        <v>1.37</v>
+      </c>
+      <c r="AL135">
+        <v>1.31</v>
+      </c>
+      <c r="AM135">
+        <v>1.58</v>
+      </c>
+      <c r="AN135">
+        <v>0.64</v>
+      </c>
+      <c r="AO135">
+        <v>0.91</v>
+      </c>
+      <c r="AP135">
+        <v>0.67</v>
+      </c>
+      <c r="AQ135">
+        <v>0.92</v>
+      </c>
+      <c r="AR135">
+        <v>1.31</v>
+      </c>
+      <c r="AS135">
+        <v>1.1</v>
+      </c>
+      <c r="AT135">
+        <v>2.41</v>
+      </c>
+      <c r="AU135">
+        <v>4</v>
+      </c>
+      <c r="AV135">
+        <v>6</v>
+      </c>
+      <c r="AW135">
+        <v>9</v>
+      </c>
+      <c r="AX135">
+        <v>6</v>
+      </c>
+      <c r="AY135">
+        <v>13</v>
+      </c>
+      <c r="AZ135">
+        <v>12</v>
+      </c>
+      <c r="BA135">
+        <v>5</v>
+      </c>
+      <c r="BB135">
+        <v>5</v>
+      </c>
+      <c r="BC135">
+        <v>10</v>
+      </c>
+      <c r="BD135">
+        <v>1.84</v>
+      </c>
+      <c r="BE135">
+        <v>6.45</v>
+      </c>
+      <c r="BF135">
+        <v>2.53</v>
+      </c>
+      <c r="BG135">
+        <v>1.28</v>
+      </c>
+      <c r="BH135">
+        <v>3.08</v>
+      </c>
+      <c r="BI135">
+        <v>1.54</v>
+      </c>
+      <c r="BJ135">
+        <v>2.25</v>
+      </c>
+      <c r="BK135">
+        <v>1.95</v>
+      </c>
+      <c r="BL135">
+        <v>1.77</v>
+      </c>
+      <c r="BM135">
+        <v>2.54</v>
+      </c>
+      <c r="BN135">
+        <v>1.43</v>
+      </c>
+      <c r="BO135">
+        <v>3.42</v>
+      </c>
+      <c r="BP135">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="136" spans="1:68">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>7859405</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45745.54166666666</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+      <c r="G136" t="s">
+        <v>72</v>
+      </c>
+      <c r="H136" t="s">
+        <v>79</v>
+      </c>
+      <c r="I136">
+        <v>1</v>
+      </c>
+      <c r="J136">
+        <v>1</v>
+      </c>
+      <c r="K136">
+        <v>2</v>
+      </c>
+      <c r="L136">
+        <v>2</v>
+      </c>
+      <c r="M136">
+        <v>3</v>
+      </c>
+      <c r="N136">
+        <v>5</v>
+      </c>
+      <c r="O136" t="s">
+        <v>182</v>
+      </c>
+      <c r="P136" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q136">
+        <v>2.5</v>
+      </c>
+      <c r="R136">
+        <v>2.25</v>
+      </c>
+      <c r="S136">
+        <v>4.33</v>
+      </c>
+      <c r="T136">
+        <v>1.36</v>
+      </c>
+      <c r="U136">
+        <v>3</v>
+      </c>
+      <c r="V136">
+        <v>2.63</v>
+      </c>
+      <c r="W136">
+        <v>1.44</v>
+      </c>
+      <c r="X136">
+        <v>7</v>
+      </c>
+      <c r="Y136">
+        <v>1.1</v>
+      </c>
+      <c r="Z136">
+        <v>1.97</v>
+      </c>
+      <c r="AA136">
+        <v>3.63</v>
+      </c>
+      <c r="AB136">
+        <v>3.47</v>
+      </c>
+      <c r="AC136">
+        <v>1.04</v>
+      </c>
+      <c r="AD136">
+        <v>9.5</v>
+      </c>
+      <c r="AE136">
+        <v>1.28</v>
+      </c>
+      <c r="AF136">
+        <v>3.68</v>
+      </c>
+      <c r="AG136">
+        <v>1.83</v>
+      </c>
+      <c r="AH136">
+        <v>1.91</v>
+      </c>
+      <c r="AI136">
+        <v>1.67</v>
+      </c>
+      <c r="AJ136">
+        <v>2.1</v>
+      </c>
+      <c r="AK136">
+        <v>1.26</v>
+      </c>
+      <c r="AL136">
+        <v>1.29</v>
+      </c>
+      <c r="AM136">
+        <v>1.82</v>
+      </c>
+      <c r="AN136">
+        <v>1.45</v>
+      </c>
+      <c r="AO136">
+        <v>0.73</v>
+      </c>
+      <c r="AP136">
+        <v>1.33</v>
+      </c>
+      <c r="AQ136">
+        <v>0.92</v>
+      </c>
+      <c r="AR136">
+        <v>1.16</v>
+      </c>
+      <c r="AS136">
+        <v>1</v>
+      </c>
+      <c r="AT136">
+        <v>2.16</v>
+      </c>
+      <c r="AU136">
+        <v>6</v>
+      </c>
+      <c r="AV136">
+        <v>8</v>
+      </c>
+      <c r="AW136">
+        <v>12</v>
+      </c>
+      <c r="AX136">
+        <v>12</v>
+      </c>
+      <c r="AY136">
+        <v>19</v>
+      </c>
+      <c r="AZ136">
+        <v>22</v>
+      </c>
+      <c r="BA136">
+        <v>7</v>
+      </c>
+      <c r="BB136">
+        <v>3</v>
+      </c>
+      <c r="BC136">
+        <v>10</v>
+      </c>
+      <c r="BD136">
+        <v>1.65</v>
+      </c>
+      <c r="BE136">
+        <v>6.75</v>
+      </c>
+      <c r="BF136">
+        <v>2.95</v>
+      </c>
+      <c r="BG136">
+        <v>1.27</v>
+      </c>
+      <c r="BH136">
+        <v>3.14</v>
+      </c>
+      <c r="BI136">
+        <v>1.52</v>
+      </c>
+      <c r="BJ136">
+        <v>2.3</v>
+      </c>
+      <c r="BK136">
+        <v>1.85</v>
+      </c>
+      <c r="BL136">
+        <v>1.83</v>
+      </c>
+      <c r="BM136">
+        <v>2.5</v>
+      </c>
+      <c r="BN136">
+        <v>1.44</v>
+      </c>
+      <c r="BO136">
+        <v>3.34</v>
+      </c>
+      <c r="BP136">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="137" spans="1:68">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>7859407</v>
+      </c>
+      <c r="C137" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" t="s">
+        <v>69</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45746.39583333334</v>
+      </c>
+      <c r="F137">
+        <v>1</v>
+      </c>
+      <c r="G137" t="s">
+        <v>75</v>
+      </c>
+      <c r="H137" t="s">
+        <v>80</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>2</v>
+      </c>
+      <c r="K137">
+        <v>2</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>2</v>
+      </c>
+      <c r="N137">
+        <v>2</v>
+      </c>
+      <c r="O137" t="s">
+        <v>89</v>
+      </c>
+      <c r="P137" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q137">
+        <v>3.75</v>
+      </c>
+      <c r="R137">
+        <v>2.05</v>
+      </c>
+      <c r="S137">
+        <v>3.1</v>
+      </c>
+      <c r="T137">
+        <v>1.44</v>
+      </c>
+      <c r="U137">
+        <v>2.63</v>
+      </c>
+      <c r="V137">
+        <v>3.4</v>
+      </c>
+      <c r="W137">
+        <v>1.3</v>
+      </c>
+      <c r="X137">
+        <v>10</v>
+      </c>
+      <c r="Y137">
+        <v>1.06</v>
+      </c>
+      <c r="Z137">
+        <v>3.05</v>
+      </c>
+      <c r="AA137">
+        <v>3.15</v>
+      </c>
+      <c r="AB137">
+        <v>2.36</v>
+      </c>
+      <c r="AC137">
+        <v>1.06</v>
+      </c>
+      <c r="AD137">
+        <v>8.25</v>
+      </c>
+      <c r="AE137">
+        <v>1.39</v>
+      </c>
+      <c r="AF137">
+        <v>2.99</v>
+      </c>
+      <c r="AG137">
+        <v>1.85</v>
+      </c>
+      <c r="AH137">
+        <v>1.75</v>
+      </c>
+      <c r="AI137">
+        <v>1.91</v>
+      </c>
+      <c r="AJ137">
+        <v>1.91</v>
+      </c>
+      <c r="AK137">
+        <v>1.57</v>
+      </c>
+      <c r="AL137">
+        <v>1.31</v>
+      </c>
+      <c r="AM137">
+        <v>1.39</v>
+      </c>
+      <c r="AN137">
+        <v>1.91</v>
+      </c>
+      <c r="AO137">
+        <v>1.64</v>
+      </c>
+      <c r="AP137">
+        <v>1.75</v>
+      </c>
+      <c r="AQ137">
+        <v>1.75</v>
+      </c>
+      <c r="AR137">
+        <v>1.48</v>
+      </c>
+      <c r="AS137">
+        <v>1.3</v>
+      </c>
+      <c r="AT137">
+        <v>2.78</v>
+      </c>
+      <c r="AU137">
+        <v>3</v>
+      </c>
+      <c r="AV137">
+        <v>4</v>
+      </c>
+      <c r="AW137">
+        <v>12</v>
+      </c>
+      <c r="AX137">
+        <v>3</v>
+      </c>
+      <c r="AY137">
+        <v>17</v>
+      </c>
+      <c r="AZ137">
+        <v>7</v>
+      </c>
+      <c r="BA137">
+        <v>3</v>
+      </c>
+      <c r="BB137">
+        <v>3</v>
+      </c>
+      <c r="BC137">
+        <v>6</v>
+      </c>
+      <c r="BD137">
+        <v>2.22</v>
+      </c>
+      <c r="BE137">
+        <v>6.35</v>
+      </c>
+      <c r="BF137">
+        <v>2.06</v>
+      </c>
+      <c r="BG137">
+        <v>1.3</v>
+      </c>
+      <c r="BH137">
+        <v>2.97</v>
+      </c>
+      <c r="BI137">
+        <v>1.57</v>
+      </c>
+      <c r="BJ137">
+        <v>2.19</v>
+      </c>
+      <c r="BK137">
+        <v>1.95</v>
+      </c>
+      <c r="BL137">
+        <v>1.77</v>
+      </c>
+      <c r="BM137">
+        <v>2.6</v>
+      </c>
+      <c r="BN137">
+        <v>1.41</v>
+      </c>
+      <c r="BO137">
+        <v>3.58</v>
+      </c>
+      <c r="BP137">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="138" spans="1:68">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>7859406</v>
+      </c>
+      <c r="C138" t="s">
+        <v>68</v>
+      </c>
+      <c r="D138" t="s">
+        <v>69</v>
+      </c>
+      <c r="E138" s="2">
+        <v>45746.39583333334</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="G138" t="s">
+        <v>73</v>
+      </c>
+      <c r="H138" t="s">
+        <v>81</v>
+      </c>
+      <c r="I138">
+        <v>1</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>1</v>
+      </c>
+      <c r="L138">
+        <v>1</v>
+      </c>
+      <c r="M138">
+        <v>1</v>
+      </c>
+      <c r="N138">
+        <v>2</v>
+      </c>
+      <c r="O138" t="s">
+        <v>91</v>
+      </c>
+      <c r="P138" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q138">
+        <v>3.4</v>
+      </c>
+      <c r="R138">
+        <v>2.25</v>
+      </c>
+      <c r="S138">
+        <v>3</v>
+      </c>
+      <c r="T138">
+        <v>1.33</v>
+      </c>
+      <c r="U138">
+        <v>3.25</v>
+      </c>
+      <c r="V138">
+        <v>2.63</v>
+      </c>
+      <c r="W138">
+        <v>1.44</v>
+      </c>
+      <c r="X138">
+        <v>7</v>
+      </c>
+      <c r="Y138">
+        <v>1.1</v>
+      </c>
+      <c r="Z138">
+        <v>2.84</v>
+      </c>
+      <c r="AA138">
+        <v>3.4</v>
+      </c>
+      <c r="AB138">
+        <v>2.36</v>
+      </c>
+      <c r="AC138">
+        <v>1.03</v>
+      </c>
+      <c r="AD138">
+        <v>11</v>
+      </c>
+      <c r="AE138">
+        <v>1.22</v>
+      </c>
+      <c r="AF138">
+        <v>4.28</v>
+      </c>
+      <c r="AG138">
+        <v>1.8</v>
+      </c>
+      <c r="AH138">
+        <v>1.92</v>
+      </c>
+      <c r="AI138">
+        <v>1.62</v>
+      </c>
+      <c r="AJ138">
+        <v>2.2</v>
+      </c>
+      <c r="AK138">
+        <v>1.58</v>
+      </c>
+      <c r="AL138">
+        <v>1.28</v>
+      </c>
+      <c r="AM138">
+        <v>1.41</v>
+      </c>
+      <c r="AN138">
+        <v>1.55</v>
+      </c>
+      <c r="AO138">
+        <v>1.82</v>
+      </c>
+      <c r="AP138">
+        <v>1.5</v>
+      </c>
+      <c r="AQ138">
+        <v>1.75</v>
+      </c>
+      <c r="AR138">
+        <v>1.54</v>
+      </c>
+      <c r="AS138">
+        <v>1.38</v>
+      </c>
+      <c r="AT138">
+        <v>2.92</v>
+      </c>
+      <c r="AU138">
+        <v>4</v>
+      </c>
+      <c r="AV138">
+        <v>3</v>
+      </c>
+      <c r="AW138">
+        <v>8</v>
+      </c>
+      <c r="AX138">
+        <v>9</v>
+      </c>
+      <c r="AY138">
+        <v>14</v>
+      </c>
+      <c r="AZ138">
+        <v>14</v>
+      </c>
+      <c r="BA138">
+        <v>7</v>
+      </c>
+      <c r="BB138">
+        <v>8</v>
+      </c>
+      <c r="BC138">
+        <v>15</v>
+      </c>
+      <c r="BD138">
+        <v>2.22</v>
+      </c>
+      <c r="BE138">
+        <v>6.45</v>
+      </c>
+      <c r="BF138">
+        <v>2.05</v>
+      </c>
+      <c r="BG138">
+        <v>1.23</v>
+      </c>
+      <c r="BH138">
+        <v>3.42</v>
+      </c>
+      <c r="BI138">
+        <v>1.45</v>
+      </c>
+      <c r="BJ138">
+        <v>2.48</v>
+      </c>
+      <c r="BK138">
+        <v>1.8</v>
+      </c>
+      <c r="BL138">
+        <v>1.91</v>
+      </c>
+      <c r="BM138">
+        <v>2.3</v>
+      </c>
+      <c r="BN138">
+        <v>1.52</v>
+      </c>
+      <c r="BO138">
+        <v>3.05</v>
+      </c>
+      <c r="BP138">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="139" spans="1:68">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>7859408</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45746.5</v>
+      </c>
+      <c r="F139">
+        <v>1</v>
+      </c>
+      <c r="G139" t="s">
+        <v>74</v>
+      </c>
+      <c r="H139" t="s">
+        <v>78</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>1</v>
+      </c>
+      <c r="K139">
+        <v>1</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>2</v>
+      </c>
+      <c r="N139">
+        <v>2</v>
+      </c>
+      <c r="O139" t="s">
+        <v>89</v>
+      </c>
+      <c r="P139" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q139">
+        <v>3</v>
+      </c>
+      <c r="R139">
+        <v>2.25</v>
+      </c>
+      <c r="S139">
+        <v>3.25</v>
+      </c>
+      <c r="T139">
+        <v>1.33</v>
+      </c>
+      <c r="U139">
+        <v>3.25</v>
+      </c>
+      <c r="V139">
+        <v>2.63</v>
+      </c>
+      <c r="W139">
+        <v>1.44</v>
+      </c>
+      <c r="X139">
+        <v>6.5</v>
+      </c>
+      <c r="Y139">
+        <v>1.11</v>
+      </c>
+      <c r="Z139">
+        <v>2.48</v>
+      </c>
+      <c r="AA139">
+        <v>3.37</v>
+      </c>
+      <c r="AB139">
+        <v>2.7</v>
+      </c>
+      <c r="AC139">
+        <v>1.03</v>
+      </c>
+      <c r="AD139">
+        <v>11.5</v>
+      </c>
+      <c r="AE139">
+        <v>1.24</v>
+      </c>
+      <c r="AF139">
+        <v>4.05</v>
+      </c>
+      <c r="AG139">
+        <v>1.57</v>
+      </c>
+      <c r="AH139">
+        <v>2.15</v>
+      </c>
+      <c r="AI139">
+        <v>1.57</v>
+      </c>
+      <c r="AJ139">
+        <v>2.25</v>
+      </c>
+      <c r="AK139">
+        <v>1.46</v>
+      </c>
+      <c r="AL139">
+        <v>1.28</v>
+      </c>
+      <c r="AM139">
+        <v>1.52</v>
+      </c>
+      <c r="AN139">
+        <v>2.27</v>
+      </c>
+      <c r="AO139">
+        <v>1.27</v>
+      </c>
+      <c r="AP139">
+        <v>2.08</v>
+      </c>
+      <c r="AQ139">
+        <v>1.42</v>
+      </c>
+      <c r="AR139">
+        <v>1.73</v>
+      </c>
+      <c r="AS139">
+        <v>1.57</v>
+      </c>
+      <c r="AT139">
+        <v>3.3</v>
+      </c>
+      <c r="AU139">
+        <v>3</v>
+      </c>
+      <c r="AV139">
+        <v>5</v>
+      </c>
+      <c r="AW139">
+        <v>8</v>
+      </c>
+      <c r="AX139">
+        <v>5</v>
+      </c>
+      <c r="AY139">
+        <v>14</v>
+      </c>
+      <c r="AZ139">
+        <v>14</v>
+      </c>
+      <c r="BA139">
+        <v>5</v>
+      </c>
+      <c r="BB139">
+        <v>2</v>
+      </c>
+      <c r="BC139">
+        <v>7</v>
+      </c>
+      <c r="BD139">
+        <v>1.73</v>
+      </c>
+      <c r="BE139">
+        <v>6.65</v>
+      </c>
+      <c r="BF139">
+        <v>2.75</v>
+      </c>
+      <c r="BG139">
+        <v>1.24</v>
+      </c>
+      <c r="BH139">
+        <v>3.34</v>
+      </c>
+      <c r="BI139">
+        <v>1.48</v>
+      </c>
+      <c r="BJ139">
+        <v>2.4</v>
+      </c>
+      <c r="BK139">
+        <v>1.83</v>
+      </c>
+      <c r="BL139">
+        <v>1.85</v>
+      </c>
+      <c r="BM139">
+        <v>2.38</v>
+      </c>
+      <c r="BN139">
+        <v>1.49</v>
+      </c>
+      <c r="BO139">
+        <v>3.14</v>
+      </c>
+      <c r="BP139">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -29735,13 +29735,13 @@
         <v>14</v>
       </c>
       <c r="BA139">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB139">
         <v>2</v>
       </c>
       <c r="BC139">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD139">
         <v>1.73</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="258">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -563,6 +563,9 @@
   </si>
   <si>
     <t>['12', '71']</t>
+  </si>
+  <si>
+    <t>['18', '90']</t>
   </si>
   <si>
     <t>['4', '6', '45+2']</t>
@@ -1146,7 +1149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP139"/>
+  <dimension ref="A1:BP140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1402,7 +1405,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q2">
         <v>7</v>
@@ -1608,7 +1611,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1814,7 +1817,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2638,7 +2641,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q8">
         <v>2.1</v>
@@ -3050,7 +3053,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q10">
         <v>1.67</v>
@@ -3337,7 +3340,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ11">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3746,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ13">
         <v>0.91</v>
@@ -3874,7 +3877,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -4080,7 +4083,7 @@
         <v>89</v>
       </c>
       <c r="P15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q15">
         <v>5.5</v>
@@ -4286,7 +4289,7 @@
         <v>89</v>
       </c>
       <c r="P16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q16">
         <v>3.8</v>
@@ -5110,7 +5113,7 @@
         <v>89</v>
       </c>
       <c r="P20" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5316,7 +5319,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q21">
         <v>2.03</v>
@@ -5394,7 +5397,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ21">
         <v>0.73</v>
@@ -5522,7 +5525,7 @@
         <v>99</v>
       </c>
       <c r="P22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q22">
         <v>2.4</v>
@@ -5728,7 +5731,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -6015,7 +6018,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ24">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR24">
         <v>0.92</v>
@@ -6140,7 +6143,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6552,7 +6555,7 @@
         <v>104</v>
       </c>
       <c r="P27" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6630,7 +6633,7 @@
         <v>1.5</v>
       </c>
       <c r="AP27">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ27">
         <v>0.92</v>
@@ -6758,7 +6761,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -6964,7 +6967,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q29">
         <v>4.33</v>
@@ -7457,7 +7460,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ31">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR31">
         <v>1.82</v>
@@ -7788,7 +7791,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -7994,7 +7997,7 @@
         <v>89</v>
       </c>
       <c r="P34" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8200,7 +8203,7 @@
         <v>111</v>
       </c>
       <c r="P35" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8406,7 +8409,7 @@
         <v>112</v>
       </c>
       <c r="P36" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q36">
         <v>2.1</v>
@@ -8612,7 +8615,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q37">
         <v>2.2</v>
@@ -8690,7 +8693,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ37">
         <v>1.73</v>
@@ -9024,7 +9027,7 @@
         <v>113</v>
       </c>
       <c r="P39" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9230,7 +9233,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q40">
         <v>3.6</v>
@@ -9642,7 +9645,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -10054,7 +10057,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q44">
         <v>2.4</v>
@@ -10260,7 +10263,7 @@
         <v>119</v>
       </c>
       <c r="P45" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q45">
         <v>2.2</v>
@@ -10672,7 +10675,7 @@
         <v>89</v>
       </c>
       <c r="P47" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10878,7 +10881,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11702,7 +11705,7 @@
         <v>89</v>
       </c>
       <c r="P52" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -11783,7 +11786,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ52">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR52">
         <v>1.2</v>
@@ -11986,7 +11989,7 @@
         <v>1.75</v>
       </c>
       <c r="AP53">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ53">
         <v>1.42</v>
@@ -12114,7 +12117,7 @@
         <v>89</v>
       </c>
       <c r="P54" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12320,7 +12323,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q55">
         <v>1.95</v>
@@ -12398,7 +12401,7 @@
         <v>0.4</v>
       </c>
       <c r="AP55">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ55">
         <v>0.82</v>
@@ -12732,7 +12735,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12938,7 +12941,7 @@
         <v>109</v>
       </c>
       <c r="P58" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q58">
         <v>4</v>
@@ -13144,7 +13147,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q59">
         <v>2.1</v>
@@ -13762,7 +13765,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -14255,7 +14258,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ64">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR64">
         <v>1.56</v>
@@ -14380,7 +14383,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q65">
         <v>3.25</v>
@@ -14586,7 +14589,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14792,7 +14795,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q67">
         <v>2.88</v>
@@ -14870,10 +14873,10 @@
         <v>1.2</v>
       </c>
       <c r="AP67">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ67">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR67">
         <v>1.79</v>
@@ -15822,7 +15825,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16234,7 +16237,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q74">
         <v>3.75</v>
@@ -16646,7 +16649,7 @@
         <v>142</v>
       </c>
       <c r="P76" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17058,7 +17061,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q78">
         <v>2.2</v>
@@ -17345,7 +17348,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ79">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR79">
         <v>0.96</v>
@@ -17548,7 +17551,7 @@
         <v>1.17</v>
       </c>
       <c r="AP80">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ80">
         <v>0.92</v>
@@ -17882,7 +17885,7 @@
         <v>147</v>
       </c>
       <c r="P82" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q82">
         <v>2.88</v>
@@ -18294,7 +18297,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q84">
         <v>5.5</v>
@@ -18500,7 +18503,7 @@
         <v>119</v>
       </c>
       <c r="P85" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18706,7 +18709,7 @@
         <v>149</v>
       </c>
       <c r="P86" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q86">
         <v>3.4</v>
@@ -18912,7 +18915,7 @@
         <v>89</v>
       </c>
       <c r="P87" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q87">
         <v>2.75</v>
@@ -19324,7 +19327,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19736,7 +19739,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -19942,7 +19945,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q92">
         <v>6</v>
@@ -20148,7 +20151,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q93">
         <v>2.4</v>
@@ -20229,7 +20232,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ93">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR93">
         <v>2.1</v>
@@ -20354,7 +20357,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q94">
         <v>2.6</v>
@@ -20560,7 +20563,7 @@
         <v>89</v>
       </c>
       <c r="P95" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -21178,7 +21181,7 @@
         <v>157</v>
       </c>
       <c r="P98" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q98">
         <v>2.5</v>
@@ -21256,7 +21259,7 @@
         <v>1.38</v>
       </c>
       <c r="AP98">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ98">
         <v>1.75</v>
@@ -21384,7 +21387,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q99">
         <v>2.3</v>
@@ -21590,7 +21593,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -22414,7 +22417,7 @@
         <v>103</v>
       </c>
       <c r="P104" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q104">
         <v>2.75</v>
@@ -22826,7 +22829,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q106">
         <v>1.67</v>
@@ -23525,7 +23528,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ109">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR109">
         <v>1.67</v>
@@ -23650,7 +23653,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23856,7 +23859,7 @@
         <v>164</v>
       </c>
       <c r="P111" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q111">
         <v>3.1</v>
@@ -24062,7 +24065,7 @@
         <v>165</v>
       </c>
       <c r="P112" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q112">
         <v>4.53</v>
@@ -24346,7 +24349,7 @@
         <v>1</v>
       </c>
       <c r="AP113">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ113">
         <v>1.09</v>
@@ -24680,7 +24683,7 @@
         <v>167</v>
       </c>
       <c r="P115" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -24761,7 +24764,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ115">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR115">
         <v>1.44</v>
@@ -24886,7 +24889,7 @@
         <v>89</v>
       </c>
       <c r="P116" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25092,7 +25095,7 @@
         <v>168</v>
       </c>
       <c r="P117" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25504,7 +25507,7 @@
         <v>91</v>
       </c>
       <c r="P119" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q119">
         <v>4.33</v>
@@ -25916,7 +25919,7 @@
         <v>171</v>
       </c>
       <c r="P121" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q121">
         <v>2.6</v>
@@ -26122,7 +26125,7 @@
         <v>172</v>
       </c>
       <c r="P122" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q122">
         <v>2.38</v>
@@ -26328,7 +26331,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q123">
         <v>2.6</v>
@@ -26740,7 +26743,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q125">
         <v>5.5</v>
@@ -26946,7 +26949,7 @@
         <v>87</v>
       </c>
       <c r="P126" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27152,7 +27155,7 @@
         <v>176</v>
       </c>
       <c r="P127" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q127">
         <v>4.5</v>
@@ -27233,7 +27236,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ127">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR127">
         <v>1.17</v>
@@ -27358,7 +27361,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q128">
         <v>3.5</v>
@@ -27564,7 +27567,7 @@
         <v>89</v>
       </c>
       <c r="P129" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q129">
         <v>5.5</v>
@@ -27976,7 +27979,7 @@
         <v>179</v>
       </c>
       <c r="P131" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q131">
         <v>2.6</v>
@@ -28054,7 +28057,7 @@
         <v>1.7</v>
       </c>
       <c r="AP131">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ131">
         <v>1.67</v>
@@ -28594,7 +28597,7 @@
         <v>89</v>
       </c>
       <c r="P134" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -29006,7 +29009,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29212,7 +29215,7 @@
         <v>89</v>
       </c>
       <c r="P137" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q137">
         <v>3.75</v>
@@ -29624,7 +29627,7 @@
         <v>89</v>
       </c>
       <c r="P139" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q139">
         <v>3</v>
@@ -29781,6 +29784,212 @@
       </c>
       <c r="BP139">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="140" spans="1:68">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>7859409</v>
+      </c>
+      <c r="C140" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" t="s">
+        <v>69</v>
+      </c>
+      <c r="E140" s="2">
+        <v>45751.60416666666</v>
+      </c>
+      <c r="F140">
+        <v>2</v>
+      </c>
+      <c r="G140" t="s">
+        <v>81</v>
+      </c>
+      <c r="H140" t="s">
+        <v>74</v>
+      </c>
+      <c r="I140">
+        <v>1</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>1</v>
+      </c>
+      <c r="L140">
+        <v>2</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>2</v>
+      </c>
+      <c r="O140" t="s">
+        <v>183</v>
+      </c>
+      <c r="P140" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q140">
+        <v>2.88</v>
+      </c>
+      <c r="R140">
+        <v>2.2</v>
+      </c>
+      <c r="S140">
+        <v>3.6</v>
+      </c>
+      <c r="T140">
+        <v>1.36</v>
+      </c>
+      <c r="U140">
+        <v>3</v>
+      </c>
+      <c r="V140">
+        <v>2.75</v>
+      </c>
+      <c r="W140">
+        <v>1.4</v>
+      </c>
+      <c r="X140">
+        <v>7</v>
+      </c>
+      <c r="Y140">
+        <v>1.1</v>
+      </c>
+      <c r="Z140">
+        <v>2.11</v>
+      </c>
+      <c r="AA140">
+        <v>3.52</v>
+      </c>
+      <c r="AB140">
+        <v>3.21</v>
+      </c>
+      <c r="AC140">
+        <v>1.05</v>
+      </c>
+      <c r="AD140">
+        <v>9</v>
+      </c>
+      <c r="AE140">
+        <v>1.28</v>
+      </c>
+      <c r="AF140">
+        <v>3.65</v>
+      </c>
+      <c r="AG140">
+        <v>1.77</v>
+      </c>
+      <c r="AH140">
+        <v>1.98</v>
+      </c>
+      <c r="AI140">
+        <v>1.67</v>
+      </c>
+      <c r="AJ140">
+        <v>2.1</v>
+      </c>
+      <c r="AK140">
+        <v>1.36</v>
+      </c>
+      <c r="AL140">
+        <v>1.31</v>
+      </c>
+      <c r="AM140">
+        <v>1.6</v>
+      </c>
+      <c r="AN140">
+        <v>2.36</v>
+      </c>
+      <c r="AO140">
+        <v>0.82</v>
+      </c>
+      <c r="AP140">
+        <v>2.42</v>
+      </c>
+      <c r="AQ140">
+        <v>0.75</v>
+      </c>
+      <c r="AR140">
+        <v>1.8</v>
+      </c>
+      <c r="AS140">
+        <v>1.52</v>
+      </c>
+      <c r="AT140">
+        <v>3.32</v>
+      </c>
+      <c r="AU140">
+        <v>3</v>
+      </c>
+      <c r="AV140">
+        <v>3</v>
+      </c>
+      <c r="AW140">
+        <v>8</v>
+      </c>
+      <c r="AX140">
+        <v>9</v>
+      </c>
+      <c r="AY140">
+        <v>16</v>
+      </c>
+      <c r="AZ140">
+        <v>14</v>
+      </c>
+      <c r="BA140">
+        <v>5</v>
+      </c>
+      <c r="BB140">
+        <v>6</v>
+      </c>
+      <c r="BC140">
+        <v>11</v>
+      </c>
+      <c r="BD140">
+        <v>1.97</v>
+      </c>
+      <c r="BE140">
+        <v>6.4</v>
+      </c>
+      <c r="BF140">
+        <v>2.33</v>
+      </c>
+      <c r="BG140">
+        <v>1.27</v>
+      </c>
+      <c r="BH140">
+        <v>3.14</v>
+      </c>
+      <c r="BI140">
+        <v>1.52</v>
+      </c>
+      <c r="BJ140">
+        <v>2.3</v>
+      </c>
+      <c r="BK140">
+        <v>1.91</v>
+      </c>
+      <c r="BL140">
+        <v>1.8</v>
+      </c>
+      <c r="BM140">
+        <v>2.5</v>
+      </c>
+      <c r="BN140">
+        <v>1.44</v>
+      </c>
+      <c r="BO140">
+        <v>3.34</v>
+      </c>
+      <c r="BP140">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="262">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -568,6 +568,12 @@
     <t>['18', '90']</t>
   </si>
   <si>
+    <t>['2', '29']</t>
+  </si>
+  <si>
+    <t>['79']</t>
+  </si>
+  <si>
     <t>['4', '6', '45+2']</t>
   </si>
   <si>
@@ -788,6 +794,12 @@
   </si>
   <si>
     <t>['37', '48']</t>
+  </si>
+  <si>
+    <t>['15', '40', '49']</t>
+  </si>
+  <si>
+    <t>['9', '90+1', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -1149,7 +1161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP140"/>
+  <dimension ref="A1:BP143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1405,7 +1417,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q2">
         <v>7</v>
@@ -1611,7 +1623,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1817,7 +1829,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2641,7 +2653,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q8">
         <v>2.1</v>
@@ -2719,10 +2731,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ8">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2925,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ9">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3053,7 +3065,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q10">
         <v>1.67</v>
@@ -3337,7 +3349,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ11">
         <v>0.75</v>
@@ -3752,7 +3764,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ13">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3877,7 +3889,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -4083,7 +4095,7 @@
         <v>89</v>
       </c>
       <c r="P15" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q15">
         <v>5.5</v>
@@ -4161,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ15">
         <v>1.75</v>
@@ -4289,7 +4301,7 @@
         <v>89</v>
       </c>
       <c r="P16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q16">
         <v>3.8</v>
@@ -4367,7 +4379,7 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ16">
         <v>1.42</v>
@@ -5113,7 +5125,7 @@
         <v>89</v>
       </c>
       <c r="P20" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5191,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ20">
         <v>0.92</v>
@@ -5319,7 +5331,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q21">
         <v>2.03</v>
@@ -5400,7 +5412,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ21">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR21">
         <v>2.09</v>
@@ -5525,7 +5537,7 @@
         <v>99</v>
       </c>
       <c r="P22" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q22">
         <v>2.4</v>
@@ -5606,7 +5618,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ22">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5731,7 +5743,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -6143,7 +6155,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6221,7 +6233,7 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ25">
         <v>1.09</v>
@@ -6430,7 +6442,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ26">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR26">
         <v>1.32</v>
@@ -6555,7 +6567,7 @@
         <v>104</v>
       </c>
       <c r="P27" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6761,7 +6773,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -6839,7 +6851,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ28">
         <v>1.73</v>
@@ -6967,7 +6979,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q29">
         <v>4.33</v>
@@ -7791,7 +7803,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -7872,7 +7884,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ33">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR33">
         <v>1.22</v>
@@ -7997,7 +8009,7 @@
         <v>89</v>
       </c>
       <c r="P34" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8203,7 +8215,7 @@
         <v>111</v>
       </c>
       <c r="P35" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8281,10 +8293,10 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ35">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR35">
         <v>1.2</v>
@@ -8409,7 +8421,7 @@
         <v>112</v>
       </c>
       <c r="P36" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q36">
         <v>2.1</v>
@@ -8487,10 +8499,10 @@
         <v>0.67</v>
       </c>
       <c r="AP36">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ36">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR36">
         <v>1.35</v>
@@ -8615,7 +8627,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q37">
         <v>2.2</v>
@@ -8899,7 +8911,7 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ38">
         <v>1.42</v>
@@ -9027,7 +9039,7 @@
         <v>113</v>
       </c>
       <c r="P39" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9233,7 +9245,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q40">
         <v>3.6</v>
@@ -9645,7 +9657,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -10057,7 +10069,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q44">
         <v>2.4</v>
@@ -10263,7 +10275,7 @@
         <v>119</v>
       </c>
       <c r="P45" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q45">
         <v>2.2</v>
@@ -10550,7 +10562,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ46">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR46">
         <v>1.2</v>
@@ -10675,7 +10687,7 @@
         <v>89</v>
       </c>
       <c r="P47" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10881,7 +10893,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -10962,7 +10974,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ48">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR48">
         <v>1.74</v>
@@ -11168,7 +11180,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ49">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR49">
         <v>1.83</v>
@@ -11371,7 +11383,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ50">
         <v>1.09</v>
@@ -11577,7 +11589,7 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ51">
         <v>0.92</v>
@@ -11705,7 +11717,7 @@
         <v>89</v>
       </c>
       <c r="P52" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12117,7 +12129,7 @@
         <v>89</v>
       </c>
       <c r="P54" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12323,7 +12335,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q55">
         <v>1.95</v>
@@ -12404,7 +12416,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ55">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR55">
         <v>1.69</v>
@@ -12610,7 +12622,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ56">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR56">
         <v>2.36</v>
@@ -12735,7 +12747,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12813,7 +12825,7 @@
         <v>0.4</v>
       </c>
       <c r="AP57">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ57">
         <v>1.75</v>
@@ -12941,7 +12953,7 @@
         <v>109</v>
       </c>
       <c r="P58" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q58">
         <v>4</v>
@@ -13019,7 +13031,7 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ58">
         <v>1.67</v>
@@ -13147,7 +13159,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q59">
         <v>2.1</v>
@@ -13228,7 +13240,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ59">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR59">
         <v>1.71</v>
@@ -13765,7 +13777,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -14383,7 +14395,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q65">
         <v>3.25</v>
@@ -14461,7 +14473,7 @@
         <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ65">
         <v>1.75</v>
@@ -14589,7 +14601,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14667,10 +14679,10 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ66">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR66">
         <v>1.38</v>
@@ -14795,7 +14807,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q67">
         <v>2.88</v>
@@ -15082,7 +15094,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ68">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR68">
         <v>2.3</v>
@@ -15285,7 +15297,7 @@
         <v>1.8</v>
       </c>
       <c r="AP69">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ69">
         <v>1.73</v>
@@ -15491,10 +15503,10 @@
         <v>0.8</v>
       </c>
       <c r="AP70">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ70">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR70">
         <v>0.89</v>
@@ -15825,7 +15837,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16237,7 +16249,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q74">
         <v>3.75</v>
@@ -16649,7 +16661,7 @@
         <v>142</v>
       </c>
       <c r="P76" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17061,7 +17073,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q78">
         <v>2.2</v>
@@ -17345,7 +17357,7 @@
         <v>1.17</v>
       </c>
       <c r="AP79">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ79">
         <v>0.75</v>
@@ -17760,7 +17772,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ81">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR81">
         <v>1.54</v>
@@ -17885,7 +17897,7 @@
         <v>147</v>
       </c>
       <c r="P82" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q82">
         <v>2.88</v>
@@ -17966,7 +17978,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ82">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR82">
         <v>1.31</v>
@@ -18172,7 +18184,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ83">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR83">
         <v>1.76</v>
@@ -18297,7 +18309,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q84">
         <v>5.5</v>
@@ -18503,7 +18515,7 @@
         <v>119</v>
       </c>
       <c r="P85" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18709,7 +18721,7 @@
         <v>149</v>
       </c>
       <c r="P86" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q86">
         <v>3.4</v>
@@ -18915,7 +18927,7 @@
         <v>89</v>
       </c>
       <c r="P87" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q87">
         <v>2.75</v>
@@ -18993,7 +19005,7 @@
         <v>0.86</v>
       </c>
       <c r="AP87">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ87">
         <v>0.92</v>
@@ -19327,7 +19339,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19405,7 +19417,7 @@
         <v>1.14</v>
       </c>
       <c r="AP89">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ89">
         <v>1.75</v>
@@ -19614,7 +19626,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ90">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR90">
         <v>2.08</v>
@@ -19739,7 +19751,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -19945,7 +19957,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q92">
         <v>6</v>
@@ -20023,7 +20035,7 @@
         <v>2</v>
       </c>
       <c r="AP92">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ92">
         <v>1.75</v>
@@ -20151,7 +20163,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q93">
         <v>2.4</v>
@@ -20357,7 +20369,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q94">
         <v>2.6</v>
@@ -20563,7 +20575,7 @@
         <v>89</v>
       </c>
       <c r="P95" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20644,7 +20656,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ95">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR95">
         <v>1.42</v>
@@ -20850,7 +20862,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ96">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR96">
         <v>1.72</v>
@@ -21181,7 +21193,7 @@
         <v>157</v>
       </c>
       <c r="P98" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q98">
         <v>2.5</v>
@@ -21387,7 +21399,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q99">
         <v>2.3</v>
@@ -21593,7 +21605,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21674,7 +21686,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ100">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR100">
         <v>1.21</v>
@@ -21877,7 +21889,7 @@
         <v>1.13</v>
       </c>
       <c r="AP101">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ101">
         <v>1.42</v>
@@ -22083,10 +22095,10 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ102">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR102">
         <v>0.9</v>
@@ -22289,7 +22301,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ103">
         <v>1.09</v>
@@ -22417,7 +22429,7 @@
         <v>103</v>
       </c>
       <c r="P104" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q104">
         <v>2.75</v>
@@ -22498,7 +22510,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ104">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR104">
         <v>1.34</v>
@@ -22829,7 +22841,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q106">
         <v>1.67</v>
@@ -23653,7 +23665,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23859,7 +23871,7 @@
         <v>164</v>
       </c>
       <c r="P111" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q111">
         <v>3.1</v>
@@ -23937,10 +23949,10 @@
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ111">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR111">
         <v>1.32</v>
@@ -24065,7 +24077,7 @@
         <v>165</v>
       </c>
       <c r="P112" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q112">
         <v>4.53</v>
@@ -24143,7 +24155,7 @@
         <v>1.88</v>
       </c>
       <c r="AP112">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ112">
         <v>1.73</v>
@@ -24558,7 +24570,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ114">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR114">
         <v>1.24</v>
@@ -24683,7 +24695,7 @@
         <v>167</v>
       </c>
       <c r="P115" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -24761,7 +24773,7 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ115">
         <v>0.75</v>
@@ -24889,7 +24901,7 @@
         <v>89</v>
       </c>
       <c r="P116" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25095,7 +25107,7 @@
         <v>168</v>
       </c>
       <c r="P117" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25382,7 +25394,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ118">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR118">
         <v>1.66</v>
@@ -25507,7 +25519,7 @@
         <v>91</v>
       </c>
       <c r="P119" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q119">
         <v>4.33</v>
@@ -25585,7 +25597,7 @@
         <v>1.56</v>
       </c>
       <c r="AP119">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ119">
         <v>1.67</v>
@@ -25919,7 +25931,7 @@
         <v>171</v>
       </c>
       <c r="P121" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q121">
         <v>2.6</v>
@@ -26125,7 +26137,7 @@
         <v>172</v>
       </c>
       <c r="P122" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q122">
         <v>2.38</v>
@@ -26203,7 +26215,7 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ122">
         <v>0.92</v>
@@ -26331,7 +26343,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q123">
         <v>2.6</v>
@@ -26743,7 +26755,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q125">
         <v>5.5</v>
@@ -26949,7 +26961,7 @@
         <v>87</v>
       </c>
       <c r="P126" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27155,7 +27167,7 @@
         <v>176</v>
       </c>
       <c r="P127" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q127">
         <v>4.5</v>
@@ -27361,7 +27373,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q128">
         <v>3.5</v>
@@ -27439,10 +27451,10 @@
         <v>0.7</v>
       </c>
       <c r="AP128">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ128">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR128">
         <v>1.34</v>
@@ -27567,7 +27579,7 @@
         <v>89</v>
       </c>
       <c r="P129" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q129">
         <v>5.5</v>
@@ -27645,7 +27657,7 @@
         <v>1.5</v>
       </c>
       <c r="AP129">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ129">
         <v>1.75</v>
@@ -27854,7 +27866,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ130">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR130">
         <v>1.42</v>
@@ -27979,7 +27991,7 @@
         <v>179</v>
       </c>
       <c r="P131" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q131">
         <v>2.6</v>
@@ -28472,7 +28484,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ133">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR133">
         <v>1.71</v>
@@ -28597,7 +28609,7 @@
         <v>89</v>
       </c>
       <c r="P134" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -29009,7 +29021,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29215,7 +29227,7 @@
         <v>89</v>
       </c>
       <c r="P137" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q137">
         <v>3.75</v>
@@ -29627,7 +29639,7 @@
         <v>89</v>
       </c>
       <c r="P139" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q139">
         <v>3</v>
@@ -29990,6 +30002,624 @@
       </c>
       <c r="BP140">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="141" spans="1:68">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>7859411</v>
+      </c>
+      <c r="C141" t="s">
+        <v>68</v>
+      </c>
+      <c r="D141" t="s">
+        <v>69</v>
+      </c>
+      <c r="E141" s="2">
+        <v>45752.5</v>
+      </c>
+      <c r="F141">
+        <v>2</v>
+      </c>
+      <c r="G141" t="s">
+        <v>79</v>
+      </c>
+      <c r="H141" t="s">
+        <v>71</v>
+      </c>
+      <c r="I141">
+        <v>2</v>
+      </c>
+      <c r="J141">
+        <v>2</v>
+      </c>
+      <c r="K141">
+        <v>4</v>
+      </c>
+      <c r="L141">
+        <v>2</v>
+      </c>
+      <c r="M141">
+        <v>3</v>
+      </c>
+      <c r="N141">
+        <v>5</v>
+      </c>
+      <c r="O141" t="s">
+        <v>184</v>
+      </c>
+      <c r="P141" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q141">
+        <v>3.5</v>
+      </c>
+      <c r="R141">
+        <v>2.05</v>
+      </c>
+      <c r="S141">
+        <v>3.4</v>
+      </c>
+      <c r="T141">
+        <v>1.5</v>
+      </c>
+      <c r="U141">
+        <v>2.5</v>
+      </c>
+      <c r="V141">
+        <v>3.4</v>
+      </c>
+      <c r="W141">
+        <v>1.3</v>
+      </c>
+      <c r="X141">
+        <v>10</v>
+      </c>
+      <c r="Y141">
+        <v>1.06</v>
+      </c>
+      <c r="Z141">
+        <v>2.7</v>
+      </c>
+      <c r="AA141">
+        <v>3.12</v>
+      </c>
+      <c r="AB141">
+        <v>2.64</v>
+      </c>
+      <c r="AC141">
+        <v>1.07</v>
+      </c>
+      <c r="AD141">
+        <v>8</v>
+      </c>
+      <c r="AE141">
+        <v>1.4</v>
+      </c>
+      <c r="AF141">
+        <v>2.9</v>
+      </c>
+      <c r="AG141">
+        <v>2.05</v>
+      </c>
+      <c r="AH141">
+        <v>1.65</v>
+      </c>
+      <c r="AI141">
+        <v>1.91</v>
+      </c>
+      <c r="AJ141">
+        <v>1.91</v>
+      </c>
+      <c r="AK141">
+        <v>1.47</v>
+      </c>
+      <c r="AL141">
+        <v>1.33</v>
+      </c>
+      <c r="AM141">
+        <v>1.44</v>
+      </c>
+      <c r="AN141">
+        <v>1.18</v>
+      </c>
+      <c r="AO141">
+        <v>0.73</v>
+      </c>
+      <c r="AP141">
+        <v>1.08</v>
+      </c>
+      <c r="AQ141">
+        <v>0.92</v>
+      </c>
+      <c r="AR141">
+        <v>1.37</v>
+      </c>
+      <c r="AS141">
+        <v>1.02</v>
+      </c>
+      <c r="AT141">
+        <v>2.39</v>
+      </c>
+      <c r="AU141">
+        <v>4</v>
+      </c>
+      <c r="AV141">
+        <v>8</v>
+      </c>
+      <c r="AW141">
+        <v>5</v>
+      </c>
+      <c r="AX141">
+        <v>4</v>
+      </c>
+      <c r="AY141">
+        <v>11</v>
+      </c>
+      <c r="AZ141">
+        <v>12</v>
+      </c>
+      <c r="BA141">
+        <v>5</v>
+      </c>
+      <c r="BB141">
+        <v>4</v>
+      </c>
+      <c r="BC141">
+        <v>9</v>
+      </c>
+      <c r="BD141">
+        <v>2.18</v>
+      </c>
+      <c r="BE141">
+        <v>6.4</v>
+      </c>
+      <c r="BF141">
+        <v>2.09</v>
+      </c>
+      <c r="BG141">
+        <v>1.31</v>
+      </c>
+      <c r="BH141">
+        <v>3.1</v>
+      </c>
+      <c r="BI141">
+        <v>1.57</v>
+      </c>
+      <c r="BJ141">
+        <v>2.15</v>
+      </c>
+      <c r="BK141">
+        <v>2</v>
+      </c>
+      <c r="BL141">
+        <v>1.68</v>
+      </c>
+      <c r="BM141">
+        <v>2.7</v>
+      </c>
+      <c r="BN141">
+        <v>1.38</v>
+      </c>
+      <c r="BO141">
+        <v>3.8</v>
+      </c>
+      <c r="BP141">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="142" spans="1:68">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>7859412</v>
+      </c>
+      <c r="C142" t="s">
+        <v>68</v>
+      </c>
+      <c r="D142" t="s">
+        <v>69</v>
+      </c>
+      <c r="E142" s="2">
+        <v>45752.5</v>
+      </c>
+      <c r="F142">
+        <v>2</v>
+      </c>
+      <c r="G142" t="s">
+        <v>77</v>
+      </c>
+      <c r="H142" t="s">
+        <v>72</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
+        <v>1</v>
+      </c>
+      <c r="K142">
+        <v>1</v>
+      </c>
+      <c r="L142">
+        <v>1</v>
+      </c>
+      <c r="M142">
+        <v>3</v>
+      </c>
+      <c r="N142">
+        <v>4</v>
+      </c>
+      <c r="O142" t="s">
+        <v>185</v>
+      </c>
+      <c r="P142" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q142">
+        <v>3.5</v>
+      </c>
+      <c r="R142">
+        <v>2.1</v>
+      </c>
+      <c r="S142">
+        <v>3.1</v>
+      </c>
+      <c r="T142">
+        <v>1.44</v>
+      </c>
+      <c r="U142">
+        <v>2.63</v>
+      </c>
+      <c r="V142">
+        <v>3.25</v>
+      </c>
+      <c r="W142">
+        <v>1.33</v>
+      </c>
+      <c r="X142">
+        <v>9</v>
+      </c>
+      <c r="Y142">
+        <v>1.07</v>
+      </c>
+      <c r="Z142">
+        <v>2.91</v>
+      </c>
+      <c r="AA142">
+        <v>3.21</v>
+      </c>
+      <c r="AB142">
+        <v>2.41</v>
+      </c>
+      <c r="AC142">
+        <v>1.07</v>
+      </c>
+      <c r="AD142">
+        <v>8</v>
+      </c>
+      <c r="AE142">
+        <v>1.36</v>
+      </c>
+      <c r="AF142">
+        <v>3.1</v>
+      </c>
+      <c r="AG142">
+        <v>1.95</v>
+      </c>
+      <c r="AH142">
+        <v>1.79</v>
+      </c>
+      <c r="AI142">
+        <v>1.75</v>
+      </c>
+      <c r="AJ142">
+        <v>2</v>
+      </c>
+      <c r="AK142">
+        <v>1.51</v>
+      </c>
+      <c r="AL142">
+        <v>1.32</v>
+      </c>
+      <c r="AM142">
+        <v>1.42</v>
+      </c>
+      <c r="AN142">
+        <v>0.82</v>
+      </c>
+      <c r="AO142">
+        <v>0.91</v>
+      </c>
+      <c r="AP142">
+        <v>0.75</v>
+      </c>
+      <c r="AQ142">
+        <v>1.08</v>
+      </c>
+      <c r="AR142">
+        <v>1.09</v>
+      </c>
+      <c r="AS142">
+        <v>1.13</v>
+      </c>
+      <c r="AT142">
+        <v>2.22</v>
+      </c>
+      <c r="AU142">
+        <v>3</v>
+      </c>
+      <c r="AV142">
+        <v>4</v>
+      </c>
+      <c r="AW142">
+        <v>13</v>
+      </c>
+      <c r="AX142">
+        <v>8</v>
+      </c>
+      <c r="AY142">
+        <v>18</v>
+      </c>
+      <c r="AZ142">
+        <v>14</v>
+      </c>
+      <c r="BA142">
+        <v>1</v>
+      </c>
+      <c r="BB142">
+        <v>3</v>
+      </c>
+      <c r="BC142">
+        <v>4</v>
+      </c>
+      <c r="BD142">
+        <v>2.12</v>
+      </c>
+      <c r="BE142">
+        <v>6.4</v>
+      </c>
+      <c r="BF142">
+        <v>2.15</v>
+      </c>
+      <c r="BG142">
+        <v>1.27</v>
+      </c>
+      <c r="BH142">
+        <v>3.3</v>
+      </c>
+      <c r="BI142">
+        <v>1.51</v>
+      </c>
+      <c r="BJ142">
+        <v>2.3</v>
+      </c>
+      <c r="BK142">
+        <v>1.9</v>
+      </c>
+      <c r="BL142">
+        <v>1.75</v>
+      </c>
+      <c r="BM142">
+        <v>2.55</v>
+      </c>
+      <c r="BN142">
+        <v>1.43</v>
+      </c>
+      <c r="BO142">
+        <v>3.5</v>
+      </c>
+      <c r="BP142">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="143" spans="1:68">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>7859410</v>
+      </c>
+      <c r="C143" t="s">
+        <v>68</v>
+      </c>
+      <c r="D143" t="s">
+        <v>69</v>
+      </c>
+      <c r="E143" s="2">
+        <v>45752.5</v>
+      </c>
+      <c r="F143">
+        <v>2</v>
+      </c>
+      <c r="G143" t="s">
+        <v>76</v>
+      </c>
+      <c r="H143" t="s">
+        <v>70</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="L143">
+        <v>1</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>1</v>
+      </c>
+      <c r="O143" t="s">
+        <v>173</v>
+      </c>
+      <c r="P143" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q143">
+        <v>2.2</v>
+      </c>
+      <c r="R143">
+        <v>2.3</v>
+      </c>
+      <c r="S143">
+        <v>5.5</v>
+      </c>
+      <c r="T143">
+        <v>1.33</v>
+      </c>
+      <c r="U143">
+        <v>3.25</v>
+      </c>
+      <c r="V143">
+        <v>2.63</v>
+      </c>
+      <c r="W143">
+        <v>1.44</v>
+      </c>
+      <c r="X143">
+        <v>7</v>
+      </c>
+      <c r="Y143">
+        <v>1.1</v>
+      </c>
+      <c r="Z143">
+        <v>1.55</v>
+      </c>
+      <c r="AA143">
+        <v>4.2</v>
+      </c>
+      <c r="AB143">
+        <v>5.4</v>
+      </c>
+      <c r="AC143">
+        <v>1.04</v>
+      </c>
+      <c r="AD143">
+        <v>10</v>
+      </c>
+      <c r="AE143">
+        <v>1.25</v>
+      </c>
+      <c r="AF143">
+        <v>3.85</v>
+      </c>
+      <c r="AG143">
+        <v>1.65</v>
+      </c>
+      <c r="AH143">
+        <v>2</v>
+      </c>
+      <c r="AI143">
+        <v>1.8</v>
+      </c>
+      <c r="AJ143">
+        <v>1.95</v>
+      </c>
+      <c r="AK143">
+        <v>1.15</v>
+      </c>
+      <c r="AL143">
+        <v>1.23</v>
+      </c>
+      <c r="AM143">
+        <v>2.3</v>
+      </c>
+      <c r="AN143">
+        <v>1.27</v>
+      </c>
+      <c r="AO143">
+        <v>0.82</v>
+      </c>
+      <c r="AP143">
+        <v>1.42</v>
+      </c>
+      <c r="AQ143">
+        <v>0.75</v>
+      </c>
+      <c r="AR143">
+        <v>1.65</v>
+      </c>
+      <c r="AS143">
+        <v>1.1</v>
+      </c>
+      <c r="AT143">
+        <v>2.75</v>
+      </c>
+      <c r="AU143">
+        <v>9</v>
+      </c>
+      <c r="AV143">
+        <v>4</v>
+      </c>
+      <c r="AW143">
+        <v>8</v>
+      </c>
+      <c r="AX143">
+        <v>9</v>
+      </c>
+      <c r="AY143">
+        <v>19</v>
+      </c>
+      <c r="AZ143">
+        <v>17</v>
+      </c>
+      <c r="BA143">
+        <v>5</v>
+      </c>
+      <c r="BB143">
+        <v>4</v>
+      </c>
+      <c r="BC143">
+        <v>9</v>
+      </c>
+      <c r="BD143">
+        <v>1.52</v>
+      </c>
+      <c r="BE143">
+        <v>8.9</v>
+      </c>
+      <c r="BF143">
+        <v>3.1</v>
+      </c>
+      <c r="BG143">
+        <v>1.23</v>
+      </c>
+      <c r="BH143">
+        <v>3.7</v>
+      </c>
+      <c r="BI143">
+        <v>1.43</v>
+      </c>
+      <c r="BJ143">
+        <v>2.5</v>
+      </c>
+      <c r="BK143">
+        <v>1.77</v>
+      </c>
+      <c r="BL143">
+        <v>1.88</v>
+      </c>
+      <c r="BM143">
+        <v>2.3</v>
+      </c>
+      <c r="BN143">
+        <v>1.51</v>
+      </c>
+      <c r="BO143">
+        <v>3.2</v>
+      </c>
+      <c r="BP143">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="263">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -572,6 +572,9 @@
   </si>
   <si>
     <t>['79']</t>
+  </si>
+  <si>
+    <t>['55', '71']</t>
   </si>
   <si>
     <t>['4', '6', '45+2']</t>
@@ -1161,7 +1164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP143"/>
+  <dimension ref="A1:BP145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1417,7 +1420,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q2">
         <v>7</v>
@@ -1623,7 +1626,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1829,7 +1832,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2653,7 +2656,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q8">
         <v>2.1</v>
@@ -3065,7 +3068,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q10">
         <v>1.67</v>
@@ -3143,10 +3146,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ10">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3555,10 +3558,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ12">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3889,7 +3892,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3970,7 +3973,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ14">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR14">
         <v>1.07</v>
@@ -4095,7 +4098,7 @@
         <v>89</v>
       </c>
       <c r="P15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q15">
         <v>5.5</v>
@@ -4301,7 +4304,7 @@
         <v>89</v>
       </c>
       <c r="P16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q16">
         <v>3.8</v>
@@ -5000,7 +5003,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ19">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR19">
         <v>1.26</v>
@@ -5125,7 +5128,7 @@
         <v>89</v>
       </c>
       <c r="P20" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5331,7 +5334,7 @@
         <v>98</v>
       </c>
       <c r="P21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q21">
         <v>2.03</v>
@@ -5537,7 +5540,7 @@
         <v>99</v>
       </c>
       <c r="P22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q22">
         <v>2.4</v>
@@ -5743,7 +5746,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5821,7 +5824,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ23">
         <v>1.67</v>
@@ -6155,7 +6158,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6236,7 +6239,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ25">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR25">
         <v>0.84</v>
@@ -6567,7 +6570,7 @@
         <v>104</v>
       </c>
       <c r="P27" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q27">
         <v>1.72</v>
@@ -6773,7 +6776,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -6854,7 +6857,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ28">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR28">
         <v>1.52</v>
@@ -6979,7 +6982,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q29">
         <v>4.33</v>
@@ -7803,7 +7806,7 @@
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8009,7 +8012,7 @@
         <v>89</v>
       </c>
       <c r="P34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8090,7 +8093,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ34">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR34">
         <v>1.26</v>
@@ -8215,7 +8218,7 @@
         <v>111</v>
       </c>
       <c r="P35" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8421,7 +8424,7 @@
         <v>112</v>
       </c>
       <c r="P36" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q36">
         <v>2.1</v>
@@ -8627,7 +8630,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q37">
         <v>2.2</v>
@@ -8708,7 +8711,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ37">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR37">
         <v>1.97</v>
@@ -9039,7 +9042,7 @@
         <v>113</v>
       </c>
       <c r="P39" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9245,7 +9248,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q40">
         <v>3.6</v>
@@ -9323,7 +9326,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ40">
         <v>1.75</v>
@@ -9657,7 +9660,7 @@
         <v>116</v>
       </c>
       <c r="P42" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9941,7 +9944,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ43">
         <v>1.75</v>
@@ -10069,7 +10072,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q44">
         <v>2.4</v>
@@ -10275,7 +10278,7 @@
         <v>119</v>
       </c>
       <c r="P45" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q45">
         <v>2.2</v>
@@ -10687,7 +10690,7 @@
         <v>89</v>
       </c>
       <c r="P47" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10893,7 +10896,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11177,7 +11180,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ49">
         <v>0.75</v>
@@ -11386,7 +11389,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ50">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR50">
         <v>0.98</v>
@@ -11717,7 +11720,7 @@
         <v>89</v>
       </c>
       <c r="P52" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12129,7 +12132,7 @@
         <v>89</v>
       </c>
       <c r="P54" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12210,7 +12213,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ54">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR54">
         <v>1.29</v>
@@ -12335,7 +12338,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q55">
         <v>1.95</v>
@@ -12619,7 +12622,7 @@
         <v>1</v>
       </c>
       <c r="AP56">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ56">
         <v>0.92</v>
@@ -12747,7 +12750,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12953,7 +12956,7 @@
         <v>109</v>
       </c>
       <c r="P58" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q58">
         <v>4</v>
@@ -13159,7 +13162,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q59">
         <v>2.1</v>
@@ -13443,7 +13446,7 @@
         <v>1.2</v>
       </c>
       <c r="AP60">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ60">
         <v>0.92</v>
@@ -13777,7 +13780,7 @@
         <v>131</v>
       </c>
       <c r="P62" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q62">
         <v>2.75</v>
@@ -13858,7 +13861,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ62">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR62">
         <v>1.17</v>
@@ -14395,7 +14398,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q65">
         <v>3.25</v>
@@ -14601,7 +14604,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14807,7 +14810,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q67">
         <v>2.88</v>
@@ -15091,7 +15094,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ68">
         <v>0.75</v>
@@ -15300,7 +15303,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ69">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR69">
         <v>1.35</v>
@@ -15709,10 +15712,10 @@
         <v>0.83</v>
       </c>
       <c r="AP71">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ71">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR71">
         <v>1.72</v>
@@ -15837,7 +15840,7 @@
         <v>89</v>
       </c>
       <c r="P72" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16249,7 +16252,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q74">
         <v>3.75</v>
@@ -16661,7 +16664,7 @@
         <v>142</v>
       </c>
       <c r="P76" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -17073,7 +17076,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q78">
         <v>2.2</v>
@@ -17151,7 +17154,7 @@
         <v>1.67</v>
       </c>
       <c r="AP78">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ78">
         <v>1.67</v>
@@ -17897,7 +17900,7 @@
         <v>147</v>
       </c>
       <c r="P82" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q82">
         <v>2.88</v>
@@ -18181,7 +18184,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ83">
         <v>1.08</v>
@@ -18309,7 +18312,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q84">
         <v>5.5</v>
@@ -18515,7 +18518,7 @@
         <v>119</v>
       </c>
       <c r="P85" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18721,7 +18724,7 @@
         <v>149</v>
       </c>
       <c r="P86" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q86">
         <v>3.4</v>
@@ -18802,7 +18805,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ86">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR86">
         <v>1.46</v>
@@ -18927,7 +18930,7 @@
         <v>89</v>
       </c>
       <c r="P87" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q87">
         <v>2.75</v>
@@ -19214,7 +19217,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ88">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR88">
         <v>1.65</v>
@@ -19339,7 +19342,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19623,7 +19626,7 @@
         <v>0.83</v>
       </c>
       <c r="AP90">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ90">
         <v>1.08</v>
@@ -19751,7 +19754,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -19957,7 +19960,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q92">
         <v>6</v>
@@ -20163,7 +20166,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q93">
         <v>2.4</v>
@@ -20241,7 +20244,7 @@
         <v>1.14</v>
       </c>
       <c r="AP93">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ93">
         <v>0.75</v>
@@ -20369,7 +20372,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q94">
         <v>2.6</v>
@@ -20575,7 +20578,7 @@
         <v>89</v>
       </c>
       <c r="P95" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q95">
         <v>3.4</v>
@@ -20859,7 +20862,7 @@
         <v>0.57</v>
       </c>
       <c r="AP96">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ96">
         <v>0.92</v>
@@ -21065,7 +21068,7 @@
         <v>0.88</v>
       </c>
       <c r="AP97">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ97">
         <v>0.92</v>
@@ -21193,7 +21196,7 @@
         <v>157</v>
       </c>
       <c r="P98" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q98">
         <v>2.5</v>
@@ -21399,7 +21402,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q99">
         <v>2.3</v>
@@ -21480,7 +21483,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ99">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR99">
         <v>1.69</v>
@@ -21605,7 +21608,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -22304,7 +22307,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ103">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR103">
         <v>1.4</v>
@@ -22429,7 +22432,7 @@
         <v>103</v>
       </c>
       <c r="P104" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q104">
         <v>2.75</v>
@@ -22841,7 +22844,7 @@
         <v>161</v>
       </c>
       <c r="P106" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q106">
         <v>1.67</v>
@@ -22919,7 +22922,7 @@
         <v>1.13</v>
       </c>
       <c r="AP106">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ106">
         <v>0.92</v>
@@ -23537,7 +23540,7 @@
         <v>1.13</v>
       </c>
       <c r="AP109">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ109">
         <v>0.75</v>
@@ -23665,7 +23668,7 @@
         <v>89</v>
       </c>
       <c r="P110" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23743,7 +23746,7 @@
         <v>1.11</v>
       </c>
       <c r="AP110">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ110">
         <v>1.42</v>
@@ -23871,7 +23874,7 @@
         <v>164</v>
       </c>
       <c r="P111" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q111">
         <v>3.1</v>
@@ -24077,7 +24080,7 @@
         <v>165</v>
       </c>
       <c r="P112" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q112">
         <v>4.53</v>
@@ -24158,7 +24161,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ112">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR112">
         <v>1.03</v>
@@ -24364,7 +24367,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ113">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR113">
         <v>1.71</v>
@@ -24695,7 +24698,7 @@
         <v>167</v>
       </c>
       <c r="P115" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -24901,7 +24904,7 @@
         <v>89</v>
       </c>
       <c r="P116" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -24982,7 +24985,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ116">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR116">
         <v>1.19</v>
@@ -25107,7 +25110,7 @@
         <v>168</v>
       </c>
       <c r="P117" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25519,7 +25522,7 @@
         <v>91</v>
       </c>
       <c r="P119" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q119">
         <v>4.33</v>
@@ -25931,7 +25934,7 @@
         <v>171</v>
       </c>
       <c r="P121" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q121">
         <v>2.6</v>
@@ -26009,7 +26012,7 @@
         <v>1.89</v>
       </c>
       <c r="AP121">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ121">
         <v>1.75</v>
@@ -26137,7 +26140,7 @@
         <v>172</v>
       </c>
       <c r="P122" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q122">
         <v>2.38</v>
@@ -26343,7 +26346,7 @@
         <v>173</v>
       </c>
       <c r="P123" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q123">
         <v>2.6</v>
@@ -26424,7 +26427,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ123">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR123">
         <v>1.5</v>
@@ -26627,7 +26630,7 @@
         <v>0.8</v>
       </c>
       <c r="AP124">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ124">
         <v>0.92</v>
@@ -26755,7 +26758,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q125">
         <v>5.5</v>
@@ -26961,7 +26964,7 @@
         <v>87</v>
       </c>
       <c r="P126" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27167,7 +27170,7 @@
         <v>176</v>
       </c>
       <c r="P127" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q127">
         <v>4.5</v>
@@ -27373,7 +27376,7 @@
         <v>177</v>
       </c>
       <c r="P128" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q128">
         <v>3.5</v>
@@ -27579,7 +27582,7 @@
         <v>89</v>
       </c>
       <c r="P129" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q129">
         <v>5.5</v>
@@ -27991,7 +27994,7 @@
         <v>179</v>
       </c>
       <c r="P131" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q131">
         <v>2.6</v>
@@ -28275,10 +28278,10 @@
         <v>1.9</v>
       </c>
       <c r="AP132">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ132">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR132">
         <v>2.23</v>
@@ -28609,7 +28612,7 @@
         <v>89</v>
       </c>
       <c r="P134" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -29021,7 +29024,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29227,7 +29230,7 @@
         <v>89</v>
       </c>
       <c r="P137" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q137">
         <v>3.75</v>
@@ -29639,7 +29642,7 @@
         <v>89</v>
       </c>
       <c r="P139" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q139">
         <v>3</v>
@@ -30051,7 +30054,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q141">
         <v>3.5</v>
@@ -30257,7 +30260,7 @@
         <v>185</v>
       </c>
       <c r="P142" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q142">
         <v>3.5</v>
@@ -30620,6 +30623,418 @@
       </c>
       <c r="BP143">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="144" spans="1:68">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>7859413</v>
+      </c>
+      <c r="C144" t="s">
+        <v>68</v>
+      </c>
+      <c r="D144" t="s">
+        <v>69</v>
+      </c>
+      <c r="E144" s="2">
+        <v>45753.39583333334</v>
+      </c>
+      <c r="F144">
+        <v>2</v>
+      </c>
+      <c r="G144" t="s">
+        <v>78</v>
+      </c>
+      <c r="H144" t="s">
+        <v>75</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="L144">
+        <v>2</v>
+      </c>
+      <c r="M144">
+        <v>1</v>
+      </c>
+      <c r="N144">
+        <v>3</v>
+      </c>
+      <c r="O144" t="s">
+        <v>186</v>
+      </c>
+      <c r="P144" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q144">
+        <v>2</v>
+      </c>
+      <c r="R144">
+        <v>2.4</v>
+      </c>
+      <c r="S144">
+        <v>6</v>
+      </c>
+      <c r="T144">
+        <v>1.33</v>
+      </c>
+      <c r="U144">
+        <v>3.25</v>
+      </c>
+      <c r="V144">
+        <v>2.5</v>
+      </c>
+      <c r="W144">
+        <v>1.5</v>
+      </c>
+      <c r="X144">
+        <v>6.5</v>
+      </c>
+      <c r="Y144">
+        <v>1.11</v>
+      </c>
+      <c r="Z144">
+        <v>1.48</v>
+      </c>
+      <c r="AA144">
+        <v>4.33</v>
+      </c>
+      <c r="AB144">
+        <v>6</v>
+      </c>
+      <c r="AC144">
+        <v>1.01</v>
+      </c>
+      <c r="AD144">
+        <v>12.5</v>
+      </c>
+      <c r="AE144">
+        <v>1.17</v>
+      </c>
+      <c r="AF144">
+        <v>4.15</v>
+      </c>
+      <c r="AG144">
+        <v>1.61</v>
+      </c>
+      <c r="AH144">
+        <v>2.1</v>
+      </c>
+      <c r="AI144">
+        <v>1.8</v>
+      </c>
+      <c r="AJ144">
+        <v>1.95</v>
+      </c>
+      <c r="AK144">
+        <v>1.11</v>
+      </c>
+      <c r="AL144">
+        <v>1.17</v>
+      </c>
+      <c r="AM144">
+        <v>2.62</v>
+      </c>
+      <c r="AN144">
+        <v>2.18</v>
+      </c>
+      <c r="AO144">
+        <v>1.09</v>
+      </c>
+      <c r="AP144">
+        <v>2.25</v>
+      </c>
+      <c r="AQ144">
+        <v>1</v>
+      </c>
+      <c r="AR144">
+        <v>2.17</v>
+      </c>
+      <c r="AS144">
+        <v>1.2</v>
+      </c>
+      <c r="AT144">
+        <v>3.37</v>
+      </c>
+      <c r="AU144">
+        <v>7</v>
+      </c>
+      <c r="AV144">
+        <v>4</v>
+      </c>
+      <c r="AW144">
+        <v>8</v>
+      </c>
+      <c r="AX144">
+        <v>1</v>
+      </c>
+      <c r="AY144">
+        <v>18</v>
+      </c>
+      <c r="AZ144">
+        <v>5</v>
+      </c>
+      <c r="BA144">
+        <v>14</v>
+      </c>
+      <c r="BB144">
+        <v>1</v>
+      </c>
+      <c r="BC144">
+        <v>15</v>
+      </c>
+      <c r="BD144">
+        <v>1.41</v>
+      </c>
+      <c r="BE144">
+        <v>9</v>
+      </c>
+      <c r="BF144">
+        <v>3.58</v>
+      </c>
+      <c r="BG144">
+        <v>1.36</v>
+      </c>
+      <c r="BH144">
+        <v>2.92</v>
+      </c>
+      <c r="BI144">
+        <v>1.62</v>
+      </c>
+      <c r="BJ144">
+        <v>2.22</v>
+      </c>
+      <c r="BK144">
+        <v>1.95</v>
+      </c>
+      <c r="BL144">
+        <v>1.75</v>
+      </c>
+      <c r="BM144">
+        <v>2.57</v>
+      </c>
+      <c r="BN144">
+        <v>1.45</v>
+      </c>
+      <c r="BO144">
+        <v>3.42</v>
+      </c>
+      <c r="BP144">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="145" spans="1:68">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>7859414</v>
+      </c>
+      <c r="C145" t="s">
+        <v>68</v>
+      </c>
+      <c r="D145" t="s">
+        <v>69</v>
+      </c>
+      <c r="E145" s="2">
+        <v>45753.5</v>
+      </c>
+      <c r="F145">
+        <v>2</v>
+      </c>
+      <c r="G145" t="s">
+        <v>80</v>
+      </c>
+      <c r="H145" t="s">
+        <v>73</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>0</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>0</v>
+      </c>
+      <c r="O145" t="s">
+        <v>89</v>
+      </c>
+      <c r="P145" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q145">
+        <v>2.75</v>
+      </c>
+      <c r="R145">
+        <v>2.1</v>
+      </c>
+      <c r="S145">
+        <v>4</v>
+      </c>
+      <c r="T145">
+        <v>1.4</v>
+      </c>
+      <c r="U145">
+        <v>2.75</v>
+      </c>
+      <c r="V145">
+        <v>3</v>
+      </c>
+      <c r="W145">
+        <v>1.36</v>
+      </c>
+      <c r="X145">
+        <v>9</v>
+      </c>
+      <c r="Y145">
+        <v>1.07</v>
+      </c>
+      <c r="Z145">
+        <v>2.08</v>
+      </c>
+      <c r="AA145">
+        <v>3.41</v>
+      </c>
+      <c r="AB145">
+        <v>3.36</v>
+      </c>
+      <c r="AC145">
+        <v>1.02</v>
+      </c>
+      <c r="AD145">
+        <v>9.35</v>
+      </c>
+      <c r="AE145">
+        <v>1.27</v>
+      </c>
+      <c r="AF145">
+        <v>3.25</v>
+      </c>
+      <c r="AG145">
+        <v>1.95</v>
+      </c>
+      <c r="AH145">
+        <v>1.79</v>
+      </c>
+      <c r="AI145">
+        <v>1.8</v>
+      </c>
+      <c r="AJ145">
+        <v>1.95</v>
+      </c>
+      <c r="AK145">
+        <v>1.3</v>
+      </c>
+      <c r="AL145">
+        <v>1.25</v>
+      </c>
+      <c r="AM145">
+        <v>1.67</v>
+      </c>
+      <c r="AN145">
+        <v>2.55</v>
+      </c>
+      <c r="AO145">
+        <v>1.73</v>
+      </c>
+      <c r="AP145">
+        <v>2.42</v>
+      </c>
+      <c r="AQ145">
+        <v>1.67</v>
+      </c>
+      <c r="AR145">
+        <v>1.73</v>
+      </c>
+      <c r="AS145">
+        <v>1.47</v>
+      </c>
+      <c r="AT145">
+        <v>3.2</v>
+      </c>
+      <c r="AU145">
+        <v>0</v>
+      </c>
+      <c r="AV145">
+        <v>3</v>
+      </c>
+      <c r="AW145">
+        <v>12</v>
+      </c>
+      <c r="AX145">
+        <v>10</v>
+      </c>
+      <c r="AY145">
+        <v>15</v>
+      </c>
+      <c r="AZ145">
+        <v>16</v>
+      </c>
+      <c r="BA145">
+        <v>6</v>
+      </c>
+      <c r="BB145">
+        <v>4</v>
+      </c>
+      <c r="BC145">
+        <v>10</v>
+      </c>
+      <c r="BD145">
+        <v>1.69</v>
+      </c>
+      <c r="BE145">
+        <v>8</v>
+      </c>
+      <c r="BF145">
+        <v>2.54</v>
+      </c>
+      <c r="BG145">
+        <v>1.26</v>
+      </c>
+      <c r="BH145">
+        <v>3.38</v>
+      </c>
+      <c r="BI145">
+        <v>1.48</v>
+      </c>
+      <c r="BJ145">
+        <v>2.45</v>
+      </c>
+      <c r="BK145">
+        <v>1.77</v>
+      </c>
+      <c r="BL145">
+        <v>1.95</v>
+      </c>
+      <c r="BM145">
+        <v>2.3</v>
+      </c>
+      <c r="BN145">
+        <v>1.57</v>
+      </c>
+      <c r="BO145">
+        <v>2.93</v>
+      </c>
+      <c r="BP145">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria Bundesliga_20242025.xlsx
@@ -673,7 +673,7 @@
     <t>['5', '66', '9001']</t>
   </si>
   <si>
-    <t>['31', '81', '9005']</t>
+    <t>['31', '81', '90+5']</t>
   </si>
   <si>
     <t>['4', '6', '45+2']</t>
